--- a/Sajjad data/by_country_and_state/USA/CA.xlsx
+++ b/Sajjad data/by_country_and_state/USA/CA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4498" uniqueCount="1908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6383" uniqueCount="2670">
   <si>
     <t>Business Name</t>
   </si>
@@ -5735,6 +5735,2292 @@
   </si>
   <si>
     <t>2026-10-24T19:45:40.406Z</t>
+  </si>
+  <si>
+    <t>Periodontics</t>
+  </si>
+  <si>
+    <t>(661) 267-0617</t>
+  </si>
+  <si>
+    <t>41250 12th St W, Palmdale, CA 93551</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Periodontics/data=!4m7!3m6!1s0x80c25a31d9214efb:0x57af744b7dd21d1!8m2!3d34.6327127!4d-118.1510716!16s%2Fg%2F11df0zrnqh!19sChIJ-04h2TFawoAR0SHdt0T3egU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:17:30.089Z</t>
+  </si>
+  <si>
+    <t>Pomona Valley Dental</t>
+  </si>
+  <si>
+    <t>(909) 623-1564</t>
+  </si>
+  <si>
+    <t>1290 N Garey Ave, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>Pomona</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pomona+Valley+Dental/data=!4m7!3m6!1s0x80c32e08d8f1d85d:0x996eec3f2d1838f2!8m2!3d34.0704588!4d-117.7518912!16s%2Fg%2F1tpbc7mm!19sChIJXdjx2Aguw4AR8jgYLT_sbpk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:17:49.209Z</t>
+  </si>
+  <si>
+    <t>Pomona Dental Clinic</t>
+  </si>
+  <si>
+    <t>(818) 672-5555</t>
+  </si>
+  <si>
+    <t>1021 E Holt Ave, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–2 AM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pomona+Dental+Clinic/data=!4m7!3m6!1s0x80c33205a3238355:0x80c889849bf3119d!8m2!3d34.0630445!4d-117.7301932!16s%2Fg%2F1v_vt5dg!19sChIJVYMjowUyw4ARnRHzm4SJyIA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:17:52.190Z</t>
+  </si>
+  <si>
+    <t>24 hr dental care</t>
+  </si>
+  <si>
+    <t>(213) 769-5749</t>
+  </si>
+  <si>
+    <t>1432 E Mission Blvd, Pomona, CA 91766</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/24+hr+dental+care/data=!4m7!3m6!1s0x80c333fa309729af:0x31285e582de29f91!8m2!3d34.0553428!4d-117.7275784!16s%2Fg%2F11yyf4s4bg!19sChIJrymXMPozw4ARkZ_iLVheKDE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:17:54.887Z</t>
+  </si>
+  <si>
+    <t>Towne Dental Office.</t>
+  </si>
+  <si>
+    <t>(909) 397-5614</t>
+  </si>
+  <si>
+    <t>2135 N Towne Ave, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Towne+Dental+Office./data=!4m7!3m6!1s0x80c32e1cfc2f83a3:0x87473c8751e2311!8m2!3d34.0814375!4d-117.7405317!16s%2Fg%2F11hhyvcrxp!19sChIJo4Mv_Bwuw4ARESMedchzdAg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:00.040Z</t>
+  </si>
+  <si>
+    <t>San Martin Inc</t>
+  </si>
+  <si>
+    <t>(909) 622-8818</t>
+  </si>
+  <si>
+    <t>117 W Willow St Ste B, Pomona, CA 91768</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/San+Martin+Inc/data=!4m7!3m6!1s0x80c32e1108c355bd:0x1055f85a502c3b4!8m2!3d34.0790081!4d-117.752867!16s%2Fg%2F1tfly4s8!19sChIJvVXDCBEuw4ARtMMCpYVfBQE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:02.569Z</t>
+  </si>
+  <si>
+    <t>comfort dental center 2</t>
+  </si>
+  <si>
+    <t>(909) 392-2100</t>
+  </si>
+  <si>
+    <t>3292 N Garey Ave, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/comfort+dental+center+2/data=!4m7!3m6!1s0x80c32e2d1a02dacf:0x269aa89015a8aeb!8m2!3d34.1068705!4d-117.7468241!16s%2Fg%2F1hc263fwz!19sChIJz9oCGi0uw4AR64paAYmqaQI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:05.335Z</t>
+  </si>
+  <si>
+    <t>St Moises Dental</t>
+  </si>
+  <si>
+    <t>(909) 865-8500</t>
+  </si>
+  <si>
+    <t>12 Rancho Camino Dr #102, Pomona, CA 91766</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/St+Moises+Dental/data=!4m7!3m6!1s0x80c32d9f51e62789:0xe51c2cc9da46f48b!8m2!3d34.0278132!4d-117.7602779!16s%2Fg%2F1tdr8g52!19sChIJiSfmUZ8tw4ARi_RG2sksHOU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:07.955Z</t>
+  </si>
+  <si>
+    <t>Garey Dental Center</t>
+  </si>
+  <si>
+    <t>(909) 623-4487</t>
+  </si>
+  <si>
+    <t>1320 N Garey Ave, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Garey+Dental+Center/data=!4m7!3m6!1s0x80c32e08d41da4ef:0x77a00f78f5218078!8m2!3d34.0709407!4d-117.7519826!16s%2Fg%2F126300lt1!19sChIJ76Qd1Aguw4AReIAh9XgPoHc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:10.515Z</t>
+  </si>
+  <si>
+    <t>Bright Smile Dental Care</t>
+  </si>
+  <si>
+    <t>(909) 364-1330</t>
+  </si>
+  <si>
+    <t>12345 Mountain Ave # O, Chino, CA 91710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bright+Smile+Dental+Care/data=!4m7!3m6!1s0x80c33314cf73a74b:0x5c1342019e52215c!8m2!3d34.0289773!4d-117.6664233!16s%2Fg%2F1thgbqyz!19sChIJS6dzzxQzw4ARXCFSngFCE1w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:17.303Z</t>
+  </si>
+  <si>
+    <t>Dr Butala Shailesh dental office</t>
+  </si>
+  <si>
+    <t>(909) 469-2230</t>
+  </si>
+  <si>
+    <t>744 E Holt Ave # A, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>Saturday10:30 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Butala+Shailesh+dental+office/data=!4m7!3m6!1s0x80c3320773bd00f9:0xbff5468b9b2967f2!8m2!3d34.0625697!4d-117.735973!16s%2Fg%2F1tfs1bnq!19sChIJ-QC9cwcyw4AR8mcpm4tG9b8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:20.108Z</t>
+  </si>
+  <si>
+    <t>Universal Dentistry</t>
+  </si>
+  <si>
+    <t>(909) 620-5825</t>
+  </si>
+  <si>
+    <t>667 Indian Hill Blvd, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Universal+Dentistry/data=!4m7!3m6!1s0x80c332198ce7f267:0x20531b62cb54f4ed!8m2!3d34.0655243!4d-117.7195355!16s%2Fg%2F1hc636rj6!19sChIJZ_LnjBkyw4AR7fRUy2IbUyA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:23.054Z</t>
+  </si>
+  <si>
+    <t>Remona Dental Center</t>
+  </si>
+  <si>
+    <t>(909) 625-3600</t>
+  </si>
+  <si>
+    <t>Pepper Tree Square Shopping Center, 324 S Indian Hill Blvd, Claremont, CA 91711</t>
+  </si>
+  <si>
+    <t>Claremont</t>
+  </si>
+  <si>
+    <t>Saturday10 AM–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Remona+Dental+Center/data=!4m7!3m6!1s0x80c331eb897253d5:0xd6ebae96d5e1ab67!8m2!3d34.0899427!4d-117.7178326!16s%2Fg%2F11g7zft2yd!19sChIJ1VNyiesxw4ARZ6vh1Zau69Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:25.710Z</t>
+  </si>
+  <si>
+    <t>Dr. Abrahim A. Mustafa, DDS</t>
+  </si>
+  <si>
+    <t>(909) 364-0633</t>
+  </si>
+  <si>
+    <t>2280 S Garey Ave, Pomona, CA 91766</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Abrahim+A.+Mustafa,+DDS/data=!4m7!3m6!1s0x80c32d834e10706b:0xf2f204bf3040413d!8m2!3d34.0302528!4d-117.748615!16s%2Fg%2F1tsykgb_!19sChIJa3AQToMtw4ARPUFAML8E8vI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:32.697Z</t>
+  </si>
+  <si>
+    <t>Latin American Dental II</t>
+  </si>
+  <si>
+    <t>(909) 469-6967</t>
+  </si>
+  <si>
+    <t>1549 E Holt Ave, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–1 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Latin+American+Dental+II/data=!4m7!3m6!1s0x80c33210ae826497:0xbe03ac82b9fb9832!8m2!3d34.0636711!4d-117.7200164!16s%2Fg%2F1tgn9wzl!19sChIJl2SCrhAyw4ARMpj7uYKsA74?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:39.600Z</t>
+  </si>
+  <si>
+    <t>Tiny Tots Dental</t>
+  </si>
+  <si>
+    <t>(909) 634-8640</t>
+  </si>
+  <si>
+    <t>243 E Mission Blvd, Pomona, CA 91766</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tiny+Tots+Dental/data=!4m7!3m6!1s0x80c32df023719559:0x11be760b02a93067!8m2!3d34.0553806!4d-117.7486138!16s%2Fg%2F12hqjbj8j!19sChIJWZVxI_Atw4ARZzCpAgt2vhE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:44.403Z</t>
+  </si>
+  <si>
+    <t>Estelle H. Liou DDS INC</t>
+  </si>
+  <si>
+    <t>(909) 865-6322</t>
+  </si>
+  <si>
+    <t>1524 N Orange Grove Ave B, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>Saturday9:30 AM–1:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Estelle+H.+Liou+DDS+INC/data=!4m7!3m6!1s0x80c32e0f165f4399:0x20e4c66a10ba221f!8m2!3d34.0729906!4d-117.7510451!16s%2Fg%2F1w9y1ckq!19sChIJmUNfFg8uw4ARHyK6EGrG5CA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:00.324Z</t>
+  </si>
+  <si>
+    <t>Union Family Dentistry</t>
+  </si>
+  <si>
+    <t>(909) 624-3553</t>
+  </si>
+  <si>
+    <t>594 Indian Hill Blvd, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Union+Family+Dentistry/data=!4m7!3m6!1s0x80c33219fa57e1d5:0x74e1472bb3f128d8!8m2!3d34.0642014!4d-117.7186444!16s%2Fg%2F1thkrzrn!19sChIJ1eFX-hkyw4AR2CjxsytH4XQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:18.191Z</t>
+  </si>
+  <si>
+    <t>Primary Care Family Dentistry</t>
+  </si>
+  <si>
+    <t>(909) 860-2656</t>
+  </si>
+  <si>
+    <t>22640 Golden Springs Dr Ste a, Diamond Bar, CA 91765</t>
+  </si>
+  <si>
+    <t>Diamond Bar</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Primary+Care+Family+Dentistry/data=!4m7!3m6!1s0x80c32c87e7a29953:0xed0e19a9ce5a07e9!8m2!3d34.0072085!4d-117.820141!16s%2Fg%2F1tfp2qwp!19sChIJU5mi54csw4AR6QdazqkZDu0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:21.042Z</t>
+  </si>
+  <si>
+    <t>Glendora Family Dental</t>
+  </si>
+  <si>
+    <t>(626) 914-1888</t>
+  </si>
+  <si>
+    <t>413 E Arrow Hwy, Glendora, CA 91740</t>
+  </si>
+  <si>
+    <t>Glendora</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Glendora+Family+Dental/data=!4m7!3m6!1s0x80c32895da816d0b:0xdc3f86dab3e2cc33!8m2!3d34.1073685!4d-117.8571191!16s%2Fg%2F1vyswtc3!19sChIJC22B2pUow4ARM8zis9qGP9w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:24.239Z</t>
+  </si>
+  <si>
+    <t>American Family Dentistry: Noorvash Taraneh F DDS</t>
+  </si>
+  <si>
+    <t>(909) 621-5848</t>
+  </si>
+  <si>
+    <t>1956 Indian Hill Blvd, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/American+Family+Dentistry:+Noorvash+Taraneh+F+DDS/data=!4m7!3m6!1s0x80c331f41ba4c423:0xe0ec8b0ace2b215a!8m2!3d34.078984!4d-117.7190434!16s%2Fg%2F1v2f0sww!19sChIJI8SkG_Qxw4ARWiErzgqL7OA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:26.896Z</t>
+  </si>
+  <si>
+    <t>Pomona Family Dental: Daher Tony DDS</t>
+  </si>
+  <si>
+    <t>(909) 593-5515</t>
+  </si>
+  <si>
+    <t>175 W La Verne Ave Suite A, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pomona+Family+Dental:+Daher+Tony+DDS/data=!4m7!3m6!1s0x80c32e162b4bd85b:0x9a4f5729fc04d228!8m2!3d34.0863601!4d-117.7520283!16s%2Fg%2F1tp0dyqb!19sChIJW9hLKxYuw4ARKNIE_ClXT5o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:29.647Z</t>
+  </si>
+  <si>
+    <t>Dr. Madhavi H. Joshi, DDS</t>
+  </si>
+  <si>
+    <t>(909) 622-2150</t>
+  </si>
+  <si>
+    <t>285 W Artesia St, Pomona, CA 91768</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Madhavi+H.+Joshi,+DDS/data=!4m7!3m6!1s0x80c32e1180b84a1b:0x84b4e7f8e64e38b!8m2!3d34.0779472!4d-117.7549682!16s%2Fg%2F1thcsmcp!19sChIJG0q4gBEuw4ARi-Nkjn9OSwg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:45.482Z</t>
+  </si>
+  <si>
+    <t>Gushansky Larissa DDS</t>
+  </si>
+  <si>
+    <t>(909) 865-8595</t>
+  </si>
+  <si>
+    <t>224 E Monterey Ave, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gushansky+Larissa+DDS/data=!4m7!3m6!1s0x80c32dfb15981491:0xae4bd5824e52bee6!8m2!3d34.0602372!4d-117.7474773!16s%2Fg%2F11b6szk4l3!19sChIJkRSYFfstw4AR5r5SToLVS64?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:50.866Z</t>
+  </si>
+  <si>
+    <t>Family &amp; Children Dentistry</t>
+  </si>
+  <si>
+    <t>(909) 623-1199</t>
+  </si>
+  <si>
+    <t>1184 E Holt Ave, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+%26+Children+Dentistry/data=!4m7!3m6!1s0x80c332056a328f69:0xd3e9ff6cf6dcb1f8!8m2!3d34.0626255!4d-117.7273749!16s%2Fg%2F1tfmj2jx!19sChIJaY8yagUyw4AR-LHc9mz_6dM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:03.098Z</t>
+  </si>
+  <si>
+    <t>Pomona Dental Practice</t>
+  </si>
+  <si>
+    <t>(909) 482-4500</t>
+  </si>
+  <si>
+    <t>1640 Indian Hill Blvd, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pomona+Dental+Practice/data=!4m7!3m6!1s0x80c331f5f0f80369:0xf3335d38f545b69a!8m2!3d34.0746871!4d-117.7188717!16s%2Fg%2F11llcd3kn4!19sChIJaQP48PUxw4ARmrZF9ThdM_M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:17.458Z</t>
+  </si>
+  <si>
+    <t>Wonderbrite Teeth Whitening</t>
+  </si>
+  <si>
+    <t>(909) 979-4020</t>
+  </si>
+  <si>
+    <t>1600 E Holt Ave # D14, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Wonderbrite+Teeth+Whitening/data=!4m7!3m6!1s0x80c332173ab43757:0x81bf982525e44df2!8m2!3d34.0618584!4d-117.7188584!16s%2Fg%2F1tmpw7nk!19sChIJVze0Ohcyw4AR8k3kJSWYv4E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:35.909Z</t>
+  </si>
+  <si>
+    <t>California Dentistry</t>
+  </si>
+  <si>
+    <t>(909) 465-5551</t>
+  </si>
+  <si>
+    <t>5436 Riverside Dr, Chino, CA 91710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/California+Dentistry/data=!4m7!3m6!1s0x80c33379a53412e7:0x5b7f2e2b1a26313c!8m2!3d34.019392!4d-117.686406!16s%2Fg%2F11stl80h2c!19sChIJ5xI0pXkzw4ARPDEmGisuf1s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:39.132Z</t>
+  </si>
+  <si>
+    <t>Ammar Emad DDS</t>
+  </si>
+  <si>
+    <t>(626) 335-6888</t>
+  </si>
+  <si>
+    <t>175 N Pennsylvania Ave, Glendora, CA 91741</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday8 AM–5 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday8 AM–12 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ammar+Emad+DDS/data=!4m7!3m6!1s0x80c32637a5beb0cf:0x6c616719ef9965bc!8m2!3d34.138156!4d-117.868393!16s%2Fg%2F1tnmr_kk!19sChIJz7C-pTcmw4ARvGWZ7xlnYWw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:58.372Z</t>
+  </si>
+  <si>
+    <t>Lee Widodo &amp; Zhang</t>
+  </si>
+  <si>
+    <t>(909) 670-1100</t>
+  </si>
+  <si>
+    <t>1532 San Bernardino Ave # A1, Pomona, CA 91767</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lee+Widodo+%26+Zhang/data=!4m7!3m6!1s0x80c331f6740c780f:0x55900530c29cf65!8m2!3d34.0756858!4d-117.7202039!16s%2Fg%2F1tk9r0xp!19sChIJD3gMdPYxw4ARZc8pDFMAWQU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:22:00.863Z</t>
+  </si>
+  <si>
+    <t>West Coast Dental Implant Study Club</t>
+  </si>
+  <si>
+    <t>(909) 860-9225</t>
+  </si>
+  <si>
+    <t>Dental school</t>
+  </si>
+  <si>
+    <t>620 N Diamond Bar Blvd, Diamond Bar, CA 91765</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+Coast+Dental+Implant+Study+Club/data=!4m7!3m6!1s0x80c32c6ac3eedc29:0x1b5328eef5c70abf!8m2!3d34.0308923!4d-117.8084214!16s%2Fg%2F1vjdqbdw!19sChIJKdzuw2osw4ARvwrH9e4oUxs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:22:03.739Z</t>
+  </si>
+  <si>
+    <t>Escondido Emergency Dental Clinic</t>
+  </si>
+  <si>
+    <t>(760) 738-8300</t>
+  </si>
+  <si>
+    <t>403 W 5th Ave, Escondido, CA 92025</t>
+  </si>
+  <si>
+    <t>Escondido</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Escondido+Emergency+Dental+Clinic/data=!4m7!3m6!1s0x80dbf50026a4a879:0xf808cf55f4fdb719!8m2!3d33.1157428!4d-117.0830721!16s%2Fg%2F11m6bsg__h!19sChIJeaikJgD124ARGbf99FXPCPg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:22:45.199Z</t>
+  </si>
+  <si>
+    <t>Dr. Ben T. Dela Cruz Jr, DMD</t>
+  </si>
+  <si>
+    <t>(760) 737-8100</t>
+  </si>
+  <si>
+    <t>1875 S Centre City Pkwy, Escondido, CA 92025</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Ben+T.+Dela+Cruz+Jr,+DMD/data=!4m7!3m6!1s0x80dbf3860f844e83:0x332c4dee7478f461!8m2!3d33.1004191!4d-117.0750109!16s%2Fg%2F1w0j4h2b!19sChIJg06ED4bz24ARYfR4dO5NLDM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:24.994Z</t>
+  </si>
+  <si>
+    <t>North County Real Dental Care</t>
+  </si>
+  <si>
+    <t>(760) 738-4538</t>
+  </si>
+  <si>
+    <t>2365 E Valley Pkwy, Escondido, CA 92027</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/North+County+Real+Dental+Care/data=!4m7!3m6!1s0x80dbf322cb30894d:0x4a43fafb156f6610!8m2!3d33.1400689!4d-117.044059!16s%2Fg%2F11fx7xj53t!19sChIJTYkwyyLz24AREGZvFfv6Q0o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:27.703Z</t>
+  </si>
+  <si>
+    <t>Zand S DDS</t>
+  </si>
+  <si>
+    <t>(760) 747-7000</t>
+  </si>
+  <si>
+    <t>240 W Mission Ave Suit B, Escondido, CA 92025</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Zand+S+DDS/data=!4m7!3m6!1s0x80dbf4a2f3e9861b:0xaeee0407312eeda9!8m2!3d33.12971!4d-117.0886478!16s%2Fg%2F1263g79pq!19sChIJG4bp86L024ARqe0uMQcE7q4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:46.010Z</t>
+  </si>
+  <si>
+    <t>Happy Smile Dental Office</t>
+  </si>
+  <si>
+    <t>(760) 839-9112</t>
+  </si>
+  <si>
+    <t>1201 Valley Pkwy, Escondido, CA 92027</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Happy+Smile+Dental+Office/data=!4m7!3m6!1s0x80dbf3688c39b9dd:0x7b8a216a28f7a708!8m2!3d33.1302745!4d-117.0665729!16s%2Fg%2F1td_yx4b!19sChIJ3bk5jGjz24ARCKf3KGohins?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:54.240Z</t>
+  </si>
+  <si>
+    <t>iSmile Dental II</t>
+  </si>
+  <si>
+    <t>(760) 233-1212</t>
+  </si>
+  <si>
+    <t>636 N Escondido Blvd, Escondido, CA 92025</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/iSmile+Dental+II/data=!4m7!3m6!1s0x80dbf4985fc26591:0xe20616f21ff6cc75!8m2!3d33.1273694!4d-117.087777!16s%2Fg%2F113hwpr51!19sChIJkWXCX5j024ARdcz2H_IWBuI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:24:07.741Z</t>
+  </si>
+  <si>
+    <t>AC Dental</t>
+  </si>
+  <si>
+    <t>(760) 746-7907</t>
+  </si>
+  <si>
+    <t>314 N Cedar St, Escondido, CA 92025</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/AC+Dental/data=!4m7!3m6!1s0x80dbf3666b73f033:0x42f2003eed34b13c!8m2!3d33.1286094!4d-117.0692838!16s%2Fg%2F1th0yn66!19sChIJM_Bza2bz24ARPLE07T4A8kI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:24:46.883Z</t>
+  </si>
+  <si>
+    <t>Aesthetic &amp; Family Dentistry</t>
+  </si>
+  <si>
+    <t>(760) 480-8883</t>
+  </si>
+  <si>
+    <t>203 N Ash St, Escondido, CA 92027</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aesthetic+%26+Family+Dentistry/data=!4m7!3m6!1s0x80dbf368b59ea6cd:0xfa60db55db93a7a1!8m2!3d33.1283324!4d-117.0663041!16s%2Fg%2F1tmqrnj4!19sChIJzaaetWjz24ARoaeT21XbYPo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:25:12.958Z</t>
+  </si>
+  <si>
+    <t>Tin Luong DDS Periodontics and Dental Implants</t>
+  </si>
+  <si>
+    <t>(760) 747-2020</t>
+  </si>
+  <si>
+    <t>342 S Kalmia St, Escondido, CA 92025</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday8 AM–5 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; FridayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tin+Luong+DDS+Periodontics+and+Dental+Implants/data=!4m7!3m6!1s0x80dbf37d4a177139:0xadf54a05c2eb184f!8m2!3d33.119915!4d-117.078016!16s%2Fg%2F1tgfdnp7!19sChIJOXEXSn3z24ARTxjrwgVK9a0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:26:24.000Z</t>
+  </si>
+  <si>
+    <t>A Better Smile Implant: Khazian Mehran DDS</t>
+  </si>
+  <si>
+    <t>(760) 738-7000</t>
+  </si>
+  <si>
+    <t>727 E Grand Ave, Escondido, CA 92025</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/A+Better+Smile+Implant:+Khazian+Mehran+DDS/data=!4m7!3m6!1s0x80dbf3646807ba83:0x6ad1c48720dc332b!8m2!3d33.1248513!4d-117.0721011!16s%2Fg%2F1tdz07l6!19sChIJg7oHaGTz24ARKzPcIIfE0Wo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:26:33.464Z</t>
+  </si>
+  <si>
+    <t>Joseph Vu Inc</t>
+  </si>
+  <si>
+    <t>(760) 741-5121</t>
+  </si>
+  <si>
+    <t>675 N Broadway # E, Escondido, CA 92025</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Joseph+Vu+Inc/data=!4m7!3m6!1s0x80dbf49f504a77b1:0x26b4d9b90eb25e63!8m2!3d33.128419!4d-117.0848943!16s%2Fg%2F1w0sd4qg!19sChIJsXdKUJ_024ARY16yDrnZtCY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:26:42.239Z</t>
+  </si>
+  <si>
+    <t>Saturday Nite Smile</t>
+  </si>
+  <si>
+    <t>(888) 389-0432</t>
+  </si>
+  <si>
+    <t>211 N Citrus Ave, Escondido, CA 92027</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Saturday+Nite+Smile/data=!4m7!3m6!1s0x80dbf317f05db91b:0x2d8219a639ceb7b!8m2!3d33.1376673!4d-117.0446822!16s%2Fg%2F1yh4g_wvm!19sChIJG7ld8Bfz24ARe-ucY5oh2AI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:26:59.799Z</t>
+  </si>
+  <si>
+    <t>Dr. Marlene Thompson</t>
+  </si>
+  <si>
+    <t>(760) 740-2595</t>
+  </si>
+  <si>
+    <t>1018 W El Norte Pkwy, Escondido, CA 92026</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Marlene+Thompson/data=!4m7!3m6!1s0x80db8b34f9669be5:0x7d041c3a247755a0!8m2!3d33.1485516!4d-117.1070501!16s%2Fg%2F1wtbv56r!19sChIJ5Ztm-TSL24ARoFV3JDocBH0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:27:52.398Z</t>
+  </si>
+  <si>
+    <t>Dr. Andy Hoang</t>
+  </si>
+  <si>
+    <t>(760) 233-2260</t>
+  </si>
+  <si>
+    <t>403 W Felicita Ave, Escondido, CA 92025</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Andy+Hoang/data=!4m7!3m6!1s0x80dbf491750db8a5:0xe20b4ab81292f9ae!8m2!3d33.1023255!4d-117.0733985!16s%2Fg%2F1thxqyfk!19sChIJpbgNdZH024ARrvmSErhKC-I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:28:22.658Z</t>
+  </si>
+  <si>
+    <t>Mark B. Martin, DDS, MAGD</t>
+  </si>
+  <si>
+    <t>(760) 489-5545</t>
+  </si>
+  <si>
+    <t>500 W El Norte Pkwy, Escondido, CA 92026</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mark+B.+Martin,+DDS,+MAGD/data=!4m7!3m6!1s0x80dbf365c6f97e41:0xa04e956ed34280e1!8m2!3d33.1446322!4d-117.0981672!16s%2Fg%2F1tcvzqb1!19sChIJQX75xmXz24AR4YBC026VTqA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:28:25.430Z</t>
+  </si>
+  <si>
+    <t>Dr. David L. Tagge, DDS</t>
+  </si>
+  <si>
+    <t>(760) 741-4061</t>
+  </si>
+  <si>
+    <t>850 E Grand Ave A, Escondido, CA 92025</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday7:30 AM–4:30 PM; Tuesday7:30 AM–4:30 PM; Wednesday7:30 AM–4:30 PM; Thursday7:30 AM–4:30 PM; Friday7:30 AM–4:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+David+L.+Tagge,+DDS/data=!4m7!3m6!1s0x80dbf365caf99fb5:0xa75fa9220427a856!8m2!3d33.1259484!4d-117.0703475!16s%2Fg%2F1tddsh4m!19sChIJtZ_5ymXz24ARVqgnBCKpX6c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:28:30.401Z</t>
+  </si>
+  <si>
+    <t>Dental Associates of Torrance</t>
+  </si>
+  <si>
+    <t>(310) 792-5600</t>
+  </si>
+  <si>
+    <t>21229 Hawthorne Blvd A, Torrance, CA 90503</t>
+  </si>
+  <si>
+    <t>Torrance</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Associates+of+Torrance/data=!4m7!3m6!1s0x80c2b4d3160dc99b:0xc9bc7a0be1a31a91!8m2!3d33.836694!4d-118.3539108!16s%2Fg%2F1tf6gx9z!19sChIJm8kNFtO0woARkRqj4Qt6vMk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:28:46.819Z</t>
+  </si>
+  <si>
+    <t>Harmony Dental</t>
+  </si>
+  <si>
+    <t>(310) 320-6789</t>
+  </si>
+  <si>
+    <t>2455 Sepulveda Blvd # F, Torrance, CA 90501</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Harmony+Dental/data=!4m7!3m6!1s0x80dd4ac1dc49a655:0xd90212e1ba0fb782!8m2!3d33.822008!4d-118.327024!16s%2Fg%2F11b6gd5f63!19sChIJVaZJ3MFK3YARgrcPuuESAtk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:30:05.186Z</t>
+  </si>
+  <si>
+    <t>Redondo Bch Family Dental</t>
+  </si>
+  <si>
+    <t>(310) 768-8281</t>
+  </si>
+  <si>
+    <t>2130 W Redondo Beach Blvd, Torrance, CA 90504</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Redondo+Bch+Family+Dental/data=!4m7!3m6!1s0x80c2b59dff5c0677:0x2f58f4ba515e003d!8m2!3d33.8856077!4d-118.316861!16s%2Fg%2F1td5lz9q!19sChIJdwZc_521woARPQBeUbr0WC8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:09.944Z</t>
+  </si>
+  <si>
+    <t>Ace Dental Group</t>
+  </si>
+  <si>
+    <t>(310) 926-2234</t>
+  </si>
+  <si>
+    <t>23000 Crenshaw Blvd #207, Torrance, CA 90505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ace+Dental+Group/data=!4m7!3m6!1s0x80c2b89ab358f661:0xb45cca1c019ad7bb!8m2!3d33.816759!4d-118.327766!16s%2Fg%2F1tl1j4ky!19sChIJYfZYs5q4woARu9eaARzKXLQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:14.887Z</t>
+  </si>
+  <si>
+    <t>Carson Vermont Family Dental</t>
+  </si>
+  <si>
+    <t>(310) 328-1452</t>
+  </si>
+  <si>
+    <t>21604 Vermont Ave, Torrance, CA 90502</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Carson+Vermont+Family+Dental/data=!4m7!3m6!1s0x80dd355d0422a2d5:0x4613af91775f7170!8m2!3d33.8333313!4d-118.2899513!16s%2Fg%2F1vh_8pmr!19sChIJ1aIiBF013YARcHFfd5GvE0Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:17.410Z</t>
+  </si>
+  <si>
+    <t>Narbonne Family Dentist</t>
+  </si>
+  <si>
+    <t>(310) 326-7231</t>
+  </si>
+  <si>
+    <t>24423 Narbonne Ave, Lomita, CA 90717</t>
+  </si>
+  <si>
+    <t>Lomita</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Narbonne+Family+Dentist/data=!4m7!3m6!1s0x80dd4a8a876801c9:0x8f47bb6697cb532c!8m2!3d33.803414!4d-118.320102!16s%2Fg%2F1wd3wc01!19sChIJyQFoh4pK3YARLFPLl2a7R48?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:20.314Z</t>
+  </si>
+  <si>
+    <t>Ma Family Dental, DDS</t>
+  </si>
+  <si>
+    <t>(310) 373-6565</t>
+  </si>
+  <si>
+    <t>3655 Lomita Blvd #109, Torrance, CA 90505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ma+Family+Dental,+DDS/data=!4m7!3m6!1s0x80dd4b001b4a5439:0x48b6b5ac8fb9c277!8m2!3d33.8152976!4d-118.3487544!16s%2Fg%2F11vr61hy7n!19sChIJOVRKGwBL3YARd8K5j6y1tkg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:23.216Z</t>
+  </si>
+  <si>
+    <t>South Bay Children's Dental</t>
+  </si>
+  <si>
+    <t>(310) 539-2773</t>
+  </si>
+  <si>
+    <t>1585 Sepulveda Blvd A, Torrance, CA 90501</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/South+Bay+Children%27s+Dental/data=!4m7!3m6!1s0x80dd4bb38a8f5535:0x1011e2349d87cce!8m2!3d33.8163533!4d-118.3055267!16s%2Fg%2F11wp_802st!19sChIJNVWPirNL3YARznzYSSMeAQE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:32:27.198Z</t>
+  </si>
+  <si>
+    <t>e-Dental Group</t>
+  </si>
+  <si>
+    <t>(310) 787-1233</t>
+  </si>
+  <si>
+    <t>23750 Crenshaw Blvd, Torrance, CA 90505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/e-Dental+Group/data=!4m7!3m6!1s0x80dd4b631aa546e3:0x4ca7af1e85972d43!8m2!3d33.8086162!4d-118.3277136!16s%2Fg%2F11vr4qr4vx!19sChIJ40alGmNL3YARQy2XhR6vp0w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:32:30.135Z</t>
+  </si>
+  <si>
+    <t>Vivian Maung DDS, MS - Maung Orthodontics - Orthodontist</t>
+  </si>
+  <si>
+    <t>(310) 984-1638</t>
+  </si>
+  <si>
+    <t>25550 Hawthorne Blvd, Torrance, CA 90505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vivian+Maung+DDS,+MS+-+Maung+Orthodontics+-+Orthodontist/data=!4m7!3m6!1s0x80dd36289a74bdf7:0x4ce296b27a646c1d!8m2!3d33.7940093!4d-118.3484998!16s%2Fg%2F1tl8l043!19sChIJ9710mig23YARHWxkerKW4kw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:32:47.884Z</t>
+  </si>
+  <si>
+    <t>Torrance Dental Group - Dr. Shokofeh Aghassibake, DDS</t>
+  </si>
+  <si>
+    <t>(310) 791-4100</t>
+  </si>
+  <si>
+    <t>23415 Crenshaw Blvd Ste 200, Torrance, CA 90505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Torrance+Dental+Group+-+Dr.+Shokofeh+Aghassibake,+DDS/data=!4m7!3m6!1s0x80dd4b1fa87a2529:0x14f9e83d5b34f6fe!8m2!3d33.812976!4d-118.3283901!16s%2Fg%2F11_t5612n!19sChIJKSV6qB9L3YAR_vY0Wz3o-RQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:33:04.473Z</t>
+  </si>
+  <si>
+    <t>James C Feng DDS Emergency Dentist of South Bay</t>
+  </si>
+  <si>
+    <t>(424) 262-9115</t>
+  </si>
+  <si>
+    <t>4010 Sepulveda Blvd #5, Torrance, CA 90505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/James+C+Feng+DDS+Emergency+Dentist+of+South+Bay/data=!4m7!3m6!1s0x80dd4b2f946b86df:0xcf33615abdafb8cc!8m2!3d33.825569!4d-118.356161!16s%2Fg%2F11bwd35w1b!19sChIJ34ZrlC9L3YARzLivvVphM88?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:33:24.331Z</t>
+  </si>
+  <si>
+    <t>ALOHA DENTAL CARE</t>
+  </si>
+  <si>
+    <t>(310) 324-9700</t>
+  </si>
+  <si>
+    <t>17521 Crenshaw Blvd, Torrance, CA 90504</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/ALOHA+DENTAL+CARE/data=!4m7!3m6!1s0x80c2b53ef2312a2d:0xc5caf1f4fa3af60!8m2!3d33.8711976!4d-118.3267207!16s%2Fg%2F11b76brkmb!19sChIJLSox8j61woARYK-jTx-vXAw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:33:59.054Z</t>
+  </si>
+  <si>
+    <t>William Scott Rees Inc</t>
+  </si>
+  <si>
+    <t>(310) 373-8461</t>
+  </si>
+  <si>
+    <t>23430 Hawthorne Blvd #305, Torrance, CA 90505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/William+Scott+Rees+Inc/data=!4m7!3m6!1s0x80dd4b1efc20b451:0xeb82fd92b4a0c7a4!8m2!3d33.8132528!4d-118.3494313!16s%2Fg%2F1td5gf9v!19sChIJUbQg_B5L3YARpMegtJL9gus?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:03.984Z</t>
+  </si>
+  <si>
+    <t>Dr. Barry Kashfian, D.M.D.</t>
+  </si>
+  <si>
+    <t>(310) 375-1111</t>
+  </si>
+  <si>
+    <t>25550 Hawthorne Blvd Ste 112, Torrance, CA 90505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Barry+Kashfian,+D.M.D./data=!4m7!3m6!1s0x80dd4baaf220bcad:0x7240a4b4baca8e2f!8m2!3d33.7939355!4d-118.3486603!16s%2Fg%2F1tw1f3_d!19sChIJrbwg8qpL3YARL47KurSkQHI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:06.317Z</t>
+  </si>
+  <si>
+    <t>Smart Dental Care</t>
+  </si>
+  <si>
+    <t>(626) 405-0707</t>
+  </si>
+  <si>
+    <t>742 E Colorado Blvd, Pasadena, CA 91101</t>
+  </si>
+  <si>
+    <t>Pasadena</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–12 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smart+Dental+Care/data=!4m7!3m6!1s0x80c2c35d51f144c3:0xa69a11d9efdacdab!8m2!3d34.1457457!4d-118.1350251!16s%2Fg%2F1tdmkrmg!19sChIJw0TxUV3DwoARq83a79kRmqY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:25.714Z</t>
+  </si>
+  <si>
+    <t>Rapid Dental Care Pasadena</t>
+  </si>
+  <si>
+    <t>(626) 659-1234</t>
+  </si>
+  <si>
+    <t>612 S Lake Ave, Pasadena, CA 91106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rapid+Dental+Care+Pasadena/data=!4m7!3m6!1s0x80c2c5e127391d53:0xb03d17283556f831!8m2!3d34.135256!4d-118.131838!16s%2Fg%2F11l351d3__!19sChIJUx05J-HFwoARMfhWNSgXPbA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:28.072Z</t>
+  </si>
+  <si>
+    <t>City Dental</t>
+  </si>
+  <si>
+    <t>(626) 799-9909</t>
+  </si>
+  <si>
+    <t>711 Fair Oaks Ave, South Pasadena, CA 91030</t>
+  </si>
+  <si>
+    <t>South Pasadena</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/City+Dental/data=!4m7!3m6!1s0x80c2c48e86ecf507:0x6ab01bfa49dcf608!8m2!3d34.1171758!4d-118.1507654!16s%2Fg%2F1wtbv4dp!19sChIJB_Xsho7EwoARCPbcSfobsGo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:46.625Z</t>
+  </si>
+  <si>
+    <t>Pasadena Dental Associates</t>
+  </si>
+  <si>
+    <t>(626) 797-6778</t>
+  </si>
+  <si>
+    <t>1302 N Altadena Dr, Pasadena, CA 91107</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pasadena+Dental+Associates/data=!4m7!3m6!1s0x80c2dcc6541d2415:0x878023d33a95a539!8m2!3d34.1684821!4d-118.0979918!16s%2Fg%2F1tvtbmdm!19sChIJFSQdVMbcwoAROaWVOtMjgIc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:56.422Z</t>
+  </si>
+  <si>
+    <t>Huntington Pavilion Dental Center</t>
+  </si>
+  <si>
+    <t>(626) 395-9588</t>
+  </si>
+  <si>
+    <t>625 S Fair Oaks Ave #230, Pasadena, CA 91105</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Huntington+Pavilion+Dental+Center/data=!4m7!3m6!1s0x80c2c37c547374a3:0x8e74f9acdf1534ea!8m2!3d34.1356168!4d-118.1507176!16s%2Fg%2F11b635dj8h!19sChIJo3RzVHzDwoAR6jQV36z5dI4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:03.090Z</t>
+  </si>
+  <si>
+    <t>Colorado Dental</t>
+  </si>
+  <si>
+    <t>(626) 584-7017</t>
+  </si>
+  <si>
+    <t>2379 E Colorado Blvd, Pasadena, CA 91107</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Colorado+Dental/data=!4m7!3m6!1s0x80c2dca87055952d:0x1ca7e7b7c0a9ace5!8m2!3d34.146665!4d-118.1008604!16s%2Fg%2F1tdhm2n5!19sChIJLZVVcKjcwoAR5aypwLfnpxw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:05.598Z</t>
+  </si>
+  <si>
+    <t>Pasadena Dental Center</t>
+  </si>
+  <si>
+    <t>(626) 440-1718</t>
+  </si>
+  <si>
+    <t>1855 E Colorado Blvd, Pasadena, CA 91107</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pasadena+Dental+Center/data=!4m7!3m6!1s0x80c2dcab537f3d0d:0x97f8d332c9b2a7e4!8m2!3d34.146444!4d-118.112093!16s%2Fg%2F1261bt326!19sChIJDT1_U6vcwoAR5KeyyTLT-Jc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:09.204Z</t>
+  </si>
+  <si>
+    <t>Pasadena Family Dental Center</t>
+  </si>
+  <si>
+    <t>(626) 431-2930</t>
+  </si>
+  <si>
+    <t>950 E Colorado Blvd #201, Pasadena, CA 91106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pasadena+Family+Dental+Center/data=!4m7!3m6!1s0x80c2c35c97ae2705:0x985bb5cf5c797e4b!8m2!3d34.1456946!4d-118.1304501!16s%2Fg%2F1thn5sdb!19sChIJBSeul1zDwoARS355XM-1W5g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:38:27.850Z</t>
+  </si>
+  <si>
+    <t>Dr Lena's Family Dentistry</t>
+  </si>
+  <si>
+    <t>(626) 795-2900</t>
+  </si>
+  <si>
+    <t>3836 E Foothill Blvd, Pasadena, CA 91107</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Lena%27s+Family+Dentistry/data=!4m7!3m6!1s0x80c2c3685899f9b1:0x5550082b56132b8!8m2!3d34.150104!4d-118.069219!16s%2Fg%2F1tc_ww82!19sChIJsfmZWGjDwoARuDJhtYIAVQU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:38:30.325Z</t>
+  </si>
+  <si>
+    <t>Dr. Yasmini C. Atacador, DDS</t>
+  </si>
+  <si>
+    <t>(626) 795-4420</t>
+  </si>
+  <si>
+    <t>2990 E Colorado Blvd #103C, Pasadena, CA 91107</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Yasmini+C.+Atacador,+DDS/data=!4m7!3m6!1s0x80c2db607b73e4c1:0x2b5c761a5d99e99a!8m2!3d34.1456789!4d-118.0884619!16s%2Fg%2F1wj_tjz6!19sChIJweRze2DbwoARmumZXRp2XCs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:39:27.769Z</t>
+  </si>
+  <si>
+    <t>Foothill Dental Group</t>
+  </si>
+  <si>
+    <t>(626) 449-1919</t>
+  </si>
+  <si>
+    <t>2063 E Foothill Blvd, Pasadena, CA 91107</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Foothill+Dental+Group/data=!4m7!3m6!1s0x80c2dcac363c6923:0x3c544121054e6271!8m2!3d34.15019!4d-118.1078177!16s%2Fg%2F1w2yv4sd!19sChIJI2k8NqzcwoARcWJOBSFBVDw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:40:36.836Z</t>
+  </si>
+  <si>
+    <t>Pasadena Dental Group</t>
+  </si>
+  <si>
+    <t>(626) 796-4718</t>
+  </si>
+  <si>
+    <t>87 E Green St #310, Pasadena, CA 91105</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pasadena+Dental+Group/data=!4m7!3m6!1s0x80c2c37039eb531d:0x1329e04dd289075b!8m2!3d34.1446895!4d-118.1485448!16s%2Fg%2F11c605rs5p!19sChIJHVPrOXDDwoARWweJ0k3gKRM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:40:39.619Z</t>
+  </si>
+  <si>
+    <t>Good Day Dental Studio</t>
+  </si>
+  <si>
+    <t>(626) 441-5000</t>
+  </si>
+  <si>
+    <t>1928 Huntington Dr, South Pasadena, CA 91030</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Good+Day+Dental+Studio/data=!4m7!3m6!1s0x80c2c4ef5090fdcd:0x2dce98fa57fba2d6!8m2!3d34.1044311!4d-118.1429494!16s%2Fg%2F1tlgy68c!19sChIJzf2QUO_EwoAR1qL7V_qYzi0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:41:25.053Z</t>
+  </si>
+  <si>
+    <t>Frank Sy DMD</t>
+  </si>
+  <si>
+    <t>(626) 401-1988</t>
+  </si>
+  <si>
+    <t>9368 Valley Blvd Ste 201, Rosemead, CA 91770</t>
+  </si>
+  <si>
+    <t>Rosemead</t>
+  </si>
+  <si>
+    <t>Saturday8:30 AM–4:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Frank+Sy+DMD/data=!4m7!3m6!1s0x80c2da7d5ce2d0cd:0xc4bea87b4ed87e50!8m2!3d34.0809182!4d-118.0648907!16s%2Fg%2F11kjq5tvtl!19sChIJzdDiXH3awoARUH7YTnuovsQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:41:45.427Z</t>
+  </si>
+  <si>
+    <t>Dr. Dennis R. Hunt, DDS</t>
+  </si>
+  <si>
+    <t>(626) 432-4250</t>
+  </si>
+  <si>
+    <t>310 S Lake Ave, Pasadena, CA 91101</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Dennis+R.+Hunt,+DDS/data=!4m7!3m6!1s0x80c2c35eecfb7885:0x3822fe17ad804f6f!8m2!3d34.1404664!4d-118.1318805!16s%2Fg%2F1wv_sh49!19sChIJhXj77F7DwoARb0-ArRf-Ijg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:41:48.141Z</t>
+  </si>
+  <si>
+    <t>Hsiou Joseph DDS</t>
+  </si>
+  <si>
+    <t>(626) 441-4511</t>
+  </si>
+  <si>
+    <t>2130 Huntington Dr Unit 202, South Pasadena, CA 91030</t>
+  </si>
+  <si>
+    <t>Saturday8:30 AM–3 PM; SundayClosed; MondayClosed; Tuesday8:30 AM–3 PM; Wednesday8 AM–12 PM; ThursdayClosed; Friday8:30 AM–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hsiou+Joseph+DDS/data=!4m7!3m6!1s0x80c2c4e823d54db7:0x254e21fdac5632f0!8m2!3d34.106414!4d-118.136044!16s%2Fg%2F1tdg3h25!19sChIJt03VI-jEwoAR8DJWrP0hTiU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:41:51.072Z</t>
+  </si>
+  <si>
+    <t>Dr. Michael D. Kim, DDS</t>
+  </si>
+  <si>
+    <t>(626) 795-9328</t>
+  </si>
+  <si>
+    <t>1092 E Green St, Pasadena, CA 91106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Michael+D.+Kim,+DDS/data=!4m7!3m6!1s0x80c2c35bb90c08c5:0x9ed7176de7631138!8m2!3d34.1443734!4d-118.1278338!16s%2Fg%2F1td4_39n!19sChIJxQgMuVvDwoAROBFj520X154?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:41:53.744Z</t>
+  </si>
+  <si>
+    <t>Vanguard Dental Institute</t>
+  </si>
+  <si>
+    <t>(626) 792-7900</t>
+  </si>
+  <si>
+    <t>212 S El Molino Ave, Pasadena, CA 91101</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vanguard+Dental+Institute/data=!4m7!3m6!1s0x80c2c36767ceee0f:0x1c84bedd962bc1cc!8m2!3d34.1421434!4d-118.1364928!16s%2Fg%2F1tj91tn5!19sChIJD-7OZ2fDwoARzMErlt2-hBw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:41:56.584Z</t>
+  </si>
+  <si>
+    <t>Philo Smile Dental Clinic</t>
+  </si>
+  <si>
+    <t>(714) 532-2884</t>
+  </si>
+  <si>
+    <t>1500 E Katella Ave Ste B, Orange, CA 92867</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Philo+Smile+Dental+Clinic/data=!4m7!3m6!1s0x80dcd70d2989eb85:0x16dcdc8d66bbcfb4!8m2!3d33.8087728!4d-117.837962!16s%2Fg%2F11z9hhjxv7!19sChIJheuJKQ3X3IARtM-7Zo3c3BY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:42:26.022Z</t>
+  </si>
+  <si>
+    <t>Preferred Dental Care</t>
+  </si>
+  <si>
+    <t>(714) 978-3333</t>
+  </si>
+  <si>
+    <t>2022 W Chapman Ave, Orange, CA 92868</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Preferred+Dental+Care/data=!4m7!3m6!1s0x80dcd9d44b9dc24f:0x680f9ce32c46522c!8m2!3d33.7875796!4d-117.8739705!16s%2Fg%2F1tr9nqkq!19sChIJT8KdS9TZ3IARLFJGLOOcD2g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:42:30.943Z</t>
+  </si>
+  <si>
+    <t>D&amp;T Dentistry</t>
+  </si>
+  <si>
+    <t>(714) 744-2449</t>
+  </si>
+  <si>
+    <t>3402 E Chapman Ave, Orange, CA 92869</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/D%26T+Dentistry/data=!4m7!3m6!1s0x80dcda1730220513:0xf47a666bf98070fe!8m2!3d33.7874408!4d-117.8171155!16s%2Fg%2F11ddwychvg!19sChIJEwUiMBfa3IAR_nCA-WtmevQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:43:09.620Z</t>
+  </si>
+  <si>
+    <t>Golden State Dental</t>
+  </si>
+  <si>
+    <t>(714) 771-7000</t>
+  </si>
+  <si>
+    <t>1335 E Katella Ave, Orange, CA 92867</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Golden+State+Dental/data=!4m7!3m6!1s0x80dcd74e3574a769:0xad79425aaf28a663!8m2!3d33.8102751!4d-117.8399013!16s%2Fg%2F1thcsn69!19sChIJaad0NU7X3IARY6Yor1pCea0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:43:38.246Z</t>
+  </si>
+  <si>
+    <t>Cambridge Dental Care</t>
+  </si>
+  <si>
+    <t>(714) 538-2811</t>
+  </si>
+  <si>
+    <t>900 E Katella Ave A, Orange, CA 92867</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cambridge+Dental+Care/data=!4m7!3m6!1s0x80dcd7450d27bf91:0x5a5647b6be0397b8!8m2!3d33.808447!4d-117.844254!16s%2Fg%2F1tk6qmcw!19sChIJkb8nDUXX3IARuJcDvrZHVlo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:43:50.649Z</t>
+  </si>
+  <si>
+    <t>Chapman Smiles Center</t>
+  </si>
+  <si>
+    <t>(714) 829-5489</t>
+  </si>
+  <si>
+    <t>2140 W Chapman Ave #107, Orange, CA 92868</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chapman+Smiles+Center/data=!4m7!3m6!1s0x80dcd9d50d8cc527:0x18c3bd3462af9580!8m2!3d33.7874237!4d-117.8757727!16s%2Fg%2F11c30_zxdy!19sChIJJ8WMDdXZ3IARgJWvYjS9wxg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:43:53.530Z</t>
+  </si>
+  <si>
+    <t>Orange Villa Family Dentistry</t>
+  </si>
+  <si>
+    <t>(714) 202-5588</t>
+  </si>
+  <si>
+    <t>2010 N Tustin St Ste A, Orange, CA 92865</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Orange+Villa+Family+Dentistry/data=!4m7!3m6!1s0x80dcd76e9919c859:0x3f468e652a790c68!8m2!3d33.8213847!4d-117.8365936!16s%2Fg%2F11h0x_48hw!19sChIJWcgZmW7X3IARaAx5KmWORj8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:44:44.301Z</t>
+  </si>
+  <si>
+    <t>Orange Dental Group</t>
+  </si>
+  <si>
+    <t>(714) 744-0044</t>
+  </si>
+  <si>
+    <t>235 S Tustin St, Orange, CA 92866</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Orange+Dental+Group/data=!4m7!3m6!1s0x80dcd9f6dd03b50b:0x2d3f5266257b47b3!8m2!3d33.7852754!4d-117.8352549!16s%2Fg%2F1tgc9tgt!19sChIJC7UD3fbZ3IARs0d7JWZSPy0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:44:50.723Z</t>
+  </si>
+  <si>
+    <t>Lakeside Family Dental</t>
+  </si>
+  <si>
+    <t>(714) 283-0500</t>
+  </si>
+  <si>
+    <t>1800 N Tustin St, Orange, CA 92865</t>
+  </si>
+  <si>
+    <t>Saturday11 AM–2 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lakeside+Family+Dental/data=!4m7!3m6!1s0x80dcd6a4cef96735:0xb6a15f1a96d80862!8m2!3d33.8175706!4d-117.8365434!16s%2Fg%2F1tg6v_cs!19sChIJNWf5zqTW3IARYgjYlhpfobY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:45:20.914Z</t>
+  </si>
+  <si>
+    <t>Comfort Smile Family Dentistry</t>
+  </si>
+  <si>
+    <t>(714) 997-4133</t>
+  </si>
+  <si>
+    <t>1920 E Katella Ave Ste j, Orange, CA 92867</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Comfort+Smile+Family+Dentistry/data=!4m7!3m6!1s0x80dcd7528f898c0d:0xec44c15b3ad05902!8m2!3d33.8082351!4d-117.8337529!16s%2Fg%2F11f656zb6_!19sChIJDYyJj1LX3IARAlnQOlvBROw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:45:25.533Z</t>
+  </si>
+  <si>
+    <t>Dr. Richmond Chung, DMD</t>
+  </si>
+  <si>
+    <t>(714) 639-0412</t>
+  </si>
+  <si>
+    <t>1500 E Katella Ave C, Orange, CA 92867</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Richmond+Chung,+DMD/data=!4m7!3m6!1s0x80dcd74e1de4a94b:0xe1bd74d8030b3197!8m2!3d33.8087684!4d-117.837948!16s%2Fg%2F1tcvpkqb!19sChIJS6nkHU7X3IARlzELA9h0veE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:46:04.060Z</t>
+  </si>
+  <si>
+    <t>GeneACampanaDDS</t>
+  </si>
+  <si>
+    <t>(714) 639-0122</t>
+  </si>
+  <si>
+    <t>1500 E Katella Ave J, Orange, CA 92867</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/GeneACampanaDDS/data=!4m7!3m6!1s0x80dcd74e1de4a94b:0x86c70eb6a07b8e7e!8m2!3d33.8088518!4d-117.8378601!16s%2Fg%2F1tdx8_p4!19sChIJS6nkHU7X3IARfo57oLYOx4Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:46:06.988Z</t>
+  </si>
+  <si>
+    <t>Dr. Sara V. Quintero, DDS</t>
+  </si>
+  <si>
+    <t>(714) 289-9908</t>
+  </si>
+  <si>
+    <t>3906 E Chapman Ave, Orange, CA 92869</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Sara+V.+Quintero,+DDS/data=!4m7!3m6!1s0x80dd29ccc1af049d:0x9bd9f808d46d3e01!8m2!3d33.7873464!4d-117.8119077!16s%2Fg%2F1tddshkh!19sChIJnQSvwcwp3YARAT5t1Aj42Zs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:46:09.602Z</t>
+  </si>
+  <si>
+    <t>Orthodontic Centre Of Orange Country</t>
+  </si>
+  <si>
+    <t>(714) 689-8171</t>
+  </si>
+  <si>
+    <t>Orange, CA 92868</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Orthodontic+Centre+Of+Orange+Country/data=!4m7!3m6!1s0x80dcd9ced15c8b0b:0x8ad75bfcfd39aaf7!8m2!3d33.7744206!4d-117.869591!16s%2Fg%2F11dx92bd61!19sChIJC4tc0c7Z3IAR96o5_fxb14o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:46:35.034Z</t>
+  </si>
+  <si>
+    <t>Dr. Orfan Chalabi, DDS</t>
+  </si>
+  <si>
+    <t>(714) 771-2270</t>
+  </si>
+  <si>
+    <t>1501 E Katella Ave, Orange, CA 92867</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Orfan+Chalabi,+DDS/data=!4m7!3m6!1s0x80dcd74e6c0c748d:0x97d672c357564d18!8m2!3d33.8099748!4d-117.8378944!16s%2Fg%2F11cn6ksb2k!19sChIJjXQMbE7X3IARGE1WV8Ny1pc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:46:37.395Z</t>
+  </si>
+  <si>
+    <t>Dr. Grace Noble Dy D.M.D.</t>
+  </si>
+  <si>
+    <t>(714) 282-0430</t>
+  </si>
+  <si>
+    <t>807 E Katella Ave, Orange, CA 92867</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Grace+Noble+Dy+D.M.D./data=!4m7!3m6!1s0x80dcd735d5d44961:0xefe4816a7ac9a912!8m2!3d33.8093935!4d-117.8456142!16s%2Fg%2F1tknkrc5!19sChIJYUnU1TXX3IAREqnJemqB5O8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:46:40.132Z</t>
+  </si>
+  <si>
+    <t>Chapman Dental</t>
+  </si>
+  <si>
+    <t>(714) 538-6566</t>
+  </si>
+  <si>
+    <t>4501 E Chapman Ave B, Orange, CA 92869</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chapman+Dental/data=!4m7!3m6!1s0x80dcda6a442ce56d:0x3f52423542fef12c!8m2!3d33.7879931!4d-117.8055336!16s%2Fg%2F1vb9db_s!19sChIJbeUsRGra3IARLPH-QjVCUj8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:48:00.386Z</t>
+  </si>
+  <si>
+    <t>Town and Country Dental</t>
+  </si>
+  <si>
+    <t>(714) 653-1992</t>
+  </si>
+  <si>
+    <t>1111 W Town and Country Rd Ste 33, Orange, CA 92868</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Town+and+Country+Dental/data=!4m7!3m6!1s0x80dcd9c5c67c7d33:0x3aba36d07cdd139!8m2!3d33.7771598!4d-117.864291!16s%2Fg%2F1tczksm5!19sChIJM318xsXZ3IAROdHNB22jqwM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:48:08.192Z</t>
+  </si>
+  <si>
+    <t>Teeth Whitening Orange</t>
+  </si>
+  <si>
+    <t>(714) 941-0684</t>
+  </si>
+  <si>
+    <t>COURTYARD OFFICE BUILDING, 172 N Tustin St, Orange, CA 92867</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Teeth+Whitening+Orange/data=!4m7!3m6!1s0x80dcd9f9efda3e6f:0x24b97a44526f21bb!8m2!3d33.789171!4d-117.8360402!16s%2Fg%2F1tdpmcsb!19sChIJbz7a7_nZ3IARuyFvUkR6uSQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:48:26.361Z</t>
+  </si>
+  <si>
+    <t>Hoffmann Keith DDS</t>
+  </si>
+  <si>
+    <t>(714) 639-1333</t>
+  </si>
+  <si>
+    <t>1500 E Katella Ave, Orange, CA 92867</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hoffmann+Keith+DDS/data=!4m7!3m6!1s0x80dcd751e32680a1:0xa244a4550f7f1f1d!8m2!3d33.8083109!4d-117.8376902!16s%2Fg%2F1tsyq25r!19sChIJoYAm41HX3IARHR9_D1WkRKI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:48:57.233Z</t>
+  </si>
+  <si>
+    <t>Affordable Dentist Dr. Rhoudenko</t>
+  </si>
+  <si>
+    <t>(714) 716-1783</t>
+  </si>
+  <si>
+    <t>100 Laguna Rd ste 210, Fullerton, CA 92835</t>
+  </si>
+  <si>
+    <t>Fullerton</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Affordable+Dentist+Dr.+Rhoudenko/data=!4m7!3m6!1s0x80dd2bd83dfc9bc7:0x588a3b844c2c3687!8m2!3d33.8925088!4d-117.9299925!16s%2Fg%2F11r_zt9gmp!19sChIJx5v8Pdgr3YARhzYsTIQ7ilg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:49:27.326Z</t>
+  </si>
+  <si>
+    <t>Eric M Meyer DDS</t>
+  </si>
+  <si>
+    <t>(209) 315-2369</t>
+  </si>
+  <si>
+    <t>2720 N Harbor Blvd, Fullerton, CA 92835</t>
+  </si>
+  <si>
+    <t>Saturday6 AM–11 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Eric+M+Meyer+DDS/data=!4m7!3m6!1s0x80dd2a80ed268b6d:0xeea661be813e6664!8m2!3d33.9011076!4d-117.9286553!16s%2Fg%2F1td7zd2g!19sChIJbYsm7YAq3YARZGY-gb5hpu4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:49:39.274Z</t>
+  </si>
+  <si>
+    <t>Family Dental</t>
+  </si>
+  <si>
+    <t>(714) 525-4538</t>
+  </si>
+  <si>
+    <t>2442 E Chapman Ave, Fullerton, CA 92831</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Dental/data=!4m7!3m6!1s0x80dcd5d0bbb10d87:0x811330174806f02d!8m2!3d33.8732367!4d-117.8882083!16s%2Fg%2F1th1d08m!19sChIJhw2xu9DV3IARLfAGSBcwE4E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:50:28.692Z</t>
+  </si>
+  <si>
+    <t>ECO DENTAL</t>
+  </si>
+  <si>
+    <t>(714) 879-0142</t>
+  </si>
+  <si>
+    <t>2210 W Commonwealth Ave, Fullerton, CA 92833</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/ECO+DENTAL/data=!4m7!3m6!1s0x80dd2bba34f841a5:0xbaceef9528898235!8m2!3d33.869887!4d-117.9674923!16s%2Fg%2F11hj72sr6g!19sChIJpUH4NLor3YARNYKJKJXvzro?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:50:41.402Z</t>
+  </si>
+  <si>
+    <t>Dr. Nada Mikhail, DMD</t>
+  </si>
+  <si>
+    <t>(714) 871-1932</t>
+  </si>
+  <si>
+    <t>125 W Orangethorpe Ave, Fullerton, CA 92832</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Nada+Mikhail,+DMD/data=!4m7!3m6!1s0x80dd2b8c96b0fc13:0xa3384d6c575d5fe4!8m2!3d33.8598501!4d-117.9254097!16s%2Fg%2F11x145wrpy!19sChIJE_ywlowr3YAR5F9dV2xNOKM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:50:46.440Z</t>
+  </si>
+  <si>
+    <t>Myers Steven A DDS</t>
+  </si>
+  <si>
+    <t>(714) 870-1051</t>
+  </si>
+  <si>
+    <t>529 N Harbor Blvd, Fullerton, CA 92832</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Myers+Steven+A+DDS/data=!4m7!3m6!1s0x80dd2a761cf23be9:0x2d3d558d62da087c!8m2!3d33.8751436!4d-117.9246563!16s%2Fg%2F1tcyfs7d!19sChIJ6TvyHHYq3YARfAjaYo1VPS0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:50:53.919Z</t>
+  </si>
+  <si>
+    <t>Sharon J Lee, DDS -Fullerton, CA</t>
+  </si>
+  <si>
+    <t>(714) 999-8840</t>
+  </si>
+  <si>
+    <t>1321 N Harbor Blvd Ste 104, Fullerton, CA 92835</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sharon+J+Lee,+DDS+-Fullerton,+CA/data=!4m7!3m6!1s0x80dd29f44ddcf695:0x71ab6e8e5f130595!8m2!3d33.8832575!4d-117.9257969!16s%2Fg%2F1vyswvc9!19sChIJlfbcTfQp3YARlQUTX45uq3E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:51:08.025Z</t>
+  </si>
+  <si>
+    <t>Sunshine Dental</t>
+  </si>
+  <si>
+    <t>(714) 738-7777</t>
+  </si>
+  <si>
+    <t>506 W Commonwealth Ave, Fullerton, CA 92832</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sunshine+Dental/data=!4m7!3m6!1s0x80dd2a0effb4cf35:0xbfdaccc274a8a0ed!8m2!3d33.8700955!4d-117.9334357!16s%2Fg%2F11gglt792c!19sChIJNc-0_w4q3YAR7aCodMLM2r8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:51:41.345Z</t>
+  </si>
+  <si>
+    <t>Allbright Dental: Dr. Rose Marie L. Tan DDS</t>
+  </si>
+  <si>
+    <t>(714) 525-4850</t>
+  </si>
+  <si>
+    <t>212 E Commonwealth Ave, Fullerton, CA 92832</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Allbright+Dental:+Dr.+Rose+Marie+L.+Tan+DDS/data=!4m7!3m6!1s0x80dcd5f9d0f0cfaf:0x3895e75da4b5f2ad!8m2!3d33.8701281!4d-117.9213612!16s%2Fg%2F1tsbmd_0!19sChIJr8_w0PnV3IARrfK1pF3nlTg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:51:56.933Z</t>
+  </si>
+  <si>
+    <t>family dentistry</t>
+  </si>
+  <si>
+    <t>(714) 871-8475</t>
+  </si>
+  <si>
+    <t>301 N Euclid St, Fullerton, CA 92832</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/family+dentistry/data=!4m7!3m6!1s0x80dd2b64f2eb6519:0xfe35b47075429e55!8m2!3d33.8724819!4d-117.9426231!16s%2Fg%2F11q9rcz0tv!19sChIJGWXr8mQr3YARVZ5CdXC0Nf4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:52:24.153Z</t>
+  </si>
+  <si>
+    <t>Barbara Macias, DDS</t>
+  </si>
+  <si>
+    <t>(714) 879-5960</t>
+  </si>
+  <si>
+    <t>100 Laguna Rd Ste. 200, Fullerton, CA 92835</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Barbara+Macias,+DDS/data=!4m7!3m6!1s0x80dd2b1c6f2da973:0x2f5a6af584180369!8m2!3d33.8925016!4d-117.9300038!16s%2Fg%2F11lg3rgq83!19sChIJc6ktbxwr3YARaQMYhPVqWi8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:52:45.038Z</t>
+  </si>
+  <si>
+    <t>Mc Lean Chris a DDS</t>
+  </si>
+  <si>
+    <t>(714) 525-4313</t>
+  </si>
+  <si>
+    <t>810 E Chapman Ave, Fullerton, CA 92831</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mc+Lean+Chris+a+DDS/data=!4m7!3m6!1s0x80dcd5ef939bfdff:0xe0e6683b9cab4b83!8m2!3d33.8737987!4d-117.9115466!16s%2Fg%2F1tjt271z!19sChIJ__2bk-_V3IARg0urnDto5uA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:53:00.007Z</t>
+  </si>
+  <si>
+    <t>Bethel Dentistry</t>
+  </si>
+  <si>
+    <t>(714) 869-3043</t>
+  </si>
+  <si>
+    <t>1821 W Commonwealth Ave, Fullerton, CA 92833</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bethel+Dentistry/data=!4m7!3m6!1s0x80dd2a37fac8e51d:0x47516840a29e6db0!8m2!3d33.8703776!4d-117.9606625!16s%2Fg%2F11cky3xpnt!19sChIJHeXI-jcq3YARsG2eokBoUUc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:53:22.351Z</t>
+  </si>
+  <si>
+    <t>Nooshin Majd</t>
+  </si>
+  <si>
+    <t>(714) 871-8422</t>
+  </si>
+  <si>
+    <t>1950 E Chapman Ave #1, Fullerton, CA 92831</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nooshin+Majd/data=!4m7!3m6!1s0x80dcd5dc61f0bd15:0x330833e70155d692!8m2!3d33.8738901!4d-117.8967616!16s%2Fg%2F11qgb6tdqf!19sChIJFb3wYdzV3IARktZVAeczCDM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:53:43.318Z</t>
+  </si>
+  <si>
+    <t>Hong Leland S DDS</t>
+  </si>
+  <si>
+    <t>(714) 525-8344</t>
+  </si>
+  <si>
+    <t>501 N Cornell Ave # D, Fullerton, CA 92831</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hong+Leland+S+DDS/data=!4m7!3m6!1s0x80dcd5ef7599b989:0x34753b6349d6acff!8m2!3d33.8743462!4d-117.9103013!16s%2Fg%2F1wyc4mwj!19sChIJibmZde_V3IAR_6zWSWM7dTQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:53:45.782Z</t>
+  </si>
+  <si>
+    <t>Ngo Michael DDS</t>
+  </si>
+  <si>
+    <t>(714) 680-3377</t>
+  </si>
+  <si>
+    <t>713 E Chapman Ave, Fullerton, CA 92831</t>
+  </si>
+  <si>
+    <t>Saturday7 AM–3:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ngo+Michael+DDS/data=!4m7!3m6!1s0x80dcd5e7c3012b13:0xf5254ea2c57b5f99!8m2!3d33.8743084!4d-117.9127115!16s%2Fg%2F1w346xqh!19sChIJEysBw-fV3IARmV97xaJOJfU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:54:00.968Z</t>
+  </si>
+  <si>
+    <t>John U Choi DDS, PhD</t>
+  </si>
+  <si>
+    <t>(714) 449-8650</t>
+  </si>
+  <si>
+    <t>301 W Bastanchury Rd #255, Fullerton, CA 92835</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/John+U+Choi+DDS,+PhD/data=!4m7!3m6!1s0x80dd2a7c0eab1a25:0x99bcdd74c88f62d0!8m2!3d33.8943575!4d-117.9321991!16s%2Fg%2F1tcylbj_!19sChIJJRqrDnwq3YAR0GKPyHTdvJk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:55:36.799Z</t>
+  </si>
+  <si>
+    <t>Yon Dental Group</t>
+  </si>
+  <si>
+    <t>(714) 519-3932</t>
+  </si>
+  <si>
+    <t>1031 Rosecrans Ave #104, Fullerton, CA 92833</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–1 PM; SundayClosed; Monday9 AM–5 PM; Tuesday9 AM–5 PM; WednesdayClosed; Thursday9 AM–5 PM; Friday9 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Yon+Dental+Group/data=!4m7!3m6!1s0x80dd2b690f1aef73:0x548d338d4d49e966!8m2!3d33.8938598!4d-117.9453735!16s%2Fg%2F11gj0w48vr!19sChIJc-8aD2kr3YARZulJTY0zjVQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:55:41.598Z</t>
+  </si>
+  <si>
+    <t>San Jose Dental Care.</t>
+  </si>
+  <si>
+    <t>(408) 998-8866</t>
+  </si>
+  <si>
+    <t>345 E Santa Clara St #102, San Jose, CA 95113</t>
+  </si>
+  <si>
+    <t>San Jose</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/San+Jose+Dental+Care./data=!4m7!3m6!1s0x808fccbe6b6b11bd:0x44b7cac1f2c0be72!8m2!3d37.3397714!4d-121.8834839!16s%2Fg%2F1tfmcgrm!19sChIJvRFra77Mj4ARcr7A8sHKt0Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:56:11.020Z</t>
+  </si>
+  <si>
+    <t>Advanced Dental Care.</t>
+  </si>
+  <si>
+    <t>(408) 937-8881</t>
+  </si>
+  <si>
+    <t>999 Story Rd Unit 9066, San Jose, CA 95122</t>
+  </si>
+  <si>
+    <t>Saturday9:30 AM–6:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Advanced+Dental+Care./data=!4m7!3m6!1s0x808fcd2aa18a3113:0x59d514fb54c9fa1d!8m2!3d37.3319025!4d-121.8566201!16s%2Fg%2F12632mlwj!19sChIJEzGKoSrNj4ARHfrJVPsU1Vk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:56:28.649Z</t>
+  </si>
+  <si>
+    <t>All Smiles Family Dentistry &amp; Orthodontics - Dental Emergency</t>
+  </si>
+  <si>
+    <t>(408) 564-0200</t>
+  </si>
+  <si>
+    <t>365 S Redwood Ave, San Jose, CA 95128</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/All+Smiles+Family+Dentistry+%26+Orthodontics+-+Dental+Emergency/data=!4m7!3m6!1s0x808fca88f94a7217:0xbf23393725b5a348!8m2!3d37.3218381!4d-121.9470443!16s%2Fg%2F11c4b76d7r!19sChIJF3JK-YjKj4ARSKO1JTc5I78?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:56:36.519Z</t>
+  </si>
+  <si>
+    <t>Bird Avenue Dental Care</t>
+  </si>
+  <si>
+    <t>(408) 297-8505</t>
+  </si>
+  <si>
+    <t>1419 Bird Ave., San Jose, CA 95125</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bird+Avenue+Dental+Care/data=!4m7!3m6!1s0x808e33f3d39f6acb:0x1eff1054e3de53b5!8m2!3d37.3066445!4d-121.8917609!16s%2Fg%2F11y4m1xqhn!19sChIJy2qf0_MzjoARtVPe41QQ_x4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:56:47.201Z</t>
+  </si>
+  <si>
+    <t>NewGen Dental</t>
+  </si>
+  <si>
+    <t>(408) 258-5555</t>
+  </si>
+  <si>
+    <t>788 N King Rd Ste 10, San Jose, CA 95133</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/NewGen+Dental/data=!4m7!3m6!1s0x808fcc5848161a29:0x8ef9e6489aecd05a!8m2!3d37.3665834!4d-121.8689321!16s%2Fg%2F11bbw_lww2!19sChIJKRoWSFjMj4ARWtDsmkjm-Y4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:57:17.106Z</t>
+  </si>
+  <si>
+    <t>Dental For Today - walk ins urgent</t>
+  </si>
+  <si>
+    <t>(408) 972-9990</t>
+  </si>
+  <si>
+    <t>459 S Capitol Ave #4, San Jose, CA 95127</t>
+  </si>
+  <si>
+    <t>Saturday10:30 AM–4 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+For+Today+-+walk+ins+urgent/data=!4m7!3m6!1s0x808e32407bc030b3:0x851e737f60c337be!8m2!3d37.3562033!4d-121.831485!16s%2Fg%2F1tpps5sz!19sChIJszDAe0AyjoARvjfDYH9zHoU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:57:53.959Z</t>
+  </si>
+  <si>
+    <t>Family Care Dentistry</t>
+  </si>
+  <si>
+    <t>(669) 308-4560</t>
+  </si>
+  <si>
+    <t>418 Jackson St, San Jose, CA 95112</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Care+Dentistry/data=!4m7!3m6!1s0x808fcd0064337131:0x5feb5ecc5a3e4f3d!8m2!3d37.3509181!4d-121.8897413!16s%2Fg%2F11zzpqdtmm!19sChIJMXEzZADNj4ARPU8-Wsxe618?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:59:26.695Z</t>
+  </si>
+  <si>
+    <t>Family Dental Care - Dr.Imelda Pintado Nagtalon</t>
+  </si>
+  <si>
+    <t>(408) 993-8491</t>
+  </si>
+  <si>
+    <t>C, 750 N Capitol Ave Ste C8, San Jose, CA 95133</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Dental+Care+-+Dr.Imelda+Pintado+Nagtalon/data=!4m7!3m6!1s0x808fcdae75500001:0x5509e2ffe31e3af7!8m2!3d37.3786873!4d-121.8505235!16s%2Fg%2F11ss_4rjyb!19sChIJAQBQda7Nj4AR9zoe4__iCVU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:59:28.737Z</t>
+  </si>
+  <si>
+    <t>McKee Family Dental: Justine Chen DDS, Darwin Chan DDS</t>
+  </si>
+  <si>
+    <t>(408) 729-8888</t>
+  </si>
+  <si>
+    <t>2360 McKee Rd #2, San Jose, CA 95116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/McKee+Family+Dental:+Justine+Chen+DDS,+Darwin+Chan+DDS/data=!4m7!3m6!1s0x808fcd0681a8c08d:0xa05b95bb685538fb!8m2!3d37.366275!4d-121.8477861!16s%2Fg%2F1tdfyzc6!19sChIJjcCogQbNj4AR-zhVaLuVW6A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:59:31.050Z</t>
+  </si>
+  <si>
+    <t>Almaden Family Dentistry</t>
+  </si>
+  <si>
+    <t>(408) 927-7378</t>
+  </si>
+  <si>
+    <t>5945 Almaden Expy, San Jose, CA 95120</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Almaden+Family+Dentistry/data=!4m7!3m6!1s0x808e31692667b1d3:0x2675486ed103ab1b!8m2!3d37.2348144!4d-121.8735711!16s%2Fg%2F1td6ybnc!19sChIJ07FnJmkxjoARG6sD0W5IdSY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:59:35.032Z</t>
+  </si>
+  <si>
+    <t>Dr. Tuyen Q. Nguyen, DDS</t>
+  </si>
+  <si>
+    <t>(408) 286-6156</t>
+  </si>
+  <si>
+    <t>634 E Santa Clara St, San Jose, CA 95112</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Tuyen+Q.+Nguyen,+DDS/data=!4m7!3m6!1s0x808fccc0234de639:0x7bed6b322da345a7!8m2!3d37.3420653!4d-121.8773529!16s%2Fg%2F1vh_8mdj!19sChIJOeZNI8DMj4ARp0WjLTJr7Xs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:01:09.042Z</t>
+  </si>
+  <si>
+    <t>South Bay Dental Center &amp; Orthodontics</t>
+  </si>
+  <si>
+    <t>(408) 259-8899</t>
+  </si>
+  <si>
+    <t>2505 Berryessa Rd, San Jose, CA 95132</t>
+  </si>
+  <si>
+    <t>Open · Closes 5:30 PM · See more hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/South+Bay+Dental+Center+%26+Orthodontics/data=!4m7!3m6!1s0x808fcc358dd22e53:0xb7e33abe67ee2d3c!8m2!3d37.3871015!4d-121.8602316!16s%2Fg%2F11b7g1wtsh!19sChIJUy7SjTXMj4ARPC3uZ74647c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:01:31.147Z</t>
+  </si>
+  <si>
+    <t>SmileWorld Dental Clinic&amp; Orthodontics</t>
+  </si>
+  <si>
+    <t>(408) 929-9797</t>
+  </si>
+  <si>
+    <t>2811 Story Rd, San Jose, CA 95127</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/SmileWorld+Dental+Clinic%26+Orthodontics/data=!4m7!3m6!1s0x808fcd448e1531ff:0x64d9b36f78edeaa0!8m2!3d37.3532753!4d-121.824149!16s%2Fg%2F1264hsm5v!19sChIJ_zEVjkTNj4ARoOrteG-z2WQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:01:33.899Z</t>
+  </si>
+  <si>
+    <t>Kwong Orthodontics</t>
+  </si>
+  <si>
+    <t>(408) 286-6330</t>
+  </si>
+  <si>
+    <t>189 N Bascom Ave #200, San Jose, CA 95128</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kwong+Orthodontics/data=!4m7!3m6!1s0x808e3181a1531ee1:0x3d761971cca0a8fb!8m2!3d37.3264793!4d-121.9323339!16s%2Fg%2F1tfqlm5x!19sChIJ4R5ToYExjoAR-6igzHEZdj0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:01:36.676Z</t>
+  </si>
+  <si>
+    <t>San Jose Dental Smiles</t>
+  </si>
+  <si>
+    <t>(408) 269-3411</t>
+  </si>
+  <si>
+    <t>3535 Ross Ave #207, San Jose, CA 95124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/San+Jose+Dental+Smiles/data=!4m7!3m6!1s0x808e354eb692a11f:0x730b240f1e21e8f7!8m2!3d37.2628325!4d-121.9165726!16s%2Fg%2F11kc5hfvjp!19sChIJH6GStk41joAR9-ghHg8kC3M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:01:39.782Z</t>
+  </si>
+  <si>
+    <t>Dr. Thao Le Orthodontics</t>
+  </si>
+  <si>
+    <t>(408) 272-7171</t>
+  </si>
+  <si>
+    <t>2175 Tully Rd, San Jose, CA 95122</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Thao+Le+Orthodontics/data=!4m7!3m6!1s0x808e32a489214e3f:0x3c564ddfc646f2de!8m2!3d37.3272919!4d-121.8193137!16s%2Fg%2F1tmxfss_!19sChIJP04hiaQyjoAR3vJGxt9NVjw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:01:42.763Z</t>
+  </si>
+  <si>
+    <t>Manila Dental Center &amp; Orthodontics III</t>
+  </si>
+  <si>
+    <t>(408) 729-8880</t>
+  </si>
+  <si>
+    <t>1605 Tully Rd, San Jose, CA 95122</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Manila+Dental+Center+%26+Orthodontics+III/data=!4m7!3m6!1s0x808e32be6f3f5f23:0x7f6f5865fec3f7e2!8m2!3d37.3207855!4d-121.8287506!16s%2Fg%2F1tgdj6pp!19sChIJI18_b74yjoAR4vfD_mVYb38?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:01:45.382Z</t>
+  </si>
+  <si>
+    <t>Sky Dental Implant Center</t>
+  </si>
+  <si>
+    <t>(408) 564-4305</t>
+  </si>
+  <si>
+    <t>2114 Senter Rd Ste 4, San Jose, CA 95112</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sky+Dental+Implant+Center/data=!4m7!3m6!1s0x808e33e25e1d025b:0x1ce7e99a62892253!8m2!3d37.3117106!4d-121.8510186!16s%2Fg%2F11ywqppnsb!19sChIJWwIdXuIzjoARUyKJYprp5xw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:02:01.199Z</t>
+  </si>
+  <si>
+    <t>Dental Implant &amp; Clinic</t>
+  </si>
+  <si>
+    <t>(408) 363-1787</t>
+  </si>
+  <si>
+    <t>3161 Senter Rd, San Jose, CA 95111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Implant+%26+Clinic/data=!4m7!3m6!1s0x808e33660a983bad:0x1e94b198f367acb4!8m2!3d37.2924511!4d-121.83327!16s%2Fg%2F11hz0dh9k0!19sChIJrTuYCmYzjoARtKxn85ixlB4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:02:03.545Z</t>
+  </si>
+  <si>
+    <t>Emergency Dentist San Jose</t>
+  </si>
+  <si>
+    <t>(408) 351-0035</t>
+  </si>
+  <si>
+    <t>1705 Ross Ave, San Jose, CA 95124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dentist+San+Jose/data=!4m7!3m6!1s0x808e35bc9ec0e331:0xe23a193f1cf37fe9!8m2!3d37.2519038!4d-121.9091158!16s%2Fg%2F11r5_wvly2!19sChIJMePAnrw1joAR6X_zHD8ZOuI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:02:18.805Z</t>
+  </si>
+  <si>
+    <t>QuickCare Family Care</t>
+  </si>
+  <si>
+    <t>(877) 540-6110</t>
+  </si>
+  <si>
+    <t>275 Rhodes Ct, San Jose, CA 95126</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/QuickCare+Family+Care/data=!4m7!3m6!1s0x808fcb78b1a434f1:0x6e5e374b58b3156e!8m2!3d37.3333384!4d-121.907558!16s%2Fg%2F11zx2zxx90!19sChIJ8TSksXjLj4ARbhWzWEs3Xm4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:02:21.275Z</t>
+  </si>
+  <si>
+    <t>Dr. Adam Askari, DDS</t>
+  </si>
+  <si>
+    <t>(408) 740-7705</t>
+  </si>
+  <si>
+    <t>2881 Hemlock Ave A, San Jose, CA 95128</t>
+  </si>
+  <si>
+    <t>Saturday7 AM–2 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Adam+Askari,+DDS/data=!4m7!3m6!1s0x808fcb204820a453:0xb54d5918c48073f0!8m2!3d37.3213363!4d-121.9449935!16s%2Fg%2F1tj_5gzb!19sChIJU6QgSCDLj4AR8HOAxBhZTbU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:02:23.936Z</t>
+  </si>
+  <si>
+    <t>Modern Dental Office/ Hien Ha DMD</t>
+  </si>
+  <si>
+    <t>(408) 885-0106</t>
+  </si>
+  <si>
+    <t>992 Story Rd #10, San Jose, CA 95122</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Modern+Dental+Office%2F+Hien+Ha+DMD/data=!4m7!3m6!1s0x808fcd2ab663146b:0xe05ba6870d606580!8m2!3d37.3308047!4d-121.855004!16s%2Fg%2F1tjrq6fd!19sChIJaxRjtirNj4ARgGVgDYemW-A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:03:14.633Z</t>
+  </si>
+  <si>
+    <t>Bright Smile Dental Office</t>
+  </si>
+  <si>
+    <t>(408) 244-8866</t>
+  </si>
+  <si>
+    <t>999 Saratoga Ave #10, San Jose, CA 95129</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bright+Smile+Dental+Office/data=!4m7!3m6!1s0x808fca95cf30371f:0x2d890f589e3b3743!8m2!3d37.3084572!4d-121.9780145!16s%2Fg%2F1tfccdxl!19sChIJHzcwz5XKj4ARQzc7nlgPiS0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:03:19.041Z</t>
+  </si>
+  <si>
+    <t>Gifford Timothy W DDS</t>
+  </si>
+  <si>
+    <t>(408) 578-6400</t>
+  </si>
+  <si>
+    <t>5595 Winfield Blvd #208, San Jose, CA 95123</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gifford+Timothy+W+DDS/data=!4m7!3m6!1s0x808e33d79376cafd:0x82d4e7f10e1ce8d1!8m2!3d37.2516201!4d-121.8668459!16s%2Fg%2F1vjdq925!19sChIJ_cp2k9czjoAR0egcDvHn1II?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:04:04.421Z</t>
+  </si>
+  <si>
+    <t>Mission Dolores Dental Care</t>
+  </si>
+  <si>
+    <t>(415) 863-2690</t>
+  </si>
+  <si>
+    <t>2272 Mission St, San Francisco, CA 94110</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mission+Dolores+Dental+Care/data=!4m7!3m6!1s0x808f7e3c8e1038ff:0x153d826f6c5e9e71!8m2!3d37.7607157!4d-122.4195677!16s%2Fg%2F1wn33xd5!19sChIJ_zgQjjx-j4ARcZ5ebG-CPRU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:06:05.115Z</t>
+  </si>
+  <si>
+    <t>California Hospital DentalGroup</t>
+  </si>
+  <si>
+    <t>(833) 567-5851</t>
+  </si>
+  <si>
+    <t>3109A Geary Blvd, San Francisco, CA 94118</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/California+Hospital+DentalGroup/data=!4m7!3m6!1s0x80858735e2a9d277:0xd194996e14849531!8m2!3d37.7816366!4d-122.4523825!16s%2Fg%2F11c5svxywv!19sChIJd9Kp4jWHhYARMZWEFG6ZlNE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:06:09.491Z</t>
   </si>
 </sst>
 </file>
@@ -6115,7 +8401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M346"/>
+  <dimension ref="A1:M491"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -20318,6 +22604,5951 @@
         <v>1907</v>
       </c>
     </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B347" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C347" t="s">
+        <v>926</v>
+      </c>
+      <c r="D347" t="s">
+        <v>1910</v>
+      </c>
+      <c r="E347" t="s">
+        <v>1828</v>
+      </c>
+      <c r="F347" t="s">
+        <v>18</v>
+      </c>
+      <c r="G347" t="s">
+        <v>19</v>
+      </c>
+      <c r="H347" t="s">
+        <v>75</v>
+      </c>
+      <c r="I347" t="s">
+        <v>81</v>
+      </c>
+      <c r="J347" t="s">
+        <v>75</v>
+      </c>
+      <c r="K347" t="s">
+        <v>23</v>
+      </c>
+      <c r="L347" t="s">
+        <v>1911</v>
+      </c>
+      <c r="M347" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B348" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C348" t="s">
+        <v>15</v>
+      </c>
+      <c r="D348" t="s">
+        <v>1915</v>
+      </c>
+      <c r="E348" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F348" t="s">
+        <v>18</v>
+      </c>
+      <c r="G348" t="s">
+        <v>19</v>
+      </c>
+      <c r="H348" t="s">
+        <v>37</v>
+      </c>
+      <c r="I348" t="s">
+        <v>21</v>
+      </c>
+      <c r="J348" t="s">
+        <v>479</v>
+      </c>
+      <c r="K348" t="s">
+        <v>23</v>
+      </c>
+      <c r="L348" t="s">
+        <v>1917</v>
+      </c>
+      <c r="M348" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B349" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C349" t="s">
+        <v>15</v>
+      </c>
+      <c r="D349" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E349" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F349" t="s">
+        <v>18</v>
+      </c>
+      <c r="G349" t="s">
+        <v>19</v>
+      </c>
+      <c r="H349" t="s">
+        <v>466</v>
+      </c>
+      <c r="I349" t="s">
+        <v>21</v>
+      </c>
+      <c r="J349" t="s">
+        <v>1922</v>
+      </c>
+      <c r="K349" t="s">
+        <v>23</v>
+      </c>
+      <c r="L349" t="s">
+        <v>1923</v>
+      </c>
+      <c r="M349" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C350" t="s">
+        <v>15</v>
+      </c>
+      <c r="D350" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E350" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F350" t="s">
+        <v>18</v>
+      </c>
+      <c r="G350" t="s">
+        <v>19</v>
+      </c>
+      <c r="H350" t="s">
+        <v>75</v>
+      </c>
+      <c r="I350" t="s">
+        <v>81</v>
+      </c>
+      <c r="J350" t="s">
+        <v>30</v>
+      </c>
+      <c r="K350" t="s">
+        <v>23</v>
+      </c>
+      <c r="L350" t="s">
+        <v>1928</v>
+      </c>
+      <c r="M350" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C351" t="s">
+        <v>15</v>
+      </c>
+      <c r="D351" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E351" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F351" t="s">
+        <v>18</v>
+      </c>
+      <c r="G351" t="s">
+        <v>19</v>
+      </c>
+      <c r="H351" t="s">
+        <v>45</v>
+      </c>
+      <c r="I351" t="s">
+        <v>21</v>
+      </c>
+      <c r="J351" t="s">
+        <v>648</v>
+      </c>
+      <c r="K351" t="s">
+        <v>23</v>
+      </c>
+      <c r="L351" t="s">
+        <v>1933</v>
+      </c>
+      <c r="M351" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B352" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C352" t="s">
+        <v>607</v>
+      </c>
+      <c r="D352" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E352" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F352" t="s">
+        <v>18</v>
+      </c>
+      <c r="G352" t="s">
+        <v>19</v>
+      </c>
+      <c r="H352" t="s">
+        <v>45</v>
+      </c>
+      <c r="I352" t="s">
+        <v>21</v>
+      </c>
+      <c r="J352" t="s">
+        <v>75</v>
+      </c>
+      <c r="K352" t="s">
+        <v>23</v>
+      </c>
+      <c r="L352" t="s">
+        <v>1938</v>
+      </c>
+      <c r="M352" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B353" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C353" t="s">
+        <v>15</v>
+      </c>
+      <c r="D353" t="s">
+        <v>1942</v>
+      </c>
+      <c r="E353" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F353" t="s">
+        <v>18</v>
+      </c>
+      <c r="G353" t="s">
+        <v>19</v>
+      </c>
+      <c r="H353" t="s">
+        <v>815</v>
+      </c>
+      <c r="I353" t="s">
+        <v>21</v>
+      </c>
+      <c r="J353" t="s">
+        <v>418</v>
+      </c>
+      <c r="K353" t="s">
+        <v>23</v>
+      </c>
+      <c r="L353" t="s">
+        <v>1943</v>
+      </c>
+      <c r="M353" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B354" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C354" t="s">
+        <v>15</v>
+      </c>
+      <c r="D354" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E354" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F354" t="s">
+        <v>18</v>
+      </c>
+      <c r="G354" t="s">
+        <v>19</v>
+      </c>
+      <c r="H354" t="s">
+        <v>960</v>
+      </c>
+      <c r="I354" t="s">
+        <v>21</v>
+      </c>
+      <c r="J354" t="s">
+        <v>46</v>
+      </c>
+      <c r="K354" t="s">
+        <v>23</v>
+      </c>
+      <c r="L354" t="s">
+        <v>1948</v>
+      </c>
+      <c r="M354" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B355" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C355" t="s">
+        <v>15</v>
+      </c>
+      <c r="D355" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E355" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F355" t="s">
+        <v>18</v>
+      </c>
+      <c r="G355" t="s">
+        <v>19</v>
+      </c>
+      <c r="H355" t="s">
+        <v>466</v>
+      </c>
+      <c r="I355" t="s">
+        <v>21</v>
+      </c>
+      <c r="J355" t="s">
+        <v>46</v>
+      </c>
+      <c r="K355" t="s">
+        <v>23</v>
+      </c>
+      <c r="L355" t="s">
+        <v>1953</v>
+      </c>
+      <c r="M355" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B356" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C356" t="s">
+        <v>28</v>
+      </c>
+      <c r="D356" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E356" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F356" t="s">
+        <v>18</v>
+      </c>
+      <c r="G356" t="s">
+        <v>19</v>
+      </c>
+      <c r="H356" t="s">
+        <v>223</v>
+      </c>
+      <c r="I356" t="s">
+        <v>21</v>
+      </c>
+      <c r="J356" t="s">
+        <v>46</v>
+      </c>
+      <c r="K356" t="s">
+        <v>23</v>
+      </c>
+      <c r="L356" t="s">
+        <v>1958</v>
+      </c>
+      <c r="M356" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B357" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C357" t="s">
+        <v>15</v>
+      </c>
+      <c r="D357" t="s">
+        <v>1962</v>
+      </c>
+      <c r="E357" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F357" t="s">
+        <v>18</v>
+      </c>
+      <c r="G357" t="s">
+        <v>19</v>
+      </c>
+      <c r="H357" t="s">
+        <v>120</v>
+      </c>
+      <c r="I357" t="s">
+        <v>21</v>
+      </c>
+      <c r="J357" t="s">
+        <v>1963</v>
+      </c>
+      <c r="K357" t="s">
+        <v>23</v>
+      </c>
+      <c r="L357" t="s">
+        <v>1964</v>
+      </c>
+      <c r="M357" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B358" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C358" t="s">
+        <v>15</v>
+      </c>
+      <c r="D358" t="s">
+        <v>1968</v>
+      </c>
+      <c r="E358" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F358" t="s">
+        <v>18</v>
+      </c>
+      <c r="G358" t="s">
+        <v>19</v>
+      </c>
+      <c r="H358" t="s">
+        <v>381</v>
+      </c>
+      <c r="I358" t="s">
+        <v>21</v>
+      </c>
+      <c r="J358" t="s">
+        <v>418</v>
+      </c>
+      <c r="K358" t="s">
+        <v>23</v>
+      </c>
+      <c r="L358" t="s">
+        <v>1969</v>
+      </c>
+      <c r="M358" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B359" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C359" t="s">
+        <v>15</v>
+      </c>
+      <c r="D359" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E359" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F359" t="s">
+        <v>18</v>
+      </c>
+      <c r="G359" t="s">
+        <v>19</v>
+      </c>
+      <c r="H359" t="s">
+        <v>45</v>
+      </c>
+      <c r="I359" t="s">
+        <v>21</v>
+      </c>
+      <c r="J359" t="s">
+        <v>1975</v>
+      </c>
+      <c r="K359" t="s">
+        <v>23</v>
+      </c>
+      <c r="L359" t="s">
+        <v>1976</v>
+      </c>
+      <c r="M359" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C360" t="s">
+        <v>15</v>
+      </c>
+      <c r="D360" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E360" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F360" t="s">
+        <v>18</v>
+      </c>
+      <c r="G360" t="s">
+        <v>19</v>
+      </c>
+      <c r="H360" t="s">
+        <v>223</v>
+      </c>
+      <c r="I360" t="s">
+        <v>21</v>
+      </c>
+      <c r="J360" t="s">
+        <v>46</v>
+      </c>
+      <c r="K360" t="s">
+        <v>23</v>
+      </c>
+      <c r="L360" t="s">
+        <v>1981</v>
+      </c>
+      <c r="M360" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C361" t="s">
+        <v>15</v>
+      </c>
+      <c r="D361" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E361" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F361" t="s">
+        <v>18</v>
+      </c>
+      <c r="G361" t="s">
+        <v>19</v>
+      </c>
+      <c r="H361" t="s">
+        <v>547</v>
+      </c>
+      <c r="I361" t="s">
+        <v>21</v>
+      </c>
+      <c r="J361" t="s">
+        <v>1986</v>
+      </c>
+      <c r="K361" t="s">
+        <v>23</v>
+      </c>
+      <c r="L361" t="s">
+        <v>1987</v>
+      </c>
+      <c r="M361" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B362" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C362" t="s">
+        <v>477</v>
+      </c>
+      <c r="D362" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E362" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F362" t="s">
+        <v>18</v>
+      </c>
+      <c r="G362" t="s">
+        <v>19</v>
+      </c>
+      <c r="H362" t="s">
+        <v>815</v>
+      </c>
+      <c r="I362" t="s">
+        <v>21</v>
+      </c>
+      <c r="J362" t="s">
+        <v>46</v>
+      </c>
+      <c r="K362" t="s">
+        <v>23</v>
+      </c>
+      <c r="L362" t="s">
+        <v>1992</v>
+      </c>
+      <c r="M362" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C363" t="s">
+        <v>15</v>
+      </c>
+      <c r="D363" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E363" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F363" t="s">
+        <v>18</v>
+      </c>
+      <c r="G363" t="s">
+        <v>19</v>
+      </c>
+      <c r="H363" t="s">
+        <v>381</v>
+      </c>
+      <c r="I363" t="s">
+        <v>21</v>
+      </c>
+      <c r="J363" t="s">
+        <v>1997</v>
+      </c>
+      <c r="K363" t="s">
+        <v>23</v>
+      </c>
+      <c r="L363" t="s">
+        <v>1998</v>
+      </c>
+      <c r="M363" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B364" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C364" t="s">
+        <v>15</v>
+      </c>
+      <c r="D364" t="s">
+        <v>2002</v>
+      </c>
+      <c r="E364" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F364" t="s">
+        <v>18</v>
+      </c>
+      <c r="G364" t="s">
+        <v>19</v>
+      </c>
+      <c r="H364" t="s">
+        <v>45</v>
+      </c>
+      <c r="I364" t="s">
+        <v>21</v>
+      </c>
+      <c r="J364" t="s">
+        <v>966</v>
+      </c>
+      <c r="K364" t="s">
+        <v>23</v>
+      </c>
+      <c r="L364" t="s">
+        <v>2003</v>
+      </c>
+      <c r="M364" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B365" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C365" t="s">
+        <v>15</v>
+      </c>
+      <c r="D365" t="s">
+        <v>2007</v>
+      </c>
+      <c r="E365" t="s">
+        <v>2008</v>
+      </c>
+      <c r="F365" t="s">
+        <v>18</v>
+      </c>
+      <c r="G365" t="s">
+        <v>19</v>
+      </c>
+      <c r="H365" t="s">
+        <v>45</v>
+      </c>
+      <c r="I365" t="s">
+        <v>21</v>
+      </c>
+      <c r="J365" t="s">
+        <v>46</v>
+      </c>
+      <c r="K365" t="s">
+        <v>23</v>
+      </c>
+      <c r="L365" t="s">
+        <v>2009</v>
+      </c>
+      <c r="M365" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B366" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C366" t="s">
+        <v>15</v>
+      </c>
+      <c r="D366" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E366" t="s">
+        <v>2014</v>
+      </c>
+      <c r="F366" t="s">
+        <v>18</v>
+      </c>
+      <c r="G366" t="s">
+        <v>19</v>
+      </c>
+      <c r="H366" t="s">
+        <v>45</v>
+      </c>
+      <c r="I366" t="s">
+        <v>21</v>
+      </c>
+      <c r="J366" t="s">
+        <v>46</v>
+      </c>
+      <c r="K366" t="s">
+        <v>23</v>
+      </c>
+      <c r="L366" t="s">
+        <v>2015</v>
+      </c>
+      <c r="M366" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B367" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C367" t="s">
+        <v>15</v>
+      </c>
+      <c r="D367" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E367" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F367" t="s">
+        <v>18</v>
+      </c>
+      <c r="G367" t="s">
+        <v>19</v>
+      </c>
+      <c r="H367" t="s">
+        <v>75</v>
+      </c>
+      <c r="I367" t="s">
+        <v>81</v>
+      </c>
+      <c r="J367" t="s">
+        <v>75</v>
+      </c>
+      <c r="K367" t="s">
+        <v>23</v>
+      </c>
+      <c r="L367" t="s">
+        <v>2020</v>
+      </c>
+      <c r="M367" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B368" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C368" t="s">
+        <v>15</v>
+      </c>
+      <c r="D368" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E368" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F368" t="s">
+        <v>18</v>
+      </c>
+      <c r="G368" t="s">
+        <v>19</v>
+      </c>
+      <c r="H368" t="s">
+        <v>75</v>
+      </c>
+      <c r="I368" t="s">
+        <v>81</v>
+      </c>
+      <c r="J368" t="s">
+        <v>75</v>
+      </c>
+      <c r="K368" t="s">
+        <v>23</v>
+      </c>
+      <c r="L368" t="s">
+        <v>2025</v>
+      </c>
+      <c r="M368" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B369" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C369" t="s">
+        <v>15</v>
+      </c>
+      <c r="D369" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E369" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F369" t="s">
+        <v>18</v>
+      </c>
+      <c r="G369" t="s">
+        <v>19</v>
+      </c>
+      <c r="H369" t="s">
+        <v>75</v>
+      </c>
+      <c r="I369" t="s">
+        <v>81</v>
+      </c>
+      <c r="J369" t="s">
+        <v>46</v>
+      </c>
+      <c r="K369" t="s">
+        <v>23</v>
+      </c>
+      <c r="L369" t="s">
+        <v>2030</v>
+      </c>
+      <c r="M369" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B370" t="s">
+        <v>2033</v>
+      </c>
+      <c r="C370" t="s">
+        <v>15</v>
+      </c>
+      <c r="D370" t="s">
+        <v>2034</v>
+      </c>
+      <c r="E370" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F370" t="s">
+        <v>18</v>
+      </c>
+      <c r="G370" t="s">
+        <v>19</v>
+      </c>
+      <c r="H370" t="s">
+        <v>211</v>
+      </c>
+      <c r="I370" t="s">
+        <v>21</v>
+      </c>
+      <c r="J370" t="s">
+        <v>46</v>
+      </c>
+      <c r="K370" t="s">
+        <v>23</v>
+      </c>
+      <c r="L370" t="s">
+        <v>2035</v>
+      </c>
+      <c r="M370" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B371" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C371" t="s">
+        <v>15</v>
+      </c>
+      <c r="D371" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E371" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F371" t="s">
+        <v>18</v>
+      </c>
+      <c r="G371" t="s">
+        <v>19</v>
+      </c>
+      <c r="H371" t="s">
+        <v>45</v>
+      </c>
+      <c r="I371" t="s">
+        <v>21</v>
+      </c>
+      <c r="J371" t="s">
+        <v>75</v>
+      </c>
+      <c r="K371" t="s">
+        <v>23</v>
+      </c>
+      <c r="L371" t="s">
+        <v>2040</v>
+      </c>
+      <c r="M371" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B372" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C372" t="s">
+        <v>15</v>
+      </c>
+      <c r="D372" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E372" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F372" t="s">
+        <v>18</v>
+      </c>
+      <c r="G372" t="s">
+        <v>19</v>
+      </c>
+      <c r="H372" t="s">
+        <v>75</v>
+      </c>
+      <c r="I372" t="s">
+        <v>81</v>
+      </c>
+      <c r="J372" t="s">
+        <v>75</v>
+      </c>
+      <c r="K372" t="s">
+        <v>23</v>
+      </c>
+      <c r="L372" t="s">
+        <v>2045</v>
+      </c>
+      <c r="M372" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B373" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C373" t="s">
+        <v>15</v>
+      </c>
+      <c r="D373" t="s">
+        <v>2049</v>
+      </c>
+      <c r="E373" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F373" t="s">
+        <v>18</v>
+      </c>
+      <c r="G373" t="s">
+        <v>19</v>
+      </c>
+      <c r="H373" t="s">
+        <v>75</v>
+      </c>
+      <c r="I373" t="s">
+        <v>81</v>
+      </c>
+      <c r="J373" t="s">
+        <v>75</v>
+      </c>
+      <c r="K373" t="s">
+        <v>23</v>
+      </c>
+      <c r="L373" t="s">
+        <v>2050</v>
+      </c>
+      <c r="M373" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B374" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C374" t="s">
+        <v>28</v>
+      </c>
+      <c r="D374" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E374" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F374" t="s">
+        <v>18</v>
+      </c>
+      <c r="G374" t="s">
+        <v>19</v>
+      </c>
+      <c r="H374" t="s">
+        <v>37</v>
+      </c>
+      <c r="I374" t="s">
+        <v>21</v>
+      </c>
+      <c r="J374" t="s">
+        <v>46</v>
+      </c>
+      <c r="K374" t="s">
+        <v>23</v>
+      </c>
+      <c r="L374" t="s">
+        <v>2055</v>
+      </c>
+      <c r="M374" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B375" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C375" t="s">
+        <v>58</v>
+      </c>
+      <c r="D375" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E375" t="s">
+        <v>2014</v>
+      </c>
+      <c r="F375" t="s">
+        <v>18</v>
+      </c>
+      <c r="G375" t="s">
+        <v>19</v>
+      </c>
+      <c r="H375" t="s">
+        <v>20</v>
+      </c>
+      <c r="I375" t="s">
+        <v>2060</v>
+      </c>
+      <c r="J375" t="s">
+        <v>2061</v>
+      </c>
+      <c r="K375" t="s">
+        <v>23</v>
+      </c>
+      <c r="L375" t="s">
+        <v>2062</v>
+      </c>
+      <c r="M375" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B376" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C376" t="s">
+        <v>28</v>
+      </c>
+      <c r="D376" t="s">
+        <v>2066</v>
+      </c>
+      <c r="E376" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F376" t="s">
+        <v>18</v>
+      </c>
+      <c r="G376" t="s">
+        <v>19</v>
+      </c>
+      <c r="H376" t="s">
+        <v>75</v>
+      </c>
+      <c r="I376" t="s">
+        <v>81</v>
+      </c>
+      <c r="J376" t="s">
+        <v>75</v>
+      </c>
+      <c r="K376" t="s">
+        <v>23</v>
+      </c>
+      <c r="L376" t="s">
+        <v>2067</v>
+      </c>
+      <c r="M376" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B377" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C377" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D377" t="s">
+        <v>2072</v>
+      </c>
+      <c r="E377" t="s">
+        <v>2008</v>
+      </c>
+      <c r="F377" t="s">
+        <v>18</v>
+      </c>
+      <c r="G377" t="s">
+        <v>19</v>
+      </c>
+      <c r="H377" t="s">
+        <v>45</v>
+      </c>
+      <c r="I377" t="s">
+        <v>21</v>
+      </c>
+      <c r="J377" t="s">
+        <v>75</v>
+      </c>
+      <c r="K377" t="s">
+        <v>23</v>
+      </c>
+      <c r="L377" t="s">
+        <v>2073</v>
+      </c>
+      <c r="M377" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B378" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C378" t="s">
+        <v>15</v>
+      </c>
+      <c r="D378" t="s">
+        <v>2077</v>
+      </c>
+      <c r="E378" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F378" t="s">
+        <v>18</v>
+      </c>
+      <c r="G378" t="s">
+        <v>19</v>
+      </c>
+      <c r="H378" t="s">
+        <v>45</v>
+      </c>
+      <c r="I378" t="s">
+        <v>21</v>
+      </c>
+      <c r="J378" t="s">
+        <v>46</v>
+      </c>
+      <c r="K378" t="s">
+        <v>23</v>
+      </c>
+      <c r="L378" t="s">
+        <v>2079</v>
+      </c>
+      <c r="M378" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B379" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C379" t="s">
+        <v>15</v>
+      </c>
+      <c r="D379" t="s">
+        <v>2083</v>
+      </c>
+      <c r="E379" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F379" t="s">
+        <v>18</v>
+      </c>
+      <c r="G379" t="s">
+        <v>19</v>
+      </c>
+      <c r="H379" t="s">
+        <v>45</v>
+      </c>
+      <c r="I379" t="s">
+        <v>21</v>
+      </c>
+      <c r="J379" t="s">
+        <v>75</v>
+      </c>
+      <c r="K379" t="s">
+        <v>23</v>
+      </c>
+      <c r="L379" t="s">
+        <v>2084</v>
+      </c>
+      <c r="M379" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B380" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C380" t="s">
+        <v>28</v>
+      </c>
+      <c r="D380" t="s">
+        <v>2088</v>
+      </c>
+      <c r="E380" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F380" t="s">
+        <v>18</v>
+      </c>
+      <c r="G380" t="s">
+        <v>19</v>
+      </c>
+      <c r="H380" t="s">
+        <v>75</v>
+      </c>
+      <c r="I380" t="s">
+        <v>81</v>
+      </c>
+      <c r="J380" t="s">
+        <v>159</v>
+      </c>
+      <c r="K380" t="s">
+        <v>23</v>
+      </c>
+      <c r="L380" t="s">
+        <v>2089</v>
+      </c>
+      <c r="M380" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B381" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C381" t="s">
+        <v>15</v>
+      </c>
+      <c r="D381" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E381" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F381" t="s">
+        <v>18</v>
+      </c>
+      <c r="G381" t="s">
+        <v>19</v>
+      </c>
+      <c r="H381" t="s">
+        <v>627</v>
+      </c>
+      <c r="I381" t="s">
+        <v>21</v>
+      </c>
+      <c r="J381" t="s">
+        <v>121</v>
+      </c>
+      <c r="K381" t="s">
+        <v>23</v>
+      </c>
+      <c r="L381" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M381" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B382" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C382" t="s">
+        <v>28</v>
+      </c>
+      <c r="D382" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E382" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F382" t="s">
+        <v>18</v>
+      </c>
+      <c r="G382" t="s">
+        <v>19</v>
+      </c>
+      <c r="H382" t="s">
+        <v>75</v>
+      </c>
+      <c r="I382" t="s">
+        <v>81</v>
+      </c>
+      <c r="J382" t="s">
+        <v>46</v>
+      </c>
+      <c r="K382" t="s">
+        <v>23</v>
+      </c>
+      <c r="L382" t="s">
+        <v>2099</v>
+      </c>
+      <c r="M382" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B383" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C383" t="s">
+        <v>15</v>
+      </c>
+      <c r="D383" t="s">
+        <v>2103</v>
+      </c>
+      <c r="E383" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F383" t="s">
+        <v>18</v>
+      </c>
+      <c r="G383" t="s">
+        <v>19</v>
+      </c>
+      <c r="H383" t="s">
+        <v>67</v>
+      </c>
+      <c r="I383" t="s">
+        <v>21</v>
+      </c>
+      <c r="J383" t="s">
+        <v>159</v>
+      </c>
+      <c r="K383" t="s">
+        <v>23</v>
+      </c>
+      <c r="L383" t="s">
+        <v>2104</v>
+      </c>
+      <c r="M383" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B384" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C384" t="s">
+        <v>73</v>
+      </c>
+      <c r="D384" t="s">
+        <v>2108</v>
+      </c>
+      <c r="E384" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F384" t="s">
+        <v>18</v>
+      </c>
+      <c r="G384" t="s">
+        <v>19</v>
+      </c>
+      <c r="H384" t="s">
+        <v>45</v>
+      </c>
+      <c r="I384" t="s">
+        <v>21</v>
+      </c>
+      <c r="J384" t="s">
+        <v>75</v>
+      </c>
+      <c r="K384" t="s">
+        <v>23</v>
+      </c>
+      <c r="L384" t="s">
+        <v>2109</v>
+      </c>
+      <c r="M384" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B385" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C385" t="s">
+        <v>15</v>
+      </c>
+      <c r="D385" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E385" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F385" t="s">
+        <v>18</v>
+      </c>
+      <c r="G385" t="s">
+        <v>19</v>
+      </c>
+      <c r="H385" t="s">
+        <v>45</v>
+      </c>
+      <c r="I385" t="s">
+        <v>21</v>
+      </c>
+      <c r="J385" t="s">
+        <v>75</v>
+      </c>
+      <c r="K385" t="s">
+        <v>23</v>
+      </c>
+      <c r="L385" t="s">
+        <v>2114</v>
+      </c>
+      <c r="M385" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B386" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C386" t="s">
+        <v>58</v>
+      </c>
+      <c r="D386" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E386" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F386" t="s">
+        <v>18</v>
+      </c>
+      <c r="G386" t="s">
+        <v>19</v>
+      </c>
+      <c r="H386" t="s">
+        <v>92</v>
+      </c>
+      <c r="I386" t="s">
+        <v>2119</v>
+      </c>
+      <c r="J386" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K386" t="s">
+        <v>23</v>
+      </c>
+      <c r="L386" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M386" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B387" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C387" t="s">
+        <v>15</v>
+      </c>
+      <c r="D387" t="s">
+        <v>2125</v>
+      </c>
+      <c r="E387" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F387" t="s">
+        <v>18</v>
+      </c>
+      <c r="G387" t="s">
+        <v>19</v>
+      </c>
+      <c r="H387" t="s">
+        <v>45</v>
+      </c>
+      <c r="I387" t="s">
+        <v>21</v>
+      </c>
+      <c r="J387" t="s">
+        <v>75</v>
+      </c>
+      <c r="K387" t="s">
+        <v>23</v>
+      </c>
+      <c r="L387" t="s">
+        <v>2126</v>
+      </c>
+      <c r="M387" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B388" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C388" t="s">
+        <v>15</v>
+      </c>
+      <c r="D388" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E388" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F388" t="s">
+        <v>18</v>
+      </c>
+      <c r="G388" t="s">
+        <v>19</v>
+      </c>
+      <c r="H388" t="s">
+        <v>120</v>
+      </c>
+      <c r="I388" t="s">
+        <v>21</v>
+      </c>
+      <c r="J388" t="s">
+        <v>46</v>
+      </c>
+      <c r="K388" t="s">
+        <v>23</v>
+      </c>
+      <c r="L388" t="s">
+        <v>2131</v>
+      </c>
+      <c r="M388" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B389" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C389" t="s">
+        <v>28</v>
+      </c>
+      <c r="D389" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E389" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F389" t="s">
+        <v>18</v>
+      </c>
+      <c r="G389" t="s">
+        <v>19</v>
+      </c>
+      <c r="H389" t="s">
+        <v>375</v>
+      </c>
+      <c r="I389" t="s">
+        <v>21</v>
+      </c>
+      <c r="J389" t="s">
+        <v>30</v>
+      </c>
+      <c r="K389" t="s">
+        <v>23</v>
+      </c>
+      <c r="L389" t="s">
+        <v>2136</v>
+      </c>
+      <c r="M389" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B390" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C390" t="s">
+        <v>15</v>
+      </c>
+      <c r="D390" t="s">
+        <v>2140</v>
+      </c>
+      <c r="E390" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F390" t="s">
+        <v>18</v>
+      </c>
+      <c r="G390" t="s">
+        <v>19</v>
+      </c>
+      <c r="H390" t="s">
+        <v>387</v>
+      </c>
+      <c r="I390" t="s">
+        <v>21</v>
+      </c>
+      <c r="J390" t="s">
+        <v>46</v>
+      </c>
+      <c r="K390" t="s">
+        <v>23</v>
+      </c>
+      <c r="L390" t="s">
+        <v>2141</v>
+      </c>
+      <c r="M390" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B391" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C391" t="s">
+        <v>910</v>
+      </c>
+      <c r="D391" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E391" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F391" t="s">
+        <v>18</v>
+      </c>
+      <c r="G391" t="s">
+        <v>19</v>
+      </c>
+      <c r="H391" t="s">
+        <v>45</v>
+      </c>
+      <c r="I391" t="s">
+        <v>21</v>
+      </c>
+      <c r="J391" t="s">
+        <v>46</v>
+      </c>
+      <c r="K391" t="s">
+        <v>23</v>
+      </c>
+      <c r="L391" t="s">
+        <v>2146</v>
+      </c>
+      <c r="M391" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B392" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C392" t="s">
+        <v>15</v>
+      </c>
+      <c r="D392" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E392" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F392" t="s">
+        <v>18</v>
+      </c>
+      <c r="G392" t="s">
+        <v>19</v>
+      </c>
+      <c r="H392" t="s">
+        <v>381</v>
+      </c>
+      <c r="I392" t="s">
+        <v>21</v>
+      </c>
+      <c r="J392" t="s">
+        <v>46</v>
+      </c>
+      <c r="K392" t="s">
+        <v>23</v>
+      </c>
+      <c r="L392" t="s">
+        <v>2151</v>
+      </c>
+      <c r="M392" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B393" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C393" t="s">
+        <v>58</v>
+      </c>
+      <c r="D393" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E393" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F393" t="s">
+        <v>18</v>
+      </c>
+      <c r="G393" t="s">
+        <v>19</v>
+      </c>
+      <c r="H393" t="s">
+        <v>75</v>
+      </c>
+      <c r="I393" t="s">
+        <v>2156</v>
+      </c>
+      <c r="J393" t="s">
+        <v>2157</v>
+      </c>
+      <c r="K393" t="s">
+        <v>23</v>
+      </c>
+      <c r="L393" t="s">
+        <v>2158</v>
+      </c>
+      <c r="M393" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B394" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C394" t="s">
+        <v>28</v>
+      </c>
+      <c r="D394" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E394" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F394" t="s">
+        <v>18</v>
+      </c>
+      <c r="G394" t="s">
+        <v>19</v>
+      </c>
+      <c r="H394" t="s">
+        <v>429</v>
+      </c>
+      <c r="I394" t="s">
+        <v>21</v>
+      </c>
+      <c r="J394" t="s">
+        <v>648</v>
+      </c>
+      <c r="K394" t="s">
+        <v>23</v>
+      </c>
+      <c r="L394" t="s">
+        <v>2164</v>
+      </c>
+      <c r="M394" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B395" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C395" t="s">
+        <v>15</v>
+      </c>
+      <c r="D395" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E395" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F395" t="s">
+        <v>18</v>
+      </c>
+      <c r="G395" t="s">
+        <v>19</v>
+      </c>
+      <c r="H395" t="s">
+        <v>381</v>
+      </c>
+      <c r="I395" t="s">
+        <v>21</v>
+      </c>
+      <c r="J395" t="s">
+        <v>159</v>
+      </c>
+      <c r="K395" t="s">
+        <v>23</v>
+      </c>
+      <c r="L395" t="s">
+        <v>2169</v>
+      </c>
+      <c r="M395" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B396" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C396" t="s">
+        <v>15</v>
+      </c>
+      <c r="D396" t="s">
+        <v>2173</v>
+      </c>
+      <c r="E396" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F396" t="s">
+        <v>18</v>
+      </c>
+      <c r="G396" t="s">
+        <v>19</v>
+      </c>
+      <c r="H396" t="s">
+        <v>92</v>
+      </c>
+      <c r="I396" t="s">
+        <v>21</v>
+      </c>
+      <c r="J396" t="s">
+        <v>75</v>
+      </c>
+      <c r="K396" t="s">
+        <v>23</v>
+      </c>
+      <c r="L396" t="s">
+        <v>2174</v>
+      </c>
+      <c r="M396" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B397" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C397" t="s">
+        <v>15</v>
+      </c>
+      <c r="D397" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E397" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F397" t="s">
+        <v>18</v>
+      </c>
+      <c r="G397" t="s">
+        <v>19</v>
+      </c>
+      <c r="H397" t="s">
+        <v>37</v>
+      </c>
+      <c r="I397" t="s">
+        <v>21</v>
+      </c>
+      <c r="J397" t="s">
+        <v>170</v>
+      </c>
+      <c r="K397" t="s">
+        <v>23</v>
+      </c>
+      <c r="L397" t="s">
+        <v>2179</v>
+      </c>
+      <c r="M397" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B398" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C398" t="s">
+        <v>15</v>
+      </c>
+      <c r="D398" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E398" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F398" t="s">
+        <v>18</v>
+      </c>
+      <c r="G398" t="s">
+        <v>19</v>
+      </c>
+      <c r="H398" t="s">
+        <v>45</v>
+      </c>
+      <c r="I398" t="s">
+        <v>21</v>
+      </c>
+      <c r="J398" t="s">
+        <v>75</v>
+      </c>
+      <c r="K398" t="s">
+        <v>23</v>
+      </c>
+      <c r="L398" t="s">
+        <v>2184</v>
+      </c>
+      <c r="M398" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B399" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C399" t="s">
+        <v>15</v>
+      </c>
+      <c r="D399" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E399" t="s">
+        <v>2189</v>
+      </c>
+      <c r="F399" t="s">
+        <v>18</v>
+      </c>
+      <c r="G399" t="s">
+        <v>19</v>
+      </c>
+      <c r="H399" t="s">
+        <v>381</v>
+      </c>
+      <c r="I399" t="s">
+        <v>21</v>
+      </c>
+      <c r="J399" t="s">
+        <v>46</v>
+      </c>
+      <c r="K399" t="s">
+        <v>23</v>
+      </c>
+      <c r="L399" t="s">
+        <v>2190</v>
+      </c>
+      <c r="M399" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B400" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C400" t="s">
+        <v>15</v>
+      </c>
+      <c r="D400" t="s">
+        <v>2194</v>
+      </c>
+      <c r="E400" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F400" t="s">
+        <v>18</v>
+      </c>
+      <c r="G400" t="s">
+        <v>19</v>
+      </c>
+      <c r="H400" t="s">
+        <v>103</v>
+      </c>
+      <c r="I400" t="s">
+        <v>21</v>
+      </c>
+      <c r="J400" t="s">
+        <v>75</v>
+      </c>
+      <c r="K400" t="s">
+        <v>23</v>
+      </c>
+      <c r="L400" t="s">
+        <v>2195</v>
+      </c>
+      <c r="M400" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B401" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C401" t="s">
+        <v>477</v>
+      </c>
+      <c r="D401" t="s">
+        <v>2199</v>
+      </c>
+      <c r="E401" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F401" t="s">
+        <v>18</v>
+      </c>
+      <c r="G401" t="s">
+        <v>19</v>
+      </c>
+      <c r="H401" t="s">
+        <v>45</v>
+      </c>
+      <c r="I401" t="s">
+        <v>21</v>
+      </c>
+      <c r="J401" t="s">
+        <v>46</v>
+      </c>
+      <c r="K401" t="s">
+        <v>23</v>
+      </c>
+      <c r="L401" t="s">
+        <v>2200</v>
+      </c>
+      <c r="M401" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B402" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C402" t="s">
+        <v>15</v>
+      </c>
+      <c r="D402" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E402" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F402" t="s">
+        <v>18</v>
+      </c>
+      <c r="G402" t="s">
+        <v>19</v>
+      </c>
+      <c r="H402" t="s">
+        <v>45</v>
+      </c>
+      <c r="I402" t="s">
+        <v>21</v>
+      </c>
+      <c r="J402" t="s">
+        <v>648</v>
+      </c>
+      <c r="K402" t="s">
+        <v>23</v>
+      </c>
+      <c r="L402" t="s">
+        <v>2205</v>
+      </c>
+      <c r="M402" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B403" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C403" t="s">
+        <v>181</v>
+      </c>
+      <c r="D403" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E403" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F403" t="s">
+        <v>18</v>
+      </c>
+      <c r="G403" t="s">
+        <v>19</v>
+      </c>
+      <c r="H403" t="s">
+        <v>20</v>
+      </c>
+      <c r="I403" t="s">
+        <v>21</v>
+      </c>
+      <c r="J403" t="s">
+        <v>46</v>
+      </c>
+      <c r="K403" t="s">
+        <v>23</v>
+      </c>
+      <c r="L403" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M403" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B404" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C404" t="s">
+        <v>15</v>
+      </c>
+      <c r="D404" t="s">
+        <v>2214</v>
+      </c>
+      <c r="E404" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F404" t="s">
+        <v>18</v>
+      </c>
+      <c r="G404" t="s">
+        <v>19</v>
+      </c>
+      <c r="H404" t="s">
+        <v>45</v>
+      </c>
+      <c r="I404" t="s">
+        <v>21</v>
+      </c>
+      <c r="J404" t="s">
+        <v>46</v>
+      </c>
+      <c r="K404" t="s">
+        <v>23</v>
+      </c>
+      <c r="L404" t="s">
+        <v>2215</v>
+      </c>
+      <c r="M404" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B405" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C405" t="s">
+        <v>73</v>
+      </c>
+      <c r="D405" t="s">
+        <v>2219</v>
+      </c>
+      <c r="E405" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F405" t="s">
+        <v>18</v>
+      </c>
+      <c r="G405" t="s">
+        <v>19</v>
+      </c>
+      <c r="H405" t="s">
+        <v>466</v>
+      </c>
+      <c r="I405" t="s">
+        <v>21</v>
+      </c>
+      <c r="J405" t="s">
+        <v>75</v>
+      </c>
+      <c r="K405" t="s">
+        <v>23</v>
+      </c>
+      <c r="L405" t="s">
+        <v>2220</v>
+      </c>
+      <c r="M405" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="406" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B406" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C406" t="s">
+        <v>28</v>
+      </c>
+      <c r="D406" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E406" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F406" t="s">
+        <v>18</v>
+      </c>
+      <c r="G406" t="s">
+        <v>19</v>
+      </c>
+      <c r="H406" t="s">
+        <v>67</v>
+      </c>
+      <c r="I406" t="s">
+        <v>21</v>
+      </c>
+      <c r="J406" t="s">
+        <v>479</v>
+      </c>
+      <c r="K406" t="s">
+        <v>23</v>
+      </c>
+      <c r="L406" t="s">
+        <v>2225</v>
+      </c>
+      <c r="M406" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B407" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C407" t="s">
+        <v>15</v>
+      </c>
+      <c r="D407" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E407" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F407" t="s">
+        <v>18</v>
+      </c>
+      <c r="G407" t="s">
+        <v>19</v>
+      </c>
+      <c r="H407" t="s">
+        <v>45</v>
+      </c>
+      <c r="I407" t="s">
+        <v>21</v>
+      </c>
+      <c r="J407" t="s">
+        <v>46</v>
+      </c>
+      <c r="K407" t="s">
+        <v>23</v>
+      </c>
+      <c r="L407" t="s">
+        <v>2230</v>
+      </c>
+      <c r="M407" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>2232</v>
+      </c>
+      <c r="B408" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C408" t="s">
+        <v>15</v>
+      </c>
+      <c r="D408" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E408" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F408" t="s">
+        <v>18</v>
+      </c>
+      <c r="G408" t="s">
+        <v>19</v>
+      </c>
+      <c r="H408" t="s">
+        <v>45</v>
+      </c>
+      <c r="I408" t="s">
+        <v>21</v>
+      </c>
+      <c r="J408" t="s">
+        <v>46</v>
+      </c>
+      <c r="K408" t="s">
+        <v>23</v>
+      </c>
+      <c r="L408" t="s">
+        <v>2235</v>
+      </c>
+      <c r="M408" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>2237</v>
+      </c>
+      <c r="B409" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C409" t="s">
+        <v>28</v>
+      </c>
+      <c r="D409" t="s">
+        <v>2239</v>
+      </c>
+      <c r="E409" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F409" t="s">
+        <v>18</v>
+      </c>
+      <c r="G409" t="s">
+        <v>19</v>
+      </c>
+      <c r="H409" t="s">
+        <v>627</v>
+      </c>
+      <c r="I409" t="s">
+        <v>21</v>
+      </c>
+      <c r="J409" t="s">
+        <v>2241</v>
+      </c>
+      <c r="K409" t="s">
+        <v>23</v>
+      </c>
+      <c r="L409" t="s">
+        <v>2242</v>
+      </c>
+      <c r="M409" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B410" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C410" t="s">
+        <v>28</v>
+      </c>
+      <c r="D410" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E410" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F410" t="s">
+        <v>18</v>
+      </c>
+      <c r="G410" t="s">
+        <v>19</v>
+      </c>
+      <c r="H410" t="s">
+        <v>120</v>
+      </c>
+      <c r="I410" t="s">
+        <v>21</v>
+      </c>
+      <c r="J410" t="s">
+        <v>648</v>
+      </c>
+      <c r="K410" t="s">
+        <v>23</v>
+      </c>
+      <c r="L410" t="s">
+        <v>2247</v>
+      </c>
+      <c r="M410" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B411" t="s">
+        <v>2250</v>
+      </c>
+      <c r="C411" t="s">
+        <v>28</v>
+      </c>
+      <c r="D411" t="s">
+        <v>2251</v>
+      </c>
+      <c r="E411" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F411" t="s">
+        <v>18</v>
+      </c>
+      <c r="G411" t="s">
+        <v>19</v>
+      </c>
+      <c r="H411" t="s">
+        <v>45</v>
+      </c>
+      <c r="I411" t="s">
+        <v>21</v>
+      </c>
+      <c r="J411" t="s">
+        <v>46</v>
+      </c>
+      <c r="K411" t="s">
+        <v>23</v>
+      </c>
+      <c r="L411" t="s">
+        <v>2253</v>
+      </c>
+      <c r="M411" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B412" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C412" t="s">
+        <v>15</v>
+      </c>
+      <c r="D412" t="s">
+        <v>2257</v>
+      </c>
+      <c r="E412" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F412" t="s">
+        <v>18</v>
+      </c>
+      <c r="G412" t="s">
+        <v>19</v>
+      </c>
+      <c r="H412" t="s">
+        <v>45</v>
+      </c>
+      <c r="I412" t="s">
+        <v>21</v>
+      </c>
+      <c r="J412" t="s">
+        <v>75</v>
+      </c>
+      <c r="K412" t="s">
+        <v>23</v>
+      </c>
+      <c r="L412" t="s">
+        <v>2258</v>
+      </c>
+      <c r="M412" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B413" t="s">
+        <v>2261</v>
+      </c>
+      <c r="C413" t="s">
+        <v>28</v>
+      </c>
+      <c r="D413" t="s">
+        <v>2262</v>
+      </c>
+      <c r="E413" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F413" t="s">
+        <v>18</v>
+      </c>
+      <c r="G413" t="s">
+        <v>19</v>
+      </c>
+      <c r="H413" t="s">
+        <v>75</v>
+      </c>
+      <c r="I413" t="s">
+        <v>81</v>
+      </c>
+      <c r="J413" t="s">
+        <v>75</v>
+      </c>
+      <c r="K413" t="s">
+        <v>23</v>
+      </c>
+      <c r="L413" t="s">
+        <v>2263</v>
+      </c>
+      <c r="M413" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B414" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C414" t="s">
+        <v>15</v>
+      </c>
+      <c r="D414" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E414" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F414" t="s">
+        <v>18</v>
+      </c>
+      <c r="G414" t="s">
+        <v>19</v>
+      </c>
+      <c r="H414" t="s">
+        <v>37</v>
+      </c>
+      <c r="I414" t="s">
+        <v>21</v>
+      </c>
+      <c r="J414" t="s">
+        <v>435</v>
+      </c>
+      <c r="K414" t="s">
+        <v>23</v>
+      </c>
+      <c r="L414" t="s">
+        <v>2268</v>
+      </c>
+      <c r="M414" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B415" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C415" t="s">
+        <v>28</v>
+      </c>
+      <c r="D415" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E415" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F415" t="s">
+        <v>18</v>
+      </c>
+      <c r="G415" t="s">
+        <v>19</v>
+      </c>
+      <c r="H415" t="s">
+        <v>45</v>
+      </c>
+      <c r="I415" t="s">
+        <v>21</v>
+      </c>
+      <c r="J415" t="s">
+        <v>75</v>
+      </c>
+      <c r="K415" t="s">
+        <v>23</v>
+      </c>
+      <c r="L415" t="s">
+        <v>2273</v>
+      </c>
+      <c r="M415" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B416" t="s">
+        <v>2276</v>
+      </c>
+      <c r="C416" t="s">
+        <v>15</v>
+      </c>
+      <c r="D416" t="s">
+        <v>2277</v>
+      </c>
+      <c r="E416" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F416" t="s">
+        <v>18</v>
+      </c>
+      <c r="G416" t="s">
+        <v>19</v>
+      </c>
+      <c r="H416" t="s">
+        <v>45</v>
+      </c>
+      <c r="I416" t="s">
+        <v>21</v>
+      </c>
+      <c r="J416" t="s">
+        <v>75</v>
+      </c>
+      <c r="K416" t="s">
+        <v>23</v>
+      </c>
+      <c r="L416" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M416" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B417" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C417" t="s">
+        <v>175</v>
+      </c>
+      <c r="D417" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E417" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F417" t="s">
+        <v>18</v>
+      </c>
+      <c r="G417" t="s">
+        <v>19</v>
+      </c>
+      <c r="H417" t="s">
+        <v>346</v>
+      </c>
+      <c r="I417" t="s">
+        <v>21</v>
+      </c>
+      <c r="J417" t="s">
+        <v>46</v>
+      </c>
+      <c r="K417" t="s">
+        <v>23</v>
+      </c>
+      <c r="L417" t="s">
+        <v>2283</v>
+      </c>
+      <c r="M417" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B418" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C418" t="s">
+        <v>15</v>
+      </c>
+      <c r="D418" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E418" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F418" t="s">
+        <v>18</v>
+      </c>
+      <c r="G418" t="s">
+        <v>19</v>
+      </c>
+      <c r="H418" t="s">
+        <v>381</v>
+      </c>
+      <c r="I418" t="s">
+        <v>21</v>
+      </c>
+      <c r="J418" t="s">
+        <v>75</v>
+      </c>
+      <c r="K418" t="s">
+        <v>23</v>
+      </c>
+      <c r="L418" t="s">
+        <v>2288</v>
+      </c>
+      <c r="M418" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B419" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C419" t="s">
+        <v>15</v>
+      </c>
+      <c r="D419" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E419" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F419" t="s">
+        <v>18</v>
+      </c>
+      <c r="G419" t="s">
+        <v>19</v>
+      </c>
+      <c r="H419" t="s">
+        <v>223</v>
+      </c>
+      <c r="I419" t="s">
+        <v>21</v>
+      </c>
+      <c r="J419" t="s">
+        <v>75</v>
+      </c>
+      <c r="K419" t="s">
+        <v>23</v>
+      </c>
+      <c r="L419" t="s">
+        <v>2293</v>
+      </c>
+      <c r="M419" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B420" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C420" t="s">
+        <v>15</v>
+      </c>
+      <c r="D420" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E420" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F420" t="s">
+        <v>18</v>
+      </c>
+      <c r="G420" t="s">
+        <v>19</v>
+      </c>
+      <c r="H420" t="s">
+        <v>466</v>
+      </c>
+      <c r="I420" t="s">
+        <v>21</v>
+      </c>
+      <c r="J420" t="s">
+        <v>1308</v>
+      </c>
+      <c r="K420" t="s">
+        <v>23</v>
+      </c>
+      <c r="L420" t="s">
+        <v>2298</v>
+      </c>
+      <c r="M420" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B421" t="s">
+        <v>2301</v>
+      </c>
+      <c r="C421" t="s">
+        <v>15</v>
+      </c>
+      <c r="D421" t="s">
+        <v>2302</v>
+      </c>
+      <c r="E421" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F421" t="s">
+        <v>18</v>
+      </c>
+      <c r="G421" t="s">
+        <v>19</v>
+      </c>
+      <c r="H421" t="s">
+        <v>37</v>
+      </c>
+      <c r="I421" t="s">
+        <v>21</v>
+      </c>
+      <c r="J421" t="s">
+        <v>46</v>
+      </c>
+      <c r="K421" t="s">
+        <v>23</v>
+      </c>
+      <c r="L421" t="s">
+        <v>2303</v>
+      </c>
+      <c r="M421" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B422" t="s">
+        <v>2306</v>
+      </c>
+      <c r="C422" t="s">
+        <v>926</v>
+      </c>
+      <c r="D422" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E422" t="s">
+        <v>2308</v>
+      </c>
+      <c r="F422" t="s">
+        <v>18</v>
+      </c>
+      <c r="G422" t="s">
+        <v>19</v>
+      </c>
+      <c r="H422" t="s">
+        <v>381</v>
+      </c>
+      <c r="I422" t="s">
+        <v>21</v>
+      </c>
+      <c r="J422" t="s">
+        <v>2309</v>
+      </c>
+      <c r="K422" t="s">
+        <v>23</v>
+      </c>
+      <c r="L422" t="s">
+        <v>2310</v>
+      </c>
+      <c r="M422" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="423" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B423" t="s">
+        <v>2313</v>
+      </c>
+      <c r="C423" t="s">
+        <v>58</v>
+      </c>
+      <c r="D423" t="s">
+        <v>2314</v>
+      </c>
+      <c r="E423" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F423" t="s">
+        <v>18</v>
+      </c>
+      <c r="G423" t="s">
+        <v>19</v>
+      </c>
+      <c r="H423" t="s">
+        <v>45</v>
+      </c>
+      <c r="I423" t="s">
+        <v>569</v>
+      </c>
+      <c r="J423" t="s">
+        <v>75</v>
+      </c>
+      <c r="K423" t="s">
+        <v>23</v>
+      </c>
+      <c r="L423" t="s">
+        <v>2315</v>
+      </c>
+      <c r="M423" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="424" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B424" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C424" t="s">
+        <v>58</v>
+      </c>
+      <c r="D424" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E424" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F424" t="s">
+        <v>18</v>
+      </c>
+      <c r="G424" t="s">
+        <v>19</v>
+      </c>
+      <c r="H424" t="s">
+        <v>45</v>
+      </c>
+      <c r="I424" t="s">
+        <v>291</v>
+      </c>
+      <c r="J424" t="s">
+        <v>2320</v>
+      </c>
+      <c r="K424" t="s">
+        <v>23</v>
+      </c>
+      <c r="L424" t="s">
+        <v>2321</v>
+      </c>
+      <c r="M424" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="425" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>2323</v>
+      </c>
+      <c r="B425" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C425" t="s">
+        <v>15</v>
+      </c>
+      <c r="D425" t="s">
+        <v>2325</v>
+      </c>
+      <c r="E425" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F425" t="s">
+        <v>18</v>
+      </c>
+      <c r="G425" t="s">
+        <v>19</v>
+      </c>
+      <c r="H425" t="s">
+        <v>20</v>
+      </c>
+      <c r="I425" t="s">
+        <v>21</v>
+      </c>
+      <c r="J425" t="s">
+        <v>75</v>
+      </c>
+      <c r="K425" t="s">
+        <v>23</v>
+      </c>
+      <c r="L425" t="s">
+        <v>2326</v>
+      </c>
+      <c r="M425" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="426" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B426" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C426" t="s">
+        <v>15</v>
+      </c>
+      <c r="D426" t="s">
+        <v>2330</v>
+      </c>
+      <c r="E426" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F426" t="s">
+        <v>18</v>
+      </c>
+      <c r="G426" t="s">
+        <v>19</v>
+      </c>
+      <c r="H426" t="s">
+        <v>547</v>
+      </c>
+      <c r="I426" t="s">
+        <v>21</v>
+      </c>
+      <c r="J426" t="s">
+        <v>46</v>
+      </c>
+      <c r="K426" t="s">
+        <v>23</v>
+      </c>
+      <c r="L426" t="s">
+        <v>2331</v>
+      </c>
+      <c r="M426" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="427" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B427" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C427" t="s">
+        <v>28</v>
+      </c>
+      <c r="D427" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E427" t="s">
+        <v>328</v>
+      </c>
+      <c r="F427" t="s">
+        <v>18</v>
+      </c>
+      <c r="G427" t="s">
+        <v>19</v>
+      </c>
+      <c r="H427" t="s">
+        <v>45</v>
+      </c>
+      <c r="I427" t="s">
+        <v>21</v>
+      </c>
+      <c r="J427" t="s">
+        <v>53</v>
+      </c>
+      <c r="K427" t="s">
+        <v>23</v>
+      </c>
+      <c r="L427" t="s">
+        <v>2336</v>
+      </c>
+      <c r="M427" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="428" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B428" t="s">
+        <v>2339</v>
+      </c>
+      <c r="C428" t="s">
+        <v>15</v>
+      </c>
+      <c r="D428" t="s">
+        <v>2340</v>
+      </c>
+      <c r="E428" t="s">
+        <v>328</v>
+      </c>
+      <c r="F428" t="s">
+        <v>18</v>
+      </c>
+      <c r="G428" t="s">
+        <v>19</v>
+      </c>
+      <c r="H428" t="s">
+        <v>381</v>
+      </c>
+      <c r="I428" t="s">
+        <v>21</v>
+      </c>
+      <c r="J428" t="s">
+        <v>46</v>
+      </c>
+      <c r="K428" t="s">
+        <v>23</v>
+      </c>
+      <c r="L428" t="s">
+        <v>2341</v>
+      </c>
+      <c r="M428" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="429" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>2343</v>
+      </c>
+      <c r="B429" t="s">
+        <v>2344</v>
+      </c>
+      <c r="C429" t="s">
+        <v>15</v>
+      </c>
+      <c r="D429" t="s">
+        <v>2345</v>
+      </c>
+      <c r="E429" t="s">
+        <v>328</v>
+      </c>
+      <c r="F429" t="s">
+        <v>18</v>
+      </c>
+      <c r="G429" t="s">
+        <v>19</v>
+      </c>
+      <c r="H429" t="s">
+        <v>45</v>
+      </c>
+      <c r="I429" t="s">
+        <v>21</v>
+      </c>
+      <c r="J429" t="s">
+        <v>121</v>
+      </c>
+      <c r="K429" t="s">
+        <v>23</v>
+      </c>
+      <c r="L429" t="s">
+        <v>2346</v>
+      </c>
+      <c r="M429" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="430" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>2348</v>
+      </c>
+      <c r="B430" t="s">
+        <v>2349</v>
+      </c>
+      <c r="C430" t="s">
+        <v>15</v>
+      </c>
+      <c r="D430" t="s">
+        <v>2350</v>
+      </c>
+      <c r="E430" t="s">
+        <v>328</v>
+      </c>
+      <c r="F430" t="s">
+        <v>18</v>
+      </c>
+      <c r="G430" t="s">
+        <v>19</v>
+      </c>
+      <c r="H430" t="s">
+        <v>37</v>
+      </c>
+      <c r="I430" t="s">
+        <v>21</v>
+      </c>
+      <c r="J430" t="s">
+        <v>46</v>
+      </c>
+      <c r="K430" t="s">
+        <v>23</v>
+      </c>
+      <c r="L430" t="s">
+        <v>2351</v>
+      </c>
+      <c r="M430" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="431" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B431" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C431" t="s">
+        <v>15</v>
+      </c>
+      <c r="D431" t="s">
+        <v>2355</v>
+      </c>
+      <c r="E431" t="s">
+        <v>328</v>
+      </c>
+      <c r="F431" t="s">
+        <v>18</v>
+      </c>
+      <c r="G431" t="s">
+        <v>19</v>
+      </c>
+      <c r="H431" t="s">
+        <v>45</v>
+      </c>
+      <c r="I431" t="s">
+        <v>21</v>
+      </c>
+      <c r="J431" t="s">
+        <v>46</v>
+      </c>
+      <c r="K431" t="s">
+        <v>23</v>
+      </c>
+      <c r="L431" t="s">
+        <v>2356</v>
+      </c>
+      <c r="M431" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="432" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B432" t="s">
+        <v>2359</v>
+      </c>
+      <c r="C432" t="s">
+        <v>15</v>
+      </c>
+      <c r="D432" t="s">
+        <v>2360</v>
+      </c>
+      <c r="E432" t="s">
+        <v>328</v>
+      </c>
+      <c r="F432" t="s">
+        <v>18</v>
+      </c>
+      <c r="G432" t="s">
+        <v>19</v>
+      </c>
+      <c r="H432" t="s">
+        <v>45</v>
+      </c>
+      <c r="I432" t="s">
+        <v>21</v>
+      </c>
+      <c r="J432" t="s">
+        <v>75</v>
+      </c>
+      <c r="K432" t="s">
+        <v>23</v>
+      </c>
+      <c r="L432" t="s">
+        <v>2361</v>
+      </c>
+      <c r="M432" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="433" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B433" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C433" t="s">
+        <v>15</v>
+      </c>
+      <c r="D433" t="s">
+        <v>2365</v>
+      </c>
+      <c r="E433" t="s">
+        <v>328</v>
+      </c>
+      <c r="F433" t="s">
+        <v>18</v>
+      </c>
+      <c r="G433" t="s">
+        <v>19</v>
+      </c>
+      <c r="H433" t="s">
+        <v>45</v>
+      </c>
+      <c r="I433" t="s">
+        <v>21</v>
+      </c>
+      <c r="J433" t="s">
+        <v>2241</v>
+      </c>
+      <c r="K433" t="s">
+        <v>23</v>
+      </c>
+      <c r="L433" t="s">
+        <v>2366</v>
+      </c>
+      <c r="M433" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="434" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B434" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C434" t="s">
+        <v>15</v>
+      </c>
+      <c r="D434" t="s">
+        <v>2370</v>
+      </c>
+      <c r="E434" t="s">
+        <v>328</v>
+      </c>
+      <c r="F434" t="s">
+        <v>18</v>
+      </c>
+      <c r="G434" t="s">
+        <v>19</v>
+      </c>
+      <c r="H434" t="s">
+        <v>429</v>
+      </c>
+      <c r="I434" t="s">
+        <v>21</v>
+      </c>
+      <c r="J434" t="s">
+        <v>170</v>
+      </c>
+      <c r="K434" t="s">
+        <v>23</v>
+      </c>
+      <c r="L434" t="s">
+        <v>2371</v>
+      </c>
+      <c r="M434" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="435" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B435" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C435" t="s">
+        <v>15</v>
+      </c>
+      <c r="D435" t="s">
+        <v>2375</v>
+      </c>
+      <c r="E435" t="s">
+        <v>328</v>
+      </c>
+      <c r="F435" t="s">
+        <v>18</v>
+      </c>
+      <c r="G435" t="s">
+        <v>19</v>
+      </c>
+      <c r="H435" t="s">
+        <v>120</v>
+      </c>
+      <c r="I435" t="s">
+        <v>21</v>
+      </c>
+      <c r="J435" t="s">
+        <v>2376</v>
+      </c>
+      <c r="K435" t="s">
+        <v>23</v>
+      </c>
+      <c r="L435" t="s">
+        <v>2377</v>
+      </c>
+      <c r="M435" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="436" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B436" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C436" t="s">
+        <v>15</v>
+      </c>
+      <c r="D436" t="s">
+        <v>2381</v>
+      </c>
+      <c r="E436" t="s">
+        <v>328</v>
+      </c>
+      <c r="F436" t="s">
+        <v>18</v>
+      </c>
+      <c r="G436" t="s">
+        <v>19</v>
+      </c>
+      <c r="H436" t="s">
+        <v>75</v>
+      </c>
+      <c r="I436" t="s">
+        <v>81</v>
+      </c>
+      <c r="J436" t="s">
+        <v>46</v>
+      </c>
+      <c r="K436" t="s">
+        <v>23</v>
+      </c>
+      <c r="L436" t="s">
+        <v>2382</v>
+      </c>
+      <c r="M436" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="437" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B437" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C437" t="s">
+        <v>15</v>
+      </c>
+      <c r="D437" t="s">
+        <v>2386</v>
+      </c>
+      <c r="E437" t="s">
+        <v>328</v>
+      </c>
+      <c r="F437" t="s">
+        <v>18</v>
+      </c>
+      <c r="G437" t="s">
+        <v>19</v>
+      </c>
+      <c r="H437" t="s">
+        <v>45</v>
+      </c>
+      <c r="I437" t="s">
+        <v>21</v>
+      </c>
+      <c r="J437" t="s">
+        <v>46</v>
+      </c>
+      <c r="K437" t="s">
+        <v>23</v>
+      </c>
+      <c r="L437" t="s">
+        <v>2387</v>
+      </c>
+      <c r="M437" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="438" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B438" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C438" t="s">
+        <v>15</v>
+      </c>
+      <c r="D438" t="s">
+        <v>2391</v>
+      </c>
+      <c r="E438" t="s">
+        <v>328</v>
+      </c>
+      <c r="F438" t="s">
+        <v>18</v>
+      </c>
+      <c r="G438" t="s">
+        <v>19</v>
+      </c>
+      <c r="H438" t="s">
+        <v>45</v>
+      </c>
+      <c r="I438" t="s">
+        <v>21</v>
+      </c>
+      <c r="J438" t="s">
+        <v>46</v>
+      </c>
+      <c r="K438" t="s">
+        <v>23</v>
+      </c>
+      <c r="L438" t="s">
+        <v>2392</v>
+      </c>
+      <c r="M438" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="439" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B439" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C439" t="s">
+        <v>15</v>
+      </c>
+      <c r="D439" t="s">
+        <v>2396</v>
+      </c>
+      <c r="E439" t="s">
+        <v>328</v>
+      </c>
+      <c r="F439" t="s">
+        <v>18</v>
+      </c>
+      <c r="G439" t="s">
+        <v>19</v>
+      </c>
+      <c r="H439" t="s">
+        <v>67</v>
+      </c>
+      <c r="I439" t="s">
+        <v>21</v>
+      </c>
+      <c r="J439" t="s">
+        <v>170</v>
+      </c>
+      <c r="K439" t="s">
+        <v>23</v>
+      </c>
+      <c r="L439" t="s">
+        <v>2397</v>
+      </c>
+      <c r="M439" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="440" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B440" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C440" t="s">
+        <v>181</v>
+      </c>
+      <c r="D440" t="s">
+        <v>2401</v>
+      </c>
+      <c r="E440" t="s">
+        <v>328</v>
+      </c>
+      <c r="F440" t="s">
+        <v>18</v>
+      </c>
+      <c r="G440" t="s">
+        <v>19</v>
+      </c>
+      <c r="H440" t="s">
+        <v>223</v>
+      </c>
+      <c r="I440" t="s">
+        <v>21</v>
+      </c>
+      <c r="J440" t="s">
+        <v>75</v>
+      </c>
+      <c r="K440" t="s">
+        <v>23</v>
+      </c>
+      <c r="L440" t="s">
+        <v>2402</v>
+      </c>
+      <c r="M440" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="441" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B441" t="s">
+        <v>2405</v>
+      </c>
+      <c r="C441" t="s">
+        <v>181</v>
+      </c>
+      <c r="D441" t="s">
+        <v>2406</v>
+      </c>
+      <c r="E441" t="s">
+        <v>328</v>
+      </c>
+      <c r="F441" t="s">
+        <v>18</v>
+      </c>
+      <c r="G441" t="s">
+        <v>19</v>
+      </c>
+      <c r="H441" t="s">
+        <v>45</v>
+      </c>
+      <c r="I441" t="s">
+        <v>21</v>
+      </c>
+      <c r="J441" t="s">
+        <v>75</v>
+      </c>
+      <c r="K441" t="s">
+        <v>23</v>
+      </c>
+      <c r="L441" t="s">
+        <v>2407</v>
+      </c>
+      <c r="M441" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="442" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B442" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C442" t="s">
+        <v>15</v>
+      </c>
+      <c r="D442" t="s">
+        <v>2411</v>
+      </c>
+      <c r="E442" t="s">
+        <v>328</v>
+      </c>
+      <c r="F442" t="s">
+        <v>18</v>
+      </c>
+      <c r="G442" t="s">
+        <v>19</v>
+      </c>
+      <c r="H442" t="s">
+        <v>37</v>
+      </c>
+      <c r="I442" t="s">
+        <v>21</v>
+      </c>
+      <c r="J442" t="s">
+        <v>159</v>
+      </c>
+      <c r="K442" t="s">
+        <v>23</v>
+      </c>
+      <c r="L442" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M442" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="443" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>2414</v>
+      </c>
+      <c r="B443" t="s">
+        <v>2415</v>
+      </c>
+      <c r="C443" t="s">
+        <v>15</v>
+      </c>
+      <c r="D443" t="s">
+        <v>2416</v>
+      </c>
+      <c r="E443" t="s">
+        <v>328</v>
+      </c>
+      <c r="F443" t="s">
+        <v>18</v>
+      </c>
+      <c r="G443" t="s">
+        <v>19</v>
+      </c>
+      <c r="H443" t="s">
+        <v>627</v>
+      </c>
+      <c r="I443" t="s">
+        <v>21</v>
+      </c>
+      <c r="J443" t="s">
+        <v>170</v>
+      </c>
+      <c r="K443" t="s">
+        <v>23</v>
+      </c>
+      <c r="L443" t="s">
+        <v>2417</v>
+      </c>
+      <c r="M443" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="444" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B444" t="s">
+        <v>2420</v>
+      </c>
+      <c r="C444" t="s">
+        <v>15</v>
+      </c>
+      <c r="D444" t="s">
+        <v>2421</v>
+      </c>
+      <c r="E444" t="s">
+        <v>328</v>
+      </c>
+      <c r="F444" t="s">
+        <v>18</v>
+      </c>
+      <c r="G444" t="s">
+        <v>19</v>
+      </c>
+      <c r="H444" t="s">
+        <v>20</v>
+      </c>
+      <c r="I444" t="s">
+        <v>21</v>
+      </c>
+      <c r="J444" t="s">
+        <v>46</v>
+      </c>
+      <c r="K444" t="s">
+        <v>23</v>
+      </c>
+      <c r="L444" t="s">
+        <v>2422</v>
+      </c>
+      <c r="M444" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="445" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B445" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C445" t="s">
+        <v>28</v>
+      </c>
+      <c r="D445" t="s">
+        <v>2426</v>
+      </c>
+      <c r="E445" t="s">
+        <v>328</v>
+      </c>
+      <c r="F445" t="s">
+        <v>18</v>
+      </c>
+      <c r="G445" t="s">
+        <v>19</v>
+      </c>
+      <c r="H445" t="s">
+        <v>75</v>
+      </c>
+      <c r="I445" t="s">
+        <v>81</v>
+      </c>
+      <c r="J445" t="s">
+        <v>46</v>
+      </c>
+      <c r="K445" t="s">
+        <v>23</v>
+      </c>
+      <c r="L445" t="s">
+        <v>2427</v>
+      </c>
+      <c r="M445" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="446" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B446" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C446" t="s">
+        <v>910</v>
+      </c>
+      <c r="D446" t="s">
+        <v>2431</v>
+      </c>
+      <c r="E446" t="s">
+        <v>328</v>
+      </c>
+      <c r="F446" t="s">
+        <v>18</v>
+      </c>
+      <c r="G446" t="s">
+        <v>19</v>
+      </c>
+      <c r="H446" t="s">
+        <v>45</v>
+      </c>
+      <c r="I446" t="s">
+        <v>21</v>
+      </c>
+      <c r="J446" t="s">
+        <v>46</v>
+      </c>
+      <c r="K446" t="s">
+        <v>23</v>
+      </c>
+      <c r="L446" t="s">
+        <v>2432</v>
+      </c>
+      <c r="M446" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="447" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>2434</v>
+      </c>
+      <c r="B447" t="s">
+        <v>2435</v>
+      </c>
+      <c r="C447" t="s">
+        <v>73</v>
+      </c>
+      <c r="D447" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E447" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F447" t="s">
+        <v>18</v>
+      </c>
+      <c r="G447" t="s">
+        <v>19</v>
+      </c>
+      <c r="H447" t="s">
+        <v>67</v>
+      </c>
+      <c r="I447" t="s">
+        <v>21</v>
+      </c>
+      <c r="J447" t="s">
+        <v>75</v>
+      </c>
+      <c r="K447" t="s">
+        <v>23</v>
+      </c>
+      <c r="L447" t="s">
+        <v>2438</v>
+      </c>
+      <c r="M447" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="448" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>2440</v>
+      </c>
+      <c r="B448" t="s">
+        <v>2441</v>
+      </c>
+      <c r="C448" t="s">
+        <v>28</v>
+      </c>
+      <c r="D448" t="s">
+        <v>2442</v>
+      </c>
+      <c r="E448" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F448" t="s">
+        <v>18</v>
+      </c>
+      <c r="G448" t="s">
+        <v>19</v>
+      </c>
+      <c r="H448" t="s">
+        <v>381</v>
+      </c>
+      <c r="I448" t="s">
+        <v>21</v>
+      </c>
+      <c r="J448" t="s">
+        <v>2443</v>
+      </c>
+      <c r="K448" t="s">
+        <v>23</v>
+      </c>
+      <c r="L448" t="s">
+        <v>2444</v>
+      </c>
+      <c r="M448" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="449" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B449" t="s">
+        <v>2447</v>
+      </c>
+      <c r="C449" t="s">
+        <v>15</v>
+      </c>
+      <c r="D449" t="s">
+        <v>2448</v>
+      </c>
+      <c r="E449" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F449" t="s">
+        <v>18</v>
+      </c>
+      <c r="G449" t="s">
+        <v>19</v>
+      </c>
+      <c r="H449" t="s">
+        <v>211</v>
+      </c>
+      <c r="I449" t="s">
+        <v>21</v>
+      </c>
+      <c r="J449" t="s">
+        <v>46</v>
+      </c>
+      <c r="K449" t="s">
+        <v>23</v>
+      </c>
+      <c r="L449" t="s">
+        <v>2449</v>
+      </c>
+      <c r="M449" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="450" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B450" t="s">
+        <v>2452</v>
+      </c>
+      <c r="C450" t="s">
+        <v>15</v>
+      </c>
+      <c r="D450" t="s">
+        <v>2453</v>
+      </c>
+      <c r="E450" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F450" t="s">
+        <v>18</v>
+      </c>
+      <c r="G450" t="s">
+        <v>19</v>
+      </c>
+      <c r="H450" t="s">
+        <v>381</v>
+      </c>
+      <c r="I450" t="s">
+        <v>21</v>
+      </c>
+      <c r="J450" t="s">
+        <v>46</v>
+      </c>
+      <c r="K450" t="s">
+        <v>23</v>
+      </c>
+      <c r="L450" t="s">
+        <v>2454</v>
+      </c>
+      <c r="M450" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="451" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B451" t="s">
+        <v>2457</v>
+      </c>
+      <c r="C451" t="s">
+        <v>28</v>
+      </c>
+      <c r="D451" t="s">
+        <v>2458</v>
+      </c>
+      <c r="E451" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F451" t="s">
+        <v>18</v>
+      </c>
+      <c r="G451" t="s">
+        <v>19</v>
+      </c>
+      <c r="H451" t="s">
+        <v>45</v>
+      </c>
+      <c r="I451" t="s">
+        <v>21</v>
+      </c>
+      <c r="J451" t="s">
+        <v>46</v>
+      </c>
+      <c r="K451" t="s">
+        <v>23</v>
+      </c>
+      <c r="L451" t="s">
+        <v>2459</v>
+      </c>
+      <c r="M451" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="452" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B452" t="s">
+        <v>2462</v>
+      </c>
+      <c r="C452" t="s">
+        <v>15</v>
+      </c>
+      <c r="D452" t="s">
+        <v>2463</v>
+      </c>
+      <c r="E452" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F452" t="s">
+        <v>18</v>
+      </c>
+      <c r="G452" t="s">
+        <v>19</v>
+      </c>
+      <c r="H452" t="s">
+        <v>37</v>
+      </c>
+      <c r="I452" t="s">
+        <v>21</v>
+      </c>
+      <c r="J452" t="s">
+        <v>46</v>
+      </c>
+      <c r="K452" t="s">
+        <v>23</v>
+      </c>
+      <c r="L452" t="s">
+        <v>2464</v>
+      </c>
+      <c r="M452" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="453" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B453" t="s">
+        <v>2467</v>
+      </c>
+      <c r="C453" t="s">
+        <v>15</v>
+      </c>
+      <c r="D453" t="s">
+        <v>2468</v>
+      </c>
+      <c r="E453" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F453" t="s">
+        <v>18</v>
+      </c>
+      <c r="G453" t="s">
+        <v>19</v>
+      </c>
+      <c r="H453" t="s">
+        <v>37</v>
+      </c>
+      <c r="I453" t="s">
+        <v>21</v>
+      </c>
+      <c r="J453" t="s">
+        <v>46</v>
+      </c>
+      <c r="K453" t="s">
+        <v>23</v>
+      </c>
+      <c r="L453" t="s">
+        <v>2469</v>
+      </c>
+      <c r="M453" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="454" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B454" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C454" t="s">
+        <v>15</v>
+      </c>
+      <c r="D454" t="s">
+        <v>2473</v>
+      </c>
+      <c r="E454" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F454" t="s">
+        <v>18</v>
+      </c>
+      <c r="G454" t="s">
+        <v>19</v>
+      </c>
+      <c r="H454" t="s">
+        <v>67</v>
+      </c>
+      <c r="I454" t="s">
+        <v>21</v>
+      </c>
+      <c r="J454" t="s">
+        <v>46</v>
+      </c>
+      <c r="K454" t="s">
+        <v>23</v>
+      </c>
+      <c r="L454" t="s">
+        <v>2474</v>
+      </c>
+      <c r="M454" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="455" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B455" t="s">
+        <v>2477</v>
+      </c>
+      <c r="C455" t="s">
+        <v>15</v>
+      </c>
+      <c r="D455" t="s">
+        <v>2478</v>
+      </c>
+      <c r="E455" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F455" t="s">
+        <v>18</v>
+      </c>
+      <c r="G455" t="s">
+        <v>19</v>
+      </c>
+      <c r="H455" t="s">
+        <v>92</v>
+      </c>
+      <c r="I455" t="s">
+        <v>21</v>
+      </c>
+      <c r="J455" t="s">
+        <v>435</v>
+      </c>
+      <c r="K455" t="s">
+        <v>23</v>
+      </c>
+      <c r="L455" t="s">
+        <v>2479</v>
+      </c>
+      <c r="M455" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="456" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B456" t="s">
+        <v>2482</v>
+      </c>
+      <c r="C456" t="s">
+        <v>15</v>
+      </c>
+      <c r="D456" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E456" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F456" t="s">
+        <v>18</v>
+      </c>
+      <c r="G456" t="s">
+        <v>19</v>
+      </c>
+      <c r="H456" t="s">
+        <v>75</v>
+      </c>
+      <c r="I456" t="s">
+        <v>81</v>
+      </c>
+      <c r="J456" t="s">
+        <v>75</v>
+      </c>
+      <c r="K456" t="s">
+        <v>23</v>
+      </c>
+      <c r="L456" t="s">
+        <v>2484</v>
+      </c>
+      <c r="M456" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="457" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B457" t="s">
+        <v>2487</v>
+      </c>
+      <c r="C457" t="s">
+        <v>333</v>
+      </c>
+      <c r="D457" t="s">
+        <v>2488</v>
+      </c>
+      <c r="E457" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F457" t="s">
+        <v>18</v>
+      </c>
+      <c r="G457" t="s">
+        <v>19</v>
+      </c>
+      <c r="H457" t="s">
+        <v>211</v>
+      </c>
+      <c r="I457" t="s">
+        <v>21</v>
+      </c>
+      <c r="J457" t="s">
+        <v>46</v>
+      </c>
+      <c r="K457" t="s">
+        <v>23</v>
+      </c>
+      <c r="L457" t="s">
+        <v>2489</v>
+      </c>
+      <c r="M457" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="458" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B458" t="s">
+        <v>2492</v>
+      </c>
+      <c r="C458" t="s">
+        <v>15</v>
+      </c>
+      <c r="D458" t="s">
+        <v>2493</v>
+      </c>
+      <c r="E458" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F458" t="s">
+        <v>18</v>
+      </c>
+      <c r="G458" t="s">
+        <v>19</v>
+      </c>
+      <c r="H458" t="s">
+        <v>45</v>
+      </c>
+      <c r="I458" t="s">
+        <v>21</v>
+      </c>
+      <c r="J458" t="s">
+        <v>46</v>
+      </c>
+      <c r="K458" t="s">
+        <v>23</v>
+      </c>
+      <c r="L458" t="s">
+        <v>2494</v>
+      </c>
+      <c r="M458" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="459" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B459" t="s">
+        <v>2497</v>
+      </c>
+      <c r="C459" t="s">
+        <v>15</v>
+      </c>
+      <c r="D459" t="s">
+        <v>2498</v>
+      </c>
+      <c r="E459" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F459" t="s">
+        <v>18</v>
+      </c>
+      <c r="G459" t="s">
+        <v>19</v>
+      </c>
+      <c r="H459" t="s">
+        <v>627</v>
+      </c>
+      <c r="I459" t="s">
+        <v>21</v>
+      </c>
+      <c r="J459" t="s">
+        <v>159</v>
+      </c>
+      <c r="K459" t="s">
+        <v>23</v>
+      </c>
+      <c r="L459" t="s">
+        <v>2499</v>
+      </c>
+      <c r="M459" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="460" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>2501</v>
+      </c>
+      <c r="B460" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C460" t="s">
+        <v>15</v>
+      </c>
+      <c r="D460" t="s">
+        <v>2503</v>
+      </c>
+      <c r="E460" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F460" t="s">
+        <v>18</v>
+      </c>
+      <c r="G460" t="s">
+        <v>19</v>
+      </c>
+      <c r="H460" t="s">
+        <v>52</v>
+      </c>
+      <c r="I460" t="s">
+        <v>21</v>
+      </c>
+      <c r="J460" t="s">
+        <v>75</v>
+      </c>
+      <c r="K460" t="s">
+        <v>23</v>
+      </c>
+      <c r="L460" t="s">
+        <v>2504</v>
+      </c>
+      <c r="M460" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="461" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B461" t="s">
+        <v>2507</v>
+      </c>
+      <c r="C461" t="s">
+        <v>15</v>
+      </c>
+      <c r="D461" t="s">
+        <v>2508</v>
+      </c>
+      <c r="E461" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F461" t="s">
+        <v>18</v>
+      </c>
+      <c r="G461" t="s">
+        <v>19</v>
+      </c>
+      <c r="H461" t="s">
+        <v>45</v>
+      </c>
+      <c r="I461" t="s">
+        <v>21</v>
+      </c>
+      <c r="J461" t="s">
+        <v>75</v>
+      </c>
+      <c r="K461" t="s">
+        <v>23</v>
+      </c>
+      <c r="L461" t="s">
+        <v>2509</v>
+      </c>
+      <c r="M461" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="462" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B462" t="s">
+        <v>2512</v>
+      </c>
+      <c r="C462" t="s">
+        <v>15</v>
+      </c>
+      <c r="D462" t="s">
+        <v>2513</v>
+      </c>
+      <c r="E462" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F462" t="s">
+        <v>18</v>
+      </c>
+      <c r="G462" t="s">
+        <v>19</v>
+      </c>
+      <c r="H462" t="s">
+        <v>45</v>
+      </c>
+      <c r="I462" t="s">
+        <v>21</v>
+      </c>
+      <c r="J462" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K462" t="s">
+        <v>23</v>
+      </c>
+      <c r="L462" t="s">
+        <v>2515</v>
+      </c>
+      <c r="M462" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="463" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B463" t="s">
+        <v>2518</v>
+      </c>
+      <c r="C463" t="s">
+        <v>926</v>
+      </c>
+      <c r="D463" t="s">
+        <v>2519</v>
+      </c>
+      <c r="E463" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F463" t="s">
+        <v>18</v>
+      </c>
+      <c r="G463" t="s">
+        <v>19</v>
+      </c>
+      <c r="H463" t="s">
+        <v>223</v>
+      </c>
+      <c r="I463" t="s">
+        <v>21</v>
+      </c>
+      <c r="J463" t="s">
+        <v>46</v>
+      </c>
+      <c r="K463" t="s">
+        <v>23</v>
+      </c>
+      <c r="L463" t="s">
+        <v>2520</v>
+      </c>
+      <c r="M463" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="464" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B464" t="s">
+        <v>2523</v>
+      </c>
+      <c r="C464" t="s">
+        <v>58</v>
+      </c>
+      <c r="D464" t="s">
+        <v>2524</v>
+      </c>
+      <c r="E464" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F464" t="s">
+        <v>18</v>
+      </c>
+      <c r="G464" t="s">
+        <v>19</v>
+      </c>
+      <c r="H464" t="s">
+        <v>223</v>
+      </c>
+      <c r="I464" t="s">
+        <v>2525</v>
+      </c>
+      <c r="J464" t="s">
+        <v>2526</v>
+      </c>
+      <c r="K464" t="s">
+        <v>23</v>
+      </c>
+      <c r="L464" t="s">
+        <v>2527</v>
+      </c>
+      <c r="M464" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="465" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B465" t="s">
+        <v>2530</v>
+      </c>
+      <c r="C465" t="s">
+        <v>15</v>
+      </c>
+      <c r="D465" t="s">
+        <v>2531</v>
+      </c>
+      <c r="E465" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F465" t="s">
+        <v>18</v>
+      </c>
+      <c r="G465" t="s">
+        <v>19</v>
+      </c>
+      <c r="H465" t="s">
+        <v>67</v>
+      </c>
+      <c r="I465" t="s">
+        <v>21</v>
+      </c>
+      <c r="J465" t="s">
+        <v>297</v>
+      </c>
+      <c r="K465" t="s">
+        <v>23</v>
+      </c>
+      <c r="L465" t="s">
+        <v>2533</v>
+      </c>
+      <c r="M465" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="466" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B466" t="s">
+        <v>2536</v>
+      </c>
+      <c r="C466" t="s">
+        <v>15</v>
+      </c>
+      <c r="D466" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E466" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F466" t="s">
+        <v>18</v>
+      </c>
+      <c r="G466" t="s">
+        <v>19</v>
+      </c>
+      <c r="H466" t="s">
+        <v>466</v>
+      </c>
+      <c r="I466" t="s">
+        <v>21</v>
+      </c>
+      <c r="J466" t="s">
+        <v>2538</v>
+      </c>
+      <c r="K466" t="s">
+        <v>23</v>
+      </c>
+      <c r="L466" t="s">
+        <v>2539</v>
+      </c>
+      <c r="M466" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="467" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B467" t="s">
+        <v>2542</v>
+      </c>
+      <c r="C467" t="s">
+        <v>73</v>
+      </c>
+      <c r="D467" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E467" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F467" t="s">
+        <v>18</v>
+      </c>
+      <c r="G467" t="s">
+        <v>19</v>
+      </c>
+      <c r="H467" t="s">
+        <v>92</v>
+      </c>
+      <c r="I467" t="s">
+        <v>21</v>
+      </c>
+      <c r="J467" t="s">
+        <v>75</v>
+      </c>
+      <c r="K467" t="s">
+        <v>23</v>
+      </c>
+      <c r="L467" t="s">
+        <v>2544</v>
+      </c>
+      <c r="M467" t="s">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="468" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>2546</v>
+      </c>
+      <c r="B468" t="s">
+        <v>2547</v>
+      </c>
+      <c r="C468" t="s">
+        <v>28</v>
+      </c>
+      <c r="D468" t="s">
+        <v>2548</v>
+      </c>
+      <c r="E468" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F468" t="s">
+        <v>18</v>
+      </c>
+      <c r="G468" t="s">
+        <v>19</v>
+      </c>
+      <c r="H468" t="s">
+        <v>67</v>
+      </c>
+      <c r="I468" t="s">
+        <v>21</v>
+      </c>
+      <c r="J468" t="s">
+        <v>121</v>
+      </c>
+      <c r="K468" t="s">
+        <v>23</v>
+      </c>
+      <c r="L468" t="s">
+        <v>2549</v>
+      </c>
+      <c r="M468" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="469" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B469" t="s">
+        <v>2552</v>
+      </c>
+      <c r="C469" t="s">
+        <v>28</v>
+      </c>
+      <c r="D469" t="s">
+        <v>2553</v>
+      </c>
+      <c r="E469" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F469" t="s">
+        <v>18</v>
+      </c>
+      <c r="G469" t="s">
+        <v>19</v>
+      </c>
+      <c r="H469" t="s">
+        <v>381</v>
+      </c>
+      <c r="I469" t="s">
+        <v>21</v>
+      </c>
+      <c r="J469" t="s">
+        <v>297</v>
+      </c>
+      <c r="K469" t="s">
+        <v>23</v>
+      </c>
+      <c r="L469" t="s">
+        <v>2554</v>
+      </c>
+      <c r="M469" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="470" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B470" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C470" t="s">
+        <v>15</v>
+      </c>
+      <c r="D470" t="s">
+        <v>2558</v>
+      </c>
+      <c r="E470" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F470" t="s">
+        <v>18</v>
+      </c>
+      <c r="G470" t="s">
+        <v>19</v>
+      </c>
+      <c r="H470" t="s">
+        <v>45</v>
+      </c>
+      <c r="I470" t="s">
+        <v>21</v>
+      </c>
+      <c r="J470" t="s">
+        <v>2559</v>
+      </c>
+      <c r="K470" t="s">
+        <v>23</v>
+      </c>
+      <c r="L470" t="s">
+        <v>2560</v>
+      </c>
+      <c r="M470" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="471" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B471" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C471" t="s">
+        <v>15</v>
+      </c>
+      <c r="D471" t="s">
+        <v>2564</v>
+      </c>
+      <c r="E471" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F471" t="s">
+        <v>18</v>
+      </c>
+      <c r="G471" t="s">
+        <v>19</v>
+      </c>
+      <c r="H471" t="s">
+        <v>75</v>
+      </c>
+      <c r="I471" t="s">
+        <v>81</v>
+      </c>
+      <c r="J471" t="s">
+        <v>30</v>
+      </c>
+      <c r="K471" t="s">
+        <v>23</v>
+      </c>
+      <c r="L471" t="s">
+        <v>2565</v>
+      </c>
+      <c r="M471" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="472" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B472" t="s">
+        <v>2568</v>
+      </c>
+      <c r="C472" t="s">
+        <v>15</v>
+      </c>
+      <c r="D472" t="s">
+        <v>2569</v>
+      </c>
+      <c r="E472" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F472" t="s">
+        <v>18</v>
+      </c>
+      <c r="G472" t="s">
+        <v>19</v>
+      </c>
+      <c r="H472" t="s">
+        <v>429</v>
+      </c>
+      <c r="I472" t="s">
+        <v>21</v>
+      </c>
+      <c r="J472" t="s">
+        <v>548</v>
+      </c>
+      <c r="K472" t="s">
+        <v>23</v>
+      </c>
+      <c r="L472" t="s">
+        <v>2570</v>
+      </c>
+      <c r="M472" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="473" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B473" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C473" t="s">
+        <v>15</v>
+      </c>
+      <c r="D473" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E473" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F473" t="s">
+        <v>18</v>
+      </c>
+      <c r="G473" t="s">
+        <v>19</v>
+      </c>
+      <c r="H473" t="s">
+        <v>45</v>
+      </c>
+      <c r="I473" t="s">
+        <v>21</v>
+      </c>
+      <c r="J473" t="s">
+        <v>75</v>
+      </c>
+      <c r="K473" t="s">
+        <v>23</v>
+      </c>
+      <c r="L473" t="s">
+        <v>2575</v>
+      </c>
+      <c r="M473" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="474" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>2577</v>
+      </c>
+      <c r="B474" t="s">
+        <v>2578</v>
+      </c>
+      <c r="C474" t="s">
+        <v>28</v>
+      </c>
+      <c r="D474" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E474" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F474" t="s">
+        <v>18</v>
+      </c>
+      <c r="G474" t="s">
+        <v>19</v>
+      </c>
+      <c r="H474" t="s">
+        <v>45</v>
+      </c>
+      <c r="I474" t="s">
+        <v>21</v>
+      </c>
+      <c r="J474" t="s">
+        <v>46</v>
+      </c>
+      <c r="K474" t="s">
+        <v>23</v>
+      </c>
+      <c r="L474" t="s">
+        <v>2580</v>
+      </c>
+      <c r="M474" t="s">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="475" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>2582</v>
+      </c>
+      <c r="B475" t="s">
+        <v>2583</v>
+      </c>
+      <c r="C475" t="s">
+        <v>15</v>
+      </c>
+      <c r="D475" t="s">
+        <v>2584</v>
+      </c>
+      <c r="E475" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F475" t="s">
+        <v>18</v>
+      </c>
+      <c r="G475" t="s">
+        <v>19</v>
+      </c>
+      <c r="H475" t="s">
+        <v>211</v>
+      </c>
+      <c r="I475" t="s">
+        <v>21</v>
+      </c>
+      <c r="J475" t="s">
+        <v>30</v>
+      </c>
+      <c r="K475" t="s">
+        <v>23</v>
+      </c>
+      <c r="L475" t="s">
+        <v>2585</v>
+      </c>
+      <c r="M475" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="476" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B476" t="s">
+        <v>2588</v>
+      </c>
+      <c r="C476" t="s">
+        <v>58</v>
+      </c>
+      <c r="D476" t="s">
+        <v>2589</v>
+      </c>
+      <c r="E476" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F476" t="s">
+        <v>18</v>
+      </c>
+      <c r="G476" t="s">
+        <v>19</v>
+      </c>
+      <c r="H476" t="s">
+        <v>466</v>
+      </c>
+      <c r="I476" t="s">
+        <v>258</v>
+      </c>
+      <c r="J476" t="s">
+        <v>2590</v>
+      </c>
+      <c r="K476" t="s">
+        <v>23</v>
+      </c>
+      <c r="L476" t="s">
+        <v>2591</v>
+      </c>
+      <c r="M476" t="s">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="477" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>2593</v>
+      </c>
+      <c r="B477" t="s">
+        <v>2594</v>
+      </c>
+      <c r="C477" t="s">
+        <v>28</v>
+      </c>
+      <c r="D477" t="s">
+        <v>2595</v>
+      </c>
+      <c r="E477" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F477" t="s">
+        <v>18</v>
+      </c>
+      <c r="G477" t="s">
+        <v>19</v>
+      </c>
+      <c r="H477" t="s">
+        <v>405</v>
+      </c>
+      <c r="I477" t="s">
+        <v>21</v>
+      </c>
+      <c r="J477" t="s">
+        <v>297</v>
+      </c>
+      <c r="K477" t="s">
+        <v>23</v>
+      </c>
+      <c r="L477" t="s">
+        <v>2596</v>
+      </c>
+      <c r="M477" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="478" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>2598</v>
+      </c>
+      <c r="B478" t="s">
+        <v>2599</v>
+      </c>
+      <c r="C478" t="s">
+        <v>181</v>
+      </c>
+      <c r="D478" t="s">
+        <v>2600</v>
+      </c>
+      <c r="E478" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F478" t="s">
+        <v>18</v>
+      </c>
+      <c r="G478" t="s">
+        <v>19</v>
+      </c>
+      <c r="H478" t="s">
+        <v>92</v>
+      </c>
+      <c r="I478" t="s">
+        <v>21</v>
+      </c>
+      <c r="J478" t="s">
+        <v>46</v>
+      </c>
+      <c r="K478" t="s">
+        <v>23</v>
+      </c>
+      <c r="L478" t="s">
+        <v>2601</v>
+      </c>
+      <c r="M478" t="s">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="479" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B479" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C479" t="s">
+        <v>15</v>
+      </c>
+      <c r="D479" t="s">
+        <v>2605</v>
+      </c>
+      <c r="E479" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F479" t="s">
+        <v>18</v>
+      </c>
+      <c r="G479" t="s">
+        <v>19</v>
+      </c>
+      <c r="H479" t="s">
+        <v>37</v>
+      </c>
+      <c r="I479" t="s">
+        <v>21</v>
+      </c>
+      <c r="J479" t="s">
+        <v>46</v>
+      </c>
+      <c r="K479" t="s">
+        <v>23</v>
+      </c>
+      <c r="L479" t="s">
+        <v>2606</v>
+      </c>
+      <c r="M479" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="480" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>2608</v>
+      </c>
+      <c r="B480" t="s">
+        <v>2609</v>
+      </c>
+      <c r="C480" t="s">
+        <v>181</v>
+      </c>
+      <c r="D480" t="s">
+        <v>2610</v>
+      </c>
+      <c r="E480" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F480" t="s">
+        <v>18</v>
+      </c>
+      <c r="G480" t="s">
+        <v>19</v>
+      </c>
+      <c r="H480" t="s">
+        <v>20</v>
+      </c>
+      <c r="I480" t="s">
+        <v>21</v>
+      </c>
+      <c r="J480" t="s">
+        <v>46</v>
+      </c>
+      <c r="K480" t="s">
+        <v>23</v>
+      </c>
+      <c r="L480" t="s">
+        <v>2611</v>
+      </c>
+      <c r="M480" t="s">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="481" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>2613</v>
+      </c>
+      <c r="B481" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C481" t="s">
+        <v>28</v>
+      </c>
+      <c r="D481" t="s">
+        <v>2615</v>
+      </c>
+      <c r="E481" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F481" t="s">
+        <v>18</v>
+      </c>
+      <c r="G481" t="s">
+        <v>19</v>
+      </c>
+      <c r="H481" t="s">
+        <v>405</v>
+      </c>
+      <c r="I481" t="s">
+        <v>21</v>
+      </c>
+      <c r="J481" t="s">
+        <v>121</v>
+      </c>
+      <c r="K481" t="s">
+        <v>23</v>
+      </c>
+      <c r="L481" t="s">
+        <v>2616</v>
+      </c>
+      <c r="M481" t="s">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="482" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>2618</v>
+      </c>
+      <c r="B482" t="s">
+        <v>2619</v>
+      </c>
+      <c r="C482" t="s">
+        <v>187</v>
+      </c>
+      <c r="D482" t="s">
+        <v>2620</v>
+      </c>
+      <c r="E482" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F482" t="s">
+        <v>18</v>
+      </c>
+      <c r="G482" t="s">
+        <v>19</v>
+      </c>
+      <c r="H482" t="s">
+        <v>92</v>
+      </c>
+      <c r="I482" t="s">
+        <v>21</v>
+      </c>
+      <c r="J482" t="s">
+        <v>297</v>
+      </c>
+      <c r="K482" t="s">
+        <v>23</v>
+      </c>
+      <c r="L482" t="s">
+        <v>2621</v>
+      </c>
+      <c r="M482" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="483" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B483" t="s">
+        <v>2624</v>
+      </c>
+      <c r="C483" t="s">
+        <v>15</v>
+      </c>
+      <c r="D483" t="s">
+        <v>2625</v>
+      </c>
+      <c r="E483" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F483" t="s">
+        <v>18</v>
+      </c>
+      <c r="G483" t="s">
+        <v>19</v>
+      </c>
+      <c r="H483" t="s">
+        <v>241</v>
+      </c>
+      <c r="I483" t="s">
+        <v>21</v>
+      </c>
+      <c r="J483" t="s">
+        <v>297</v>
+      </c>
+      <c r="K483" t="s">
+        <v>23</v>
+      </c>
+      <c r="L483" t="s">
+        <v>2626</v>
+      </c>
+      <c r="M483" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="484" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>2628</v>
+      </c>
+      <c r="B484" t="s">
+        <v>2629</v>
+      </c>
+      <c r="C484" t="s">
+        <v>73</v>
+      </c>
+      <c r="D484" t="s">
+        <v>2630</v>
+      </c>
+      <c r="E484" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F484" t="s">
+        <v>18</v>
+      </c>
+      <c r="G484" t="s">
+        <v>19</v>
+      </c>
+      <c r="H484" t="s">
+        <v>815</v>
+      </c>
+      <c r="I484" t="s">
+        <v>21</v>
+      </c>
+      <c r="J484" t="s">
+        <v>75</v>
+      </c>
+      <c r="K484" t="s">
+        <v>23</v>
+      </c>
+      <c r="L484" t="s">
+        <v>2631</v>
+      </c>
+      <c r="M484" t="s">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="485" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>2633</v>
+      </c>
+      <c r="B485" t="s">
+        <v>2634</v>
+      </c>
+      <c r="C485" t="s">
+        <v>73</v>
+      </c>
+      <c r="D485" t="s">
+        <v>2635</v>
+      </c>
+      <c r="E485" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F485" t="s">
+        <v>18</v>
+      </c>
+      <c r="G485" t="s">
+        <v>19</v>
+      </c>
+      <c r="H485" t="s">
+        <v>45</v>
+      </c>
+      <c r="I485" t="s">
+        <v>21</v>
+      </c>
+      <c r="J485" t="s">
+        <v>75</v>
+      </c>
+      <c r="K485" t="s">
+        <v>23</v>
+      </c>
+      <c r="L485" t="s">
+        <v>2636</v>
+      </c>
+      <c r="M485" t="s">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="486" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>2638</v>
+      </c>
+      <c r="B486" t="s">
+        <v>2639</v>
+      </c>
+      <c r="C486" t="s">
+        <v>15</v>
+      </c>
+      <c r="D486" t="s">
+        <v>2640</v>
+      </c>
+      <c r="E486" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F486" t="s">
+        <v>18</v>
+      </c>
+      <c r="G486" t="s">
+        <v>19</v>
+      </c>
+      <c r="H486" t="s">
+        <v>67</v>
+      </c>
+      <c r="I486" t="s">
+        <v>21</v>
+      </c>
+      <c r="J486" t="s">
+        <v>2641</v>
+      </c>
+      <c r="K486" t="s">
+        <v>23</v>
+      </c>
+      <c r="L486" t="s">
+        <v>2642</v>
+      </c>
+      <c r="M486" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="487" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>2644</v>
+      </c>
+      <c r="B487" t="s">
+        <v>2645</v>
+      </c>
+      <c r="C487" t="s">
+        <v>15</v>
+      </c>
+      <c r="D487" t="s">
+        <v>2646</v>
+      </c>
+      <c r="E487" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F487" t="s">
+        <v>18</v>
+      </c>
+      <c r="G487" t="s">
+        <v>19</v>
+      </c>
+      <c r="H487" t="s">
+        <v>381</v>
+      </c>
+      <c r="I487" t="s">
+        <v>21</v>
+      </c>
+      <c r="J487" t="s">
+        <v>121</v>
+      </c>
+      <c r="K487" t="s">
+        <v>23</v>
+      </c>
+      <c r="L487" t="s">
+        <v>2647</v>
+      </c>
+      <c r="M487" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="488" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>2649</v>
+      </c>
+      <c r="B488" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C488" t="s">
+        <v>15</v>
+      </c>
+      <c r="D488" t="s">
+        <v>2651</v>
+      </c>
+      <c r="E488" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F488" t="s">
+        <v>18</v>
+      </c>
+      <c r="G488" t="s">
+        <v>19</v>
+      </c>
+      <c r="H488" t="s">
+        <v>627</v>
+      </c>
+      <c r="I488" t="s">
+        <v>21</v>
+      </c>
+      <c r="J488" t="s">
+        <v>297</v>
+      </c>
+      <c r="K488" t="s">
+        <v>23</v>
+      </c>
+      <c r="L488" t="s">
+        <v>2652</v>
+      </c>
+      <c r="M488" t="s">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="489" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>2654</v>
+      </c>
+      <c r="B489" t="s">
+        <v>2655</v>
+      </c>
+      <c r="C489" t="s">
+        <v>58</v>
+      </c>
+      <c r="D489" t="s">
+        <v>2656</v>
+      </c>
+      <c r="E489" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F489" t="s">
+        <v>18</v>
+      </c>
+      <c r="G489" t="s">
+        <v>19</v>
+      </c>
+      <c r="H489" t="s">
+        <v>45</v>
+      </c>
+      <c r="I489" t="s">
+        <v>60</v>
+      </c>
+      <c r="J489" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K489" t="s">
+        <v>23</v>
+      </c>
+      <c r="L489" t="s">
+        <v>2657</v>
+      </c>
+      <c r="M489" t="s">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="490" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B490" t="s">
+        <v>2660</v>
+      </c>
+      <c r="C490" t="s">
+        <v>28</v>
+      </c>
+      <c r="D490" t="s">
+        <v>2661</v>
+      </c>
+      <c r="E490" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F490" t="s">
+        <v>18</v>
+      </c>
+      <c r="G490" t="s">
+        <v>19</v>
+      </c>
+      <c r="H490" t="s">
+        <v>67</v>
+      </c>
+      <c r="I490" t="s">
+        <v>21</v>
+      </c>
+      <c r="J490" t="s">
+        <v>46</v>
+      </c>
+      <c r="K490" t="s">
+        <v>23</v>
+      </c>
+      <c r="L490" t="s">
+        <v>2663</v>
+      </c>
+      <c r="M490" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="491" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>2665</v>
+      </c>
+      <c r="B491" t="s">
+        <v>2666</v>
+      </c>
+      <c r="C491" t="s">
+        <v>28</v>
+      </c>
+      <c r="D491" t="s">
+        <v>2667</v>
+      </c>
+      <c r="E491" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F491" t="s">
+        <v>18</v>
+      </c>
+      <c r="G491" t="s">
+        <v>19</v>
+      </c>
+      <c r="H491" t="s">
+        <v>45</v>
+      </c>
+      <c r="I491" t="s">
+        <v>21</v>
+      </c>
+      <c r="J491" t="s">
+        <v>30</v>
+      </c>
+      <c r="K491" t="s">
+        <v>23</v>
+      </c>
+      <c r="L491" t="s">
+        <v>2668</v>
+      </c>
+      <c r="M491" t="s">
+        <v>2669</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/Sajjad data/by_country_and_state/USA/CA.xlsx
+++ b/Sajjad data/by_country_and_state/USA/CA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6383" uniqueCount="2670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8307" uniqueCount="3436">
   <si>
     <t>Business Name</t>
   </si>
@@ -8021,6 +8021,2304 @@
   </si>
   <si>
     <t>2026-10-24T23:06:09.491Z</t>
+  </si>
+  <si>
+    <t>Noe Valley Family-Cosmetic</t>
+  </si>
+  <si>
+    <t>(415) 647-6000</t>
+  </si>
+  <si>
+    <t>1508 Church St, San Francisco, CA 94131</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Noe+Valley+Family-Cosmetic/data=!4m7!3m6!1s0x808f7e6bcdad80ed:0xd44c418c0dc2daaa!8m2!3d37.7466219!4d-122.4271488!16s%2Fg%2F1tfcnl2d!19sChIJ7YCtzWt-j4ARqtrCDYxBTNQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:31:46.603Z</t>
+  </si>
+  <si>
+    <t>Dr. Blair A. Keck, DDS</t>
+  </si>
+  <si>
+    <t>(415) 863-9255</t>
+  </si>
+  <si>
+    <t>4128 18th St, San Francisco, CA 94114</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Blair+A.+Keck,+DDS/data=!4m7!3m6!1s0x808f7e04cbfa59a1:0x2a0fe5fabca0de1b!8m2!3d37.7609473!4d-122.4357421!16s%2Fg%2F1tgw57xh!19sChIJoVn6ywR-j4ARG96gvPrlDyo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:31:51.043Z</t>
+  </si>
+  <si>
+    <t>Dr. Gregory A. Chong, DDS</t>
+  </si>
+  <si>
+    <t>(415) 223-3194</t>
+  </si>
+  <si>
+    <t>460 Bush St 2nd floor, San Francisco, CA 94108</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Gregory+A.+Chong,+DDS/data=!4m7!3m6!1s0x808587571694f851:0xe0c6e932f3918b3!8m2!3d37.7908997!4d-122.4051181!16s%2Fg%2F1tdg3fvg!19sChIJUfiUFleHhYARsxg5L5NuDA4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:31:56.007Z</t>
+  </si>
+  <si>
+    <t>Dr. Louise Stephens, DDS</t>
+  </si>
+  <si>
+    <t>(415) 334-9500</t>
+  </si>
+  <si>
+    <t>2355 Ocean Ave #1, San Francisco, CA 94127</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Louise+Stephens,+DDS/data=!4m7!3m6!1s0x808f7dc7895e21c5:0x5b647d9fac6b1e58!8m2!3d37.7296422!4d-122.4691411!16s%2Fg%2F1td726y5!19sChIJxSFeicd9j4ARWB5rrJ99ZFs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:00.316Z</t>
+  </si>
+  <si>
+    <t>S.F. Children's Dental - Surgery Center</t>
+  </si>
+  <si>
+    <t>(650) 999-3935</t>
+  </si>
+  <si>
+    <t>2460 Mission St Ste 109, San Francisco, CA 94110</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/S.F.+Children%27s+Dental+-+Surgery+Center/data=!4m7!3m6!1s0x808f7f00ef0ee345:0x57bfb7f7209f870a!8m2!3d37.7576522!4d-122.4192222!16s%2Fg%2F11zd3rll4d!19sChIJReMO7wB_j4ARCoefIPe3v1c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:33:25.941Z</t>
+  </si>
+  <si>
+    <t>Lakeside Dental Care</t>
+  </si>
+  <si>
+    <t>(415) 469-7777</t>
+  </si>
+  <si>
+    <t>1185 Vicente St, San Francisco, CA 94116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lakeside+Dental+Care/data=!4m7!3m6!1s0x808f7dbeb19e6503:0xc844517b69440e05!8m2!3d37.7389909!4d-122.4795176!16s%2Fg%2F11c310k72l!19sChIJA2Wesb59j4ARBQ5EaXtRRMg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:33:31.035Z</t>
+  </si>
+  <si>
+    <t>Healthy Smiles Dentistry</t>
+  </si>
+  <si>
+    <t>(628) 900-0609</t>
+  </si>
+  <si>
+    <t>582 Grove St, San Francisco, CA 94102</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Healthy+Smiles+Dentistry/data=!4m7!3m6!1s0x80858198b78530af:0x4d863d3738e3250b!8m2!3d37.7776196!4d-122.4262099!16s%2Fg%2F11z7w0wsrt!19sChIJrzCFt5iBhYARCyXjODc9hk0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:33:40.826Z</t>
+  </si>
+  <si>
+    <t>Emergency Dental Assist</t>
+  </si>
+  <si>
+    <t>(415) 873-5440</t>
+  </si>
+  <si>
+    <t>4200 17th St, San Francisco, CA 94114</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dental+Assist/data=!4m7!3m6!1s0x808f7fa69dbc14fd:0x7c8cc3c7c14fba97!8m2!3d37.7623699!4d-122.4396625!16s%2Fg%2F11zf8l0nb8!19sChIJ_RS8naZ_j4ARl7pPwcfDjHw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:34:09.300Z</t>
+  </si>
+  <si>
+    <t>SF Emergency Dental</t>
+  </si>
+  <si>
+    <t>(855) 900-2637</t>
+  </si>
+  <si>
+    <t>1196 Valencia St, San Francisco, CA 94110</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/SF+Emergency+Dental/data=!4m7!3m6!1s0x808f7f2efa15c01d:0x7506bd80cee1df46!8m2!3d37.7539483!4d-122.4210636!16s%2Fg%2F11fwvcpnxs!19sChIJHcAV-i5_j4ARRt_hzoC9BnU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:34:12.046Z</t>
+  </si>
+  <si>
+    <t>Emergency Dentist San Francisco</t>
+  </si>
+  <si>
+    <t>(628) 333-6988</t>
+  </si>
+  <si>
+    <t>1315 Egbert Ave, San Francisco, CA 94124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dentist+San+Francisco/data=!4m7!3m6!1s0x808f7f90ed42befb:0xc97baff0b1d7fa94!8m2!3d37.7216521!4d-122.3912876!16s%2Fg%2F11n8sb2r74!19sChIJ-75C7ZB_j4ARlPrXsfCve8k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:34:14.882Z</t>
+  </si>
+  <si>
+    <t>Laurel Heights Dental Care</t>
+  </si>
+  <si>
+    <t>(415) 668-2200</t>
+  </si>
+  <si>
+    <t>3929 Sacramento St, San Francisco, CA 94118</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Laurel+Heights+Dental+Care/data=!4m7!3m6!1s0x808587307c470b0b:0xca20f5bfbd546894!8m2!3d37.7866744!4d-122.4575831!16s%2Fg%2F1vq7527h!19sChIJCwtHfDCHhYARlGhUvb_1IMo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:34:18.020Z</t>
+  </si>
+  <si>
+    <t>Tan &amp; Thai Dental Care</t>
+  </si>
+  <si>
+    <t>(415) 821-0101</t>
+  </si>
+  <si>
+    <t>2460 Mission St #201, San Francisco, CA 94110</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tan+%26+Thai+Dental+Care/data=!4m7!3m6!1s0x808f7f78dd322b69:0x1385b5d77d8dd96d!8m2!3d37.7576788!4d-122.4191558!16s%2Fg%2F11y1hz9xk5!19sChIJaSsy3Xh_j4ARbdmNfde1hRM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:34:36.717Z</t>
+  </si>
+  <si>
+    <t>Periodontic Faculty Practice</t>
+  </si>
+  <si>
+    <t>(415) 476-1731</t>
+  </si>
+  <si>
+    <t>707 Parnassus Ave, San Francisco, CA 94143</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Periodontic+Faculty+Practice/data=!4m7!3m6!1s0x80858759121bd325:0x180879a16bfabf0c!8m2!3d37.7618923!4d-122.4613991!16s%2Fg%2F1tdb4ht1!19sChIJJdMbElmHhYARDL_6a6F5CBg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:35:58.965Z</t>
+  </si>
+  <si>
+    <t>Nguyen , Binh DDS Periodontics Specialist / Implants</t>
+  </si>
+  <si>
+    <t>(415) 386-8790</t>
+  </si>
+  <si>
+    <t>319 8th Ave, San Francisco, CA 94118</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday10 AM–5 PM; TuesdayClosed; Wednesday10 AM–5 PM; ThursdayClosed; Friday10 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nguyen+,+Binh+DDS+Periodontics+Specialist+%2F+Implants/data=!4m7!3m6!1s0x8085873dca3c0001:0xb7e1821e64f2ab0e!8m2!3d37.7824263!4d-122.4668259!16s%2Fg%2F11k3_jxldp!19sChIJAQA8yj2HhYARDqvyZB6C4bc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:02.394Z</t>
+  </si>
+  <si>
+    <t>Craig D Mukai Inc</t>
+  </si>
+  <si>
+    <t>(415) 397-4095</t>
+  </si>
+  <si>
+    <t>450 Sutter St #2329, San Francisco, CA 94108</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Craig+D+Mukai+Inc/data=!4m7!3m6!1s0x8085808ea55c18a9:0x8acc43937444ec75!8m2!3d37.7896776!4d-122.4078539!16s%2Fg%2F1tdjx773!19sChIJqRhcpY6AhYARdexEdJNDzIo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:05.880Z</t>
+  </si>
+  <si>
+    <t>Hu Herman DDS</t>
+  </si>
+  <si>
+    <t>(415) 474-0101</t>
+  </si>
+  <si>
+    <t>1711 Lombard St, San Francisco, CA 94123</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday9 AM–6 PM; Tuesday9 AM–6 PM; WednesdayClosed; Thursday9 AM–6 PM; Friday9 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hu+Herman+DDS/data=!4m7!3m6!1s0x808580db87f943ab:0x796ca76e8b8bb1cc!8m2!3d37.8004223!4d-122.4297816!16s%2Fg%2F1tlw992v!19sChIJq0P5h9uAhYARzLGLi26nbHk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:08.448Z</t>
+  </si>
+  <si>
+    <t>Dr. Neetal Smith, DDS</t>
+  </si>
+  <si>
+    <t>(415) 921-9210</t>
+  </si>
+  <si>
+    <t>2001 Union St #690, San Francisco, CA 94123</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Neetal+Smith,+DDS/data=!4m7!3m6!1s0x808f7e2b20053ce9:0x769c0247acceb353!8m2!3d37.797202!4d-122.432491!16s%2Fg%2F1tdqzyvh!19sChIJ6TwFICt-j4ARU7POrEcCnHY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:13.319Z</t>
+  </si>
+  <si>
+    <t>San Francisco Dental Artistry</t>
+  </si>
+  <si>
+    <t>(415) 399-0609</t>
+  </si>
+  <si>
+    <t>369 Pine St #200, San Francisco, CA 94104</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/San+Francisco+Dental+Artistry/data=!4m7!3m6!1s0x8085808a03158595:0x5f8044fd88d621c9!8m2!3d37.79176!4d-122.402057!16s%2Fg%2F1td9dz_x!19sChIJlYUVA4qAhYARySHWiP1EgF8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:16.395Z</t>
+  </si>
+  <si>
+    <t>Hiura Bruce T DDS</t>
+  </si>
+  <si>
+    <t>(415) 776-5855</t>
+  </si>
+  <si>
+    <t>2305 Van Ness Ave Unit E, San Francisco, CA 94109</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hiura+Bruce+T+DDS/data=!4m7!3m6!1s0x808580e9d4d604a5:0xcd66628b1f415298!8m2!3d37.7969165!4d-122.42396!16s%2Fg%2F1thxl8yj!19sChIJpQTW1OmAhYARmFJBH4tiZs0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:21.158Z</t>
+  </si>
+  <si>
+    <t>Tower Dental Care</t>
+  </si>
+  <si>
+    <t>(559) 233-5625</t>
+  </si>
+  <si>
+    <t>5670 N Fresno St Ste 107, Fresno, CA 93710</t>
+  </si>
+  <si>
+    <t>Fresno</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tower+Dental+Care/data=!4m7!3m6!1s0x80946753ec35e2bd:0x4d341b7eef98a99f!8m2!3d36.820677!4d-119.780899!16s%2Fg%2F1tl9mtsb!19sChIJveI17FNnlIARn6mY734bNE0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:37.529Z</t>
+  </si>
+  <si>
+    <t>Canyon Family Dental.</t>
+  </si>
+  <si>
+    <t>(855) 925-3858</t>
+  </si>
+  <si>
+    <t>4577 Cesar Chavez Boulevard #102, Fresno, CA 93702</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Canyon+Family+Dental./data=!4m7!3m6!1s0x80945e573b31f529:0xe7e15ea2c932742!8m2!3d36.736517!4d-119.7466581!16s%2Fg%2F1thqb2vf!19sChIJKfUxO1delIARQieTLOoVfg4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:42.136Z</t>
+  </si>
+  <si>
+    <t>Hispano Dental Care Fresno</t>
+  </si>
+  <si>
+    <t>(559) 225-3391</t>
+  </si>
+  <si>
+    <t>2735 N Blackstone Ave, Fresno, CA 93703</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hispano+Dental+Care+Fresno/data=!4m7!3m6!1s0x809467607394e943:0xfeaff1b8f1cc661!8m2!3d36.7752607!4d-119.7911687!16s%2Fg%2F1thml76c!19sChIJQ-mUc2BnlIARYcYcjxv_6g8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:44.836Z</t>
+  </si>
+  <si>
+    <t>Family Dental Care.</t>
+  </si>
+  <si>
+    <t>(559) 251-7191</t>
+  </si>
+  <si>
+    <t>4857 Cesar Chavez Blvd, Fresno, CA 93727</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Dental+Care./data=!4m7!3m6!1s0x80945efb706416a5:0xe60b7ddfc9082ab2!8m2!3d36.7373458!4d-119.7336726!16s%2Fg%2F1tfl0g1k!19sChIJpRZkcPtelIARsioIyd99C-Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:51.925Z</t>
+  </si>
+  <si>
+    <t>Dental Experts</t>
+  </si>
+  <si>
+    <t>(559) 436-1790</t>
+  </si>
+  <si>
+    <t>6246 N First St Ste 102, Fresno, CA 93710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Experts/data=!4m7!3m6!1s0x2b4cb1694caa921b:0xfc257713321cad6c!8m2!3d36.8274532!4d-119.7718832!16s%2Fg%2F11xfrp8p1b!19sChIJG5KqTGmxTCsRbK0cMhN3Jfw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:54.629Z</t>
+  </si>
+  <si>
+    <t>SurabianDentalCenter</t>
+  </si>
+  <si>
+    <t>(559) 459-5725</t>
+  </si>
+  <si>
+    <t>290 N Wayte Ln, Fresno, CA 93741</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/SurabianDentalCenter/data=!4m7!3m6!1s0x80945e1c9f1c7b85:0xb6cb9a1bc76716d7!8m2!3d36.7469728!4d-119.7831866!16s%2Fg%2F11c59nzhwp!19sChIJhXscnxxelIAR1xZnxxuay7Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:36:57.241Z</t>
+  </si>
+  <si>
+    <t>Figarden family dentistry</t>
+  </si>
+  <si>
+    <t>(833) 246-4254</t>
+  </si>
+  <si>
+    <t>4210 W Figarden Dr #101, Fresno, CA 93722</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Figarden+family+dentistry/data=!4m7!3m6!1s0x809468b9064c2c2d:0x7b9ffe2fa1c71cbd!8m2!3d36.8300068!4d-119.8671298!16s%2Fg%2F1pv5x5vn_!19sChIJLSxMBrlolIARvRzHoS_-n3s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:39:24.954Z</t>
+  </si>
+  <si>
+    <t>Dr. Alessandra Desabelle</t>
+  </si>
+  <si>
+    <t>(559) 444-0444</t>
+  </si>
+  <si>
+    <t>1409 N Fresno St, Fresno, CA 93703</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Alessandra+Desabelle/data=!4m7!3m6!1s0x80945dfc1457d3b9:0x6a11a0d861ebb195!8m2!3d36.7617245!4d-119.7818057!16s%2Fg%2F11rwxgjxsx!19sChIJudNXFPxdlIARlbHrYdigEWo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:39:30.256Z</t>
+  </si>
+  <si>
+    <t>Pauline Family Dental Care</t>
+  </si>
+  <si>
+    <t>(559) 249-3322</t>
+  </si>
+  <si>
+    <t>5446 N Palm Ave Ste 109, Fresno, CA 93704</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pauline+Family+Dental+Care/data=!4m7!3m6!1s0x809467ebc9729719:0xe75d1b6b9063fd96!8m2!3d36.8164308!4d-119.8079927!16s%2Fg%2F11wwsf_m72!19sChIJGZdyyetnlIARlv1jkGsbXec?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:39:32.998Z</t>
+  </si>
+  <si>
+    <t>Palm Bluff Dentistry</t>
+  </si>
+  <si>
+    <t>(559) 315-3028</t>
+  </si>
+  <si>
+    <t>7585 N Colonial Ave, Fresno, CA 93711</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Palm+Bluff+Dentistry/data=!4m7!3m6!1s0x809468165fb9398f:0x2b138c80c3b6cf5b!8m2!3d36.8475086!4d-119.8047121!16s%2Fg%2F11c2njxlqv!19sChIJjzm5XxZolIARW8-2w4CMEys?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:39:38.174Z</t>
+  </si>
+  <si>
+    <t>An Lac Dental, Inc.</t>
+  </si>
+  <si>
+    <t>(559) 493-5888</t>
+  </si>
+  <si>
+    <t>5160 N Fresno St #102, Fresno, CA 93710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/An+Lac+Dental,+Inc./data=!4m7!3m6!1s0x80945d642525cb23:0xe09d2382d1f9cd66!8m2!3d36.8115712!4d-119.7811609!16s%2Fg%2F11cn7bp2tv!19sChIJI8slJWRdlIARZs350YIjneA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:39:40.494Z</t>
+  </si>
+  <si>
+    <t>All Smiles Family &amp; Children Dentistry</t>
+  </si>
+  <si>
+    <t>(559) 477-4411</t>
+  </si>
+  <si>
+    <t>4125 E Ventura Ave, Fresno, CA 93702</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/All+Smiles+Family+%26+Children+Dentistry/data=!4m7!3m6!1s0x80945e4542af2f49:0xa1b751fccf2d388b!8m2!3d36.7360576!4d-119.7555791!16s%2Fg%2F11f29_4gdw!19sChIJSS-vQkVelIARizgtz_xRt6E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:40:49.980Z</t>
+  </si>
+  <si>
+    <t>Childrens Dental Surgery Center of Fresno Inc</t>
+  </si>
+  <si>
+    <t>(559) 224-5437</t>
+  </si>
+  <si>
+    <t>Surgical center</t>
+  </si>
+  <si>
+    <t>3796 N Fresno St Ste 103, Fresno, CA 93726</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Childrens+Dental+Surgery+Center+of+Fresno+Inc/data=!4m7!3m6!1s0x80945d8f6d9b4407:0x4bd8327c4791c5a2!8m2!3d36.7865845!4d-119.7812585!16s%2Fg%2F1xgzc0bb!19sChIJB0SbbY9dlIARosWRR3wy2Es?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:40:52.935Z</t>
+  </si>
+  <si>
+    <t>Dr. Kunal Bhakta</t>
+  </si>
+  <si>
+    <t>(559) 299-3949</t>
+  </si>
+  <si>
+    <t>7005 N Chestnut Ave Ste 101, Fresno, CA 93720</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kunal+Bhakta/data=!4m7!3m6!1s0x80945cda1c03b9dd:0x7e01cd6ee2362d82!8m2!3d36.838205!4d-119.7364801!16s%2Fg%2F11sf48dg22!19sChIJ3bkDHNpclIARgi024m7NAX4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:41:00.322Z</t>
+  </si>
+  <si>
+    <t>Dr. Jeffrey B. Evans, DDS</t>
+  </si>
+  <si>
+    <t>(559) 439-5300</t>
+  </si>
+  <si>
+    <t>7525 N Cedar Ave Ste 105, Fresno, CA 93720</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jeffrey+B.+Evans,+DDS/data=!4m7!3m6!1s0x809442cd1cc659e1:0x1de8b205ec89d0ad!8m2!3d36.8449246!4d-119.7573825!16s%2Fg%2F1thsg4xf!19sChIJ4VnGHM1ClIARrdCJ7AWy6B0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:41:07.055Z</t>
+  </si>
+  <si>
+    <t>Dr. Pasqualino Diciccio, DDS</t>
+  </si>
+  <si>
+    <t>(559) 225-2251</t>
+  </si>
+  <si>
+    <t>7055 N Fresno St #302, Fresno, CA 93720</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Pasqualino+Diciccio,+DDS/data=!4m7!3m6!1s0x809442ad0655ca31:0x5ce53406c7788219!8m2!3d36.8386904!4d-119.7819853!16s%2Fg%2F1tlbjtdp!19sChIJMcpVBq1ClIARGYJ4xwY05Vw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:41:23.242Z</t>
+  </si>
+  <si>
+    <t>Hybridge Dental Implants</t>
+  </si>
+  <si>
+    <t>(559) 277-3001</t>
+  </si>
+  <si>
+    <t>6495 N Palm Ave, Fresno, CA 93704</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hybridge+Dental+Implants/data=!4m7!3m6!1s0x8094680ba9700001:0xfe57608bd221f321!8m2!3d36.8318427!4d-119.8089593!16s%2Fg%2F11y2clyzn5!19sChIJAQBwqQtolIARIfMh0otgV_4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:41:39.567Z</t>
+  </si>
+  <si>
+    <t>James Van Volkinburg Inc</t>
+  </si>
+  <si>
+    <t>(559) 439-5280</t>
+  </si>
+  <si>
+    <t>5479 N Fresno St #104, Fresno, CA 93710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/James+Van+Volkinburg+Inc/data=!4m7!3m6!1s0x80945d5dee3a1b97:0x4ad24d2d8cc333f1!8m2!3d36.817442!4d-119.782051!16s%2Fg%2F1tj9c7gb!19sChIJlxs67l1dlIAR8TPDjC1N0ko?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:41:43.917Z</t>
+  </si>
+  <si>
+    <t>Dentista Urgente Hispano Fresno</t>
+  </si>
+  <si>
+    <t>(866) 228-3130</t>
+  </si>
+  <si>
+    <t>535 N Cedar Ave, Fresno, CA 93702</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentista+Urgente+Hispano+Fresno/data=!4m7!3m6!1s0x80945fb42ef9869d:0xdc2ff55003c485d4!8m2!3d36.7511367!4d-119.7547821!16s%2Fg%2F11nnsb_cm0!19sChIJnYb5LrRflIAR1IXEA1D1L9w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:42:02.329Z</t>
+  </si>
+  <si>
+    <t>Emergency Dental Fresno</t>
+  </si>
+  <si>
+    <t>(559) 206-8920</t>
+  </si>
+  <si>
+    <t>920 F St, Fresno, CA 93706</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dental+Fresno/data=!4m7!3m6!1s0x8094612afefd4499:0x1e87180c1646bab4!8m2!3d36.7299042!4d-119.7939677!16s%2Fg%2F11r98_0lcy!19sChIJmUT9_iphlIARtLpGFgwYhx4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:42:05.516Z</t>
+  </si>
+  <si>
+    <t>Prime Urgent Dental</t>
+  </si>
+  <si>
+    <t>(559) 745-1272</t>
+  </si>
+  <si>
+    <t>1717 Van Ness Ave, Fresno, CA 93721</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Prime+Urgent+Dental/data=!4m7!3m6!1s0x8094611052e2317d:0xbbf64e59b10a83fa!8m2!3d36.7418411!4d-119.7972823!16s%2Fg%2F11vt646r2z!19sChIJfTHiUhBhlIAR-oMKsVlO9rs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:42:08.590Z</t>
+  </si>
+  <si>
+    <t>Quick Dental Service</t>
+  </si>
+  <si>
+    <t>(559) 340-5412</t>
+  </si>
+  <si>
+    <t>2160 S Fine Ave, Fresno, CA 93725</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Quick+Dental+Service/data=!4m7!3m6!1s0x80945ff855c4425f:0x77908abf95c21faf!8m2!3d36.7122351!4d-119.7293331!16s%2Fg%2F11zf5_0hm7!19sChIJX0LEVfhflIARrx_Clb-KkHc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:42:13.703Z</t>
+  </si>
+  <si>
+    <t>Top Emergency Dentistry</t>
+  </si>
+  <si>
+    <t>(559) 282-4432</t>
+  </si>
+  <si>
+    <t>2120 Mono St, Fresno, CA 93721</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Top+Emergency+Dentistry/data=!4m7!3m6!1s0x80945f07b42ca2d7:0xff997ddc35105b5b!8m2!3d36.7317675!4d-119.7853898!16s%2Fg%2F11m71_68wt!19sChIJ16IstAdflIARW1sQNdx9mf8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:42:16.635Z</t>
+  </si>
+  <si>
+    <t>Sorensen Jason D.D.S. Oral &amp; Maxillofacial Surgery</t>
+  </si>
+  <si>
+    <t>(559) 447-0544</t>
+  </si>
+  <si>
+    <t>1480 W Herndon Ave, Fresno, CA 93711</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sorensen+Jason+D.D.S.+Oral+%26+Maxillofacial+Surgery/data=!4m7!3m6!1s0x8094686e5cddde59:0x3d08168c5e594383!8m2!3d36.837771!4d-119.819516!16s%2Fg%2F1tdy99hm!19sChIJWd7dXG5olIARg0NZXowWCD0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:43:48.206Z</t>
+  </si>
+  <si>
+    <t>Central California Oral &amp; Maxillofacial Surgery</t>
+  </si>
+  <si>
+    <t>(559) 431-4220</t>
+  </si>
+  <si>
+    <t>7585 N Colonial Ave #105, Fresno, CA 93711</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Central+California+Oral+%26+Maxillofacial+Surgery/data=!4m7!3m6!1s0x80945d4bba9b3503:0xcfd1a4a955c8efbd!8m2!3d36.8474765!4d-119.8047363!16s%2Fg%2F1tfv0ss_!19sChIJAzWbuktdlIARve_IVamk0c8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:43:51.354Z</t>
+  </si>
+  <si>
+    <t>Jackson Sidney L DDS</t>
+  </si>
+  <si>
+    <t>(559) 447-3003</t>
+  </si>
+  <si>
+    <t>7433 N First St #101, Fresno, CA 93720</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jackson+Sidney+L+DDS/data=!4m7!3m6!1s0x809442b1adbe4631:0x41efa761746e82f3!8m2!3d36.8455997!4d-119.7751997!16s%2Fg%2F1tg6vylj!19sChIJMUa-rbFClIAR84JudGGn70E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:43:53.276Z</t>
+  </si>
+  <si>
+    <t>Dr. Hadi D. Hamdan, DDS</t>
+  </si>
+  <si>
+    <t>(559) 490-1326</t>
+  </si>
+  <si>
+    <t>1255 W Shields Ave, Fresno, CA 93705</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–4:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Hadi+D.+Hamdan,+DDS/data=!4m7!3m6!1s0x80946705cbf9f34d:0x9196980eb435dc6!8m2!3d36.7790442!4d-119.8262328!16s%2Fg%2F1v3gs4dc!19sChIJTfP5ywVnlIARxl1D64BpGQk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:43:55.520Z</t>
+  </si>
+  <si>
+    <t>Forester Dental</t>
+  </si>
+  <si>
+    <t>(559) 432-1300</t>
+  </si>
+  <si>
+    <t>7525 N Cedar Ave Unit 117, Fresno, CA 93720</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Forester+Dental/data=!4m7!3m6!1s0x809442cd1cc65981:0x8487db7e56e46a98!8m2!3d36.8454595!4d-119.7570228!16s%2Fg%2F1tgf3g79!19sChIJgVnGHM1ClIARmGrkVn7bh4Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:43:58.615Z</t>
+  </si>
+  <si>
+    <t>Donald J Kinosian Inc</t>
+  </si>
+  <si>
+    <t>(559) 299-0251</t>
+  </si>
+  <si>
+    <t>334 Shaw Ave #111, Clovis, CA 93612</t>
+  </si>
+  <si>
+    <t>Clovis</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Donald+J+Kinosian+Inc/data=!4m7!3m6!1s0x80945c7080f8d25f:0x6659ca1e59776dc7!8m2!3d36.8081398!4d-119.7049713!16s%2Fg%2F1tctm0nb!19sChIJX9L4gHBclIARx213WR7KWWY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:01.728Z</t>
+  </si>
+  <si>
+    <t>Nuova Dental Office</t>
+  </si>
+  <si>
+    <t>(916) 594-9474</t>
+  </si>
+  <si>
+    <t>925 Secret River Dr # J, Sacramento, CA 95831</t>
+  </si>
+  <si>
+    <t>Sacramento</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nuova+Dental+Office/data=!4m7!3m6!1s0x809acf74fcfb0efb:0x22e8de827ea06232!8m2!3d38.4949792!4d-121.5251046!16s%2Fg%2F11vwxvd1l3!19sChIJ-w77_HTPmoARMmKgfoLe6CI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:20.064Z</t>
+  </si>
+  <si>
+    <t>Signature Dental</t>
+  </si>
+  <si>
+    <t>(916) 515-1588</t>
+  </si>
+  <si>
+    <t>1942 Del Paso Rd Ste 132, Sacramento, CA 95834</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Signature+Dental/data=!4m7!3m6!1s0x809ad623c6a54c11:0x8004becdee848c43!8m2!3d38.6552729!4d-121.5055557!16s%2Fg%2F1t_hz75c!19sChIJEUylxiPWmoARQ4yE7s2-BIA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:23.083Z</t>
+  </si>
+  <si>
+    <t>Santa Cruz Palm Dental</t>
+  </si>
+  <si>
+    <t>(916) 391-7525</t>
+  </si>
+  <si>
+    <t>7275 E Southgate Dr #110, Sacramento, CA 95823</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Santa+Cruz+Palm+Dental/data=!4m7!3m6!1s0x809ac57a31d0d6a7:0x79f111c362b88d3c!8m2!3d38.4933928!4d-121.4362435!16s%2Fg%2F1v9409nt!19sChIJp9bQMXrFmoARPI24YsMR8Xk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:25.547Z</t>
+  </si>
+  <si>
+    <t>Vintage Park Dental</t>
+  </si>
+  <si>
+    <t>(916) 682-2000</t>
+  </si>
+  <si>
+    <t>8065 Elk Grove Florin Rd #110, Sacramento, CA 95829</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vintage+Park+Dental/data=!4m7!3m6!1s0x809ac6a41b5e6405:0xcbc735f0c3f2cddf!8m2!3d38.4647448!4d-121.3704873!16s%2Fg%2F1hc72n942!19sChIJBWReG6TGmoAR383yw_A1x8s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:28.242Z</t>
+  </si>
+  <si>
+    <t>Star Dental Practice</t>
+  </si>
+  <si>
+    <t>(916) 993-9207</t>
+  </si>
+  <si>
+    <t>1620 W El Camino Ave #170, Sacramento, CA 95833</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Star+Dental+Practice/data=!4m7!3m6!1s0x809ad6fb3232c2f5:0x26b0efbd5b80173f!8m2!3d38.6120564!4d-121.4986132!16s%2Fg%2F11f4ldjzts!19sChIJ9cIyMvvWmoARPxeAW73vsCY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:30.551Z</t>
+  </si>
+  <si>
+    <t>Pocket Dental</t>
+  </si>
+  <si>
+    <t>(916) 428-5318</t>
+  </si>
+  <si>
+    <t>905 Secret River Dr # A, Sacramento, CA 95831</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pocket+Dental/data=!4m7!3m6!1s0x809ace0354075021:0xee3e3e60a790e9fb!8m2!3d38.4950478!4d-121.5259136!16s%2Fg%2F11cmmb3sdk!19sChIJIVAHVAPOmoAR--mQp2A-Pu4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:32.999Z</t>
+  </si>
+  <si>
+    <t>Dental Clinic</t>
+  </si>
+  <si>
+    <t>(916) 481-1111</t>
+  </si>
+  <si>
+    <t>3517 Marconi Ave, Sacramento, CA 95821</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Clinic/data=!4m7!3m6!1s0x809adbdf5846d4c7:0x38e39bc790504022!8m2!3d38.6181936!4d-121.3818136!16s%2Fg%2F11b6_6v9_l!19sChIJx9RGWN_bmoARIkBQkMeb4zg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:44:35.876Z</t>
+  </si>
+  <si>
+    <t>Sacramento Family Dentistry</t>
+  </si>
+  <si>
+    <t>(279) 399-3010</t>
+  </si>
+  <si>
+    <t>7030 East Pkwy, Sacramento, CA 95823</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sacramento+Family+Dentistry/data=!4m7!3m6!1s0x809ac57082cba4fd:0xefa6ffe7801e24da!8m2!3d38.498506!4d-121.4511162!16s%2Fg%2F1tksnm7h!19sChIJ_aTLgnDFmoAR2iQegOf_pu8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:45:51.998Z</t>
+  </si>
+  <si>
+    <t>North Natomas Family Dentistry: Pham Quynh-Trang DDS</t>
+  </si>
+  <si>
+    <t>(916) 419-8777</t>
+  </si>
+  <si>
+    <t>4261 Truxel Rd # A3, Sacramento, CA 95834</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/North+Natomas+Family+Dentistry:+Pham+Quynh-Trang+DDS/data=!4m7!3m6!1s0x809ad6239c332f1d:0x7bfd29bf11e3228b!8m2!3d38.648688!4d-121.5105245!16s%2Fg%2F1tfzxr76!19sChIJHS8znCPWmoARiyLjEb8p_Xs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:45:59.238Z</t>
+  </si>
+  <si>
+    <t>Therese L OBrien DDS Inc.</t>
+  </si>
+  <si>
+    <t>(916) 447-3600</t>
+  </si>
+  <si>
+    <t>2409 L St #2, Sacramento, CA 95816</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Therese+L+OBrien+DDS+Inc./data=!4m7!3m6!1s0x809ad0c23b2938eb:0xf46f14f79d38fd71!8m2!3d38.5731954!4d-121.4750956!16s%2Fg%2F1v2gd_tb!19sChIJ6zgpO8LQmoARcf04nfcUb_Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:46:02.594Z</t>
+  </si>
+  <si>
+    <t>Pioneer Family Dental</t>
+  </si>
+  <si>
+    <t>(916) 689-3310</t>
+  </si>
+  <si>
+    <t>7850 Stockton Blvd #160, Sacramento, CA 95823</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pioneer+Family+Dental/data=!4m7!3m6!1s0x809ac5c086277da7:0x8e8694404790a297!8m2!3d38.4736161!4d-121.4196671!16s%2Fg%2F1thn5rvl!19sChIJp30nhsDFmoARl6KQR0CUho4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:46:05.227Z</t>
+  </si>
+  <si>
+    <t>Dr. Luzminda Corpuz DMD Modern Family Dental</t>
+  </si>
+  <si>
+    <t>(916) 928-9300</t>
+  </si>
+  <si>
+    <t>3711 Truxel Rd #1, Sacramento, CA 95834</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Luzminda+Corpuz+DMD+Modern+Family+Dental/data=!4m7!3m6!1s0x809ad6389c6963c3:0xdcc47e5e90d2ae4e!8m2!3d38.6381205!4d-121.5063636!16s%2Fg%2F1thcn09n!19sChIJw2NpnDjWmoARTq7SkF5-xNw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:46:07.661Z</t>
+  </si>
+  <si>
+    <t>Sacramento Dentist DDS</t>
+  </si>
+  <si>
+    <t>(279) 399-2880</t>
+  </si>
+  <si>
+    <t>1624 K St, Sacramento, CA 95814</t>
+  </si>
+  <si>
+    <t>Saturday6 AM–9 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sacramento+Dentist+DDS/data=!4m7!3m6!1s0x809ad0ea219af293:0xa614b2baf571039b!8m2!3d38.5766496!4d-121.4849362!16s%2Fg%2F1tdp58zf!19sChIJk_KaIerQmoARmwNx9bqyFKY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:46:12.460Z</t>
+  </si>
+  <si>
+    <t>Elkhorn Family Dental</t>
+  </si>
+  <si>
+    <t>(916) 344-5553</t>
+  </si>
+  <si>
+    <t>5315 Elkhorn Blvd, Sacramento, CA 95842</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Elkhorn+Family+Dental/data=!4m7!3m6!1s0x809adf3814da4619:0x5b4dda8e0a059b8f!8m2!3d38.6873501!4d-121.3408289!16s%2Fg%2F1tf7mtlf!19sChIJGUbaFDjfmoARj5sFCo7aTVs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:46:15.358Z</t>
+  </si>
+  <si>
+    <t>Ralph J. Isola, DDS</t>
+  </si>
+  <si>
+    <t>(916) 737-1155</t>
+  </si>
+  <si>
+    <t>5700 J St Suite #B, Sacramento, CA 95819</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ralph+J.+Isola,+DDS/data=!4m7!3m6!1s0x809ada880d78db93:0xe519e23b362662f4!8m2!3d38.564019!4d-121.433464!16s%2Fg%2F1w0p5wnt!19sChIJk9t4DYjamoAR9GImNjviGeU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:47:50.449Z</t>
+  </si>
+  <si>
+    <t>Apple Periodontics &amp; dental Implants</t>
+  </si>
+  <si>
+    <t>(916) 917-5057</t>
+  </si>
+  <si>
+    <t>717 13th St A, Sacramento, CA 95814</t>
+  </si>
+  <si>
+    <t>SaturdayOpen 24 hours; SundayOpen 24 hours; MondayOpen 24 hours; TuesdayOpen 24 hours; WednesdayOpen 24 hours; ThursdayOpen 24 hours; FridayOpen 24 hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Apple+Periodontics+%26+dental+Implants/data=!4m7!3m6!1s0x809ad0d683575643:0x8dcdbf964ffae00e!8m2!3d38.5817536!4d-121.4878031!16s%2Fg%2F11cs1smgg1!19sChIJQ1ZXg9bQmoARDuD6T5a_zY0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:48:19.644Z</t>
+  </si>
+  <si>
+    <t>Dentist Hispano Sacramento Urgente</t>
+  </si>
+  <si>
+    <t>(916) 885-0807</t>
+  </si>
+  <si>
+    <t>2530 J St, Sacramento, CA 95816</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentist+Hispano+Sacramento+Urgente/data=!4m7!3m6!1s0x809ad19e125e6347:0x9565840c7b2d6a00!8m2!3d38.5744324!4d-121.4721504!16s%2Fg%2F11rfmncy65!19sChIJR2NeEp7RmoARAGotewyEZZU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:49:15.677Z</t>
+  </si>
+  <si>
+    <t>Sacramento Dental Care</t>
+  </si>
+  <si>
+    <t>(279) 255-1313</t>
+  </si>
+  <si>
+    <t>200 P St, Sacramento, CA 95814</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–9 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sacramento+Dental+Care/data=!4m7!3m6!1s0x809ad14d0873224b:0xcc17aeaef3e32c50!8m2!3d38.5760266!4d-121.5075142!16s%2Fg%2F1tdv_3zz!19sChIJSyJzCE3RmoARUCzj866uF8w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:49:30.421Z</t>
+  </si>
+  <si>
+    <t>Dental Group</t>
+  </si>
+  <si>
+    <t>(916) 442-5228</t>
+  </si>
+  <si>
+    <t>1111 24th St #204, Sacramento, CA 95816</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Group/data=!4m7!3m6!1s0x809ad1003198c57f:0x42ad0d8e3e276a9a!8m2!3d38.5738109!4d-121.4749757!16s%2Fg%2F11y93prtq3!19sChIJf8WYMQDRmoARmmonPo4NrUI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:49:32.923Z</t>
+  </si>
+  <si>
+    <t>Encore Dental Services</t>
+  </si>
+  <si>
+    <t>(916) 421-1010</t>
+  </si>
+  <si>
+    <t>2378 Fruitridge Rd, Sacramento, CA 95822</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Encore+Dental+Services/data=!4m7!3m6!1s0x809ad03111729e33:0x771983fd99c8eb9f!8m2!3d38.5243931!4d-121.4837794!16s%2Fg%2F1th825pk!19sChIJM55yETHQmoARn-vImf2DGXc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:49:35.689Z</t>
+  </si>
+  <si>
+    <t>McEwen Dental</t>
+  </si>
+  <si>
+    <t>(916) 567-9707</t>
+  </si>
+  <si>
+    <t>730 Howe Ave #200, Sacramento, CA 95825</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/McEwen+Dental/data=!4m7!3m6!1s0x809adbd6b0b5a39b:0xefef322a328d4e9!8m2!3d38.5788515!4d-121.4145051!16s%2Fg%2F1thw_ptv!19sChIJm6O1sNbbmoAR6dQooyLz_g4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:49:53.738Z</t>
+  </si>
+  <si>
+    <t>Heidiologi &amp; Co.</t>
+  </si>
+  <si>
+    <t>(916) 704-4782</t>
+  </si>
+  <si>
+    <t>3560 J St Ste B, Sacramento, CA 95816</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Heidiologi+%26+Co./data=!4m7!3m6!1s0x809adb04592f756d:0x38b9bdcc34830954!8m2!3d38.570757!4d-121.4585552!16s%2Fg%2F11zjl66sv6!19sChIJbXUvWQTbmoARVAmDNMy9uTg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:50:05.963Z</t>
+  </si>
+  <si>
+    <t>Matthew Korn</t>
+  </si>
+  <si>
+    <t>(916) 446-9100</t>
+  </si>
+  <si>
+    <t>2830 G St #100, Sacramento, CA 958163784</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Matthew+Korn/data=!4m7!3m6!1s0x809ad0bf0ae3a211:0x1e3fcb814f3e3bc6!8m2!3d38.5765506!4d-121.4669145!16s%2Fg%2F11sh2cd7kb!19sChIJEaLjCr_QmoARxjs-T4HLPx4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:50:23.985Z</t>
+  </si>
+  <si>
+    <t>Natomas Periodontics &amp; Implantology/Ching-Yin Tsai DDS, MS</t>
+  </si>
+  <si>
+    <t>(916) 515-0008</t>
+  </si>
+  <si>
+    <t>1948 Del Paso Rd Ste 138, Sacramento, CA 95834</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Natomas+Periodontics+%26+Implantology%2FChing-Yin+Tsai+DDS,+MS/data=!4m7!3m6!1s0x809ad6237b1f2657:0x883925561c17bd4e!8m2!3d38.6546139!4d-121.5054343!16s%2Fg%2F1th28ngn!19sChIJVyYfeyPWmoARTr0XHFYlOYg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:50:26.544Z</t>
+  </si>
+  <si>
+    <t>Dr. Jonathan C. Szymanowski, DMD</t>
+  </si>
+  <si>
+    <t>(916) 929-5052</t>
+  </si>
+  <si>
+    <t>99 Scripps Dr STE 200, Sacramento, CA 95825</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jonathan+C.+Szymanowski,+DMD/data=!4m7!3m6!1s0x809ada58174a8dc9:0x623931cc480287de!8m2!3d38.5716976!4d-121.4092322!16s%2Fg%2F12m9fvmqy!19sChIJyY1KF1jamoAR3ocCSMwxOWI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:50:31.522Z</t>
+  </si>
+  <si>
+    <t>Dr. Pedram P. Towfighi, DDS</t>
+  </si>
+  <si>
+    <t>(916) 971-3461</t>
+  </si>
+  <si>
+    <t>1810 Professional Dr B, Sacramento, CA 95825</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Pedram+P.+Towfighi,+DDS/data=!4m7!3m6!1s0x809adbc78bb71f87:0x2483365ff6590555!8m2!3d38.598016!4d-121.386709!16s%2Fg%2F1tf60jvk!19sChIJhx-3i8fbmoARVQVZ9l82gyQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:50:42.325Z</t>
+  </si>
+  <si>
+    <t>Sarmad Paydar</t>
+  </si>
+  <si>
+    <t>(916) 834-6837</t>
+  </si>
+  <si>
+    <t>1017 L St, Sacramento, CA 95814</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sarmad+Paydar/data=!4m7!3m6!1s0x809ad1284d37869d:0x37d9847c60ce16a0!8m2!3d38.5779595!4d-121.4933614!16s%2Fg%2F11sd2ymnh7!19sChIJnYY3TSjRmoARoBbOYHyE2Tc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:50:45.017Z</t>
+  </si>
+  <si>
+    <t>Healthy Smile Dental Care</t>
+  </si>
+  <si>
+    <t>(510) 451-9100</t>
+  </si>
+  <si>
+    <t>1904 Franklin St #810, Oakland, CA 94612</t>
+  </si>
+  <si>
+    <t>Oakland</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Healthy+Smile+Dental+Care/data=!4m7!3m6!1s0x808f80b2f03f0945:0xdc2923ff37cd6670!8m2!3d37.8073226!4d-122.267425!16s%2Fg%2F1txnppty!19sChIJRQk_8LKAj4ARcGbNN_8jKdw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:51:02.255Z</t>
+  </si>
+  <si>
+    <t>Union Dental</t>
+  </si>
+  <si>
+    <t>(510) 430-9388</t>
+  </si>
+  <si>
+    <t>433 Hegenberger Rd, Oakland, CA 94621</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Union+Dental/data=!4m7!3m6!1s0x808f85bd71d98bdb:0xea67c8d1386846c0!8m2!3d37.7369715!4d-122.1984983!16s%2Fg%2F1tk_jyv2!19sChIJ24vZcb2Fj4ARwEZoONHIZ-o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:52:28.304Z</t>
+  </si>
+  <si>
+    <t>West Oakland Health Center: Smith Merritt DDS</t>
+  </si>
+  <si>
+    <t>(510) 430-9401</t>
+  </si>
+  <si>
+    <t>7450 International Blvd #7450, Oakland, CA 94621</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+Oakland+Health+Center:+Smith+Merritt+DDS/data=!4m7!3m6!1s0x808f85fab150a6c7:0x9013f34196ce7792!8m2!3d37.7588783!4d-122.1856043!16s%2Fg%2F1tnmrzc2!19sChIJx6ZQsfqFj4ARknfOlkHzE5A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:52:36.937Z</t>
+  </si>
+  <si>
+    <t>Dr. Draak Davis Family Dental.</t>
+  </si>
+  <si>
+    <t>(510) 465-5555</t>
+  </si>
+  <si>
+    <t>1624 Franklin St #1206, Oakland, CA 94612</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Draak+Davis+Family+Dental./data=!4m7!3m6!1s0x808f80b3a79e90c1:0x36850839ec0392e2!8m2!3d37.8056442!4d-122.268134!16s%2Fg%2F1ptvwqv_6!19sChIJwZCep7OAj4AR4pID7DkIhTY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:54:03.299Z</t>
+  </si>
+  <si>
+    <t>Dr. Dung Q. Pham, DDS.</t>
+  </si>
+  <si>
+    <t>(510) 444-4808</t>
+  </si>
+  <si>
+    <t>300 12th St, Oakland, CA 94607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Dung+Q.+Pham,+DDS./data=!4m7!3m6!1s0x808f80b5aba12a87:0x36c931a9545aed48!8m2!3d37.8023557!4d-122.2692669!16s%2Fg%2F1tj46465!19sChIJhyqhq7WAj4ARSO1aVKkxyTY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:54:05.848Z</t>
+  </si>
+  <si>
+    <t>Cosmetic Dentist SF</t>
+  </si>
+  <si>
+    <t>(510) 601-7605</t>
+  </si>
+  <si>
+    <t>3300 Webster St #903, Oakland, CA 94609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cosmetic+Dentist+SF/data=!4m7!3m6!1s0x80857dff76aac097:0x338ae5959f5eea9d!8m2!3d37.8211014!4d-122.261563!16s%2Fg%2F11ddyj1d66!19sChIJl8Cqdv99hYARnepen5XlijM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:54:25.284Z</t>
+  </si>
+  <si>
+    <t>Dentistry For Children</t>
+  </si>
+  <si>
+    <t>(510) 568-8178</t>
+  </si>
+  <si>
+    <t>8201 Edgewater Dr Ste 105106, Oakland, CA 94621</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentistry+For+Children/data=!4m7!3m6!1s0x808f85bc2eee43dd:0xd7912f70e8b42456!8m2!3d37.7385126!4d-122.2007806!16s%2Fg%2F1td0yq3t!19sChIJ3UPuLryFj4ARViS06HAvkdc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:54:40.288Z</t>
+  </si>
+  <si>
+    <t>Dr. Brian Trinh DDS</t>
+  </si>
+  <si>
+    <t>(510) 836-4811</t>
+  </si>
+  <si>
+    <t>1624 Franklin St Unit 910, Oakland, CA 94612</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Brian+Trinh+DDS/data=!4m7!3m6!1s0x808f80b3a7990d7b:0x4ac51dc0677386b9!8m2!3d37.8058065!4d-122.2683037!16s%2Fg%2F1tjbsdgt!19sChIJew2Zp7OAj4ARuYZzZ8AdxUo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:54:45.641Z</t>
+  </si>
+  <si>
+    <t>Edward Rothman, DDS</t>
+  </si>
+  <si>
+    <t>(510) 428-3316</t>
+  </si>
+  <si>
+    <t>747 52nd St, Oakland, CA 94609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Edward+Rothman,+DDS/data=!4m7!3m6!1s0x80857e0ad08c4db7:0xc22c8a751c9018e0!8m2!3d37.8369!4d-122.267!16s%2Fg%2F1vjdq8xh!19sChIJt02M0Ap-hYAR4BiQHHWKLMI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:54:48.712Z</t>
+  </si>
+  <si>
+    <t>Dr. Timothy H. Han, DDS</t>
+  </si>
+  <si>
+    <t>(510) 839-2045</t>
+  </si>
+  <si>
+    <t>320 13th St Ste 250, Oakland, CA 94612</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Timothy+H.+Han,+DDS/data=!4m7!3m6!1s0x808f80b4594da807:0x64c709a15c823664!8m2!3d37.8025588!4d-122.268486!16s%2Fg%2F1tplkzd4!19sChIJB6hNWbSAj4ARZDaCXKEJx2Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:55:11.043Z</t>
+  </si>
+  <si>
+    <t>Joanne V. Lagos, DDS, MSPH</t>
+  </si>
+  <si>
+    <t>(510) 444-0583</t>
+  </si>
+  <si>
+    <t>195 Perry Pl, Oakland, CA 94610</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Joanne+V.+Lagos,+DDS,+MSPH/data=!4m7!3m6!1s0x808f875a13182701:0xfb72bfe9fce230e4!8m2!3d37.8172375!4d-122.2530801!16s%2Fg%2F1thk8zzc!19sChIJAScYE1qHj4AR5DDi_Om_cvs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:55:16.110Z</t>
+  </si>
+  <si>
+    <t>Bay Area Dental Specialty Group</t>
+  </si>
+  <si>
+    <t>(510) 533-1123</t>
+  </si>
+  <si>
+    <t>3301 E 12th St #163, Oakland, CA 94601</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bay+Area+Dental+Specialty+Group/data=!4m7!3m6!1s0x808f86f4bde97c5f:0x466bca84054a0002!8m2!3d37.776124!4d-122.2249103!16s%2Fg%2F1th5jptr!19sChIJX3zpvfSGj4ARAgBKBYTKa0Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:55:41.559Z</t>
+  </si>
+  <si>
+    <t>Brandon Kang, DDS</t>
+  </si>
+  <si>
+    <t>(239) 675-0688</t>
+  </si>
+  <si>
+    <t>Oral and maxillofacial surgeon</t>
+  </si>
+  <si>
+    <t>2961 Summit St Ste A, Oakland, CA 94609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brandon+Kang,+DDS/data=!4m7!3m6!1s0x808f87906b1c74eb:0x9048e16a1c9fb7ff!8m2!3d37.8187092!4d-122.2650135!16s%2Fg%2F11jp1ffj2p!19sChIJ63Qca5CHj4AR_7efHGrhSJA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:55:53.284Z</t>
+  </si>
+  <si>
+    <t>Emergency Dental Line</t>
+  </si>
+  <si>
+    <t>(510) 800-7016</t>
+  </si>
+  <si>
+    <t>2595 Telegraph Ave, Berkeley, CA 94704</t>
+  </si>
+  <si>
+    <t>Berkeley</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dental+Line/data=!4m7!3m6!1s0x80857d4880ae63c1:0xfa158d7de621f5a1!8m2!3d37.8635205!4d-122.2584098!16s%2Fg%2F11zf8ln_q5!19sChIJwWOugEh9hYARofUh5n2NFfo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:56:05.926Z</t>
+  </si>
+  <si>
+    <t>Oakland Dental Group</t>
+  </si>
+  <si>
+    <t>(510) 893-5708</t>
+  </si>
+  <si>
+    <t>388 9th St STE 210, Oakland, CA 94607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Oakland+Dental+Group/data=!4m7!3m6!1s0x808f80b67d7d1c95:0xd315dfd381742319!8m2!3d37.8002809!4d-122.2711915!16s%2Fg%2F11hbpwz_8v!19sChIJlRx9fbaAj4ARGSN0gdPfFdM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:56:32.906Z</t>
+  </si>
+  <si>
+    <t>Breeze Smile Dental | Dentist Solutions</t>
+  </si>
+  <si>
+    <t>(858) 437-6103</t>
+  </si>
+  <si>
+    <t>2144 Poplar St, Oakland, CA 94607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Breeze+Smile+Dental+%7C+Dentist+Solutions/data=!4m7!3m6!1s0x80857f30c0baf4b1:0x32a67e8ea7014726!8m2!3d37.8159729!4d-122.2869651!16s%2Fg%2F11zdb_m0b4!19sChIJsfS6wDB_hYARJkcBp45-pjI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:56:56.280Z</t>
+  </si>
+  <si>
+    <t>Nice Dental: Wang Shiyu DDS</t>
+  </si>
+  <si>
+    <t>(510) 534-7600</t>
+  </si>
+  <si>
+    <t>3022 International Blvd, Oakland, CA 94601</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nice+Dental:+Wang+Shiyu+DDS/data=!4m7!3m6!1s0x808f86f161545547:0x6057ef5513bd573a!8m2!3d37.7786453!4d-122.2275241!16s%2Fg%2F1tcyxnmy!19sChIJR1VUYfGGj4AROle9E1XvV2A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:57:00.911Z</t>
+  </si>
+  <si>
+    <t>Geraci Timothy F DDS</t>
+  </si>
+  <si>
+    <t>(510) 465-4060</t>
+  </si>
+  <si>
+    <t>3300 Webster St #905, Oakland, CA 94609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Geraci+Timothy+F+DDS/data=!4m7!3m6!1s0x80857dff0d3119e5:0x7da1a5decac3643f!8m2!3d37.8211303!4d-122.2620467!16s%2Fg%2F1tfc27cp!19sChIJ5RkxDf99hYARP2TDyt6loX0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:57:20.592Z</t>
+  </si>
+  <si>
+    <t>Dr. Yn-Low H. Wu, DDS</t>
+  </si>
+  <si>
+    <t>(510) 763-3711</t>
+  </si>
+  <si>
+    <t>3334 Webster St, Oakland, CA 94609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Yn-Low+H.+Wu,+DDS/data=!4m7!3m6!1s0x80857dff6d48566d:0x4189b2d02d13377!8m2!3d37.8215689!4d-122.2618601!16s%2Fg%2F1vtqwb0j!19sChIJbVZIbf99hYARdzPRAi2bGAQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:57:23.515Z</t>
+  </si>
+  <si>
+    <t>Bruce Gretchen J DDS</t>
+  </si>
+  <si>
+    <t>(510) 268-8838</t>
+  </si>
+  <si>
+    <t>1624 Franklin St #320, Oakland, CA 94612</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday9 AM–5 PM; TuesdayClosed; WednesdayClosed; ThursdayClosed; FridayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bruce+Gretchen+J+DDS/data=!4m7!3m6!1s0x808f80b3a7990d7b:0x8b1bbf97808aa8b7!8m2!3d37.8058065!4d-122.2683037!16s%2Fg%2F1tnpl72q!19sChIJew2Zp7OAj4ARt6iKgJe_G4s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:57:27.372Z</t>
+  </si>
+  <si>
+    <t>Davis Lowell B DDS</t>
+  </si>
+  <si>
+    <t>(510) 834-3414</t>
+  </si>
+  <si>
+    <t>2844 Summit St #202, Oakland, CA 94609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Davis+Lowell+B+DDS/data=!4m7!3m6!1s0x808f875520e29cf7:0xfb82aeca4556a593!8m2!3d37.8174696!4d-122.2640835!16s%2Fg%2F1vysws3g!19sChIJ95ziIFWHj4ARk6VWRcqugvs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:57:30.621Z</t>
+  </si>
+  <si>
+    <t>Dr. Harry Lin, DDS</t>
+  </si>
+  <si>
+    <t>(510) 839-1986</t>
+  </si>
+  <si>
+    <t>933 Jackson St, Oakland, CA 94607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Harry+Lin,+DDS/data=!4m7!3m6!1s0x808f80ca93d892f3:0x9267e389b1f54adc!8m2!3d37.7987865!4d-122.2674261!16s%2Fg%2F1tg4lmcd!19sChIJ85LYk8qAj4AR3Er1sYnjZ5I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:57:33.813Z</t>
+  </si>
+  <si>
+    <t>Pirnazar Noushin DDS</t>
+  </si>
+  <si>
+    <t>(510) 654-2226</t>
+  </si>
+  <si>
+    <t>4185 Piedmont Ave, Oakland, CA 94611</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pirnazar+Noushin+DDS/data=!4m7!3m6!1s0x80857def2c01df6b:0x5addd5a9e8f791f6!8m2!3d37.8375157!4d-122.2515854!16s%2Fg%2F1hc5q33p_!19sChIJa98BLO99hYAR9pH36KnV3Vo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:57:37.173Z</t>
+  </si>
+  <si>
+    <t>South California Dental Practice</t>
+  </si>
+  <si>
+    <t>(209) 941-0814</t>
+  </si>
+  <si>
+    <t>20 S S California St, Stockton, CA 95202</t>
+  </si>
+  <si>
+    <t>Stockton</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/South+California+Dental+Practice/data=!4m7!3m6!1s0x809012a2948d0cab:0x2500aa14df57f995!8m2!3d37.9532211!4d-121.2841616!16s%2Fg%2F1thtpvcg!19sChIJqwyNlKISkIARlflX3xSqACU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:57:58.441Z</t>
+  </si>
+  <si>
+    <t>William Low Family Dental</t>
+  </si>
+  <si>
+    <t>(888) 483-3192</t>
+  </si>
+  <si>
+    <t>1341 N El Dorado St, Stockton, CA 95202</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/William+Low+Family+Dental/data=!4m7!3m6!1s0x80900d002eca007d:0x7b1555a6a262e82e!8m2!3d37.9663043!4d-121.293708!16s%2Fg%2F11yxn2lpgs!19sChIJfQDKLgANkIARLuhioqZVFXs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:58:01.216Z</t>
+  </si>
+  <si>
+    <t>Charter Way Dental</t>
+  </si>
+  <si>
+    <t>(209) 948-8400</t>
+  </si>
+  <si>
+    <t>5 W Yokuts Ave, Stockton, CA 95207</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Charter+Way+Dental/data=!4m7!3m6!1s0x80900cf8e63db4f9:0x1686a6f251c7e268!8m2!3d37.998871!4d-121.3061324!16s%2Fg%2F1262xpsq7!19sChIJ-bQ95vgMkIARaOLHUfKmhhY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:58:03.969Z</t>
+  </si>
+  <si>
+    <t>Clínica Dental Familiar en Español</t>
+  </si>
+  <si>
+    <t>(209) 763-6801</t>
+  </si>
+  <si>
+    <t>3400 CA-99, Stockton, CA 95215</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cl%C3%ADnica+Dental+Familiar+en+Espa%C3%B1ol/data=!4m7!3m6!1s0x80906d3d6701a33b:0xb3acf3abce0dd5fe!8m2!3d37.9268511!4d-121.2305196!16s%2Fg%2F11rg9kzv1h!19sChIJO6MBZz1tkIAR_tUNzqvzrLM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:58:06.940Z</t>
+  </si>
+  <si>
+    <t>WEST LANE FAMILY DENTAL</t>
+  </si>
+  <si>
+    <t>(209) 477-3660</t>
+  </si>
+  <si>
+    <t>8118 West Ln #107, Stockton, CA 95210</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/WEST+LANE+FAMILY+DENTAL/data=!4m7!3m6!1s0x80900d023f74f665:0x7c52901a9724cc75!8m2!3d38.0233653!4d-121.2939485!16s%2Fg%2F11yvjzlcsn!19sChIJZfZ0PwINkIARdcwklxqQUnw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:59:27.198Z</t>
+  </si>
+  <si>
+    <t>star shine dental and implants</t>
+  </si>
+  <si>
+    <t>(209) 951-0805</t>
+  </si>
+  <si>
+    <t>73 W March Ln # B, Stockton, CA 95207</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/star+shine+dental+and+implants/data=!4m7!3m6!1s0x80900d7be64d228b:0xfe9d9a9f2d1311b0!8m2!3d37.99558!4d-121.3070113!16s%2Fg%2F11z7nrz_s2!19sChIJiyJN5nsNkIARsBETLZ-anf4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:00:31.893Z</t>
+  </si>
+  <si>
+    <t>Daniel R. Cotton</t>
+  </si>
+  <si>
+    <t>(209) 951-8000</t>
+  </si>
+  <si>
+    <t>2509 W March Ln #110, Stockton, CA 95207</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Daniel+R.+Cotton/data=!4m7!3m6!1s0x80900c33b8c6a707:0x3711d83689a6ca4c!8m2!3d37.9866925!4d-121.3386821!16s%2Fg%2F1thz1xj6!19sChIJB6fGuDMMkIARTMqmiTbYETc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:00:55.965Z</t>
+  </si>
+  <si>
+    <t>United Dental Group</t>
+  </si>
+  <si>
+    <t>(510) 790-8088</t>
+  </si>
+  <si>
+    <t>34400 Fremont Blvd, Fremont, CA 94555</t>
+  </si>
+  <si>
+    <t>Fremont</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/United+Dental+Group/data=!4m7!3m6!1s0x808fbe2ce2d6d4b3:0x6b5b84c29fe77eba!8m2!3d37.5756182!4d-122.040305!16s%2Fg%2F1tq6dqwx!19sChIJs9TW4iy-j4ARun7nn8KEW2s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:03:59.608Z</t>
+  </si>
+  <si>
+    <t>Dental Care Center, Bhumika Jain DDS</t>
+  </si>
+  <si>
+    <t>(510) 745-9222</t>
+  </si>
+  <si>
+    <t>39470 Fremont Blvd Apt 2117, Fremont, CA 94538</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Care+Center,+Bhumika+Jain+DDS/data=!4m7!3m6!1s0x808fc166eecde447:0xfcb42e5d77a596a7!8m2!3d37.545621!4d-121.98084!16s%2Fg%2F11tx72vjfm!19sChIJR-TN7mbBj4ARp5ald10utPw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:04:32.622Z</t>
+  </si>
+  <si>
+    <t>South Bay Dental Practice</t>
+  </si>
+  <si>
+    <t>(510) 796-7600</t>
+  </si>
+  <si>
+    <t>3200 Mowry Ave Ste B, Fremont, CA 94538</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/South+Bay+Dental+Practice/data=!4m7!3m6!1s0x808fc07f7704b3b1:0x5cd88e03bbb2114c!8m2!3d37.5533772!4d-121.9838564!16s%2Fg%2F11h1ybbv7b!19sChIJsbMEd3_Aj4ARTBGyuwOO2Fw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:04:46.168Z</t>
+  </si>
+  <si>
+    <t>Mariano Dental Care, Dr. Seneca Mariano D.D.S.</t>
+  </si>
+  <si>
+    <t>(510) 201-7390</t>
+  </si>
+  <si>
+    <t>6094 Mowry Ave, Newark, CA 94560</t>
+  </si>
+  <si>
+    <t>Newark</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mariano+Dental+Care,+Dr.+Seneca+Mariano+D.D.S./data=!4m7!3m6!1s0x808fbf4f68b3f083:0x164c7a8e1800327d!8m2!3d37.523937!4d-122.008107!16s%2Fg%2F11ckdzd3qs!19sChIJg_CzaE-_j4ARfTIAGI56TBY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:04:53.936Z</t>
+  </si>
+  <si>
+    <t>Randall I. Hashimoto, DDS: Hashimoto Family Dentistry</t>
+  </si>
+  <si>
+    <t>(510) 793-6954</t>
+  </si>
+  <si>
+    <t>2211 Parkside Dr Ste G, Fremont, CA 94536</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Randall+I.+Hashimoto,+DDS:+Hashimoto+Family+Dentistry/data=!4m7!3m6!1s0x808fc087d66270bd:0xc6ce94300c787ef5!8m2!3d37.5597496!4d-121.9808883!16s%2Fg%2F1tl7nz1q!19sChIJvXBi1ofAj4AR9X54DDCUzsY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:06:11.656Z</t>
+  </si>
+  <si>
+    <t>Family Dental Care : Maria Ana Canuto DDS</t>
+  </si>
+  <si>
+    <t>(510) 713-7751</t>
+  </si>
+  <si>
+    <t>36612 Newark Blvd, Newark, CA 94560</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Dental+Care+:+Maria+Ana+Canuto+DDS/data=!4m7!3m6!1s0x808fbf03eea4054d:0xe75df1693cdb359f!8m2!3d37.5399393!4d-122.0334469!16s%2Fg%2F1tdqzy_z!19sChIJTQWk7gO_j4ARnzXbPGnxXec?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:06:14.712Z</t>
+  </si>
+  <si>
+    <t>Geronimo Rosalie DMD</t>
+  </si>
+  <si>
+    <t>(510) 440-1406</t>
+  </si>
+  <si>
+    <t>39200 Liberty St Ste C, Fremont, CA 94538</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Geronimo+Rosalie+DMD/data=!4m7!3m6!1s0x808fc12804c63cc9:0x3fd4c3d0cb8d2b74!8m2!3d37.5507146!4d-121.9813021!16s%2Fg%2F1td5gc2m!19sChIJyTzGBCjBj4ARdCuNy9DD1D8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:06:17.676Z</t>
+  </si>
+  <si>
+    <t>Thornton Dental</t>
+  </si>
+  <si>
+    <t>(510) 793-8121</t>
+  </si>
+  <si>
+    <t>4364 Thornton Ave, Fremont, CA 94536</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Thornton+Dental/data=!4m7!3m6!1s0x808fbf98b20ee6c7:0xe32e8ee373722cd1!8m2!3d37.5563102!4d-122.0144084!16s%2Fg%2F1tfl9x6d!19sChIJx-YOspi_j4AR0Sxyc-OOLuM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:06:20.657Z</t>
+  </si>
+  <si>
+    <t>Barakzoy Mostafa DDS</t>
+  </si>
+  <si>
+    <t>(510) 505-9409</t>
+  </si>
+  <si>
+    <t>2410 Dyer Lane, 2287 Mowry Ave Suite H, Fremont, CA 94536</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Saturday8:30 AM–3:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Barakzoy+Mostafa+DDS/data=!4m7!3m6!1s0x808fc07f775c575d:0x5925e325c038be9!8m2!3d37.556526!4d-121.9830003!16s%2Fg%2F1vqmjlxg!19sChIJXVdcd3_Aj4AR6YsDXDJekgU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:06:23.707Z</t>
+  </si>
+  <si>
+    <t>Lisa Tao Dental</t>
+  </si>
+  <si>
+    <t>(510) 344-6487</t>
+  </si>
+  <si>
+    <t>39783 Paseo Padre Pkwy, Fremont, CA 94538</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lisa+Tao+Dental/data=!4m7!3m6!1s0x808fc0eacdaf57b5:0x83e6dc99f6be8e2e!8m2!3d37.5474238!4d-121.9698597!16s%2Fg%2F11ddxwq11b!19sChIJtVevzerAj4ARLo6-9pnc5oM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:06:29.444Z</t>
+  </si>
+  <si>
+    <t>Little Plum Pediatric Dentistry</t>
+  </si>
+  <si>
+    <t>(510) 505-8707</t>
+  </si>
+  <si>
+    <t>39141 Civic Center Dr Ste 220, Fremont, CA 94538</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Little+Plum+Pediatric+Dentistry/data=!4m7!3m6!1s0x808fc10fa7721c89:0x58a830bac5a9629a!8m2!3d37.5540199!4d-121.9767632!16s%2Fg%2F11zd6f29gj!19sChIJiRxypw_Bj4ARmmKpxbowqFg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:07:21.168Z</t>
+  </si>
+  <si>
+    <t>Youthful Tooth &amp; Adult Care</t>
+  </si>
+  <si>
+    <t>(510) 438-9201</t>
+  </si>
+  <si>
+    <t>39411 Fremont Blvd, Fremont, CA 94538</t>
+  </si>
+  <si>
+    <t>Saturday9:30 AM–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Youthful+Tooth+%26+Adult+Care/data=!4m7!3m6!1s0x808fc099c201e03f:0x14509b0e7bde9171!8m2!3d37.5446477!4d-121.981428!16s%2Fg%2F1tftfk94!19sChIJP-ABwpnAj4ARcZHeew6bUBQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:07:24.507Z</t>
+  </si>
+  <si>
+    <t>David Morris, D.D.S.</t>
+  </si>
+  <si>
+    <t>(510) 790-3382</t>
+  </si>
+  <si>
+    <t>39560 Stevenson Pl #118, Fremont, CA 94539</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/David+Morris,+D.D.S./data=!4m7!3m6!1s0x808fc0e54ab5f07b:0xffc0b25cdb52b47d!8m2!3d37.5592652!4d-121.9565602!16s%2Fg%2F1tfvt5l4!19sChIJe_C1SuXAj4ARfbRS21yywP8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:07:27.366Z</t>
+  </si>
+  <si>
+    <t>Stepping Stones Pediatric Dentistry</t>
+  </si>
+  <si>
+    <t>(510) 902-4272</t>
+  </si>
+  <si>
+    <t>39560 Stevenson Pl, Fremont, CA 94539</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stepping+Stones+Pediatric+Dentistry/data=!4m7!3m6!1s0x808fc0e52cf00001:0x90a40fdabfc9ccac!8m2!3d37.5592938!4d-121.9563319!16s%2Fg%2F11s6b2cyc2!19sChIJAQDwLOXAj4ARrMzJv9oPpJA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:07:31.927Z</t>
+  </si>
+  <si>
+    <t>ZP Dental</t>
+  </si>
+  <si>
+    <t>(510) 818-0182</t>
+  </si>
+  <si>
+    <t>39560 Stevenson Pl #220, Fremont, CA 94539</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/ZP+Dental/data=!4m7!3m6!1s0x808fc0fab56a4a31:0xc99c1e3380fe4302!8m2!3d37.5595177!4d-121.9562935!16s%2Fg%2F1tgcmjm7!19sChIJMUpqtfrAj4ARAkP-gDMenMk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:07:34.333Z</t>
+  </si>
+  <si>
+    <t>Dr Atousa Zarrinjooee, DDS</t>
+  </si>
+  <si>
+    <t>(510) 795-0307</t>
+  </si>
+  <si>
+    <t>34117 Fremont Blvd, Fremont, CA 94555</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–3:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Atousa+Zarrinjooee,+DDS/data=!4m7!3m6!1s0x808fbe2bffe14a2f:0xa86aca617b900a82!8m2!3d37.5761639!4d-122.0439665!16s%2Fg%2F11fy9q4j56!19sChIJL0rh_yu-j4ARggqQe2HKaqg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:07:37.253Z</t>
+  </si>
+  <si>
+    <t>Bhogal Dental Group</t>
+  </si>
+  <si>
+    <t>(510) 797-2840</t>
+  </si>
+  <si>
+    <t>37070 Newark Blvd, Newark, CA 94560</t>
+  </si>
+  <si>
+    <t>Saturday12–6 AM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bhogal+Dental+Group/data=!4m7!3m6!1s0x808fbf1ada13babf:0x8cfa97079e4c44bb!8m2!3d37.5367269!4d-122.0293941!16s%2Fg%2F1q5bnbswy!19sChIJv7oT2hq_j4ARu0RMngeX-ow?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:07:54.223Z</t>
+  </si>
+  <si>
+    <t>Dr. Michael S. Tancio, DMD - TANCIO DENTAL CARE</t>
+  </si>
+  <si>
+    <t>(510) 573-1180</t>
+  </si>
+  <si>
+    <t>39453 Fremont Blvd, Fremont, CA 94538</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Michael+S.+Tancio,+DMD+-+TANCIO+DENTAL+CARE/data=!4m7!3m6!1s0x808fc0920ae4930d:0x146e00fbc103537c!8m2!3d37.5436573!4d-121.9821371!16s%2Fg%2F1tfv5c77!19sChIJDZPkCpLAj4ARfFMDwfsAbhQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:07:58.922Z</t>
+  </si>
+  <si>
+    <t>Fremont Urgent Dental</t>
+  </si>
+  <si>
+    <t>(510) 737-5264</t>
+  </si>
+  <si>
+    <t>4910 Paseo Padre Pkwy Ste, Fremont, CA 94555</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fremont+Urgent+Dental/data=!4m7!3m6!1s0x808fbf39f0e70869:0x7046478a5c155a32!8m2!3d37.5666705!4d-122.0538864!16s%2Fg%2F11l31xxfsg!19sChIJaQjn8Dm_j4ARMloVXIpHRnA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:08:20.822Z</t>
+  </si>
+  <si>
+    <t>Fremont Periodontics &amp; Implant</t>
+  </si>
+  <si>
+    <t>(510) 796-8333</t>
+  </si>
+  <si>
+    <t>39210 Liberty St Ste 214, Fremont, CA 94538</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fremont+Periodontics+%26+Implant/data=!4m7!3m6!1s0x808fc09a45cbea19:0xb6240c27ccbbe277!8m2!3d37.5480387!4d-121.983363!16s%2Fg%2F1260gk54d!19sChIJGerLRZrAj4ARd-K7zCcMJLY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:09:55.254Z</t>
+  </si>
+  <si>
+    <t>Friendly Smile Dentistry</t>
+  </si>
+  <si>
+    <t>(209) 572-1992</t>
+  </si>
+  <si>
+    <t>3125 Coffee Rd #5, Modesto, CA 95355</t>
+  </si>
+  <si>
+    <t>Modesto</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Friendly+Smile+Dentistry/data=!4m7!3m6!1s0x809056a607aed7b1:0x83cfb986d6756dcc!8m2!3d37.6835614!4d-120.9763813!16s%2Fg%2F1tjynz8c!19sChIJsdeuB6ZWkIARzG111oa5z4M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:11:12.952Z</t>
+  </si>
+  <si>
+    <t>Melko Family Dentistry</t>
+  </si>
+  <si>
+    <t>(855) 235-0325</t>
+  </si>
+  <si>
+    <t>3609 Coffee Rd #3, Modesto, CA 95355</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Melko+Family+Dentistry/data=!4m7!3m6!1s0x809056cf66a5ccef:0x4dc6a81d7d0ff1b9!8m2!3d37.6920978!4d-120.9765257!16s%2Fg%2F11bbt2_3z8!19sChIJ78ylZs9WkIARufEPfR2oxk0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:12:50.504Z</t>
+  </si>
+  <si>
+    <t>Brewer, Dr. Amanda</t>
+  </si>
+  <si>
+    <t>(209) 578-0707</t>
+  </si>
+  <si>
+    <t>1213 Coffee Rd # H, Modesto, CA 95355</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brewer,+Dr.+Amanda/data=!4m7!3m6!1s0x8090541b2d7cae79:0xd490d278322200ef!8m2!3d37.6597484!4d-120.9759134!16s%2Fg%2F1hc49w328!19sChIJea58LRtUkIAR7wAiMnjSkNQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:12:59.541Z</t>
+  </si>
+  <si>
+    <t>McHenry Village Dental</t>
+  </si>
+  <si>
+    <t>(209) 527-5727</t>
+  </si>
+  <si>
+    <t>1700 McHenry Ave, Modesto, CA 95350</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/McHenry+Village+Dental/data=!4m7!3m6!1s0x8090515371d78ff5:0x8012fad109eb1a91!8m2!3d37.6679026!4d-120.9905431!16s%2Fg%2F1td6b36w!19sChIJ9Y_XcVNRkIARkRrrCdH6EoA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:13:05.032Z</t>
+  </si>
+  <si>
+    <t>Veneers Dentist Modesto</t>
+  </si>
+  <si>
+    <t>(209) 390-8212</t>
+  </si>
+  <si>
+    <t>1213 Coffee Rd, Modesto, CA 95355</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Veneers+Dentist+Modesto/data=!4m7!3m6!1s0x8090541b29ce3323:0xfe413727a249eae2!8m2!3d37.660409!4d-120.9760649!16s%2Fg%2F1th5_0x4!19sChIJIzPOKRtUkIAR4upJoic3Qf4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:13:38.403Z</t>
+  </si>
+  <si>
+    <t>Dr. Corbin M. Kinser, DDS</t>
+  </si>
+  <si>
+    <t>(209) 577-6649</t>
+  </si>
+  <si>
+    <t>1211 14th St, Modesto, CA 95354</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Corbin+M.+Kinser,+DDS/data=!4m7!3m6!1s0x809053edfffa57ff:0x44c9ce007f8a40c6!8m2!3d37.6454756!4d-120.9993458!16s%2Fg%2F1tmcmgsz!19sChIJ_1f6_-1TkIARxkCKfwDOyUQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:13:54.722Z</t>
+  </si>
+  <si>
+    <t>Pediatric Dental Specialists: Elson Stacie</t>
+  </si>
+  <si>
+    <t>(209) 571-7283</t>
+  </si>
+  <si>
+    <t>3109 Coffee Rd # B, Modesto, CA 95355</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pediatric+Dental+Specialists:+Elson+Stacie/data=!4m7!3m6!1s0x809056b9d6ff030d:0x2fd67ae685a24e52!8m2!3d37.6832241!4d-120.9764038!16s%2Fg%2F1td6sgqt!19sChIJDQP_1rlWkIARUk6iheZ61i8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:13:57.717Z</t>
+  </si>
+  <si>
+    <t>Dr. Amandeep Gill</t>
+  </si>
+  <si>
+    <t>(209) 549-1721</t>
+  </si>
+  <si>
+    <t>1518 Coffee Rd # B, Modesto, CA 95355</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Amandeep+Gill/data=!4m7!3m6!1s0x8090541d4680740f:0x5f537c67df8ad30!8m2!3d37.6661305!4d-120.9752919!16s%2Fg%2F11p07bbhwm!19sChIJD3SARh1UkIARMK34fcY39QU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:14:00.901Z</t>
+  </si>
+  <si>
+    <t>Bauman David G DDS</t>
+  </si>
+  <si>
+    <t>(209) 575-9501</t>
+  </si>
+  <si>
+    <t>1213 Coffee Rd Suite G, Modesto, CA 95355</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bauman+David+G+DDS/data=!4m7!3m6!1s0x8090541b29ce3323:0xd25f1b22f75946e5!8m2!3d37.660409!4d-120.9760649!16s%2Fg%2F1tdjx7sj!19sChIJIzPOKRtUkIAR5UZZ9yIbX9I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:14:04.116Z</t>
+  </si>
+  <si>
+    <t>West Orthodontics</t>
+  </si>
+  <si>
+    <t>(209) 524-5515</t>
+  </si>
+  <si>
+    <t>1236 Floyd Ave, Modesto, CA 95350</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+Orthodontics/data=!4m7!3m6!1s0x809056b07107291b:0x656f968bc5017647!8m2!3d37.6777206!4d-120.97665!16s%2Fg%2F1txc78c5!19sChIJGykHcbBWkIARR3YBxYuWb2U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:14:13.681Z</t>
+  </si>
+  <si>
+    <t>Strasser Jr Myron R DDS</t>
+  </si>
+  <si>
+    <t>(209) 529-8872</t>
+  </si>
+  <si>
+    <t>1429 College Ave # J, Modesto, CA 95350</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Strasser+Jr+Myron+R+DDS/data=!4m7!3m6!1s0x8090515d1ad59e6b:0x7d0810dfebc0cd11!8m2!3d37.6653593!4d-121.0081091!16s%2Fg%2F1wrgkd82!19sChIJa57VGl1RkIAREc3A698QCH0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:14:30.436Z</t>
+  </si>
+  <si>
+    <t>Tae Een Park DDS</t>
+  </si>
+  <si>
+    <t>(209) 527-5115</t>
+  </si>
+  <si>
+    <t>1429 College Ave Ste D, Modesto, CA 95350</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tae+Een+Park+DDS/data=!4m7!3m6!1s0x8090515d1ad59e6b:0x754f1afb584c635e!8m2!3d37.6655311!4d-121.0083389!16s%2Fg%2F1tffzrf8!19sChIJa57VGl1RkIARXmNMWPsaT3U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:14:35.953Z</t>
+  </si>
+  <si>
+    <t>Urgent Dentist Station</t>
+  </si>
+  <si>
+    <t>(209) 308-1268</t>
+  </si>
+  <si>
+    <t>724 10th St, Modesto, CA 95354</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dentist+Station/data=!4m7!3m6!1s0x809053233bb802d5:0x2b4d266a88b26929!8m2!3d37.6383833!4d-120.9974163!16s%2Fg%2F11p1rf3xtn!19sChIJ1QK4OyNTkIARKWmyiGomTSs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:14:53.776Z</t>
+  </si>
+  <si>
+    <t>Dentista Hispano 24/7 Modesto</t>
+  </si>
+  <si>
+    <t>(920) 325-1935</t>
+  </si>
+  <si>
+    <t>1204 McHenry Ave, Modesto, CA 95350</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentista+Hispano+24%2F7+Modesto/data=!4m7!3m6!1s0x80905361f0a4e4c7:0xca5b051e594f588c!8m2!3d37.6603072!4d-120.9934014!16s%2Fg%2F11nnqzcvh3!19sChIJx-Sk8GFTkIARjFhPWR4FW8o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:14:56.172Z</t>
+  </si>
+  <si>
+    <t>Western Dentistry</t>
+  </si>
+  <si>
+    <t>(209) 248-8551</t>
+  </si>
+  <si>
+    <t>400 12th St, Modesto, CA 95354</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Western+Dentistry/data=!4m7!3m6!1s0x80905389146f982d:0x3ca3def16c4faaa4!8m2!3d37.6367884!4d-120.991646!16s%2Fg%2F11c2qgp7wp!19sChIJLZhvFIlTkIARpKpPbPHeozw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:15:04.837Z</t>
+  </si>
+  <si>
+    <t>Bronze &amp; Bright</t>
+  </si>
+  <si>
+    <t>(209) 622-8708</t>
+  </si>
+  <si>
+    <t>1521 K St, Modesto, CA 95354</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bronze+%26+Bright/data=!4m7!3m6!1s0x8090535ae6dee281:0xb383ded412a3928c!8m2!3d37.6453775!4d-120.9965533!16s%2Fg%2F11swrvbg0g!19sChIJgeLe5lpTkIARjJKjEtTeg7M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:15:54.372Z</t>
+  </si>
+  <si>
+    <t>Cali Teeth Whitening</t>
+  </si>
+  <si>
+    <t>(209) 450-1272</t>
+  </si>
+  <si>
+    <t>1518 Coffee Rd, Modesto, CA 95355</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cali+Teeth+Whitening/data=!4m7!3m6!1s0x8090541d469b0381:0xdbd0b7974bd567e8!8m2!3d37.6661244!4d-120.9752392!16s%2Fg%2F11gh3510_8!19sChIJgQObRh1UkIAR6GfVS5e30Ns?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:16:01.373Z</t>
+  </si>
+  <si>
+    <t>Roy H. Morita, DDS, Inc.</t>
+  </si>
+  <si>
+    <t>(209) 524-6128</t>
+  </si>
+  <si>
+    <t>1308 Celeste Dr suite b, Modesto, CA 95355</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Roy+H.+Morita,+DDS,+Inc./data=!4m7!3m6!1s0x809056a672f824e9:0x2b48adbdd85431f2!8m2!3d37.6716141!4d-120.9745792!16s%2Fg%2F1vfwd2pf!19sChIJ6ST4cqZWkIAR8jFU2L2tSCs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:16:13.212Z</t>
+  </si>
+  <si>
+    <t>Essential Dental Care</t>
+  </si>
+  <si>
+    <t>(707) 568-0480</t>
+  </si>
+  <si>
+    <t>55 Mission Cir Ste 103, Santa Rosa, CA 95409</t>
+  </si>
+  <si>
+    <t>Santa Rosa</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Essential+Dental+Care/data=!4m7!3m6!1s0x808447d33ed84991:0x70ab33972b3ef19!8m2!3d38.4571584!4d-122.6739849!16s%2Fg%2F1trplf3l!19sChIJkUnYPtNHhIARGe-zcjmzCgc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:16:38.304Z</t>
+  </si>
+  <si>
+    <t>Zen Dental Care</t>
+  </si>
+  <si>
+    <t>(707) 595-3615</t>
+  </si>
+  <si>
+    <t>1591 Farmers Ln, Santa Rosa, CA 95405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Zen+Dental+Care/data=!4m7!3m6!1s0x808439ada577c3f5:0xc124cd46bbda9e31!8m2!3d38.4340399!4d-122.6886939!16s%2Fg%2F1wc31gfv!19sChIJ9cN3pa05hIARMZ7au0bNJME?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:16:40.896Z</t>
+  </si>
+  <si>
+    <t>Gina Fontana DDS</t>
+  </si>
+  <si>
+    <t>(707) 579-0843</t>
+  </si>
+  <si>
+    <t>95 Montgomery Dr #218, Santa Rosa, CA 95404</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gina+Fontana+DDS/data=!4m7!3m6!1s0x8084480a22380b9d:0xff92a105b4d499de!8m2!3d38.4427556!4d-122.7043406!16s%2Fg%2F1v3khq_p!19sChIJnQs4IgpIhIAR3pnUtAWhkv8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:17:40.168Z</t>
+  </si>
+  <si>
+    <t>Justin Phillips, DDS</t>
+  </si>
+  <si>
+    <t>(707) 542-1026</t>
+  </si>
+  <si>
+    <t>2655 Cleveland Ave Ste B, Santa Rosa, CA 95403</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Justin+Phillips,+DDS/data=!4m7!3m6!1s0x8084387ab7174825:0x21e792af0784cfb5!8m2!3d38.4633588!4d-122.7291258!16s%2Fg%2F1v27vqjg!19sChIJJUgXt3o4hIARtc-EB6-S5yE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:19:28.954Z</t>
+  </si>
+  <si>
+    <t>Daniel Sullivan, DDS</t>
+  </si>
+  <si>
+    <t>(707) 545-5260</t>
+  </si>
+  <si>
+    <t>4655 Hoen Ave # 6, Santa Rosa, CA 95405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Daniel+Sullivan,+DDS/data=!4m7!3m6!1s0x8084488efea1c00d:0xce9182554bdbc56a!8m2!3d38.4421346!4d-122.6648094!16s%2Fg%2F1tscp6y6!19sChIJDcCh_o5IhIARasXbS1WCkc4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T04:20:29.243Z</t>
   </si>
 </sst>
 </file>
@@ -8401,7 +10699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M491"/>
+  <dimension ref="A1:M639"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -28549,6 +30847,6074 @@
         <v>2669</v>
       </c>
     </row>
+    <row r="492" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>2670</v>
+      </c>
+      <c r="B492" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C492" t="s">
+        <v>28</v>
+      </c>
+      <c r="D492" t="s">
+        <v>2672</v>
+      </c>
+      <c r="E492" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F492" t="s">
+        <v>18</v>
+      </c>
+      <c r="G492" t="s">
+        <v>19</v>
+      </c>
+      <c r="H492" t="s">
+        <v>45</v>
+      </c>
+      <c r="I492" t="s">
+        <v>21</v>
+      </c>
+      <c r="J492" t="s">
+        <v>75</v>
+      </c>
+      <c r="K492" t="s">
+        <v>23</v>
+      </c>
+      <c r="L492" t="s">
+        <v>2673</v>
+      </c>
+      <c r="M492" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="493" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>2675</v>
+      </c>
+      <c r="B493" t="s">
+        <v>2676</v>
+      </c>
+      <c r="C493" t="s">
+        <v>15</v>
+      </c>
+      <c r="D493" t="s">
+        <v>2677</v>
+      </c>
+      <c r="E493" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F493" t="s">
+        <v>18</v>
+      </c>
+      <c r="G493" t="s">
+        <v>19</v>
+      </c>
+      <c r="H493" t="s">
+        <v>37</v>
+      </c>
+      <c r="I493" t="s">
+        <v>21</v>
+      </c>
+      <c r="J493" t="s">
+        <v>121</v>
+      </c>
+      <c r="K493" t="s">
+        <v>23</v>
+      </c>
+      <c r="L493" t="s">
+        <v>2678</v>
+      </c>
+      <c r="M493" t="s">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="494" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B494" t="s">
+        <v>2681</v>
+      </c>
+      <c r="C494" t="s">
+        <v>15</v>
+      </c>
+      <c r="D494" t="s">
+        <v>2682</v>
+      </c>
+      <c r="E494" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F494" t="s">
+        <v>18</v>
+      </c>
+      <c r="G494" t="s">
+        <v>19</v>
+      </c>
+      <c r="H494" t="s">
+        <v>405</v>
+      </c>
+      <c r="I494" t="s">
+        <v>21</v>
+      </c>
+      <c r="J494" t="s">
+        <v>75</v>
+      </c>
+      <c r="K494" t="s">
+        <v>23</v>
+      </c>
+      <c r="L494" t="s">
+        <v>2683</v>
+      </c>
+      <c r="M494" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="495" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>2685</v>
+      </c>
+      <c r="B495" t="s">
+        <v>2686</v>
+      </c>
+      <c r="C495" t="s">
+        <v>15</v>
+      </c>
+      <c r="D495" t="s">
+        <v>2687</v>
+      </c>
+      <c r="E495" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F495" t="s">
+        <v>18</v>
+      </c>
+      <c r="G495" t="s">
+        <v>19</v>
+      </c>
+      <c r="H495" t="s">
+        <v>45</v>
+      </c>
+      <c r="I495" t="s">
+        <v>21</v>
+      </c>
+      <c r="J495" t="s">
+        <v>46</v>
+      </c>
+      <c r="K495" t="s">
+        <v>23</v>
+      </c>
+      <c r="L495" t="s">
+        <v>2688</v>
+      </c>
+      <c r="M495" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="496" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B496" t="s">
+        <v>2691</v>
+      </c>
+      <c r="C496" t="s">
+        <v>15</v>
+      </c>
+      <c r="D496" t="s">
+        <v>2692</v>
+      </c>
+      <c r="E496" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F496" t="s">
+        <v>18</v>
+      </c>
+      <c r="G496" t="s">
+        <v>19</v>
+      </c>
+      <c r="H496" t="s">
+        <v>45</v>
+      </c>
+      <c r="I496" t="s">
+        <v>21</v>
+      </c>
+      <c r="J496" t="s">
+        <v>46</v>
+      </c>
+      <c r="K496" t="s">
+        <v>23</v>
+      </c>
+      <c r="L496" t="s">
+        <v>2693</v>
+      </c>
+      <c r="M496" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="497" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B497" t="s">
+        <v>2696</v>
+      </c>
+      <c r="C497" t="s">
+        <v>28</v>
+      </c>
+      <c r="D497" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E497" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F497" t="s">
+        <v>18</v>
+      </c>
+      <c r="G497" t="s">
+        <v>19</v>
+      </c>
+      <c r="H497" t="s">
+        <v>45</v>
+      </c>
+      <c r="I497" t="s">
+        <v>21</v>
+      </c>
+      <c r="J497" t="s">
+        <v>46</v>
+      </c>
+      <c r="K497" t="s">
+        <v>23</v>
+      </c>
+      <c r="L497" t="s">
+        <v>2698</v>
+      </c>
+      <c r="M497" t="s">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="498" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>2700</v>
+      </c>
+      <c r="B498" t="s">
+        <v>2701</v>
+      </c>
+      <c r="C498" t="s">
+        <v>28</v>
+      </c>
+      <c r="D498" t="s">
+        <v>2702</v>
+      </c>
+      <c r="E498" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F498" t="s">
+        <v>18</v>
+      </c>
+      <c r="G498" t="s">
+        <v>19</v>
+      </c>
+      <c r="H498" t="s">
+        <v>45</v>
+      </c>
+      <c r="I498" t="s">
+        <v>21</v>
+      </c>
+      <c r="J498" t="s">
+        <v>30</v>
+      </c>
+      <c r="K498" t="s">
+        <v>23</v>
+      </c>
+      <c r="L498" t="s">
+        <v>2703</v>
+      </c>
+      <c r="M498" t="s">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="499" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B499" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C499" t="s">
+        <v>73</v>
+      </c>
+      <c r="D499" t="s">
+        <v>2707</v>
+      </c>
+      <c r="E499" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F499" t="s">
+        <v>18</v>
+      </c>
+      <c r="G499" t="s">
+        <v>19</v>
+      </c>
+      <c r="H499" t="s">
+        <v>45</v>
+      </c>
+      <c r="I499" t="s">
+        <v>21</v>
+      </c>
+      <c r="J499" t="s">
+        <v>75</v>
+      </c>
+      <c r="K499" t="s">
+        <v>23</v>
+      </c>
+      <c r="L499" t="s">
+        <v>2708</v>
+      </c>
+      <c r="M499" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="500" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B500" t="s">
+        <v>2711</v>
+      </c>
+      <c r="C500" t="s">
+        <v>73</v>
+      </c>
+      <c r="D500" t="s">
+        <v>2712</v>
+      </c>
+      <c r="E500" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F500" t="s">
+        <v>18</v>
+      </c>
+      <c r="G500" t="s">
+        <v>19</v>
+      </c>
+      <c r="H500" t="s">
+        <v>375</v>
+      </c>
+      <c r="I500" t="s">
+        <v>21</v>
+      </c>
+      <c r="J500" t="s">
+        <v>75</v>
+      </c>
+      <c r="K500" t="s">
+        <v>23</v>
+      </c>
+      <c r="L500" t="s">
+        <v>2713</v>
+      </c>
+      <c r="M500" t="s">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="501" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B501" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C501" t="s">
+        <v>73</v>
+      </c>
+      <c r="D501" t="s">
+        <v>2717</v>
+      </c>
+      <c r="E501" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F501" t="s">
+        <v>18</v>
+      </c>
+      <c r="G501" t="s">
+        <v>19</v>
+      </c>
+      <c r="H501" t="s">
+        <v>45</v>
+      </c>
+      <c r="I501" t="s">
+        <v>21</v>
+      </c>
+      <c r="J501" t="s">
+        <v>75</v>
+      </c>
+      <c r="K501" t="s">
+        <v>23</v>
+      </c>
+      <c r="L501" t="s">
+        <v>2718</v>
+      </c>
+      <c r="M501" t="s">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="502" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B502" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C502" t="s">
+        <v>15</v>
+      </c>
+      <c r="D502" t="s">
+        <v>2722</v>
+      </c>
+      <c r="E502" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F502" t="s">
+        <v>18</v>
+      </c>
+      <c r="G502" t="s">
+        <v>19</v>
+      </c>
+      <c r="H502" t="s">
+        <v>45</v>
+      </c>
+      <c r="I502" t="s">
+        <v>21</v>
+      </c>
+      <c r="J502" t="s">
+        <v>75</v>
+      </c>
+      <c r="K502" t="s">
+        <v>23</v>
+      </c>
+      <c r="L502" t="s">
+        <v>2723</v>
+      </c>
+      <c r="M502" t="s">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="503" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>2725</v>
+      </c>
+      <c r="B503" t="s">
+        <v>2726</v>
+      </c>
+      <c r="C503" t="s">
+        <v>28</v>
+      </c>
+      <c r="D503" t="s">
+        <v>2727</v>
+      </c>
+      <c r="E503" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F503" t="s">
+        <v>18</v>
+      </c>
+      <c r="G503" t="s">
+        <v>19</v>
+      </c>
+      <c r="H503" t="s">
+        <v>37</v>
+      </c>
+      <c r="I503" t="s">
+        <v>21</v>
+      </c>
+      <c r="J503" t="s">
+        <v>46</v>
+      </c>
+      <c r="K503" t="s">
+        <v>23</v>
+      </c>
+      <c r="L503" t="s">
+        <v>2728</v>
+      </c>
+      <c r="M503" t="s">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="504" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>2730</v>
+      </c>
+      <c r="B504" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C504" t="s">
+        <v>15</v>
+      </c>
+      <c r="D504" t="s">
+        <v>2732</v>
+      </c>
+      <c r="E504" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F504" t="s">
+        <v>18</v>
+      </c>
+      <c r="G504" t="s">
+        <v>19</v>
+      </c>
+      <c r="H504" t="s">
+        <v>241</v>
+      </c>
+      <c r="I504" t="s">
+        <v>21</v>
+      </c>
+      <c r="J504" t="s">
+        <v>46</v>
+      </c>
+      <c r="K504" t="s">
+        <v>23</v>
+      </c>
+      <c r="L504" t="s">
+        <v>2733</v>
+      </c>
+      <c r="M504" t="s">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="505" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B505" t="s">
+        <v>2736</v>
+      </c>
+      <c r="C505" t="s">
+        <v>58</v>
+      </c>
+      <c r="D505" t="s">
+        <v>2737</v>
+      </c>
+      <c r="E505" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F505" t="s">
+        <v>18</v>
+      </c>
+      <c r="G505" t="s">
+        <v>19</v>
+      </c>
+      <c r="H505" t="s">
+        <v>375</v>
+      </c>
+      <c r="I505" t="s">
+        <v>569</v>
+      </c>
+      <c r="J505" t="s">
+        <v>2738</v>
+      </c>
+      <c r="K505" t="s">
+        <v>23</v>
+      </c>
+      <c r="L505" t="s">
+        <v>2739</v>
+      </c>
+      <c r="M505" t="s">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="506" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>2741</v>
+      </c>
+      <c r="B506" t="s">
+        <v>2742</v>
+      </c>
+      <c r="C506" t="s">
+        <v>58</v>
+      </c>
+      <c r="D506" t="s">
+        <v>2743</v>
+      </c>
+      <c r="E506" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F506" t="s">
+        <v>18</v>
+      </c>
+      <c r="G506" t="s">
+        <v>19</v>
+      </c>
+      <c r="H506" t="s">
+        <v>45</v>
+      </c>
+      <c r="I506" t="s">
+        <v>695</v>
+      </c>
+      <c r="J506" t="s">
+        <v>75</v>
+      </c>
+      <c r="K506" t="s">
+        <v>23</v>
+      </c>
+      <c r="L506" t="s">
+        <v>2744</v>
+      </c>
+      <c r="M506" t="s">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="507" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>2746</v>
+      </c>
+      <c r="B507" t="s">
+        <v>2747</v>
+      </c>
+      <c r="C507" t="s">
+        <v>58</v>
+      </c>
+      <c r="D507" t="s">
+        <v>2748</v>
+      </c>
+      <c r="E507" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F507" t="s">
+        <v>18</v>
+      </c>
+      <c r="G507" t="s">
+        <v>19</v>
+      </c>
+      <c r="H507" t="s">
+        <v>37</v>
+      </c>
+      <c r="I507" t="s">
+        <v>581</v>
+      </c>
+      <c r="J507" t="s">
+        <v>2749</v>
+      </c>
+      <c r="K507" t="s">
+        <v>23</v>
+      </c>
+      <c r="L507" t="s">
+        <v>2750</v>
+      </c>
+      <c r="M507" t="s">
+        <v>2751</v>
+      </c>
+    </row>
+    <row r="508" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>2752</v>
+      </c>
+      <c r="B508" t="s">
+        <v>2753</v>
+      </c>
+      <c r="C508" t="s">
+        <v>58</v>
+      </c>
+      <c r="D508" t="s">
+        <v>2754</v>
+      </c>
+      <c r="E508" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F508" t="s">
+        <v>18</v>
+      </c>
+      <c r="G508" t="s">
+        <v>19</v>
+      </c>
+      <c r="H508" t="s">
+        <v>45</v>
+      </c>
+      <c r="I508" t="s">
+        <v>569</v>
+      </c>
+      <c r="J508" t="s">
+        <v>75</v>
+      </c>
+      <c r="K508" t="s">
+        <v>23</v>
+      </c>
+      <c r="L508" t="s">
+        <v>2755</v>
+      </c>
+      <c r="M508" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="509" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>2757</v>
+      </c>
+      <c r="B509" t="s">
+        <v>2758</v>
+      </c>
+      <c r="C509" t="s">
+        <v>15</v>
+      </c>
+      <c r="D509" t="s">
+        <v>2759</v>
+      </c>
+      <c r="E509" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F509" t="s">
+        <v>18</v>
+      </c>
+      <c r="G509" t="s">
+        <v>19</v>
+      </c>
+      <c r="H509" t="s">
+        <v>103</v>
+      </c>
+      <c r="I509" t="s">
+        <v>21</v>
+      </c>
+      <c r="J509" t="s">
+        <v>46</v>
+      </c>
+      <c r="K509" t="s">
+        <v>23</v>
+      </c>
+      <c r="L509" t="s">
+        <v>2760</v>
+      </c>
+      <c r="M509" t="s">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="510" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>2762</v>
+      </c>
+      <c r="B510" t="s">
+        <v>2763</v>
+      </c>
+      <c r="C510" t="s">
+        <v>15</v>
+      </c>
+      <c r="D510" t="s">
+        <v>2764</v>
+      </c>
+      <c r="E510" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F510" t="s">
+        <v>18</v>
+      </c>
+      <c r="G510" t="s">
+        <v>19</v>
+      </c>
+      <c r="H510" t="s">
+        <v>92</v>
+      </c>
+      <c r="I510" t="s">
+        <v>21</v>
+      </c>
+      <c r="J510" t="s">
+        <v>648</v>
+      </c>
+      <c r="K510" t="s">
+        <v>23</v>
+      </c>
+      <c r="L510" t="s">
+        <v>2765</v>
+      </c>
+      <c r="M510" t="s">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="511" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>2767</v>
+      </c>
+      <c r="B511" t="s">
+        <v>2768</v>
+      </c>
+      <c r="C511" t="s">
+        <v>15</v>
+      </c>
+      <c r="D511" t="s">
+        <v>2769</v>
+      </c>
+      <c r="E511" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F511" t="s">
+        <v>18</v>
+      </c>
+      <c r="G511" t="s">
+        <v>19</v>
+      </c>
+      <c r="H511" t="s">
+        <v>67</v>
+      </c>
+      <c r="I511" t="s">
+        <v>21</v>
+      </c>
+      <c r="J511" t="s">
+        <v>46</v>
+      </c>
+      <c r="K511" t="s">
+        <v>23</v>
+      </c>
+      <c r="L511" t="s">
+        <v>2771</v>
+      </c>
+      <c r="M511" t="s">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="512" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>2773</v>
+      </c>
+      <c r="B512" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C512" t="s">
+        <v>28</v>
+      </c>
+      <c r="D512" t="s">
+        <v>2775</v>
+      </c>
+      <c r="E512" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F512" t="s">
+        <v>18</v>
+      </c>
+      <c r="G512" t="s">
+        <v>19</v>
+      </c>
+      <c r="H512" t="s">
+        <v>20</v>
+      </c>
+      <c r="I512" t="s">
+        <v>21</v>
+      </c>
+      <c r="J512" t="s">
+        <v>30</v>
+      </c>
+      <c r="K512" t="s">
+        <v>23</v>
+      </c>
+      <c r="L512" t="s">
+        <v>2776</v>
+      </c>
+      <c r="M512" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="513" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>2778</v>
+      </c>
+      <c r="B513" t="s">
+        <v>2779</v>
+      </c>
+      <c r="C513" t="s">
+        <v>28</v>
+      </c>
+      <c r="D513" t="s">
+        <v>2780</v>
+      </c>
+      <c r="E513" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F513" t="s">
+        <v>18</v>
+      </c>
+      <c r="G513" t="s">
+        <v>19</v>
+      </c>
+      <c r="H513" t="s">
+        <v>960</v>
+      </c>
+      <c r="I513" t="s">
+        <v>21</v>
+      </c>
+      <c r="J513" t="s">
+        <v>46</v>
+      </c>
+      <c r="K513" t="s">
+        <v>23</v>
+      </c>
+      <c r="L513" t="s">
+        <v>2781</v>
+      </c>
+      <c r="M513" t="s">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="514" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>2783</v>
+      </c>
+      <c r="B514" t="s">
+        <v>2784</v>
+      </c>
+      <c r="C514" t="s">
+        <v>28</v>
+      </c>
+      <c r="D514" t="s">
+        <v>2785</v>
+      </c>
+      <c r="E514" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F514" t="s">
+        <v>18</v>
+      </c>
+      <c r="G514" t="s">
+        <v>19</v>
+      </c>
+      <c r="H514" t="s">
+        <v>547</v>
+      </c>
+      <c r="I514" t="s">
+        <v>21</v>
+      </c>
+      <c r="J514" t="s">
+        <v>30</v>
+      </c>
+      <c r="K514" t="s">
+        <v>23</v>
+      </c>
+      <c r="L514" t="s">
+        <v>2786</v>
+      </c>
+      <c r="M514" t="s">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="515" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B515" t="s">
+        <v>2789</v>
+      </c>
+      <c r="C515" t="s">
+        <v>28</v>
+      </c>
+      <c r="D515" t="s">
+        <v>2790</v>
+      </c>
+      <c r="E515" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F515" t="s">
+        <v>18</v>
+      </c>
+      <c r="G515" t="s">
+        <v>19</v>
+      </c>
+      <c r="H515" t="s">
+        <v>67</v>
+      </c>
+      <c r="I515" t="s">
+        <v>21</v>
+      </c>
+      <c r="J515" t="s">
+        <v>170</v>
+      </c>
+      <c r="K515" t="s">
+        <v>23</v>
+      </c>
+      <c r="L515" t="s">
+        <v>2791</v>
+      </c>
+      <c r="M515" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="516" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>2793</v>
+      </c>
+      <c r="B516" t="s">
+        <v>2794</v>
+      </c>
+      <c r="C516" t="s">
+        <v>15</v>
+      </c>
+      <c r="D516" t="s">
+        <v>2795</v>
+      </c>
+      <c r="E516" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F516" t="s">
+        <v>18</v>
+      </c>
+      <c r="G516" t="s">
+        <v>19</v>
+      </c>
+      <c r="H516" t="s">
+        <v>466</v>
+      </c>
+      <c r="I516" t="s">
+        <v>21</v>
+      </c>
+      <c r="J516" t="s">
+        <v>30</v>
+      </c>
+      <c r="K516" t="s">
+        <v>23</v>
+      </c>
+      <c r="L516" t="s">
+        <v>2796</v>
+      </c>
+      <c r="M516" t="s">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="517" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>2798</v>
+      </c>
+      <c r="B517" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C517" t="s">
+        <v>28</v>
+      </c>
+      <c r="D517" t="s">
+        <v>2800</v>
+      </c>
+      <c r="E517" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F517" t="s">
+        <v>18</v>
+      </c>
+      <c r="G517" t="s">
+        <v>19</v>
+      </c>
+      <c r="H517" t="s">
+        <v>405</v>
+      </c>
+      <c r="I517" t="s">
+        <v>21</v>
+      </c>
+      <c r="J517" t="s">
+        <v>30</v>
+      </c>
+      <c r="K517" t="s">
+        <v>23</v>
+      </c>
+      <c r="L517" t="s">
+        <v>2801</v>
+      </c>
+      <c r="M517" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>2803</v>
+      </c>
+      <c r="B518" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C518" t="s">
+        <v>15</v>
+      </c>
+      <c r="D518" t="s">
+        <v>2805</v>
+      </c>
+      <c r="E518" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F518" t="s">
+        <v>18</v>
+      </c>
+      <c r="G518" t="s">
+        <v>19</v>
+      </c>
+      <c r="H518" t="s">
+        <v>45</v>
+      </c>
+      <c r="I518" t="s">
+        <v>21</v>
+      </c>
+      <c r="J518" t="s">
+        <v>75</v>
+      </c>
+      <c r="K518" t="s">
+        <v>23</v>
+      </c>
+      <c r="L518" t="s">
+        <v>2806</v>
+      </c>
+      <c r="M518" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="519" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>2808</v>
+      </c>
+      <c r="B519" t="s">
+        <v>2809</v>
+      </c>
+      <c r="C519" t="s">
+        <v>28</v>
+      </c>
+      <c r="D519" t="s">
+        <v>2810</v>
+      </c>
+      <c r="E519" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F519" t="s">
+        <v>18</v>
+      </c>
+      <c r="G519" t="s">
+        <v>19</v>
+      </c>
+      <c r="H519" t="s">
+        <v>75</v>
+      </c>
+      <c r="I519" t="s">
+        <v>81</v>
+      </c>
+      <c r="J519" t="s">
+        <v>46</v>
+      </c>
+      <c r="K519" t="s">
+        <v>23</v>
+      </c>
+      <c r="L519" t="s">
+        <v>2811</v>
+      </c>
+      <c r="M519" t="s">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="520" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B520" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C520" t="s">
+        <v>15</v>
+      </c>
+      <c r="D520" t="s">
+        <v>2815</v>
+      </c>
+      <c r="E520" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F520" t="s">
+        <v>18</v>
+      </c>
+      <c r="G520" t="s">
+        <v>19</v>
+      </c>
+      <c r="H520" t="s">
+        <v>37</v>
+      </c>
+      <c r="I520" t="s">
+        <v>21</v>
+      </c>
+      <c r="J520" t="s">
+        <v>46</v>
+      </c>
+      <c r="K520" t="s">
+        <v>23</v>
+      </c>
+      <c r="L520" t="s">
+        <v>2816</v>
+      </c>
+      <c r="M520" t="s">
+        <v>2817</v>
+      </c>
+    </row>
+    <row r="521" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>2818</v>
+      </c>
+      <c r="B521" t="s">
+        <v>2819</v>
+      </c>
+      <c r="C521" t="s">
+        <v>15</v>
+      </c>
+      <c r="D521" t="s">
+        <v>2820</v>
+      </c>
+      <c r="E521" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F521" t="s">
+        <v>18</v>
+      </c>
+      <c r="G521" t="s">
+        <v>19</v>
+      </c>
+      <c r="H521" t="s">
+        <v>381</v>
+      </c>
+      <c r="I521" t="s">
+        <v>21</v>
+      </c>
+      <c r="J521" t="s">
+        <v>340</v>
+      </c>
+      <c r="K521" t="s">
+        <v>23</v>
+      </c>
+      <c r="L521" t="s">
+        <v>2821</v>
+      </c>
+      <c r="M521" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="522" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>2823</v>
+      </c>
+      <c r="B522" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C522" t="s">
+        <v>477</v>
+      </c>
+      <c r="D522" t="s">
+        <v>2825</v>
+      </c>
+      <c r="E522" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F522" t="s">
+        <v>18</v>
+      </c>
+      <c r="G522" t="s">
+        <v>19</v>
+      </c>
+      <c r="H522" t="s">
+        <v>346</v>
+      </c>
+      <c r="I522" t="s">
+        <v>21</v>
+      </c>
+      <c r="J522" t="s">
+        <v>30</v>
+      </c>
+      <c r="K522" t="s">
+        <v>23</v>
+      </c>
+      <c r="L522" t="s">
+        <v>2826</v>
+      </c>
+      <c r="M522" t="s">
+        <v>2827</v>
+      </c>
+    </row>
+    <row r="523" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B523" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C523" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D523" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E523" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F523" t="s">
+        <v>18</v>
+      </c>
+      <c r="G523" t="s">
+        <v>19</v>
+      </c>
+      <c r="H523" t="s">
+        <v>75</v>
+      </c>
+      <c r="I523" t="s">
+        <v>81</v>
+      </c>
+      <c r="J523" t="s">
+        <v>75</v>
+      </c>
+      <c r="K523" t="s">
+        <v>23</v>
+      </c>
+      <c r="L523" t="s">
+        <v>2832</v>
+      </c>
+      <c r="M523" t="s">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="524" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>2834</v>
+      </c>
+      <c r="B524" t="s">
+        <v>2835</v>
+      </c>
+      <c r="C524" t="s">
+        <v>477</v>
+      </c>
+      <c r="D524" t="s">
+        <v>2836</v>
+      </c>
+      <c r="E524" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F524" t="s">
+        <v>18</v>
+      </c>
+      <c r="G524" t="s">
+        <v>19</v>
+      </c>
+      <c r="H524" t="s">
+        <v>45</v>
+      </c>
+      <c r="I524" t="s">
+        <v>21</v>
+      </c>
+      <c r="J524" t="s">
+        <v>75</v>
+      </c>
+      <c r="K524" t="s">
+        <v>23</v>
+      </c>
+      <c r="L524" t="s">
+        <v>2837</v>
+      </c>
+      <c r="M524" t="s">
+        <v>2838</v>
+      </c>
+    </row>
+    <row r="525" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>2839</v>
+      </c>
+      <c r="B525" t="s">
+        <v>2840</v>
+      </c>
+      <c r="C525" t="s">
+        <v>477</v>
+      </c>
+      <c r="D525" t="s">
+        <v>2841</v>
+      </c>
+      <c r="E525" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F525" t="s">
+        <v>18</v>
+      </c>
+      <c r="G525" t="s">
+        <v>19</v>
+      </c>
+      <c r="H525" t="s">
+        <v>45</v>
+      </c>
+      <c r="I525" t="s">
+        <v>21</v>
+      </c>
+      <c r="J525" t="s">
+        <v>46</v>
+      </c>
+      <c r="K525" t="s">
+        <v>23</v>
+      </c>
+      <c r="L525" t="s">
+        <v>2842</v>
+      </c>
+      <c r="M525" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="526" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>2844</v>
+      </c>
+      <c r="B526" t="s">
+        <v>2845</v>
+      </c>
+      <c r="C526" t="s">
+        <v>181</v>
+      </c>
+      <c r="D526" t="s">
+        <v>2846</v>
+      </c>
+      <c r="E526" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F526" t="s">
+        <v>18</v>
+      </c>
+      <c r="G526" t="s">
+        <v>19</v>
+      </c>
+      <c r="H526" t="s">
+        <v>92</v>
+      </c>
+      <c r="I526" t="s">
+        <v>21</v>
+      </c>
+      <c r="J526" t="s">
+        <v>75</v>
+      </c>
+      <c r="K526" t="s">
+        <v>23</v>
+      </c>
+      <c r="L526" t="s">
+        <v>2847</v>
+      </c>
+      <c r="M526" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="527" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
+        <v>2849</v>
+      </c>
+      <c r="B527" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C527" t="s">
+        <v>15</v>
+      </c>
+      <c r="D527" t="s">
+        <v>2851</v>
+      </c>
+      <c r="E527" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F527" t="s">
+        <v>18</v>
+      </c>
+      <c r="G527" t="s">
+        <v>19</v>
+      </c>
+      <c r="H527" t="s">
+        <v>45</v>
+      </c>
+      <c r="I527" t="s">
+        <v>21</v>
+      </c>
+      <c r="J527" t="s">
+        <v>75</v>
+      </c>
+      <c r="K527" t="s">
+        <v>23</v>
+      </c>
+      <c r="L527" t="s">
+        <v>2852</v>
+      </c>
+      <c r="M527" t="s">
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="528" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
+        <v>2854</v>
+      </c>
+      <c r="B528" t="s">
+        <v>2855</v>
+      </c>
+      <c r="C528" t="s">
+        <v>58</v>
+      </c>
+      <c r="D528" t="s">
+        <v>2856</v>
+      </c>
+      <c r="E528" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F528" t="s">
+        <v>18</v>
+      </c>
+      <c r="G528" t="s">
+        <v>19</v>
+      </c>
+      <c r="H528" t="s">
+        <v>223</v>
+      </c>
+      <c r="I528" t="s">
+        <v>291</v>
+      </c>
+      <c r="J528" t="s">
+        <v>75</v>
+      </c>
+      <c r="K528" t="s">
+        <v>23</v>
+      </c>
+      <c r="L528" t="s">
+        <v>2857</v>
+      </c>
+      <c r="M528" t="s">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="529" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>2859</v>
+      </c>
+      <c r="B529" t="s">
+        <v>2860</v>
+      </c>
+      <c r="C529" t="s">
+        <v>73</v>
+      </c>
+      <c r="D529" t="s">
+        <v>2861</v>
+      </c>
+      <c r="E529" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F529" t="s">
+        <v>18</v>
+      </c>
+      <c r="G529" t="s">
+        <v>19</v>
+      </c>
+      <c r="H529" t="s">
+        <v>120</v>
+      </c>
+      <c r="I529" t="s">
+        <v>21</v>
+      </c>
+      <c r="J529" t="s">
+        <v>75</v>
+      </c>
+      <c r="K529" t="s">
+        <v>23</v>
+      </c>
+      <c r="L529" t="s">
+        <v>2862</v>
+      </c>
+      <c r="M529" t="s">
+        <v>2863</v>
+      </c>
+    </row>
+    <row r="530" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
+        <v>2864</v>
+      </c>
+      <c r="B530" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C530" t="s">
+        <v>73</v>
+      </c>
+      <c r="D530" t="s">
+        <v>2866</v>
+      </c>
+      <c r="E530" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F530" t="s">
+        <v>18</v>
+      </c>
+      <c r="G530" t="s">
+        <v>19</v>
+      </c>
+      <c r="H530" t="s">
+        <v>120</v>
+      </c>
+      <c r="I530" t="s">
+        <v>21</v>
+      </c>
+      <c r="J530" t="s">
+        <v>75</v>
+      </c>
+      <c r="K530" t="s">
+        <v>23</v>
+      </c>
+      <c r="L530" t="s">
+        <v>2867</v>
+      </c>
+      <c r="M530" t="s">
+        <v>2868</v>
+      </c>
+    </row>
+    <row r="531" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>2869</v>
+      </c>
+      <c r="B531" t="s">
+        <v>2870</v>
+      </c>
+      <c r="C531" t="s">
+        <v>73</v>
+      </c>
+      <c r="D531" t="s">
+        <v>2871</v>
+      </c>
+      <c r="E531" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F531" t="s">
+        <v>18</v>
+      </c>
+      <c r="G531" t="s">
+        <v>19</v>
+      </c>
+      <c r="H531" t="s">
+        <v>223</v>
+      </c>
+      <c r="I531" t="s">
+        <v>21</v>
+      </c>
+      <c r="J531" t="s">
+        <v>75</v>
+      </c>
+      <c r="K531" t="s">
+        <v>23</v>
+      </c>
+      <c r="L531" t="s">
+        <v>2872</v>
+      </c>
+      <c r="M531" t="s">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="532" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>2874</v>
+      </c>
+      <c r="B532" t="s">
+        <v>2875</v>
+      </c>
+      <c r="C532" t="s">
+        <v>73</v>
+      </c>
+      <c r="D532" t="s">
+        <v>2876</v>
+      </c>
+      <c r="E532" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F532" t="s">
+        <v>18</v>
+      </c>
+      <c r="G532" t="s">
+        <v>19</v>
+      </c>
+      <c r="H532" t="s">
+        <v>45</v>
+      </c>
+      <c r="I532" t="s">
+        <v>21</v>
+      </c>
+      <c r="J532" t="s">
+        <v>75</v>
+      </c>
+      <c r="K532" t="s">
+        <v>23</v>
+      </c>
+      <c r="L532" t="s">
+        <v>2877</v>
+      </c>
+      <c r="M532" t="s">
+        <v>2878</v>
+      </c>
+    </row>
+    <row r="533" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
+        <v>2879</v>
+      </c>
+      <c r="B533" t="s">
+        <v>2880</v>
+      </c>
+      <c r="C533" t="s">
+        <v>73</v>
+      </c>
+      <c r="D533" t="s">
+        <v>2881</v>
+      </c>
+      <c r="E533" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F533" t="s">
+        <v>18</v>
+      </c>
+      <c r="G533" t="s">
+        <v>19</v>
+      </c>
+      <c r="H533" t="s">
+        <v>120</v>
+      </c>
+      <c r="I533" t="s">
+        <v>21</v>
+      </c>
+      <c r="J533" t="s">
+        <v>75</v>
+      </c>
+      <c r="K533" t="s">
+        <v>23</v>
+      </c>
+      <c r="L533" t="s">
+        <v>2882</v>
+      </c>
+      <c r="M533" t="s">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="534" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
+        <v>2884</v>
+      </c>
+      <c r="B534" t="s">
+        <v>2885</v>
+      </c>
+      <c r="C534" t="s">
+        <v>910</v>
+      </c>
+      <c r="D534" t="s">
+        <v>2886</v>
+      </c>
+      <c r="E534" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F534" t="s">
+        <v>18</v>
+      </c>
+      <c r="G534" t="s">
+        <v>19</v>
+      </c>
+      <c r="H534" t="s">
+        <v>103</v>
+      </c>
+      <c r="I534" t="s">
+        <v>21</v>
+      </c>
+      <c r="J534" t="s">
+        <v>46</v>
+      </c>
+      <c r="K534" t="s">
+        <v>23</v>
+      </c>
+      <c r="L534" t="s">
+        <v>2887</v>
+      </c>
+      <c r="M534" t="s">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="535" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
+        <v>2889</v>
+      </c>
+      <c r="B535" t="s">
+        <v>2890</v>
+      </c>
+      <c r="C535" t="s">
+        <v>910</v>
+      </c>
+      <c r="D535" t="s">
+        <v>2891</v>
+      </c>
+      <c r="E535" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F535" t="s">
+        <v>18</v>
+      </c>
+      <c r="G535" t="s">
+        <v>19</v>
+      </c>
+      <c r="H535" t="s">
+        <v>103</v>
+      </c>
+      <c r="I535" t="s">
+        <v>21</v>
+      </c>
+      <c r="J535" t="s">
+        <v>46</v>
+      </c>
+      <c r="K535" t="s">
+        <v>23</v>
+      </c>
+      <c r="L535" t="s">
+        <v>2892</v>
+      </c>
+      <c r="M535" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="536" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A536" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B536" t="s">
+        <v>2895</v>
+      </c>
+      <c r="C536" t="s">
+        <v>15</v>
+      </c>
+      <c r="D536" t="s">
+        <v>2896</v>
+      </c>
+      <c r="E536" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F536" t="s">
+        <v>18</v>
+      </c>
+      <c r="G536" t="s">
+        <v>19</v>
+      </c>
+      <c r="H536" t="s">
+        <v>92</v>
+      </c>
+      <c r="I536" t="s">
+        <v>21</v>
+      </c>
+      <c r="J536" t="s">
+        <v>75</v>
+      </c>
+      <c r="K536" t="s">
+        <v>23</v>
+      </c>
+      <c r="L536" t="s">
+        <v>2897</v>
+      </c>
+      <c r="M536" t="s">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="537" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
+        <v>2899</v>
+      </c>
+      <c r="B537" t="s">
+        <v>2900</v>
+      </c>
+      <c r="C537" t="s">
+        <v>15</v>
+      </c>
+      <c r="D537" t="s">
+        <v>2901</v>
+      </c>
+      <c r="E537" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F537" t="s">
+        <v>18</v>
+      </c>
+      <c r="G537" t="s">
+        <v>19</v>
+      </c>
+      <c r="H537" t="s">
+        <v>381</v>
+      </c>
+      <c r="I537" t="s">
+        <v>21</v>
+      </c>
+      <c r="J537" t="s">
+        <v>2902</v>
+      </c>
+      <c r="K537" t="s">
+        <v>23</v>
+      </c>
+      <c r="L537" t="s">
+        <v>2903</v>
+      </c>
+      <c r="M537" t="s">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="538" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
+        <v>2905</v>
+      </c>
+      <c r="B538" t="s">
+        <v>2906</v>
+      </c>
+      <c r="C538" t="s">
+        <v>15</v>
+      </c>
+      <c r="D538" t="s">
+        <v>2907</v>
+      </c>
+      <c r="E538" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F538" t="s">
+        <v>18</v>
+      </c>
+      <c r="G538" t="s">
+        <v>19</v>
+      </c>
+      <c r="H538" t="s">
+        <v>45</v>
+      </c>
+      <c r="I538" t="s">
+        <v>21</v>
+      </c>
+      <c r="J538" t="s">
+        <v>46</v>
+      </c>
+      <c r="K538" t="s">
+        <v>23</v>
+      </c>
+      <c r="L538" t="s">
+        <v>2908</v>
+      </c>
+      <c r="M538" t="s">
+        <v>2909</v>
+      </c>
+    </row>
+    <row r="539" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B539" t="s">
+        <v>2911</v>
+      </c>
+      <c r="C539" t="s">
+        <v>15</v>
+      </c>
+      <c r="D539" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E539" t="s">
+        <v>2913</v>
+      </c>
+      <c r="F539" t="s">
+        <v>18</v>
+      </c>
+      <c r="G539" t="s">
+        <v>19</v>
+      </c>
+      <c r="H539" t="s">
+        <v>45</v>
+      </c>
+      <c r="I539" t="s">
+        <v>21</v>
+      </c>
+      <c r="J539" t="s">
+        <v>46</v>
+      </c>
+      <c r="K539" t="s">
+        <v>23</v>
+      </c>
+      <c r="L539" t="s">
+        <v>2914</v>
+      </c>
+      <c r="M539" t="s">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="540" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
+        <v>2916</v>
+      </c>
+      <c r="B540" t="s">
+        <v>2917</v>
+      </c>
+      <c r="C540" t="s">
+        <v>28</v>
+      </c>
+      <c r="D540" t="s">
+        <v>2918</v>
+      </c>
+      <c r="E540" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F540" t="s">
+        <v>18</v>
+      </c>
+      <c r="G540" t="s">
+        <v>19</v>
+      </c>
+      <c r="H540" t="s">
+        <v>45</v>
+      </c>
+      <c r="I540" t="s">
+        <v>21</v>
+      </c>
+      <c r="J540" t="s">
+        <v>46</v>
+      </c>
+      <c r="K540" t="s">
+        <v>23</v>
+      </c>
+      <c r="L540" t="s">
+        <v>2920</v>
+      </c>
+      <c r="M540" t="s">
+        <v>2921</v>
+      </c>
+    </row>
+    <row r="541" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B541" t="s">
+        <v>2923</v>
+      </c>
+      <c r="C541" t="s">
+        <v>28</v>
+      </c>
+      <c r="D541" t="s">
+        <v>2924</v>
+      </c>
+      <c r="E541" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F541" t="s">
+        <v>18</v>
+      </c>
+      <c r="G541" t="s">
+        <v>19</v>
+      </c>
+      <c r="H541" t="s">
+        <v>37</v>
+      </c>
+      <c r="I541" t="s">
+        <v>21</v>
+      </c>
+      <c r="J541" t="s">
+        <v>46</v>
+      </c>
+      <c r="K541" t="s">
+        <v>23</v>
+      </c>
+      <c r="L541" t="s">
+        <v>2925</v>
+      </c>
+      <c r="M541" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="542" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>2927</v>
+      </c>
+      <c r="B542" t="s">
+        <v>2928</v>
+      </c>
+      <c r="C542" t="s">
+        <v>28</v>
+      </c>
+      <c r="D542" t="s">
+        <v>2929</v>
+      </c>
+      <c r="E542" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F542" t="s">
+        <v>18</v>
+      </c>
+      <c r="G542" t="s">
+        <v>19</v>
+      </c>
+      <c r="H542" t="s">
+        <v>37</v>
+      </c>
+      <c r="I542" t="s">
+        <v>21</v>
+      </c>
+      <c r="J542" t="s">
+        <v>479</v>
+      </c>
+      <c r="K542" t="s">
+        <v>23</v>
+      </c>
+      <c r="L542" t="s">
+        <v>2930</v>
+      </c>
+      <c r="M542" t="s">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="543" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B543" t="s">
+        <v>2933</v>
+      </c>
+      <c r="C543" t="s">
+        <v>28</v>
+      </c>
+      <c r="D543" t="s">
+        <v>2934</v>
+      </c>
+      <c r="E543" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F543" t="s">
+        <v>18</v>
+      </c>
+      <c r="G543" t="s">
+        <v>19</v>
+      </c>
+      <c r="H543" t="s">
+        <v>45</v>
+      </c>
+      <c r="I543" t="s">
+        <v>21</v>
+      </c>
+      <c r="J543" t="s">
+        <v>46</v>
+      </c>
+      <c r="K543" t="s">
+        <v>23</v>
+      </c>
+      <c r="L543" t="s">
+        <v>2935</v>
+      </c>
+      <c r="M543" t="s">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="544" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
+        <v>2937</v>
+      </c>
+      <c r="B544" t="s">
+        <v>2938</v>
+      </c>
+      <c r="C544" t="s">
+        <v>28</v>
+      </c>
+      <c r="D544" t="s">
+        <v>2939</v>
+      </c>
+      <c r="E544" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F544" t="s">
+        <v>18</v>
+      </c>
+      <c r="G544" t="s">
+        <v>19</v>
+      </c>
+      <c r="H544" t="s">
+        <v>939</v>
+      </c>
+      <c r="I544" t="s">
+        <v>21</v>
+      </c>
+      <c r="J544" t="s">
+        <v>30</v>
+      </c>
+      <c r="K544" t="s">
+        <v>23</v>
+      </c>
+      <c r="L544" t="s">
+        <v>2940</v>
+      </c>
+      <c r="M544" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="545" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>2942</v>
+      </c>
+      <c r="B545" t="s">
+        <v>2943</v>
+      </c>
+      <c r="C545" t="s">
+        <v>28</v>
+      </c>
+      <c r="D545" t="s">
+        <v>2944</v>
+      </c>
+      <c r="E545" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F545" t="s">
+        <v>18</v>
+      </c>
+      <c r="G545" t="s">
+        <v>19</v>
+      </c>
+      <c r="H545" t="s">
+        <v>621</v>
+      </c>
+      <c r="I545" t="s">
+        <v>21</v>
+      </c>
+      <c r="J545" t="s">
+        <v>30</v>
+      </c>
+      <c r="K545" t="s">
+        <v>23</v>
+      </c>
+      <c r="L545" t="s">
+        <v>2945</v>
+      </c>
+      <c r="M545" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="546" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>2947</v>
+      </c>
+      <c r="B546" t="s">
+        <v>2948</v>
+      </c>
+      <c r="C546" t="s">
+        <v>333</v>
+      </c>
+      <c r="D546" t="s">
+        <v>2949</v>
+      </c>
+      <c r="E546" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F546" t="s">
+        <v>18</v>
+      </c>
+      <c r="G546" t="s">
+        <v>19</v>
+      </c>
+      <c r="H546" t="s">
+        <v>241</v>
+      </c>
+      <c r="I546" t="s">
+        <v>21</v>
+      </c>
+      <c r="J546" t="s">
+        <v>75</v>
+      </c>
+      <c r="K546" t="s">
+        <v>23</v>
+      </c>
+      <c r="L546" t="s">
+        <v>2950</v>
+      </c>
+      <c r="M546" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="547" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>2952</v>
+      </c>
+      <c r="B547" t="s">
+        <v>2953</v>
+      </c>
+      <c r="C547" t="s">
+        <v>15</v>
+      </c>
+      <c r="D547" t="s">
+        <v>2954</v>
+      </c>
+      <c r="E547" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F547" t="s">
+        <v>18</v>
+      </c>
+      <c r="G547" t="s">
+        <v>19</v>
+      </c>
+      <c r="H547" t="s">
+        <v>120</v>
+      </c>
+      <c r="I547" t="s">
+        <v>21</v>
+      </c>
+      <c r="J547" t="s">
+        <v>30</v>
+      </c>
+      <c r="K547" t="s">
+        <v>23</v>
+      </c>
+      <c r="L547" t="s">
+        <v>2955</v>
+      </c>
+      <c r="M547" t="s">
+        <v>2956</v>
+      </c>
+    </row>
+    <row r="548" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>2957</v>
+      </c>
+      <c r="B548" t="s">
+        <v>2958</v>
+      </c>
+      <c r="C548" t="s">
+        <v>15</v>
+      </c>
+      <c r="D548" t="s">
+        <v>2959</v>
+      </c>
+      <c r="E548" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F548" t="s">
+        <v>18</v>
+      </c>
+      <c r="G548" t="s">
+        <v>19</v>
+      </c>
+      <c r="H548" t="s">
+        <v>45</v>
+      </c>
+      <c r="I548" t="s">
+        <v>21</v>
+      </c>
+      <c r="J548" t="s">
+        <v>46</v>
+      </c>
+      <c r="K548" t="s">
+        <v>23</v>
+      </c>
+      <c r="L548" t="s">
+        <v>2960</v>
+      </c>
+      <c r="M548" t="s">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="549" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>2962</v>
+      </c>
+      <c r="B549" t="s">
+        <v>2963</v>
+      </c>
+      <c r="C549" t="s">
+        <v>15</v>
+      </c>
+      <c r="D549" t="s">
+        <v>2964</v>
+      </c>
+      <c r="E549" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F549" t="s">
+        <v>18</v>
+      </c>
+      <c r="G549" t="s">
+        <v>19</v>
+      </c>
+      <c r="H549" t="s">
+        <v>37</v>
+      </c>
+      <c r="I549" t="s">
+        <v>21</v>
+      </c>
+      <c r="J549" t="s">
+        <v>46</v>
+      </c>
+      <c r="K549" t="s">
+        <v>23</v>
+      </c>
+      <c r="L549" t="s">
+        <v>2965</v>
+      </c>
+      <c r="M549" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="550" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>2967</v>
+      </c>
+      <c r="B550" t="s">
+        <v>2968</v>
+      </c>
+      <c r="C550" t="s">
+        <v>15</v>
+      </c>
+      <c r="D550" t="s">
+        <v>2969</v>
+      </c>
+      <c r="E550" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F550" t="s">
+        <v>18</v>
+      </c>
+      <c r="G550" t="s">
+        <v>19</v>
+      </c>
+      <c r="H550" t="s">
+        <v>398</v>
+      </c>
+      <c r="I550" t="s">
+        <v>21</v>
+      </c>
+      <c r="J550" t="s">
+        <v>340</v>
+      </c>
+      <c r="K550" t="s">
+        <v>23</v>
+      </c>
+      <c r="L550" t="s">
+        <v>2970</v>
+      </c>
+      <c r="M550" t="s">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="551" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>2972</v>
+      </c>
+      <c r="B551" t="s">
+        <v>2973</v>
+      </c>
+      <c r="C551" t="s">
+        <v>15</v>
+      </c>
+      <c r="D551" t="s">
+        <v>2974</v>
+      </c>
+      <c r="E551" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F551" t="s">
+        <v>18</v>
+      </c>
+      <c r="G551" t="s">
+        <v>19</v>
+      </c>
+      <c r="H551" t="s">
+        <v>939</v>
+      </c>
+      <c r="I551" t="s">
+        <v>21</v>
+      </c>
+      <c r="J551" t="s">
+        <v>297</v>
+      </c>
+      <c r="K551" t="s">
+        <v>23</v>
+      </c>
+      <c r="L551" t="s">
+        <v>2975</v>
+      </c>
+      <c r="M551" t="s">
+        <v>2976</v>
+      </c>
+    </row>
+    <row r="552" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>2977</v>
+      </c>
+      <c r="B552" t="s">
+        <v>2978</v>
+      </c>
+      <c r="C552" t="s">
+        <v>15</v>
+      </c>
+      <c r="D552" t="s">
+        <v>2979</v>
+      </c>
+      <c r="E552" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F552" t="s">
+        <v>18</v>
+      </c>
+      <c r="G552" t="s">
+        <v>19</v>
+      </c>
+      <c r="H552" t="s">
+        <v>45</v>
+      </c>
+      <c r="I552" t="s">
+        <v>21</v>
+      </c>
+      <c r="J552" t="s">
+        <v>2980</v>
+      </c>
+      <c r="K552" t="s">
+        <v>23</v>
+      </c>
+      <c r="L552" t="s">
+        <v>2981</v>
+      </c>
+      <c r="M552" t="s">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="553" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>2983</v>
+      </c>
+      <c r="B553" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C553" t="s">
+        <v>15</v>
+      </c>
+      <c r="D553" t="s">
+        <v>2985</v>
+      </c>
+      <c r="E553" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F553" t="s">
+        <v>18</v>
+      </c>
+      <c r="G553" t="s">
+        <v>19</v>
+      </c>
+      <c r="H553" t="s">
+        <v>381</v>
+      </c>
+      <c r="I553" t="s">
+        <v>21</v>
+      </c>
+      <c r="J553" t="s">
+        <v>46</v>
+      </c>
+      <c r="K553" t="s">
+        <v>23</v>
+      </c>
+      <c r="L553" t="s">
+        <v>2986</v>
+      </c>
+      <c r="M553" t="s">
+        <v>2987</v>
+      </c>
+    </row>
+    <row r="554" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>2988</v>
+      </c>
+      <c r="B554" t="s">
+        <v>2989</v>
+      </c>
+      <c r="C554" t="s">
+        <v>15</v>
+      </c>
+      <c r="D554" t="s">
+        <v>2990</v>
+      </c>
+      <c r="E554" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F554" t="s">
+        <v>18</v>
+      </c>
+      <c r="G554" t="s">
+        <v>19</v>
+      </c>
+      <c r="H554" t="s">
+        <v>211</v>
+      </c>
+      <c r="I554" t="s">
+        <v>21</v>
+      </c>
+      <c r="J554" t="s">
+        <v>46</v>
+      </c>
+      <c r="K554" t="s">
+        <v>23</v>
+      </c>
+      <c r="L554" t="s">
+        <v>2991</v>
+      </c>
+      <c r="M554" t="s">
+        <v>2992</v>
+      </c>
+    </row>
+    <row r="555" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>2993</v>
+      </c>
+      <c r="B555" t="s">
+        <v>2994</v>
+      </c>
+      <c r="C555" t="s">
+        <v>58</v>
+      </c>
+      <c r="D555" t="s">
+        <v>2995</v>
+      </c>
+      <c r="E555" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F555" t="s">
+        <v>18</v>
+      </c>
+      <c r="G555" t="s">
+        <v>19</v>
+      </c>
+      <c r="H555" t="s">
+        <v>92</v>
+      </c>
+      <c r="I555" t="s">
+        <v>581</v>
+      </c>
+      <c r="J555" t="s">
+        <v>2996</v>
+      </c>
+      <c r="K555" t="s">
+        <v>23</v>
+      </c>
+      <c r="L555" t="s">
+        <v>2997</v>
+      </c>
+      <c r="M555" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="556" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>2999</v>
+      </c>
+      <c r="B556" t="s">
+        <v>3000</v>
+      </c>
+      <c r="C556" t="s">
+        <v>73</v>
+      </c>
+      <c r="D556" t="s">
+        <v>3001</v>
+      </c>
+      <c r="E556" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F556" t="s">
+        <v>18</v>
+      </c>
+      <c r="G556" t="s">
+        <v>19</v>
+      </c>
+      <c r="H556" t="s">
+        <v>627</v>
+      </c>
+      <c r="I556" t="s">
+        <v>21</v>
+      </c>
+      <c r="J556" t="s">
+        <v>75</v>
+      </c>
+      <c r="K556" t="s">
+        <v>23</v>
+      </c>
+      <c r="L556" t="s">
+        <v>3002</v>
+      </c>
+      <c r="M556" t="s">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="557" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>3004</v>
+      </c>
+      <c r="B557" t="s">
+        <v>3005</v>
+      </c>
+      <c r="C557" t="s">
+        <v>15</v>
+      </c>
+      <c r="D557" t="s">
+        <v>3006</v>
+      </c>
+      <c r="E557" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F557" t="s">
+        <v>18</v>
+      </c>
+      <c r="G557" t="s">
+        <v>19</v>
+      </c>
+      <c r="H557" t="s">
+        <v>45</v>
+      </c>
+      <c r="I557" t="s">
+        <v>21</v>
+      </c>
+      <c r="J557" t="s">
+        <v>3007</v>
+      </c>
+      <c r="K557" t="s">
+        <v>23</v>
+      </c>
+      <c r="L557" t="s">
+        <v>3008</v>
+      </c>
+      <c r="M557" t="s">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="558" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>3010</v>
+      </c>
+      <c r="B558" t="s">
+        <v>3011</v>
+      </c>
+      <c r="C558" t="s">
+        <v>28</v>
+      </c>
+      <c r="D558" t="s">
+        <v>3012</v>
+      </c>
+      <c r="E558" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F558" t="s">
+        <v>18</v>
+      </c>
+      <c r="G558" t="s">
+        <v>19</v>
+      </c>
+      <c r="H558" t="s">
+        <v>992</v>
+      </c>
+      <c r="I558" t="s">
+        <v>21</v>
+      </c>
+      <c r="J558" t="s">
+        <v>75</v>
+      </c>
+      <c r="K558" t="s">
+        <v>23</v>
+      </c>
+      <c r="L558" t="s">
+        <v>3013</v>
+      </c>
+      <c r="M558" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="559" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>3015</v>
+      </c>
+      <c r="B559" t="s">
+        <v>3016</v>
+      </c>
+      <c r="C559" t="s">
+        <v>15</v>
+      </c>
+      <c r="D559" t="s">
+        <v>3017</v>
+      </c>
+      <c r="E559" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F559" t="s">
+        <v>18</v>
+      </c>
+      <c r="G559" t="s">
+        <v>19</v>
+      </c>
+      <c r="H559" t="s">
+        <v>67</v>
+      </c>
+      <c r="I559" t="s">
+        <v>21</v>
+      </c>
+      <c r="J559" t="s">
+        <v>46</v>
+      </c>
+      <c r="K559" t="s">
+        <v>23</v>
+      </c>
+      <c r="L559" t="s">
+        <v>3018</v>
+      </c>
+      <c r="M559" t="s">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="560" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B560" t="s">
+        <v>3021</v>
+      </c>
+      <c r="C560" t="s">
+        <v>15</v>
+      </c>
+      <c r="D560" t="s">
+        <v>3022</v>
+      </c>
+      <c r="E560" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F560" t="s">
+        <v>18</v>
+      </c>
+      <c r="G560" t="s">
+        <v>19</v>
+      </c>
+      <c r="H560" t="s">
+        <v>67</v>
+      </c>
+      <c r="I560" t="s">
+        <v>21</v>
+      </c>
+      <c r="J560" t="s">
+        <v>46</v>
+      </c>
+      <c r="K560" t="s">
+        <v>23</v>
+      </c>
+      <c r="L560" t="s">
+        <v>3023</v>
+      </c>
+      <c r="M560" t="s">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="561" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>3025</v>
+      </c>
+      <c r="B561" t="s">
+        <v>3026</v>
+      </c>
+      <c r="C561" t="s">
+        <v>526</v>
+      </c>
+      <c r="D561" t="s">
+        <v>3027</v>
+      </c>
+      <c r="E561" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F561" t="s">
+        <v>18</v>
+      </c>
+      <c r="G561" t="s">
+        <v>19</v>
+      </c>
+      <c r="H561" t="s">
+        <v>75</v>
+      </c>
+      <c r="I561" t="s">
+        <v>81</v>
+      </c>
+      <c r="J561" t="s">
+        <v>75</v>
+      </c>
+      <c r="K561" t="s">
+        <v>23</v>
+      </c>
+      <c r="L561" t="s">
+        <v>3028</v>
+      </c>
+      <c r="M561" t="s">
+        <v>3029</v>
+      </c>
+    </row>
+    <row r="562" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>3030</v>
+      </c>
+      <c r="B562" t="s">
+        <v>3031</v>
+      </c>
+      <c r="C562" t="s">
+        <v>58</v>
+      </c>
+      <c r="D562" t="s">
+        <v>3032</v>
+      </c>
+      <c r="E562" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F562" t="s">
+        <v>18</v>
+      </c>
+      <c r="G562" t="s">
+        <v>19</v>
+      </c>
+      <c r="H562" t="s">
+        <v>45</v>
+      </c>
+      <c r="I562" t="s">
+        <v>3033</v>
+      </c>
+      <c r="J562" t="s">
+        <v>75</v>
+      </c>
+      <c r="K562" t="s">
+        <v>23</v>
+      </c>
+      <c r="L562" t="s">
+        <v>3034</v>
+      </c>
+      <c r="M562" t="s">
+        <v>3035</v>
+      </c>
+    </row>
+    <row r="563" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>3036</v>
+      </c>
+      <c r="B563" t="s">
+        <v>3037</v>
+      </c>
+      <c r="C563" t="s">
+        <v>15</v>
+      </c>
+      <c r="D563" t="s">
+        <v>3038</v>
+      </c>
+      <c r="E563" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F563" t="s">
+        <v>18</v>
+      </c>
+      <c r="G563" t="s">
+        <v>19</v>
+      </c>
+      <c r="H563" t="s">
+        <v>92</v>
+      </c>
+      <c r="I563" t="s">
+        <v>21</v>
+      </c>
+      <c r="J563" t="s">
+        <v>46</v>
+      </c>
+      <c r="K563" t="s">
+        <v>23</v>
+      </c>
+      <c r="L563" t="s">
+        <v>3039</v>
+      </c>
+      <c r="M563" t="s">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="564" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B564" t="s">
+        <v>3042</v>
+      </c>
+      <c r="C564" t="s">
+        <v>58</v>
+      </c>
+      <c r="D564" t="s">
+        <v>3043</v>
+      </c>
+      <c r="E564" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F564" t="s">
+        <v>18</v>
+      </c>
+      <c r="G564" t="s">
+        <v>19</v>
+      </c>
+      <c r="H564" t="s">
+        <v>45</v>
+      </c>
+      <c r="I564" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J564" t="s">
+        <v>75</v>
+      </c>
+      <c r="K564" t="s">
+        <v>23</v>
+      </c>
+      <c r="L564" t="s">
+        <v>3044</v>
+      </c>
+      <c r="M564" t="s">
+        <v>3045</v>
+      </c>
+    </row>
+    <row r="565" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>3046</v>
+      </c>
+      <c r="B565" t="s">
+        <v>3047</v>
+      </c>
+      <c r="C565" t="s">
+        <v>58</v>
+      </c>
+      <c r="D565" t="s">
+        <v>3048</v>
+      </c>
+      <c r="E565" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F565" t="s">
+        <v>18</v>
+      </c>
+      <c r="G565" t="s">
+        <v>19</v>
+      </c>
+      <c r="H565" t="s">
+        <v>45</v>
+      </c>
+      <c r="I565" t="s">
+        <v>569</v>
+      </c>
+      <c r="J565" t="s">
+        <v>75</v>
+      </c>
+      <c r="K565" t="s">
+        <v>23</v>
+      </c>
+      <c r="L565" t="s">
+        <v>3049</v>
+      </c>
+      <c r="M565" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="566" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>3051</v>
+      </c>
+      <c r="B566" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C566" t="s">
+        <v>58</v>
+      </c>
+      <c r="D566" t="s">
+        <v>3053</v>
+      </c>
+      <c r="E566" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F566" t="s">
+        <v>18</v>
+      </c>
+      <c r="G566" t="s">
+        <v>19</v>
+      </c>
+      <c r="H566" t="s">
+        <v>75</v>
+      </c>
+      <c r="I566" t="s">
+        <v>534</v>
+      </c>
+      <c r="J566" t="s">
+        <v>75</v>
+      </c>
+      <c r="K566" t="s">
+        <v>23</v>
+      </c>
+      <c r="L566" t="s">
+        <v>3054</v>
+      </c>
+      <c r="M566" t="s">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="567" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B567" t="s">
+        <v>3057</v>
+      </c>
+      <c r="C567" t="s">
+        <v>15</v>
+      </c>
+      <c r="D567" t="s">
+        <v>3058</v>
+      </c>
+      <c r="E567" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F567" t="s">
+        <v>18</v>
+      </c>
+      <c r="G567" t="s">
+        <v>19</v>
+      </c>
+      <c r="H567" t="s">
+        <v>37</v>
+      </c>
+      <c r="I567" t="s">
+        <v>21</v>
+      </c>
+      <c r="J567" t="s">
+        <v>30</v>
+      </c>
+      <c r="K567" t="s">
+        <v>23</v>
+      </c>
+      <c r="L567" t="s">
+        <v>3060</v>
+      </c>
+      <c r="M567" t="s">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>3062</v>
+      </c>
+      <c r="B568" t="s">
+        <v>3063</v>
+      </c>
+      <c r="C568" t="s">
+        <v>15</v>
+      </c>
+      <c r="D568" t="s">
+        <v>3064</v>
+      </c>
+      <c r="E568" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F568" t="s">
+        <v>18</v>
+      </c>
+      <c r="G568" t="s">
+        <v>19</v>
+      </c>
+      <c r="H568" t="s">
+        <v>627</v>
+      </c>
+      <c r="I568" t="s">
+        <v>21</v>
+      </c>
+      <c r="J568" t="s">
+        <v>46</v>
+      </c>
+      <c r="K568" t="s">
+        <v>23</v>
+      </c>
+      <c r="L568" t="s">
+        <v>3065</v>
+      </c>
+      <c r="M568" t="s">
+        <v>3066</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>3067</v>
+      </c>
+      <c r="B569" t="s">
+        <v>3068</v>
+      </c>
+      <c r="C569" t="s">
+        <v>15</v>
+      </c>
+      <c r="D569" t="s">
+        <v>3069</v>
+      </c>
+      <c r="E569" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F569" t="s">
+        <v>18</v>
+      </c>
+      <c r="G569" t="s">
+        <v>19</v>
+      </c>
+      <c r="H569" t="s">
+        <v>45</v>
+      </c>
+      <c r="I569" t="s">
+        <v>21</v>
+      </c>
+      <c r="J569" t="s">
+        <v>46</v>
+      </c>
+      <c r="K569" t="s">
+        <v>23</v>
+      </c>
+      <c r="L569" t="s">
+        <v>3070</v>
+      </c>
+      <c r="M569" t="s">
+        <v>3071</v>
+      </c>
+    </row>
+    <row r="570" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
+        <v>3072</v>
+      </c>
+      <c r="B570" t="s">
+        <v>3073</v>
+      </c>
+      <c r="C570" t="s">
+        <v>15</v>
+      </c>
+      <c r="D570" t="s">
+        <v>3074</v>
+      </c>
+      <c r="E570" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F570" t="s">
+        <v>18</v>
+      </c>
+      <c r="G570" t="s">
+        <v>19</v>
+      </c>
+      <c r="H570" t="s">
+        <v>37</v>
+      </c>
+      <c r="I570" t="s">
+        <v>21</v>
+      </c>
+      <c r="J570" t="s">
+        <v>30</v>
+      </c>
+      <c r="K570" t="s">
+        <v>23</v>
+      </c>
+      <c r="L570" t="s">
+        <v>3075</v>
+      </c>
+      <c r="M570" t="s">
+        <v>3076</v>
+      </c>
+    </row>
+    <row r="571" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
+        <v>3077</v>
+      </c>
+      <c r="B571" t="s">
+        <v>3078</v>
+      </c>
+      <c r="C571" t="s">
+        <v>15</v>
+      </c>
+      <c r="D571" t="s">
+        <v>3079</v>
+      </c>
+      <c r="E571" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F571" t="s">
+        <v>18</v>
+      </c>
+      <c r="G571" t="s">
+        <v>19</v>
+      </c>
+      <c r="H571" t="s">
+        <v>346</v>
+      </c>
+      <c r="I571" t="s">
+        <v>21</v>
+      </c>
+      <c r="J571" t="s">
+        <v>30</v>
+      </c>
+      <c r="K571" t="s">
+        <v>23</v>
+      </c>
+      <c r="L571" t="s">
+        <v>3080</v>
+      </c>
+      <c r="M571" t="s">
+        <v>3081</v>
+      </c>
+    </row>
+    <row r="572" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
+        <v>3082</v>
+      </c>
+      <c r="B572" t="s">
+        <v>3083</v>
+      </c>
+      <c r="C572" t="s">
+        <v>15</v>
+      </c>
+      <c r="D572" t="s">
+        <v>3084</v>
+      </c>
+      <c r="E572" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F572" t="s">
+        <v>18</v>
+      </c>
+      <c r="G572" t="s">
+        <v>19</v>
+      </c>
+      <c r="H572" t="s">
+        <v>75</v>
+      </c>
+      <c r="I572" t="s">
+        <v>81</v>
+      </c>
+      <c r="J572" t="s">
+        <v>75</v>
+      </c>
+      <c r="K572" t="s">
+        <v>23</v>
+      </c>
+      <c r="L572" t="s">
+        <v>3085</v>
+      </c>
+      <c r="M572" t="s">
+        <v>3086</v>
+      </c>
+    </row>
+    <row r="573" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>3087</v>
+      </c>
+      <c r="B573" t="s">
+        <v>3088</v>
+      </c>
+      <c r="C573" t="s">
+        <v>15</v>
+      </c>
+      <c r="D573" t="s">
+        <v>3089</v>
+      </c>
+      <c r="E573" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F573" t="s">
+        <v>18</v>
+      </c>
+      <c r="G573" t="s">
+        <v>19</v>
+      </c>
+      <c r="H573" t="s">
+        <v>547</v>
+      </c>
+      <c r="I573" t="s">
+        <v>21</v>
+      </c>
+      <c r="J573" t="s">
+        <v>75</v>
+      </c>
+      <c r="K573" t="s">
+        <v>23</v>
+      </c>
+      <c r="L573" t="s">
+        <v>3090</v>
+      </c>
+      <c r="M573" t="s">
+        <v>3091</v>
+      </c>
+    </row>
+    <row r="574" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
+        <v>3092</v>
+      </c>
+      <c r="B574" t="s">
+        <v>3093</v>
+      </c>
+      <c r="C574" t="s">
+        <v>15</v>
+      </c>
+      <c r="D574" t="s">
+        <v>3094</v>
+      </c>
+      <c r="E574" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F574" t="s">
+        <v>18</v>
+      </c>
+      <c r="G574" t="s">
+        <v>19</v>
+      </c>
+      <c r="H574" t="s">
+        <v>92</v>
+      </c>
+      <c r="I574" t="s">
+        <v>21</v>
+      </c>
+      <c r="J574" t="s">
+        <v>75</v>
+      </c>
+      <c r="K574" t="s">
+        <v>23</v>
+      </c>
+      <c r="L574" t="s">
+        <v>3095</v>
+      </c>
+      <c r="M574" t="s">
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="575" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
+        <v>3097</v>
+      </c>
+      <c r="B575" t="s">
+        <v>3098</v>
+      </c>
+      <c r="C575" t="s">
+        <v>477</v>
+      </c>
+      <c r="D575" t="s">
+        <v>3099</v>
+      </c>
+      <c r="E575" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F575" t="s">
+        <v>18</v>
+      </c>
+      <c r="G575" t="s">
+        <v>19</v>
+      </c>
+      <c r="H575" t="s">
+        <v>75</v>
+      </c>
+      <c r="I575" t="s">
+        <v>81</v>
+      </c>
+      <c r="J575" t="s">
+        <v>30</v>
+      </c>
+      <c r="K575" t="s">
+        <v>23</v>
+      </c>
+      <c r="L575" t="s">
+        <v>3100</v>
+      </c>
+      <c r="M575" t="s">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="576" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
+        <v>3102</v>
+      </c>
+      <c r="B576" t="s">
+        <v>3103</v>
+      </c>
+      <c r="C576" t="s">
+        <v>15</v>
+      </c>
+      <c r="D576" t="s">
+        <v>3104</v>
+      </c>
+      <c r="E576" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F576" t="s">
+        <v>18</v>
+      </c>
+      <c r="G576" t="s">
+        <v>19</v>
+      </c>
+      <c r="H576" t="s">
+        <v>381</v>
+      </c>
+      <c r="I576" t="s">
+        <v>21</v>
+      </c>
+      <c r="J576" t="s">
+        <v>46</v>
+      </c>
+      <c r="K576" t="s">
+        <v>23</v>
+      </c>
+      <c r="L576" t="s">
+        <v>3105</v>
+      </c>
+      <c r="M576" t="s">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="577" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
+        <v>3107</v>
+      </c>
+      <c r="B577" t="s">
+        <v>3108</v>
+      </c>
+      <c r="C577" t="s">
+        <v>15</v>
+      </c>
+      <c r="D577" t="s">
+        <v>3109</v>
+      </c>
+      <c r="E577" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F577" t="s">
+        <v>18</v>
+      </c>
+      <c r="G577" t="s">
+        <v>19</v>
+      </c>
+      <c r="H577" t="s">
+        <v>381</v>
+      </c>
+      <c r="I577" t="s">
+        <v>21</v>
+      </c>
+      <c r="J577" t="s">
+        <v>46</v>
+      </c>
+      <c r="K577" t="s">
+        <v>23</v>
+      </c>
+      <c r="L577" t="s">
+        <v>3110</v>
+      </c>
+      <c r="M577" t="s">
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="578" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
+        <v>3112</v>
+      </c>
+      <c r="B578" t="s">
+        <v>3113</v>
+      </c>
+      <c r="C578" t="s">
+        <v>607</v>
+      </c>
+      <c r="D578" t="s">
+        <v>3114</v>
+      </c>
+      <c r="E578" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F578" t="s">
+        <v>18</v>
+      </c>
+      <c r="G578" t="s">
+        <v>19</v>
+      </c>
+      <c r="H578" t="s">
+        <v>375</v>
+      </c>
+      <c r="I578" t="s">
+        <v>21</v>
+      </c>
+      <c r="J578" t="s">
+        <v>75</v>
+      </c>
+      <c r="K578" t="s">
+        <v>23</v>
+      </c>
+      <c r="L578" t="s">
+        <v>3115</v>
+      </c>
+      <c r="M578" t="s">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="579" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
+        <v>3117</v>
+      </c>
+      <c r="B579" t="s">
+        <v>3118</v>
+      </c>
+      <c r="C579" t="s">
+        <v>3119</v>
+      </c>
+      <c r="D579" t="s">
+        <v>3120</v>
+      </c>
+      <c r="E579" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F579" t="s">
+        <v>18</v>
+      </c>
+      <c r="G579" t="s">
+        <v>19</v>
+      </c>
+      <c r="H579" t="s">
+        <v>37</v>
+      </c>
+      <c r="I579" t="s">
+        <v>21</v>
+      </c>
+      <c r="J579" t="s">
+        <v>30</v>
+      </c>
+      <c r="K579" t="s">
+        <v>23</v>
+      </c>
+      <c r="L579" t="s">
+        <v>3121</v>
+      </c>
+      <c r="M579" t="s">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="580" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A580" t="s">
+        <v>3123</v>
+      </c>
+      <c r="B580" t="s">
+        <v>3124</v>
+      </c>
+      <c r="C580" t="s">
+        <v>73</v>
+      </c>
+      <c r="D580" t="s">
+        <v>3125</v>
+      </c>
+      <c r="E580" t="s">
+        <v>3126</v>
+      </c>
+      <c r="F580" t="s">
+        <v>18</v>
+      </c>
+      <c r="G580" t="s">
+        <v>19</v>
+      </c>
+      <c r="H580" t="s">
+        <v>45</v>
+      </c>
+      <c r="I580" t="s">
+        <v>21</v>
+      </c>
+      <c r="J580" t="s">
+        <v>75</v>
+      </c>
+      <c r="K580" t="s">
+        <v>23</v>
+      </c>
+      <c r="L580" t="s">
+        <v>3127</v>
+      </c>
+      <c r="M580" t="s">
+        <v>3128</v>
+      </c>
+    </row>
+    <row r="581" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A581" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B581" t="s">
+        <v>3130</v>
+      </c>
+      <c r="C581" t="s">
+        <v>15</v>
+      </c>
+      <c r="D581" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E581" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F581" t="s">
+        <v>18</v>
+      </c>
+      <c r="G581" t="s">
+        <v>19</v>
+      </c>
+      <c r="H581" t="s">
+        <v>45</v>
+      </c>
+      <c r="I581" t="s">
+        <v>21</v>
+      </c>
+      <c r="J581" t="s">
+        <v>1612</v>
+      </c>
+      <c r="K581" t="s">
+        <v>23</v>
+      </c>
+      <c r="L581" t="s">
+        <v>3132</v>
+      </c>
+      <c r="M581" t="s">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="582" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A582" t="s">
+        <v>3134</v>
+      </c>
+      <c r="B582" t="s">
+        <v>3135</v>
+      </c>
+      <c r="C582" t="s">
+        <v>28</v>
+      </c>
+      <c r="D582" t="s">
+        <v>3136</v>
+      </c>
+      <c r="E582" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F582" t="s">
+        <v>18</v>
+      </c>
+      <c r="G582" t="s">
+        <v>19</v>
+      </c>
+      <c r="H582" t="s">
+        <v>75</v>
+      </c>
+      <c r="I582" t="s">
+        <v>81</v>
+      </c>
+      <c r="J582" t="s">
+        <v>121</v>
+      </c>
+      <c r="K582" t="s">
+        <v>23</v>
+      </c>
+      <c r="L582" t="s">
+        <v>3137</v>
+      </c>
+      <c r="M582" t="s">
+        <v>3138</v>
+      </c>
+    </row>
+    <row r="583" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A583" t="s">
+        <v>3139</v>
+      </c>
+      <c r="B583" t="s">
+        <v>3140</v>
+      </c>
+      <c r="C583" t="s">
+        <v>15</v>
+      </c>
+      <c r="D583" t="s">
+        <v>3141</v>
+      </c>
+      <c r="E583" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F583" t="s">
+        <v>18</v>
+      </c>
+      <c r="G583" t="s">
+        <v>19</v>
+      </c>
+      <c r="H583" t="s">
+        <v>45</v>
+      </c>
+      <c r="I583" t="s">
+        <v>21</v>
+      </c>
+      <c r="J583" t="s">
+        <v>46</v>
+      </c>
+      <c r="K583" t="s">
+        <v>23</v>
+      </c>
+      <c r="L583" t="s">
+        <v>3142</v>
+      </c>
+      <c r="M583" t="s">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="584" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A584" t="s">
+        <v>3144</v>
+      </c>
+      <c r="B584" t="s">
+        <v>3145</v>
+      </c>
+      <c r="C584" t="s">
+        <v>58</v>
+      </c>
+      <c r="D584" t="s">
+        <v>3146</v>
+      </c>
+      <c r="E584" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F584" t="s">
+        <v>18</v>
+      </c>
+      <c r="G584" t="s">
+        <v>19</v>
+      </c>
+      <c r="H584" t="s">
+        <v>45</v>
+      </c>
+      <c r="I584" t="s">
+        <v>569</v>
+      </c>
+      <c r="J584" t="s">
+        <v>75</v>
+      </c>
+      <c r="K584" t="s">
+        <v>23</v>
+      </c>
+      <c r="L584" t="s">
+        <v>3147</v>
+      </c>
+      <c r="M584" t="s">
+        <v>3148</v>
+      </c>
+    </row>
+    <row r="585" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A585" t="s">
+        <v>3149</v>
+      </c>
+      <c r="B585" t="s">
+        <v>3150</v>
+      </c>
+      <c r="C585" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D585" t="s">
+        <v>3151</v>
+      </c>
+      <c r="E585" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F585" t="s">
+        <v>18</v>
+      </c>
+      <c r="G585" t="s">
+        <v>19</v>
+      </c>
+      <c r="H585" t="s">
+        <v>45</v>
+      </c>
+      <c r="I585" t="s">
+        <v>291</v>
+      </c>
+      <c r="J585" t="s">
+        <v>75</v>
+      </c>
+      <c r="K585" t="s">
+        <v>23</v>
+      </c>
+      <c r="L585" t="s">
+        <v>3152</v>
+      </c>
+      <c r="M585" t="s">
+        <v>3153</v>
+      </c>
+    </row>
+    <row r="586" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A586" t="s">
+        <v>3154</v>
+      </c>
+      <c r="B586" t="s">
+        <v>3155</v>
+      </c>
+      <c r="C586" t="s">
+        <v>58</v>
+      </c>
+      <c r="D586" t="s">
+        <v>3156</v>
+      </c>
+      <c r="E586" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F586" t="s">
+        <v>18</v>
+      </c>
+      <c r="G586" t="s">
+        <v>19</v>
+      </c>
+      <c r="H586" t="s">
+        <v>120</v>
+      </c>
+      <c r="I586" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J586" t="s">
+        <v>3157</v>
+      </c>
+      <c r="K586" t="s">
+        <v>23</v>
+      </c>
+      <c r="L586" t="s">
+        <v>3158</v>
+      </c>
+      <c r="M586" t="s">
+        <v>3159</v>
+      </c>
+    </row>
+    <row r="587" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A587" t="s">
+        <v>3160</v>
+      </c>
+      <c r="B587" t="s">
+        <v>3161</v>
+      </c>
+      <c r="C587" t="s">
+        <v>58</v>
+      </c>
+      <c r="D587" t="s">
+        <v>3162</v>
+      </c>
+      <c r="E587" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F587" t="s">
+        <v>18</v>
+      </c>
+      <c r="G587" t="s">
+        <v>19</v>
+      </c>
+      <c r="H587" t="s">
+        <v>375</v>
+      </c>
+      <c r="I587" t="s">
+        <v>569</v>
+      </c>
+      <c r="J587" t="s">
+        <v>75</v>
+      </c>
+      <c r="K587" t="s">
+        <v>23</v>
+      </c>
+      <c r="L587" t="s">
+        <v>3163</v>
+      </c>
+      <c r="M587" t="s">
+        <v>3164</v>
+      </c>
+    </row>
+    <row r="588" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A588" t="s">
+        <v>3165</v>
+      </c>
+      <c r="B588" t="s">
+        <v>3166</v>
+      </c>
+      <c r="C588" t="s">
+        <v>15</v>
+      </c>
+      <c r="D588" t="s">
+        <v>3167</v>
+      </c>
+      <c r="E588" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F588" t="s">
+        <v>18</v>
+      </c>
+      <c r="G588" t="s">
+        <v>19</v>
+      </c>
+      <c r="H588" t="s">
+        <v>120</v>
+      </c>
+      <c r="I588" t="s">
+        <v>21</v>
+      </c>
+      <c r="J588" t="s">
+        <v>121</v>
+      </c>
+      <c r="K588" t="s">
+        <v>23</v>
+      </c>
+      <c r="L588" t="s">
+        <v>3168</v>
+      </c>
+      <c r="M588" t="s">
+        <v>3169</v>
+      </c>
+    </row>
+    <row r="589" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A589" t="s">
+        <v>3170</v>
+      </c>
+      <c r="B589" t="s">
+        <v>3171</v>
+      </c>
+      <c r="C589" t="s">
+        <v>15</v>
+      </c>
+      <c r="D589" t="s">
+        <v>3172</v>
+      </c>
+      <c r="E589" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F589" t="s">
+        <v>18</v>
+      </c>
+      <c r="G589" t="s">
+        <v>19</v>
+      </c>
+      <c r="H589" t="s">
+        <v>45</v>
+      </c>
+      <c r="I589" t="s">
+        <v>21</v>
+      </c>
+      <c r="J589" t="s">
+        <v>75</v>
+      </c>
+      <c r="K589" t="s">
+        <v>23</v>
+      </c>
+      <c r="L589" t="s">
+        <v>3173</v>
+      </c>
+      <c r="M589" t="s">
+        <v>3174</v>
+      </c>
+    </row>
+    <row r="590" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A590" t="s">
+        <v>3175</v>
+      </c>
+      <c r="B590" t="s">
+        <v>3176</v>
+      </c>
+      <c r="C590" t="s">
+        <v>15</v>
+      </c>
+      <c r="D590" t="s">
+        <v>3177</v>
+      </c>
+      <c r="E590" t="s">
+        <v>3178</v>
+      </c>
+      <c r="F590" t="s">
+        <v>18</v>
+      </c>
+      <c r="G590" t="s">
+        <v>19</v>
+      </c>
+      <c r="H590" t="s">
+        <v>103</v>
+      </c>
+      <c r="I590" t="s">
+        <v>21</v>
+      </c>
+      <c r="J590" t="s">
+        <v>46</v>
+      </c>
+      <c r="K590" t="s">
+        <v>23</v>
+      </c>
+      <c r="L590" t="s">
+        <v>3179</v>
+      </c>
+      <c r="M590" t="s">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="591" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
+        <v>3181</v>
+      </c>
+      <c r="B591" t="s">
+        <v>3182</v>
+      </c>
+      <c r="C591" t="s">
+        <v>607</v>
+      </c>
+      <c r="D591" t="s">
+        <v>3183</v>
+      </c>
+      <c r="E591" t="s">
+        <v>3178</v>
+      </c>
+      <c r="F591" t="s">
+        <v>18</v>
+      </c>
+      <c r="G591" t="s">
+        <v>19</v>
+      </c>
+      <c r="H591" t="s">
+        <v>120</v>
+      </c>
+      <c r="I591" t="s">
+        <v>21</v>
+      </c>
+      <c r="J591" t="s">
+        <v>46</v>
+      </c>
+      <c r="K591" t="s">
+        <v>23</v>
+      </c>
+      <c r="L591" t="s">
+        <v>3184</v>
+      </c>
+      <c r="M591" t="s">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="592" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A592" t="s">
+        <v>3186</v>
+      </c>
+      <c r="B592" t="s">
+        <v>3187</v>
+      </c>
+      <c r="C592" t="s">
+        <v>28</v>
+      </c>
+      <c r="D592" t="s">
+        <v>3188</v>
+      </c>
+      <c r="E592" t="s">
+        <v>3178</v>
+      </c>
+      <c r="F592" t="s">
+        <v>18</v>
+      </c>
+      <c r="G592" t="s">
+        <v>19</v>
+      </c>
+      <c r="H592" t="s">
+        <v>627</v>
+      </c>
+      <c r="I592" t="s">
+        <v>21</v>
+      </c>
+      <c r="J592" t="s">
+        <v>46</v>
+      </c>
+      <c r="K592" t="s">
+        <v>23</v>
+      </c>
+      <c r="L592" t="s">
+        <v>3189</v>
+      </c>
+      <c r="M592" t="s">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="593" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A593" t="s">
+        <v>3191</v>
+      </c>
+      <c r="B593" t="s">
+        <v>3192</v>
+      </c>
+      <c r="C593" t="s">
+        <v>28</v>
+      </c>
+      <c r="D593" t="s">
+        <v>3193</v>
+      </c>
+      <c r="E593" t="s">
+        <v>3178</v>
+      </c>
+      <c r="F593" t="s">
+        <v>18</v>
+      </c>
+      <c r="G593" t="s">
+        <v>19</v>
+      </c>
+      <c r="H593" t="s">
+        <v>223</v>
+      </c>
+      <c r="I593" t="s">
+        <v>21</v>
+      </c>
+      <c r="J593" t="s">
+        <v>648</v>
+      </c>
+      <c r="K593" t="s">
+        <v>23</v>
+      </c>
+      <c r="L593" t="s">
+        <v>3194</v>
+      </c>
+      <c r="M593" t="s">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="594" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A594" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B594" t="s">
+        <v>3197</v>
+      </c>
+      <c r="C594" t="s">
+        <v>28</v>
+      </c>
+      <c r="D594" t="s">
+        <v>3198</v>
+      </c>
+      <c r="E594" t="s">
+        <v>3178</v>
+      </c>
+      <c r="F594" t="s">
+        <v>18</v>
+      </c>
+      <c r="G594" t="s">
+        <v>19</v>
+      </c>
+      <c r="H594" t="s">
+        <v>45</v>
+      </c>
+      <c r="I594" t="s">
+        <v>21</v>
+      </c>
+      <c r="J594" t="s">
+        <v>46</v>
+      </c>
+      <c r="K594" t="s">
+        <v>23</v>
+      </c>
+      <c r="L594" t="s">
+        <v>3199</v>
+      </c>
+      <c r="M594" t="s">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="595" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A595" t="s">
+        <v>3201</v>
+      </c>
+      <c r="B595" t="s">
+        <v>3202</v>
+      </c>
+      <c r="C595" t="s">
+        <v>15</v>
+      </c>
+      <c r="D595" t="s">
+        <v>3203</v>
+      </c>
+      <c r="E595" t="s">
+        <v>3178</v>
+      </c>
+      <c r="F595" t="s">
+        <v>18</v>
+      </c>
+      <c r="G595" t="s">
+        <v>19</v>
+      </c>
+      <c r="H595" t="s">
+        <v>45</v>
+      </c>
+      <c r="I595" t="s">
+        <v>21</v>
+      </c>
+      <c r="J595" t="s">
+        <v>121</v>
+      </c>
+      <c r="K595" t="s">
+        <v>23</v>
+      </c>
+      <c r="L595" t="s">
+        <v>3204</v>
+      </c>
+      <c r="M595" t="s">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="596" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A596" t="s">
+        <v>3206</v>
+      </c>
+      <c r="B596" t="s">
+        <v>3207</v>
+      </c>
+      <c r="C596" t="s">
+        <v>15</v>
+      </c>
+      <c r="D596" t="s">
+        <v>3208</v>
+      </c>
+      <c r="E596" t="s">
+        <v>3178</v>
+      </c>
+      <c r="F596" t="s">
+        <v>18</v>
+      </c>
+      <c r="G596" t="s">
+        <v>19</v>
+      </c>
+      <c r="H596" t="s">
+        <v>92</v>
+      </c>
+      <c r="I596" t="s">
+        <v>21</v>
+      </c>
+      <c r="J596" t="s">
+        <v>46</v>
+      </c>
+      <c r="K596" t="s">
+        <v>23</v>
+      </c>
+      <c r="L596" t="s">
+        <v>3209</v>
+      </c>
+      <c r="M596" t="s">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="597" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
+        <v>3211</v>
+      </c>
+      <c r="B597" t="s">
+        <v>3212</v>
+      </c>
+      <c r="C597" t="s">
+        <v>28</v>
+      </c>
+      <c r="D597" t="s">
+        <v>3213</v>
+      </c>
+      <c r="E597" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F597" t="s">
+        <v>18</v>
+      </c>
+      <c r="G597" t="s">
+        <v>19</v>
+      </c>
+      <c r="H597" t="s">
+        <v>20</v>
+      </c>
+      <c r="I597" t="s">
+        <v>21</v>
+      </c>
+      <c r="J597" t="s">
+        <v>297</v>
+      </c>
+      <c r="K597" t="s">
+        <v>23</v>
+      </c>
+      <c r="L597" t="s">
+        <v>3215</v>
+      </c>
+      <c r="M597" t="s">
+        <v>3216</v>
+      </c>
+    </row>
+    <row r="598" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A598" t="s">
+        <v>3217</v>
+      </c>
+      <c r="B598" t="s">
+        <v>3218</v>
+      </c>
+      <c r="C598" t="s">
+        <v>15</v>
+      </c>
+      <c r="D598" t="s">
+        <v>3219</v>
+      </c>
+      <c r="E598" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F598" t="s">
+        <v>18</v>
+      </c>
+      <c r="G598" t="s">
+        <v>19</v>
+      </c>
+      <c r="H598" t="s">
+        <v>45</v>
+      </c>
+      <c r="I598" t="s">
+        <v>21</v>
+      </c>
+      <c r="J598" t="s">
+        <v>340</v>
+      </c>
+      <c r="K598" t="s">
+        <v>23</v>
+      </c>
+      <c r="L598" t="s">
+        <v>3220</v>
+      </c>
+      <c r="M598" t="s">
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="599" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A599" t="s">
+        <v>3222</v>
+      </c>
+      <c r="B599" t="s">
+        <v>3223</v>
+      </c>
+      <c r="C599" t="s">
+        <v>28</v>
+      </c>
+      <c r="D599" t="s">
+        <v>3224</v>
+      </c>
+      <c r="E599" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F599" t="s">
+        <v>18</v>
+      </c>
+      <c r="G599" t="s">
+        <v>19</v>
+      </c>
+      <c r="H599" t="s">
+        <v>45</v>
+      </c>
+      <c r="I599" t="s">
+        <v>21</v>
+      </c>
+      <c r="J599" t="s">
+        <v>75</v>
+      </c>
+      <c r="K599" t="s">
+        <v>23</v>
+      </c>
+      <c r="L599" t="s">
+        <v>3225</v>
+      </c>
+      <c r="M599" t="s">
+        <v>3226</v>
+      </c>
+    </row>
+    <row r="600" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A600" t="s">
+        <v>3227</v>
+      </c>
+      <c r="B600" t="s">
+        <v>3228</v>
+      </c>
+      <c r="C600" t="s">
+        <v>15</v>
+      </c>
+      <c r="D600" t="s">
+        <v>3229</v>
+      </c>
+      <c r="E600" t="s">
+        <v>3230</v>
+      </c>
+      <c r="F600" t="s">
+        <v>18</v>
+      </c>
+      <c r="G600" t="s">
+        <v>19</v>
+      </c>
+      <c r="H600" t="s">
+        <v>45</v>
+      </c>
+      <c r="I600" t="s">
+        <v>21</v>
+      </c>
+      <c r="J600" t="s">
+        <v>46</v>
+      </c>
+      <c r="K600" t="s">
+        <v>23</v>
+      </c>
+      <c r="L600" t="s">
+        <v>3231</v>
+      </c>
+      <c r="M600" t="s">
+        <v>3232</v>
+      </c>
+    </row>
+    <row r="601" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
+        <v>3233</v>
+      </c>
+      <c r="B601" t="s">
+        <v>3234</v>
+      </c>
+      <c r="C601" t="s">
+        <v>15</v>
+      </c>
+      <c r="D601" t="s">
+        <v>3235</v>
+      </c>
+      <c r="E601" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F601" t="s">
+        <v>18</v>
+      </c>
+      <c r="G601" t="s">
+        <v>19</v>
+      </c>
+      <c r="H601" t="s">
+        <v>67</v>
+      </c>
+      <c r="I601" t="s">
+        <v>21</v>
+      </c>
+      <c r="J601" t="s">
+        <v>46</v>
+      </c>
+      <c r="K601" t="s">
+        <v>23</v>
+      </c>
+      <c r="L601" t="s">
+        <v>3236</v>
+      </c>
+      <c r="M601" t="s">
+        <v>3237</v>
+      </c>
+    </row>
+    <row r="602" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A602" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B602" t="s">
+        <v>3239</v>
+      </c>
+      <c r="C602" t="s">
+        <v>28</v>
+      </c>
+      <c r="D602" t="s">
+        <v>3240</v>
+      </c>
+      <c r="E602" t="s">
+        <v>3230</v>
+      </c>
+      <c r="F602" t="s">
+        <v>18</v>
+      </c>
+      <c r="G602" t="s">
+        <v>19</v>
+      </c>
+      <c r="H602" t="s">
+        <v>45</v>
+      </c>
+      <c r="I602" t="s">
+        <v>21</v>
+      </c>
+      <c r="J602" t="s">
+        <v>46</v>
+      </c>
+      <c r="K602" t="s">
+        <v>23</v>
+      </c>
+      <c r="L602" t="s">
+        <v>3241</v>
+      </c>
+      <c r="M602" t="s">
+        <v>3242</v>
+      </c>
+    </row>
+    <row r="603" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A603" t="s">
+        <v>3243</v>
+      </c>
+      <c r="B603" t="s">
+        <v>3244</v>
+      </c>
+      <c r="C603" t="s">
+        <v>15</v>
+      </c>
+      <c r="D603" t="s">
+        <v>3245</v>
+      </c>
+      <c r="E603" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F603" t="s">
+        <v>18</v>
+      </c>
+      <c r="G603" t="s">
+        <v>19</v>
+      </c>
+      <c r="H603" t="s">
+        <v>20</v>
+      </c>
+      <c r="I603" t="s">
+        <v>21</v>
+      </c>
+      <c r="J603" t="s">
+        <v>68</v>
+      </c>
+      <c r="K603" t="s">
+        <v>23</v>
+      </c>
+      <c r="L603" t="s">
+        <v>3246</v>
+      </c>
+      <c r="M603" t="s">
+        <v>3247</v>
+      </c>
+    </row>
+    <row r="604" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A604" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B604" t="s">
+        <v>3249</v>
+      </c>
+      <c r="C604" t="s">
+        <v>28</v>
+      </c>
+      <c r="D604" t="s">
+        <v>3250</v>
+      </c>
+      <c r="E604" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F604" t="s">
+        <v>18</v>
+      </c>
+      <c r="G604" t="s">
+        <v>19</v>
+      </c>
+      <c r="H604" t="s">
+        <v>960</v>
+      </c>
+      <c r="I604" t="s">
+        <v>21</v>
+      </c>
+      <c r="J604" t="s">
+        <v>121</v>
+      </c>
+      <c r="K604" t="s">
+        <v>23</v>
+      </c>
+      <c r="L604" t="s">
+        <v>3251</v>
+      </c>
+      <c r="M604" t="s">
+        <v>3252</v>
+      </c>
+    </row>
+    <row r="605" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A605" t="s">
+        <v>3253</v>
+      </c>
+      <c r="B605" t="s">
+        <v>3254</v>
+      </c>
+      <c r="C605" t="s">
+        <v>15</v>
+      </c>
+      <c r="D605" t="s">
+        <v>3255</v>
+      </c>
+      <c r="E605" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F605" t="s">
+        <v>18</v>
+      </c>
+      <c r="G605" t="s">
+        <v>19</v>
+      </c>
+      <c r="H605" t="s">
+        <v>3256</v>
+      </c>
+      <c r="I605" t="s">
+        <v>21</v>
+      </c>
+      <c r="J605" t="s">
+        <v>3257</v>
+      </c>
+      <c r="K605" t="s">
+        <v>23</v>
+      </c>
+      <c r="L605" t="s">
+        <v>3258</v>
+      </c>
+      <c r="M605" t="s">
+        <v>3259</v>
+      </c>
+    </row>
+    <row r="606" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A606" t="s">
+        <v>3260</v>
+      </c>
+      <c r="B606" t="s">
+        <v>3261</v>
+      </c>
+      <c r="C606" t="s">
+        <v>15</v>
+      </c>
+      <c r="D606" t="s">
+        <v>3262</v>
+      </c>
+      <c r="E606" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F606" t="s">
+        <v>18</v>
+      </c>
+      <c r="G606" t="s">
+        <v>19</v>
+      </c>
+      <c r="H606" t="s">
+        <v>381</v>
+      </c>
+      <c r="I606" t="s">
+        <v>21</v>
+      </c>
+      <c r="J606" t="s">
+        <v>3263</v>
+      </c>
+      <c r="K606" t="s">
+        <v>23</v>
+      </c>
+      <c r="L606" t="s">
+        <v>3264</v>
+      </c>
+      <c r="M606" t="s">
+        <v>3265</v>
+      </c>
+    </row>
+    <row r="607" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A607" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B607" t="s">
+        <v>3267</v>
+      </c>
+      <c r="C607" t="s">
+        <v>477</v>
+      </c>
+      <c r="D607" t="s">
+        <v>3268</v>
+      </c>
+      <c r="E607" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F607" t="s">
+        <v>18</v>
+      </c>
+      <c r="G607" t="s">
+        <v>19</v>
+      </c>
+      <c r="H607" t="s">
+        <v>75</v>
+      </c>
+      <c r="I607" t="s">
+        <v>81</v>
+      </c>
+      <c r="J607" t="s">
+        <v>75</v>
+      </c>
+      <c r="K607" t="s">
+        <v>23</v>
+      </c>
+      <c r="L607" t="s">
+        <v>3269</v>
+      </c>
+      <c r="M607" t="s">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="608" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A608" t="s">
+        <v>3271</v>
+      </c>
+      <c r="B608" t="s">
+        <v>3272</v>
+      </c>
+      <c r="C608" t="s">
+        <v>15</v>
+      </c>
+      <c r="D608" t="s">
+        <v>3273</v>
+      </c>
+      <c r="E608" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F608" t="s">
+        <v>18</v>
+      </c>
+      <c r="G608" t="s">
+        <v>19</v>
+      </c>
+      <c r="H608" t="s">
+        <v>1113</v>
+      </c>
+      <c r="I608" t="s">
+        <v>21</v>
+      </c>
+      <c r="J608" t="s">
+        <v>3274</v>
+      </c>
+      <c r="K608" t="s">
+        <v>23</v>
+      </c>
+      <c r="L608" t="s">
+        <v>3275</v>
+      </c>
+      <c r="M608" t="s">
+        <v>3276</v>
+      </c>
+    </row>
+    <row r="609" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A609" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B609" t="s">
+        <v>3278</v>
+      </c>
+      <c r="C609" t="s">
+        <v>477</v>
+      </c>
+      <c r="D609" t="s">
+        <v>3279</v>
+      </c>
+      <c r="E609" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F609" t="s">
+        <v>18</v>
+      </c>
+      <c r="G609" t="s">
+        <v>19</v>
+      </c>
+      <c r="H609" t="s">
+        <v>45</v>
+      </c>
+      <c r="I609" t="s">
+        <v>21</v>
+      </c>
+      <c r="J609" t="s">
+        <v>46</v>
+      </c>
+      <c r="K609" t="s">
+        <v>23</v>
+      </c>
+      <c r="L609" t="s">
+        <v>3280</v>
+      </c>
+      <c r="M609" t="s">
+        <v>3281</v>
+      </c>
+    </row>
+    <row r="610" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A610" t="s">
+        <v>3282</v>
+      </c>
+      <c r="B610" t="s">
+        <v>3283</v>
+      </c>
+      <c r="C610" t="s">
+        <v>477</v>
+      </c>
+      <c r="D610" t="s">
+        <v>3284</v>
+      </c>
+      <c r="E610" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F610" t="s">
+        <v>18</v>
+      </c>
+      <c r="G610" t="s">
+        <v>19</v>
+      </c>
+      <c r="H610" t="s">
+        <v>75</v>
+      </c>
+      <c r="I610" t="s">
+        <v>81</v>
+      </c>
+      <c r="J610" t="s">
+        <v>75</v>
+      </c>
+      <c r="K610" t="s">
+        <v>23</v>
+      </c>
+      <c r="L610" t="s">
+        <v>3285</v>
+      </c>
+      <c r="M610" t="s">
+        <v>3286</v>
+      </c>
+    </row>
+    <row r="611" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B611" t="s">
+        <v>3288</v>
+      </c>
+      <c r="C611" t="s">
+        <v>15</v>
+      </c>
+      <c r="D611" t="s">
+        <v>3289</v>
+      </c>
+      <c r="E611" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F611" t="s">
+        <v>18</v>
+      </c>
+      <c r="G611" t="s">
+        <v>19</v>
+      </c>
+      <c r="H611" t="s">
+        <v>103</v>
+      </c>
+      <c r="I611" t="s">
+        <v>21</v>
+      </c>
+      <c r="J611" t="s">
+        <v>75</v>
+      </c>
+      <c r="K611" t="s">
+        <v>23</v>
+      </c>
+      <c r="L611" t="s">
+        <v>3290</v>
+      </c>
+      <c r="M611" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="612" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
+        <v>3292</v>
+      </c>
+      <c r="B612" t="s">
+        <v>3293</v>
+      </c>
+      <c r="C612" t="s">
+        <v>15</v>
+      </c>
+      <c r="D612" t="s">
+        <v>3294</v>
+      </c>
+      <c r="E612" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F612" t="s">
+        <v>18</v>
+      </c>
+      <c r="G612" t="s">
+        <v>19</v>
+      </c>
+      <c r="H612" t="s">
+        <v>37</v>
+      </c>
+      <c r="I612" t="s">
+        <v>21</v>
+      </c>
+      <c r="J612" t="s">
+        <v>3295</v>
+      </c>
+      <c r="K612" t="s">
+        <v>23</v>
+      </c>
+      <c r="L612" t="s">
+        <v>3296</v>
+      </c>
+      <c r="M612" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="613" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A613" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B613" t="s">
+        <v>3299</v>
+      </c>
+      <c r="C613" t="s">
+        <v>28</v>
+      </c>
+      <c r="D613" t="s">
+        <v>3300</v>
+      </c>
+      <c r="E613" t="s">
+        <v>3230</v>
+      </c>
+      <c r="F613" t="s">
+        <v>18</v>
+      </c>
+      <c r="G613" t="s">
+        <v>19</v>
+      </c>
+      <c r="H613" t="s">
+        <v>381</v>
+      </c>
+      <c r="I613" t="s">
+        <v>21</v>
+      </c>
+      <c r="J613" t="s">
+        <v>3301</v>
+      </c>
+      <c r="K613" t="s">
+        <v>23</v>
+      </c>
+      <c r="L613" t="s">
+        <v>3302</v>
+      </c>
+      <c r="M613" t="s">
+        <v>3303</v>
+      </c>
+    </row>
+    <row r="614" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A614" t="s">
+        <v>3304</v>
+      </c>
+      <c r="B614" t="s">
+        <v>3305</v>
+      </c>
+      <c r="C614" t="s">
+        <v>15</v>
+      </c>
+      <c r="D614" t="s">
+        <v>3306</v>
+      </c>
+      <c r="E614" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F614" t="s">
+        <v>18</v>
+      </c>
+      <c r="G614" t="s">
+        <v>19</v>
+      </c>
+      <c r="H614" t="s">
+        <v>92</v>
+      </c>
+      <c r="I614" t="s">
+        <v>21</v>
+      </c>
+      <c r="J614" t="s">
+        <v>121</v>
+      </c>
+      <c r="K614" t="s">
+        <v>23</v>
+      </c>
+      <c r="L614" t="s">
+        <v>3307</v>
+      </c>
+      <c r="M614" t="s">
+        <v>3308</v>
+      </c>
+    </row>
+    <row r="615" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A615" t="s">
+        <v>3309</v>
+      </c>
+      <c r="B615" t="s">
+        <v>3310</v>
+      </c>
+      <c r="C615" t="s">
+        <v>73</v>
+      </c>
+      <c r="D615" t="s">
+        <v>3311</v>
+      </c>
+      <c r="E615" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F615" t="s">
+        <v>18</v>
+      </c>
+      <c r="G615" t="s">
+        <v>19</v>
+      </c>
+      <c r="H615" t="s">
+        <v>45</v>
+      </c>
+      <c r="I615" t="s">
+        <v>21</v>
+      </c>
+      <c r="J615" t="s">
+        <v>75</v>
+      </c>
+      <c r="K615" t="s">
+        <v>23</v>
+      </c>
+      <c r="L615" t="s">
+        <v>3312</v>
+      </c>
+      <c r="M615" t="s">
+        <v>3313</v>
+      </c>
+    </row>
+    <row r="616" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A616" t="s">
+        <v>3314</v>
+      </c>
+      <c r="B616" t="s">
+        <v>3315</v>
+      </c>
+      <c r="C616" t="s">
+        <v>15</v>
+      </c>
+      <c r="D616" t="s">
+        <v>3316</v>
+      </c>
+      <c r="E616" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F616" t="s">
+        <v>18</v>
+      </c>
+      <c r="G616" t="s">
+        <v>19</v>
+      </c>
+      <c r="H616" t="s">
+        <v>375</v>
+      </c>
+      <c r="I616" t="s">
+        <v>21</v>
+      </c>
+      <c r="J616" t="s">
+        <v>75</v>
+      </c>
+      <c r="K616" t="s">
+        <v>23</v>
+      </c>
+      <c r="L616" t="s">
+        <v>3317</v>
+      </c>
+      <c r="M616" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="617" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A617" t="s">
+        <v>3319</v>
+      </c>
+      <c r="B617" t="s">
+        <v>3320</v>
+      </c>
+      <c r="C617" t="s">
+        <v>28</v>
+      </c>
+      <c r="D617" t="s">
+        <v>3321</v>
+      </c>
+      <c r="E617" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F617" t="s">
+        <v>18</v>
+      </c>
+      <c r="G617" t="s">
+        <v>19</v>
+      </c>
+      <c r="H617" t="s">
+        <v>67</v>
+      </c>
+      <c r="I617" t="s">
+        <v>21</v>
+      </c>
+      <c r="J617" t="s">
+        <v>46</v>
+      </c>
+      <c r="K617" t="s">
+        <v>23</v>
+      </c>
+      <c r="L617" t="s">
+        <v>3323</v>
+      </c>
+      <c r="M617" t="s">
+        <v>3324</v>
+      </c>
+    </row>
+    <row r="618" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A618" t="s">
+        <v>3325</v>
+      </c>
+      <c r="B618" t="s">
+        <v>3326</v>
+      </c>
+      <c r="C618" t="s">
+        <v>607</v>
+      </c>
+      <c r="D618" t="s">
+        <v>3327</v>
+      </c>
+      <c r="E618" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F618" t="s">
+        <v>18</v>
+      </c>
+      <c r="G618" t="s">
+        <v>19</v>
+      </c>
+      <c r="H618" t="s">
+        <v>45</v>
+      </c>
+      <c r="I618" t="s">
+        <v>21</v>
+      </c>
+      <c r="J618" t="s">
+        <v>46</v>
+      </c>
+      <c r="K618" t="s">
+        <v>23</v>
+      </c>
+      <c r="L618" t="s">
+        <v>3328</v>
+      </c>
+      <c r="M618" t="s">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="619" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A619" t="s">
+        <v>3330</v>
+      </c>
+      <c r="B619" t="s">
+        <v>3331</v>
+      </c>
+      <c r="C619" t="s">
+        <v>15</v>
+      </c>
+      <c r="D619" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E619" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F619" t="s">
+        <v>18</v>
+      </c>
+      <c r="G619" t="s">
+        <v>19</v>
+      </c>
+      <c r="H619" t="s">
+        <v>45</v>
+      </c>
+      <c r="I619" t="s">
+        <v>21</v>
+      </c>
+      <c r="J619" t="s">
+        <v>46</v>
+      </c>
+      <c r="K619" t="s">
+        <v>23</v>
+      </c>
+      <c r="L619" t="s">
+        <v>3333</v>
+      </c>
+      <c r="M619" t="s">
+        <v>3334</v>
+      </c>
+    </row>
+    <row r="620" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A620" t="s">
+        <v>3335</v>
+      </c>
+      <c r="B620" t="s">
+        <v>3336</v>
+      </c>
+      <c r="C620" t="s">
+        <v>28</v>
+      </c>
+      <c r="D620" t="s">
+        <v>3337</v>
+      </c>
+      <c r="E620" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F620" t="s">
+        <v>18</v>
+      </c>
+      <c r="G620" t="s">
+        <v>19</v>
+      </c>
+      <c r="H620" t="s">
+        <v>381</v>
+      </c>
+      <c r="I620" t="s">
+        <v>21</v>
+      </c>
+      <c r="J620" t="s">
+        <v>46</v>
+      </c>
+      <c r="K620" t="s">
+        <v>23</v>
+      </c>
+      <c r="L620" t="s">
+        <v>3338</v>
+      </c>
+      <c r="M620" t="s">
+        <v>3339</v>
+      </c>
+    </row>
+    <row r="621" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A621" t="s">
+        <v>3340</v>
+      </c>
+      <c r="B621" t="s">
+        <v>3341</v>
+      </c>
+      <c r="C621" t="s">
+        <v>175</v>
+      </c>
+      <c r="D621" t="s">
+        <v>3342</v>
+      </c>
+      <c r="E621" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F621" t="s">
+        <v>18</v>
+      </c>
+      <c r="G621" t="s">
+        <v>19</v>
+      </c>
+      <c r="H621" t="s">
+        <v>75</v>
+      </c>
+      <c r="I621" t="s">
+        <v>81</v>
+      </c>
+      <c r="J621" t="s">
+        <v>46</v>
+      </c>
+      <c r="K621" t="s">
+        <v>23</v>
+      </c>
+      <c r="L621" t="s">
+        <v>3343</v>
+      </c>
+      <c r="M621" t="s">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="622" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A622" t="s">
+        <v>3345</v>
+      </c>
+      <c r="B622" t="s">
+        <v>3346</v>
+      </c>
+      <c r="C622" t="s">
+        <v>15</v>
+      </c>
+      <c r="D622" t="s">
+        <v>3347</v>
+      </c>
+      <c r="E622" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F622" t="s">
+        <v>18</v>
+      </c>
+      <c r="G622" t="s">
+        <v>19</v>
+      </c>
+      <c r="H622" t="s">
+        <v>45</v>
+      </c>
+      <c r="I622" t="s">
+        <v>21</v>
+      </c>
+      <c r="J622" t="s">
+        <v>46</v>
+      </c>
+      <c r="K622" t="s">
+        <v>23</v>
+      </c>
+      <c r="L622" t="s">
+        <v>3348</v>
+      </c>
+      <c r="M622" t="s">
+        <v>3349</v>
+      </c>
+    </row>
+    <row r="623" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A623" t="s">
+        <v>3350</v>
+      </c>
+      <c r="B623" t="s">
+        <v>3351</v>
+      </c>
+      <c r="C623" t="s">
+        <v>15</v>
+      </c>
+      <c r="D623" t="s">
+        <v>3352</v>
+      </c>
+      <c r="E623" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F623" t="s">
+        <v>18</v>
+      </c>
+      <c r="G623" t="s">
+        <v>19</v>
+      </c>
+      <c r="H623" t="s">
+        <v>75</v>
+      </c>
+      <c r="I623" t="s">
+        <v>81</v>
+      </c>
+      <c r="J623" t="s">
+        <v>46</v>
+      </c>
+      <c r="K623" t="s">
+        <v>23</v>
+      </c>
+      <c r="L623" t="s">
+        <v>3353</v>
+      </c>
+      <c r="M623" t="s">
+        <v>3354</v>
+      </c>
+    </row>
+    <row r="624" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A624" t="s">
+        <v>3355</v>
+      </c>
+      <c r="B624" t="s">
+        <v>3356</v>
+      </c>
+      <c r="C624" t="s">
+        <v>15</v>
+      </c>
+      <c r="D624" t="s">
+        <v>3357</v>
+      </c>
+      <c r="E624" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F624" t="s">
+        <v>18</v>
+      </c>
+      <c r="G624" t="s">
+        <v>19</v>
+      </c>
+      <c r="H624" t="s">
+        <v>45</v>
+      </c>
+      <c r="I624" t="s">
+        <v>21</v>
+      </c>
+      <c r="J624" t="s">
+        <v>75</v>
+      </c>
+      <c r="K624" t="s">
+        <v>23</v>
+      </c>
+      <c r="L624" t="s">
+        <v>3358</v>
+      </c>
+      <c r="M624" t="s">
+        <v>3359</v>
+      </c>
+    </row>
+    <row r="625" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A625" t="s">
+        <v>3360</v>
+      </c>
+      <c r="B625" t="s">
+        <v>3361</v>
+      </c>
+      <c r="C625" t="s">
+        <v>477</v>
+      </c>
+      <c r="D625" t="s">
+        <v>3362</v>
+      </c>
+      <c r="E625" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F625" t="s">
+        <v>18</v>
+      </c>
+      <c r="G625" t="s">
+        <v>19</v>
+      </c>
+      <c r="H625" t="s">
+        <v>75</v>
+      </c>
+      <c r="I625" t="s">
+        <v>81</v>
+      </c>
+      <c r="J625" t="s">
+        <v>75</v>
+      </c>
+      <c r="K625" t="s">
+        <v>23</v>
+      </c>
+      <c r="L625" t="s">
+        <v>3363</v>
+      </c>
+      <c r="M625" t="s">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="626" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A626" t="s">
+        <v>3365</v>
+      </c>
+      <c r="B626" t="s">
+        <v>3366</v>
+      </c>
+      <c r="C626" t="s">
+        <v>181</v>
+      </c>
+      <c r="D626" t="s">
+        <v>3367</v>
+      </c>
+      <c r="E626" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F626" t="s">
+        <v>18</v>
+      </c>
+      <c r="G626" t="s">
+        <v>19</v>
+      </c>
+      <c r="H626" t="s">
+        <v>67</v>
+      </c>
+      <c r="I626" t="s">
+        <v>21</v>
+      </c>
+      <c r="J626" t="s">
+        <v>46</v>
+      </c>
+      <c r="K626" t="s">
+        <v>23</v>
+      </c>
+      <c r="L626" t="s">
+        <v>3368</v>
+      </c>
+      <c r="M626" t="s">
+        <v>3369</v>
+      </c>
+    </row>
+    <row r="627" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A627" t="s">
+        <v>3370</v>
+      </c>
+      <c r="B627" t="s">
+        <v>3371</v>
+      </c>
+      <c r="C627" t="s">
+        <v>910</v>
+      </c>
+      <c r="D627" t="s">
+        <v>3372</v>
+      </c>
+      <c r="E627" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F627" t="s">
+        <v>18</v>
+      </c>
+      <c r="G627" t="s">
+        <v>19</v>
+      </c>
+      <c r="H627" t="s">
+        <v>92</v>
+      </c>
+      <c r="I627" t="s">
+        <v>21</v>
+      </c>
+      <c r="J627" t="s">
+        <v>46</v>
+      </c>
+      <c r="K627" t="s">
+        <v>23</v>
+      </c>
+      <c r="L627" t="s">
+        <v>3373</v>
+      </c>
+      <c r="M627" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="628" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A628" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B628" t="s">
+        <v>3376</v>
+      </c>
+      <c r="C628" t="s">
+        <v>15</v>
+      </c>
+      <c r="D628" t="s">
+        <v>3377</v>
+      </c>
+      <c r="E628" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F628" t="s">
+        <v>18</v>
+      </c>
+      <c r="G628" t="s">
+        <v>19</v>
+      </c>
+      <c r="H628" t="s">
+        <v>211</v>
+      </c>
+      <c r="I628" t="s">
+        <v>21</v>
+      </c>
+      <c r="J628" t="s">
+        <v>46</v>
+      </c>
+      <c r="K628" t="s">
+        <v>23</v>
+      </c>
+      <c r="L628" t="s">
+        <v>3378</v>
+      </c>
+      <c r="M628" t="s">
+        <v>3379</v>
+      </c>
+    </row>
+    <row r="629" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A629" t="s">
+        <v>3380</v>
+      </c>
+      <c r="B629" t="s">
+        <v>3381</v>
+      </c>
+      <c r="C629" t="s">
+        <v>73</v>
+      </c>
+      <c r="D629" t="s">
+        <v>3382</v>
+      </c>
+      <c r="E629" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F629" t="s">
+        <v>18</v>
+      </c>
+      <c r="G629" t="s">
+        <v>19</v>
+      </c>
+      <c r="H629" t="s">
+        <v>75</v>
+      </c>
+      <c r="I629" t="s">
+        <v>81</v>
+      </c>
+      <c r="J629" t="s">
+        <v>75</v>
+      </c>
+      <c r="K629" t="s">
+        <v>23</v>
+      </c>
+      <c r="L629" t="s">
+        <v>3383</v>
+      </c>
+      <c r="M629" t="s">
+        <v>3384</v>
+      </c>
+    </row>
+    <row r="630" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A630" t="s">
+        <v>3385</v>
+      </c>
+      <c r="B630" t="s">
+        <v>3386</v>
+      </c>
+      <c r="C630" t="s">
+        <v>73</v>
+      </c>
+      <c r="D630" t="s">
+        <v>3387</v>
+      </c>
+      <c r="E630" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F630" t="s">
+        <v>18</v>
+      </c>
+      <c r="G630" t="s">
+        <v>19</v>
+      </c>
+      <c r="H630" t="s">
+        <v>223</v>
+      </c>
+      <c r="I630" t="s">
+        <v>21</v>
+      </c>
+      <c r="J630" t="s">
+        <v>75</v>
+      </c>
+      <c r="K630" t="s">
+        <v>23</v>
+      </c>
+      <c r="L630" t="s">
+        <v>3388</v>
+      </c>
+      <c r="M630" t="s">
+        <v>3389</v>
+      </c>
+    </row>
+    <row r="631" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A631" t="s">
+        <v>3390</v>
+      </c>
+      <c r="B631" t="s">
+        <v>3391</v>
+      </c>
+      <c r="C631" t="s">
+        <v>28</v>
+      </c>
+      <c r="D631" t="s">
+        <v>3392</v>
+      </c>
+      <c r="E631" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F631" t="s">
+        <v>18</v>
+      </c>
+      <c r="G631" t="s">
+        <v>19</v>
+      </c>
+      <c r="H631" t="s">
+        <v>103</v>
+      </c>
+      <c r="I631" t="s">
+        <v>21</v>
+      </c>
+      <c r="J631" t="s">
+        <v>75</v>
+      </c>
+      <c r="K631" t="s">
+        <v>23</v>
+      </c>
+      <c r="L631" t="s">
+        <v>3393</v>
+      </c>
+      <c r="M631" t="s">
+        <v>3394</v>
+      </c>
+    </row>
+    <row r="632" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A632" t="s">
+        <v>3395</v>
+      </c>
+      <c r="B632" t="s">
+        <v>3396</v>
+      </c>
+      <c r="C632" t="s">
+        <v>526</v>
+      </c>
+      <c r="D632" t="s">
+        <v>3397</v>
+      </c>
+      <c r="E632" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F632" t="s">
+        <v>18</v>
+      </c>
+      <c r="G632" t="s">
+        <v>19</v>
+      </c>
+      <c r="H632" t="s">
+        <v>37</v>
+      </c>
+      <c r="I632" t="s">
+        <v>21</v>
+      </c>
+      <c r="J632" t="s">
+        <v>75</v>
+      </c>
+      <c r="K632" t="s">
+        <v>23</v>
+      </c>
+      <c r="L632" t="s">
+        <v>3398</v>
+      </c>
+      <c r="M632" t="s">
+        <v>3399</v>
+      </c>
+    </row>
+    <row r="633" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A633" t="s">
+        <v>3400</v>
+      </c>
+      <c r="B633" t="s">
+        <v>3401</v>
+      </c>
+      <c r="C633" t="s">
+        <v>526</v>
+      </c>
+      <c r="D633" t="s">
+        <v>3402</v>
+      </c>
+      <c r="E633" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F633" t="s">
+        <v>18</v>
+      </c>
+      <c r="G633" t="s">
+        <v>19</v>
+      </c>
+      <c r="H633" t="s">
+        <v>75</v>
+      </c>
+      <c r="I633" t="s">
+        <v>81</v>
+      </c>
+      <c r="J633" t="s">
+        <v>46</v>
+      </c>
+      <c r="K633" t="s">
+        <v>23</v>
+      </c>
+      <c r="L633" t="s">
+        <v>3403</v>
+      </c>
+      <c r="M633" t="s">
+        <v>3404</v>
+      </c>
+    </row>
+    <row r="634" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A634" t="s">
+        <v>3405</v>
+      </c>
+      <c r="B634" t="s">
+        <v>3406</v>
+      </c>
+      <c r="C634" t="s">
+        <v>58</v>
+      </c>
+      <c r="D634" t="s">
+        <v>3407</v>
+      </c>
+      <c r="E634" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F634" t="s">
+        <v>18</v>
+      </c>
+      <c r="G634" t="s">
+        <v>19</v>
+      </c>
+      <c r="H634" t="s">
+        <v>45</v>
+      </c>
+      <c r="I634" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J634" t="s">
+        <v>75</v>
+      </c>
+      <c r="K634" t="s">
+        <v>23</v>
+      </c>
+      <c r="L634" t="s">
+        <v>3408</v>
+      </c>
+      <c r="M634" t="s">
+        <v>3409</v>
+      </c>
+    </row>
+    <row r="635" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A635" t="s">
+        <v>3410</v>
+      </c>
+      <c r="B635" t="s">
+        <v>3411</v>
+      </c>
+      <c r="C635" t="s">
+        <v>15</v>
+      </c>
+      <c r="D635" t="s">
+        <v>3412</v>
+      </c>
+      <c r="E635" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F635" t="s">
+        <v>18</v>
+      </c>
+      <c r="G635" t="s">
+        <v>19</v>
+      </c>
+      <c r="H635" t="s">
+        <v>20</v>
+      </c>
+      <c r="I635" t="s">
+        <v>21</v>
+      </c>
+      <c r="J635" t="s">
+        <v>30</v>
+      </c>
+      <c r="K635" t="s">
+        <v>23</v>
+      </c>
+      <c r="L635" t="s">
+        <v>3414</v>
+      </c>
+      <c r="M635" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="636" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A636" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B636" t="s">
+        <v>3417</v>
+      </c>
+      <c r="C636" t="s">
+        <v>28</v>
+      </c>
+      <c r="D636" t="s">
+        <v>3418</v>
+      </c>
+      <c r="E636" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F636" t="s">
+        <v>18</v>
+      </c>
+      <c r="G636" t="s">
+        <v>19</v>
+      </c>
+      <c r="H636" t="s">
+        <v>381</v>
+      </c>
+      <c r="I636" t="s">
+        <v>21</v>
+      </c>
+      <c r="J636" t="s">
+        <v>46</v>
+      </c>
+      <c r="K636" t="s">
+        <v>23</v>
+      </c>
+      <c r="L636" t="s">
+        <v>3419</v>
+      </c>
+      <c r="M636" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="637" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A637" t="s">
+        <v>3421</v>
+      </c>
+      <c r="B637" t="s">
+        <v>3422</v>
+      </c>
+      <c r="C637" t="s">
+        <v>15</v>
+      </c>
+      <c r="D637" t="s">
+        <v>3423</v>
+      </c>
+      <c r="E637" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F637" t="s">
+        <v>18</v>
+      </c>
+      <c r="G637" t="s">
+        <v>19</v>
+      </c>
+      <c r="H637" t="s">
+        <v>45</v>
+      </c>
+      <c r="I637" t="s">
+        <v>21</v>
+      </c>
+      <c r="J637" t="s">
+        <v>30</v>
+      </c>
+      <c r="K637" t="s">
+        <v>23</v>
+      </c>
+      <c r="L637" t="s">
+        <v>3424</v>
+      </c>
+      <c r="M637" t="s">
+        <v>3425</v>
+      </c>
+    </row>
+    <row r="638" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A638" t="s">
+        <v>3426</v>
+      </c>
+      <c r="B638" t="s">
+        <v>3427</v>
+      </c>
+      <c r="C638" t="s">
+        <v>28</v>
+      </c>
+      <c r="D638" t="s">
+        <v>3428</v>
+      </c>
+      <c r="E638" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F638" t="s">
+        <v>18</v>
+      </c>
+      <c r="G638" t="s">
+        <v>19</v>
+      </c>
+      <c r="H638" t="s">
+        <v>37</v>
+      </c>
+      <c r="I638" t="s">
+        <v>21</v>
+      </c>
+      <c r="J638" t="s">
+        <v>75</v>
+      </c>
+      <c r="K638" t="s">
+        <v>23</v>
+      </c>
+      <c r="L638" t="s">
+        <v>3429</v>
+      </c>
+      <c r="M638" t="s">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="639" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A639" t="s">
+        <v>3431</v>
+      </c>
+      <c r="B639" t="s">
+        <v>3432</v>
+      </c>
+      <c r="C639" t="s">
+        <v>15</v>
+      </c>
+      <c r="D639" t="s">
+        <v>3433</v>
+      </c>
+      <c r="E639" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F639" t="s">
+        <v>18</v>
+      </c>
+      <c r="G639" t="s">
+        <v>19</v>
+      </c>
+      <c r="H639" t="s">
+        <v>37</v>
+      </c>
+      <c r="I639" t="s">
+        <v>21</v>
+      </c>
+      <c r="J639" t="s">
+        <v>46</v>
+      </c>
+      <c r="K639" t="s">
+        <v>23</v>
+      </c>
+      <c r="L639" t="s">
+        <v>3434</v>
+      </c>
+      <c r="M639" t="s">
+        <v>3435</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/Sajjad data/by_country_and_state/USA/CA.xlsx
+++ b/Sajjad data/by_country_and_state/USA/CA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8307" uniqueCount="3436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9243" uniqueCount="3811">
   <si>
     <t>Business Name</t>
   </si>
@@ -10319,6 +10319,1131 @@
   </si>
   <si>
     <t>2026-10-25T04:20:29.243Z</t>
+  </si>
+  <si>
+    <t>Santa Rosa Kids Dental Office</t>
+  </si>
+  <si>
+    <t>(707) 595-0601</t>
+  </si>
+  <si>
+    <t>3918 Princeton Dr, Santa Rosa, CA 95405</t>
+  </si>
+  <si>
+    <t>SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Santa+Rosa+Kids+Dental+Office/data=!4m7!3m6!1s0x80844906ff4b9101:0x88fe7f9da4ed5f6a!8m2!3d38.4432685!4d-122.6740549!16s%2Fg%2F11z2hdl50z!19sChIJAZFL_wZJhIARal_tpJ1__og?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:10.123Z</t>
+  </si>
+  <si>
+    <t>Hodges Frank R DDS</t>
+  </si>
+  <si>
+    <t>(707) 544-4611</t>
+  </si>
+  <si>
+    <t>1111 Sonoma Ave Ste 102, Santa Rosa, CA 95405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hodges+Frank+R+DDS/data=!4m7!3m6!1s0x8084480a3e5cc2b3:0x8824b784444cf318!8m2!3d38.4420154!4d-122.6999965!16s%2Fg%2F1tj73trq!19sChIJs8JcPgpIhIARGPNMRIS3JIg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:12.513Z</t>
+  </si>
+  <si>
+    <t>Van Roy Laura DDS</t>
+  </si>
+  <si>
+    <t>(707) 838-1686</t>
+  </si>
+  <si>
+    <t>8741 Brooks Rd S #202, Windsor, CA 95492</t>
+  </si>
+  <si>
+    <t>Windsor</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Van+Roy+Laura+DDS/data=!4m7!3m6!1s0x80843e09b78a4f47:0xc6cfa65a2708bbef!8m2!3d38.5477196!4d-122.8067042!16s%2Fg%2F1v46_kzd!19sChIJR0-Ktwk-hIAR77sIJ1qmz8Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:14.715Z</t>
+  </si>
+  <si>
+    <t>Briggs Pediatric Dentistry</t>
+  </si>
+  <si>
+    <t>(707) 584-3718</t>
+  </si>
+  <si>
+    <t>1310 Medical Center Dr, Rohnert Park, CA 94928</t>
+  </si>
+  <si>
+    <t>Rohnert Park</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Briggs+Pediatric+Dentistry/data=!4m7!3m6!1s0x80844a45edc7dd1f:0x24cd217c1bed8646!8m2!3d38.3478415!4d-122.6850953!16s%2Fg%2F1thn5qyc!19sChIJH93H7UVKhIARRobtG3whzSQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:16.881Z</t>
+  </si>
+  <si>
+    <t>Emergency Dental Direct</t>
+  </si>
+  <si>
+    <t>(707) 768-0018</t>
+  </si>
+  <si>
+    <t>608 Mendocino Ave, Santa Rosa, CA 95401</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dental+Direct/data=!4m7!3m6!1s0x8084478b1097d6e3:0x73316853a101e3e8!8m2!3d38.4448689!4d-122.7170805!16s%2Fg%2F11zxclxyvm!19sChIJ49aXEItHhIAR6OMBoVNoMXM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:00:12.638Z</t>
+  </si>
+  <si>
+    <t>Rincon Valley Dentistry of Santa Rosa</t>
+  </si>
+  <si>
+    <t>(707) 539-2176</t>
+  </si>
+  <si>
+    <t>6543 Montecito Blvd, Santa Rosa, CA 95409</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rincon+Valley+Dentistry+of+Santa+Rosa/data=!4m7!3m6!1s0x808447b34ddd9be3:0xef13a20d28865506!8m2!3d38.4758253!4d-122.6732712!16s%2Fg%2F1hc10r4ps!19sChIJ45vdTbNHhIARBlWGKA2iE-8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:00:14.820Z</t>
+  </si>
+  <si>
+    <t>MC Dental Group- Carlos Flores DDS</t>
+  </si>
+  <si>
+    <t>(707) 595-7500</t>
+  </si>
+  <si>
+    <t>2213 Mendocino Ave, Santa Rosa, CA 95403</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/MC+Dental+Group-+Carlos+Flores+DDS/data=!4m7!3m6!1s0x808449fbb6f12169:0x449b01dc7a1d963f!8m2!3d38.461495!4d-122.717749!16s%2Fg%2F11j0ygy0zq!19sChIJaSHxtvtJhIARP5YdetwBm0Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:00:32.235Z</t>
+  </si>
+  <si>
+    <t>Patricia A. Murray, DMD, PhD</t>
+  </si>
+  <si>
+    <t>(707) 525-1600</t>
+  </si>
+  <si>
+    <t>1100 Sonoma Ave Ste D, Santa Rosa, CA 95405</t>
+  </si>
+  <si>
+    <t>SundayClosed; Monday8 AM–5 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday8 AM–5 PM; SaturdayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Patricia+A.+Murray,+DMD,+PhD/data=!4m7!3m6!1s0x8084480a2c5b8f03:0xef513d4ab0434219!8m2!3d38.4406573!4d-122.700735!16s%2Fg%2F1vr3dd03!19sChIJA49bLApIhIARGUJDsEo9Ue8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:01:19.506Z</t>
+  </si>
+  <si>
+    <t>Robert S. Gilbaugh, DDS</t>
+  </si>
+  <si>
+    <t>(707) 575-1194</t>
+  </si>
+  <si>
+    <t>1100 Sonoma Ave, Santa Rosa, CA 95405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Robert+S.+Gilbaugh,+DDS/data=!4m7!3m6!1s0x8084480a2c5b8f03:0xa0206ca7757e73d1!8m2!3d38.4406871!4d-122.70078!16s%2Fg%2F1v9lb_gm!19sChIJA49bLApIhIAR0XN-dadsIKA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:01:21.884Z</t>
+  </si>
+  <si>
+    <t>Simonds James a DDS</t>
+  </si>
+  <si>
+    <t>(707) 525-0555</t>
+  </si>
+  <si>
+    <t>2213 Mendocino Ave A, Santa Rosa, CA 95403</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Simonds+James+a+DDS/data=!4m7!3m6!1s0x80844789fc27add3:0x6dc737a83a9a96aa!8m2!3d38.46148!4d-122.717557!16s%2Fg%2F1tl9ms_h!19sChIJ060n_IlHhIARqpaaOqg3x20?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:01:26.040Z</t>
+  </si>
+  <si>
+    <t>Elk Grove Dental Care</t>
+  </si>
+  <si>
+    <t>(916) 478-2521</t>
+  </si>
+  <si>
+    <t>9105 Bruceville Rd Ste 8A, Elk Grove, CA 95758</t>
+  </si>
+  <si>
+    <t>Elk Grove</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Elk+Grove+Dental+Care/data=!4m7!3m6!1s0x809ac648b31f78c3:0x631a14abd88f9296!8m2!3d38.4268479!4d-121.4172966!16s%2Fg%2F1tfxgykv!19sChIJw3gfs0jGmoARlpKP2KsUGmM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:01:50.321Z</t>
+  </si>
+  <si>
+    <t>Wellness Dental Care</t>
+  </si>
+  <si>
+    <t>(916) 691-0685</t>
+  </si>
+  <si>
+    <t>9390 Big Horn Blvd #175, Elk Grove, CA 95758</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Wellness+Dental+Care/data=!4m7!3m6!1s0x809ac7acbcde56bb:0xaf7c467a2ca2fae8!8m2!3d38.4205363!4d-121.4084144!16s%2Fg%2F1tdb4jj9!19sChIJu1bevKzHmoAR6PqiLHpGfK8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:02:58.915Z</t>
+  </si>
+  <si>
+    <t>Elk Grove Dentist</t>
+  </si>
+  <si>
+    <t>(916) 683-9080</t>
+  </si>
+  <si>
+    <t>9045 Bruceville Rd #170, Elk Grove, CA 95758</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Elk+Grove+Dentist/data=!4m7!3m6!1s0x809ac6549f244d2f:0x62d25c0d3a461f5!8m2!3d38.429166!4d-121.4172639!16s%2Fg%2F1tgcs3q8!19sChIJL00kn1TGmoAR9WGk08AlLQY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:17.902Z</t>
+  </si>
+  <si>
+    <t>Aesthetic Family Dentistry</t>
+  </si>
+  <si>
+    <t>(916) 714-0702</t>
+  </si>
+  <si>
+    <t>9638 Elk Grove Florin Rd, Elk Grove, CA 95624</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aesthetic+Family+Dentistry/data=!4m7!3m6!1s0x809ac713529e156d:0x9869e799220e86ce!8m2!3d38.4076628!4d-121.3718182!16s%2Fg%2F11gv0n1q_b!19sChIJbRWeUhPHmoARzoYOIpnnaZg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:39.323Z</t>
+  </si>
+  <si>
+    <t>Family Dentistry - Amor R. Cristobal, DMD</t>
+  </si>
+  <si>
+    <t>(916) 478-2728</t>
+  </si>
+  <si>
+    <t>7805 Laguna Blvd #320, Elk Grove, CA 95758</t>
+  </si>
+  <si>
+    <t>Closed · Opens 8:15 AM Mon · See more hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Dentistry+-+Amor+R.+Cristobal,+DMD/data=!4m7!3m6!1s0x809ac64dd62d97dd:0x460f6ee7589d1415!8m2!3d38.4239819!4d-121.4108356!16s%2Fg%2F1tk6w4nq!19sChIJ3Zct1k3GmoARFRSdWOduD0Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:43.378Z</t>
+  </si>
+  <si>
+    <t>Dr. Stanley M. Arellano, DDS</t>
+  </si>
+  <si>
+    <t>(916) 581-6989</t>
+  </si>
+  <si>
+    <t>9024 Franklin Blvd Ste 100, Elk Grove, CA 95758</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Stanley+M.+Arellano,+DDS/data=!4m7!3m6!1s0x809ac620ae9c4def:0x68994df324560883!8m2!3d38.4292579!4d-121.447542!16s%2Fg%2F113g1x2xq!19sChIJ702criDGmoARgwhWJPNNmWg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:51.177Z</t>
+  </si>
+  <si>
+    <t>Dr. David M. Burke, DDS</t>
+  </si>
+  <si>
+    <t>(916) 684-4780</t>
+  </si>
+  <si>
+    <t>7949, 7811 Laguna Blvd #190, Elk Grove, CA 95758</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+David+M.+Burke,+DDS/data=!4m7!3m6!1s0x809ac64dee1674dd:0xd28352f177d6c50e!8m2!3d38.4231872!4d-121.4114379!16s%2Fg%2F1tf28ym5!19sChIJ3XQW7k3GmoARDsXWd_FSg9I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:24.882Z</t>
+  </si>
+  <si>
+    <t>Laguna Bond Dental</t>
+  </si>
+  <si>
+    <t>(916) 686-8989</t>
+  </si>
+  <si>
+    <t>9141 E Stockton Blvd Ste 230, Elk Grove, CA 95624</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Laguna+Bond+Dental/data=!4m7!3m6!1s0x809ac6fe637ec57f:0x858ac3f486d2ddbe!8m2!3d38.4265588!4d-121.3941484!16s%2Fg%2F1tjg_m9z!19sChIJf8V-Y_7GmoARvt3ShvTDioU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:44.700Z</t>
+  </si>
+  <si>
+    <t>Innovation Dental Group Elk Grove</t>
+  </si>
+  <si>
+    <t>(916) 392-1088</t>
+  </si>
+  <si>
+    <t>4809 Laguna Blvd Unit 90, Elk Grove, CA 95758</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Innovation+Dental+Group+Elk+Grove/data=!4m7!3m6!1s0x809ac95e095756fd:0xef69c1e18ce6c673!8m2!3d38.4246021!4d-121.4497692!16s%2Fg%2F11ghp_xzqd!19sChIJ_VZXCV7JmoARc8bmjOHBae8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:58.743Z</t>
+  </si>
+  <si>
+    <t>Sunnyvale Town Center Dental Group</t>
+  </si>
+  <si>
+    <t>(408) 736-0888</t>
+  </si>
+  <si>
+    <t>516 W Remington Dr Bldg. #5A, Sunnyvale, CA 94087</t>
+  </si>
+  <si>
+    <t>Sunnyvale</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sunnyvale+Town+Center+Dental+Group/data=!4m7!3m6!1s0x808fb7e7bd54195f:0xa873e4e0a70a490d!8m2!3d37.3585572!4d-122.0332236!16s%2Fg%2F11mcshtmx7!19sChIJXxlUvee3j4ARDUkKp-Dkc6g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:07:16.967Z</t>
+  </si>
+  <si>
+    <t>Quality Dental</t>
+  </si>
+  <si>
+    <t>(408) 732-0001</t>
+  </si>
+  <si>
+    <t>1286 Kifer Rd Ste 106, Sunnyvale, CA 94086</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Quality+Dental/data=!4m7!3m6!1s0x808fc9fdb3fa7d7d:0xd91c6827e5a5e110!8m2!3d37.3733591!4d-121.9902812!16s%2Fg%2F1hc2_8tbm!19sChIJfX36s_3Jj4AREOGl5SdoHNk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:07:44.110Z</t>
+  </si>
+  <si>
+    <t>Lakewood Dental Care</t>
+  </si>
+  <si>
+    <t>(408) 541-1900</t>
+  </si>
+  <si>
+    <t>1153 Lawrence Expy, Sunnyvale, CA 94089</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lakewood+Dental+Care/data=!4m7!3m6!1s0x808fb6296b7ef461:0x9f60c3c8870ff44f!8m2!3d37.3978575!4d-121.9970333!16s%2Fg%2F1vwlpcfs!19sChIJYfR-aym2j4ART_QPh8jDYJ8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:18.384Z</t>
+  </si>
+  <si>
+    <t>Silicon Valley Dental Implant Center, Kim Alexander Y. DDS</t>
+  </si>
+  <si>
+    <t>(408) 730-8000</t>
+  </si>
+  <si>
+    <t>565 E El Camino Real, Sunnyvale, CA 94087</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Silicon+Valley+Dental+Implant+Center,+Kim+Alexander+Y.+DDS/data=!4m7!3m6!1s0x808fb670936b083d:0xe90fae6fddc5c504!8m2!3d37.3636256!4d-122.0261697!16s%2Fg%2F1tp2_md6!19sChIJPQhrk3C2j4ARBMXF3W-uD-k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:10:30.446Z</t>
+  </si>
+  <si>
+    <t>Bruce R. Jespersen, DDS</t>
+  </si>
+  <si>
+    <t>(408) 446-5787</t>
+  </si>
+  <si>
+    <t>425 E Remington Dr #3, Sunnyvale, CA 94087</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bruce+R.+Jespersen,+DDS/data=!4m7!3m6!1s0x808fb5a9bf6cb25b:0x915e294d10e51c0b!8m2!3d37.3592697!4d-122.0289859!16s%2Fg%2F1td9d_bb!19sChIJW7Jsv6m1j4ARCxzlEE0pXpE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:12:23.574Z</t>
+  </si>
+  <si>
+    <t>SUDIP GHOSH DDS, MS, Inc.</t>
+  </si>
+  <si>
+    <t>(408) 736-7878</t>
+  </si>
+  <si>
+    <t>303 W El Camino Real, Sunnyvale, CA 94087</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/SUDIP+GHOSH+DDS,+MS,+Inc./data=!4m7!3m6!1s0x808fb6610bae3813:0xacdb28db77c8b532!8m2!3d37.3690226!4d-122.0352238!16s%2Fg%2F11c59vx3lp!19sChIJEziuC2G2j4ARMrXId9so26w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:12:25.865Z</t>
+  </si>
+  <si>
+    <t>Chang Steve H DDS</t>
+  </si>
+  <si>
+    <t>(408) 732-5592</t>
+  </si>
+  <si>
+    <t>990 W Fremont Ave Ste N, Sunnyvale, CA 94087</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chang+Steve+H+DDS/data=!4m7!3m6!1s0x808fb69c175194a7:0xca89df2a2592540!8m2!3d37.3517795!4d-122.0545876!16s%2Fg%2F1xgrn527!19sChIJp5RRF5y2j4ARQCVZovKdqAw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:12:33.220Z</t>
+  </si>
+  <si>
+    <t>Hieu Pham DDS, MD</t>
+  </si>
+  <si>
+    <t>(408) 738-3930</t>
+  </si>
+  <si>
+    <t>990 W Fremont Ave Suite V, Sunnyvale, CA 94087</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hieu+Pham+DDS,+MD/data=!4m7!3m6!1s0x808fb69c175194a7:0x1479f5ba6b930aa!8m2!3d37.3511904!4d-122.0548483!16s%2Fg%2F1tlwfwt8!19sChIJp5RRF5y2j4ARqjC5plufRwE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:12:35.661Z</t>
+  </si>
+  <si>
+    <t>Bayside Dental Care</t>
+  </si>
+  <si>
+    <t>(510) 940-0200</t>
+  </si>
+  <si>
+    <t>933 C St, Hayward, CA 94541</t>
+  </si>
+  <si>
+    <t>Hayward</t>
+  </si>
+  <si>
+    <t>SundayOpen 24 hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bayside+Dental+Care/data=!4m7!3m6!1s0x808f93d8eb507c8d:0xfd87204e0cfcb20e!8m2!3d37.6712314!4d-122.0824105!16s%2Fg%2F1trpr0j2!19sChIJjXxQ69iTj4ARDrL8DE4gh_0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:12:51.656Z</t>
+  </si>
+  <si>
+    <t>Hayward Family Dental Amuer M. Blanco DMD</t>
+  </si>
+  <si>
+    <t>(510) 201-6932</t>
+  </si>
+  <si>
+    <t>27092 Hesperian Blvd, Hayward, CA 94545</t>
+  </si>
+  <si>
+    <t>Sunday7 AM–11 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hayward+Family+Dental+Amuer+M.+Blanco+DMD/data=!4m7!3m6!1s0x808f96b07a674d7d:0x70adf891e93cadd4!8m2!3d37.6325621!4d-122.0975125!16s%2Fg%2F1tlz_d_6!19sChIJfU1nerCWj4AR1K086ZH4rXA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:12:53.839Z</t>
+  </si>
+  <si>
+    <t>Nguyen Khaie DDS</t>
+  </si>
+  <si>
+    <t>(510) 538-9701</t>
+  </si>
+  <si>
+    <t>1644 B St, Hayward, CA 94541</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nguyen+Khaie+DDS/data=!4m7!3m6!1s0x808f93cfcf0c5bdf:0xf815f0e1401f2e3c!8m2!3d37.6791181!4d-122.0718009!16s%2Fg%2F1tgdj6v9!19sChIJ31sMz8-Tj4ARPC4fQOHwFfg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:12:56.175Z</t>
+  </si>
+  <si>
+    <t>Healthy Teeth, Happy Smile Dentistry</t>
+  </si>
+  <si>
+    <t>(510) 690-9896</t>
+  </si>
+  <si>
+    <t>26953 Mission Blvd Ste j, Hayward, CA 94544</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Healthy+Teeth,+Happy+Smile+Dentistry/data=!4m7!3m6!1s0x808f940cfcdd1503:0x18ec0c8db428f4f3!8m2!3d37.6443748!4d-122.0624704!16s%2Fg%2F1vqth0b4!19sChIJAxXd_AyUj4AR8_QotI0M7Bg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:12:58.806Z</t>
+  </si>
+  <si>
+    <t>E Z Dental</t>
+  </si>
+  <si>
+    <t>(510) 293-0900</t>
+  </si>
+  <si>
+    <t>434 W Harder Rd, Hayward, CA 94544</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/E+Z+Dental/data=!4m7!3m6!1s0x808f915445d779d3:0xa480fd62d7f81e78!8m2!3d37.6469146!4d-122.0883382!16s%2Fg%2F1tk9q_lx!19sChIJ03nXRVSRj4AReB7412L9gKQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:02.719Z</t>
+  </si>
+  <si>
+    <t>Big Smile Dental</t>
+  </si>
+  <si>
+    <t>(510) 999-8014</t>
+  </si>
+  <si>
+    <t>22429 Foothill Blvd, Hayward, CA 94541</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Big+Smile+Dental/data=!4m7!3m6!1s0x808f931388816b31:0x9453506513e18883!8m2!3d37.6763001!4d-122.0830686!16s%2Fg%2F11q49krvtj!19sChIJMWuBiBOTj4ARg4jhE2VQU5Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:04.641Z</t>
+  </si>
+  <si>
+    <t>Allegro Dental Group</t>
+  </si>
+  <si>
+    <t>(510) 940-8659</t>
+  </si>
+  <si>
+    <t>1866 B St #203, Hayward, CA 94541</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Allegro+Dental+Group/data=!4m7!3m6!1s0x808f937af2f53f57:0xdd19caa854fc60f6!8m2!3d37.6828764!4d-122.0658068!16s%2Fg%2F11g0pdry6d!19sChIJVz_18nqTj4AR9mD8VKjKGd0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:08.892Z</t>
+  </si>
+  <si>
+    <t>Mary Debbie Carag-Francisco, DDS.</t>
+  </si>
+  <si>
+    <t>(510) 733-3381</t>
+  </si>
+  <si>
+    <t>146 Harder Rd Ste b, Hayward, CA 94544</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mary+Debbie+Carag-Francisco,+DDS./data=!4m7!3m6!1s0x808f93f8dfde135b:0xef8488151db0293d!8m2!3d37.6497043!4d-122.0765705!16s%2Fg%2F1tdcglrt!19sChIJWxPe3_iTj4ARPSmwHRWIhO8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:11.225Z</t>
+  </si>
+  <si>
+    <t>ESDL DE LEON, DDS INC</t>
+  </si>
+  <si>
+    <t>(510) 582-8277</t>
+  </si>
+  <si>
+    <t>1375 B St, Hayward, CA 94547</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/ESDL+DE+LEON,+DDS+INC/data=!4m7!3m6!1s0x808f93d09030a675:0x80e0daceb6a25ffd!8m2!3d37.6772608!4d-122.0761479!16s%2Fg%2F11bzyqx2nj!19sChIJdaYwkNCTj4AR_V-its7a4IA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:13.466Z</t>
+  </si>
+  <si>
+    <t>Dentist Maria T.Rodriguez</t>
+  </si>
+  <si>
+    <t>(510) 264-1410</t>
+  </si>
+  <si>
+    <t>Hayward, CA 94541</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentist+Maria+T.Rodriguez/data=!4m7!3m6!1s0x808f91067458d993:0xa89c67cd12519f7d!8m2!3d37.6737239!4d-122.1007867!16s%2Fg%2F11hctkt67s!19sChIJk9lYdAaRj4ARfZ9REs1nnKg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:27.025Z</t>
+  </si>
+  <si>
+    <t>H. Vincent Lai, D.D.S.</t>
+  </si>
+  <si>
+    <t>(510) 733-6282</t>
+  </si>
+  <si>
+    <t>20652 Redwood Rd, Castro Valley, CA 94546</t>
+  </si>
+  <si>
+    <t>Castro Valley</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/H.+Vincent+Lai,+D.D.S./data=!4m7!3m6!1s0x808f922f8accaa13:0x20810e1b1f4e8eff!8m2!3d37.696004!4d-122.0734684!16s%2Fg%2F1v4k6rk_!19sChIJE6rMii-Sj4AR_45OHxsOgSA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:31.094Z</t>
+  </si>
+  <si>
+    <t>Family &amp; Cosmetic Dentistry - Amy M Nguyen DDS</t>
+  </si>
+  <si>
+    <t>(510) 825-6091</t>
+  </si>
+  <si>
+    <t>567 W A St Ste B, Hayward, CA 94541</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+%26+Cosmetic+Dentistry+-+Amy+M+Nguyen+DDS/data=!4m7!3m6!1s0x808f9113405e0c39:0x858c0650f5bfa431!8m2!3d37.6663641!4d-122.111126!16s%2Fg%2F11qw2p81v5!19sChIJOQxeQBORj4ARMaS_9VAGjIU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:45.105Z</t>
+  </si>
+  <si>
+    <t>Tri-City Family Dentistry</t>
+  </si>
+  <si>
+    <t>(510) 487-4899</t>
+  </si>
+  <si>
+    <t>31874 Alvarado Blvd, Union City, CA 94587</t>
+  </si>
+  <si>
+    <t>Union City</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tri-City+Family+Dentistry/data=!4m7!3m6!1s0x808f95e8507e80ad:0x9885f1dfbd0c183e!8m2!3d37.590311!4d-122.070327!16s%2Fg%2F1tfdz2d7!19sChIJrYB-UOiVj4ARPhgMvd_xhZg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:47.530Z</t>
+  </si>
+  <si>
+    <t>Lawrence C. Lee, DDS</t>
+  </si>
+  <si>
+    <t>(510) 782-1875</t>
+  </si>
+  <si>
+    <t>777 Southland Dr Boardroom, Hayward, CA 94545</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lawrence+C.+Lee,+DDS/data=!4m7!3m6!1s0x808f9147440b1761:0x7fa7845c729ab956!8m2!3d37.6522075!4d-122.1056824!16s%2Fg%2F1tffv510!19sChIJYRcLREeRj4ARVrmaclyEp38?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:51.139Z</t>
+  </si>
+  <si>
+    <t>Tran Andy M DDS</t>
+  </si>
+  <si>
+    <t>(510) 783-2772</t>
+  </si>
+  <si>
+    <t>1191 W Tennyson Rd #1, Hayward, CA 94544</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tran+Andy+M+DDS/data=!4m7!3m6!1s0x808f9419381f0443:0xf5bcb89cfe996181!8m2!3d37.6318444!4d-122.0773676!16s%2Fg%2F1th5_0pl!19sChIJQwQfOBmUj4ARgWGZ_py4vPU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:14:05.684Z</t>
+  </si>
+  <si>
+    <t>Dr. Han C Lin, DDS</t>
+  </si>
+  <si>
+    <t>(510) 581-1772</t>
+  </si>
+  <si>
+    <t>22273 Main St, Hayward, CA 94541</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Han+C+Lin,+DDS/data=!4m7!3m6!1s0x808f917da8929e6d:0x927b73a2184822b4!8m2!3d37.6760086!4d-122.0861212!16s%2Fg%2F1tdz51nw!19sChIJbZ6SqH2Rj4ARtCJIGKJze5I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:17:29.614Z</t>
+  </si>
+  <si>
+    <t>Fontabla Rosalyn DDS</t>
+  </si>
+  <si>
+    <t>(510) 477-6887</t>
+  </si>
+  <si>
+    <t>31111 Mission Blvd, Hayward, CA 94544</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fontabla+Rosalyn+DDS/data=!4m7!3m6!1s0x808f95004ee448af:0x3453de6f54db94ac!8m2!3d37.6191309!4d-122.0363152!16s%2Fg%2F1vxz9w2w!19sChIJr0jkTgCVj4ARrJTbVG_eUzQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:17:32.068Z</t>
+  </si>
+  <si>
+    <t>Dr. Wayman Tang, DDS</t>
+  </si>
+  <si>
+    <t>(510) 888-9298</t>
+  </si>
+  <si>
+    <t>4027 E Castro Valley Blvd, Castro Valley, CA 94552</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Wayman+Tang,+DDS/data=!4m7!3m6!1s0x808f924d7783332f:0xf9982eaa1427f6e7!8m2!3d37.6951398!4d-122.0500669!16s%2Fg%2F1thxl95f!19sChIJLzODd02Sj4AR5_YnFKoumPk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:17:33.827Z</t>
+  </si>
+  <si>
+    <t>Foothill Dental - Clelen C Tanner, DDS</t>
+  </si>
+  <si>
+    <t>(510) 733-1455</t>
+  </si>
+  <si>
+    <t>21911 Foothill Blvd, Hayward, CA 94541</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Foothill+Dental+-+Clelen+C+Tanner,+DDS/data=!4m7!3m6!1s0x808f917f05f4f7ef:0xb3044a166c218e52!8m2!3d37.681011!4d-122.086896!16s%2Fg%2F1tsyq01y!19sChIJ7_f0BX-Rj4ARUo4hbBZKBLM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:17:36.091Z</t>
+  </si>
+  <si>
+    <t>Dental Care of Sherwood Gardens</t>
+  </si>
+  <si>
+    <t>(855) 321-3612</t>
+  </si>
+  <si>
+    <t>929 N Main St, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>Salinas</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Care+of+Sherwood+Gardens/data=!4m7!3m6!1s0x808df8ca5abcbf13:0x900af999a0e6f08f!8m2!3d36.6915834!4d-121.6535859!16s%2Fg%2F1tfxy7y2!19sChIJE7-8Wsr4jYARj_DmoJn5CpA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:17:52.155Z</t>
+  </si>
+  <si>
+    <t>Creek Bridge Dental</t>
+  </si>
+  <si>
+    <t>(831) 449-3264</t>
+  </si>
+  <si>
+    <t>1558 Constitution Blvd, Salinas, CA 93905</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Creek+Bridge+Dental/data=!4m7!3m6!1s0x80920752282e00e5:0x4b685ee9aade4936!8m2!3d36.6989179!4d-121.6189895!16s%2Fg%2F1t_kgsc_!19sChIJ5QAuKFIHkoARNknequleaEs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:17:55.627Z</t>
+  </si>
+  <si>
+    <t>Crystal Dental</t>
+  </si>
+  <si>
+    <t>(831) 422-7500</t>
+  </si>
+  <si>
+    <t>1542 N Sanborn Rd, Salinas, CA 93905</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Crystal+Dental/data=!4m7!3m6!1s0x8092073c53e269a1:0x9b17d79963c5b087!8m2!3d36.6937945!4d-121.5969806!16s%2Fg%2F1tw1f1vd!19sChIJoWniUzwHkoARh7DFY5nXF5s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:17:57.699Z</t>
+  </si>
+  <si>
+    <t>Xudong (Don) Yang DDS</t>
+  </si>
+  <si>
+    <t>(831) 757-3951</t>
+  </si>
+  <si>
+    <t>780 E Romie Ln Ste E, Salinas, CA 93901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Xudong+%28Don%29+Yang+DDS/data=!4m7!3m6!1s0x808df862b1c86379:0x2bd55e807e654797!8m2!3d36.6582773!4d-121.6401352!16s%2Fg%2F1tpf7b_9!19sChIJeWPIsWL4jYARl0dlfoBe1Ss?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:17:59.923Z</t>
+  </si>
+  <si>
+    <t>Craig Varjian Inc</t>
+  </si>
+  <si>
+    <t>(831) 443-1878</t>
+  </si>
+  <si>
+    <t>640 E Alvin Dr # D, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Craig+Varjian+Inc/data=!4m7!3m6!1s0x808dff54436fbd77:0x6f970fc22fa1de6!8m2!3d36.703232!4d-121.6324308!16s%2Fg%2F1tg7s7kp!19sChIJd71vQ1T_jYAR5h36Ivxw-QY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:18:02.399Z</t>
+  </si>
+  <si>
+    <t>Today's Dental Practice:Harshita Patel DDS</t>
+  </si>
+  <si>
+    <t>(831) 443-2700</t>
+  </si>
+  <si>
+    <t>640 E Alvin Dr # A, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Today%27s+Dental+Practice:Harshita+Patel+DDS/data=!4m7!3m6!1s0x808dff54436fbd77:0x30439d4cd761936c!8m2!3d36.7033312!4d-121.6321019!16s%2Fg%2F1td0b4xn!19sChIJd71vQ1T_jYARbJNh10ydQzA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:18:04.481Z</t>
+  </si>
+  <si>
+    <t>Val Cristobal Viray Jr Inc</t>
+  </si>
+  <si>
+    <t>(831) 422-5557</t>
+  </si>
+  <si>
+    <t>1326 Natividad Rd # D, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Val+Cristobal+Viray+Jr+Inc/data=!4m7!3m6!1s0x808df8acdc9e64b5:0xf6c7ce09be024178!8m2!3d36.6990447!4d-121.6352162!16s%2Fg%2F1tg6kskh!19sChIJtWSe3Kz4jYAReEECvgnOx_Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:18:06.858Z</t>
+  </si>
+  <si>
+    <t>Aparna Nayudu Dds Inc</t>
+  </si>
+  <si>
+    <t>(831) 757-7504</t>
+  </si>
+  <si>
+    <t>1089 S Main St, Salinas, CA 93901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aparna+Nayudu+Dds+Inc/data=!4m7!3m6!1s0x808df8f1121b1545:0xb401542d5e43ee7d!8m2!3d36.6600823!4d-121.6571601!16s%2Fg%2F11bbw_m8q1!19sChIJRRUbEvH4jYARfe5DXi1UAbQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:18:09.043Z</t>
+  </si>
+  <si>
+    <t>Yang Peter T DDS</t>
+  </si>
+  <si>
+    <t>(831) 753-6598</t>
+  </si>
+  <si>
+    <t>41 W Romie Ln, Salinas, CA 93901</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>Sunday9 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Yang+Peter+T+DDS/data=!4m7!3m6!1s0x808df8ec6e3f6a01:0x23413d259b90e542!8m2!3d36.6628854!4d-121.6600025!16s%2Fg%2F1tfqg0l0!19sChIJAWo_buz4jYARQuWQmyU9QSM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:18:11.290Z</t>
+  </si>
+  <si>
+    <t>Asbury-Falo Theresa DDS</t>
+  </si>
+  <si>
+    <t>(831) 449-9128</t>
+  </si>
+  <si>
+    <t>11 W Laurel Dr #135, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Asbury-Falo+Theresa+DDS/data=!4m7!3m6!1s0x808dff3675c73d97:0x38ecd1edab9bc8d1!8m2!3d36.69901!4d-121.6526868!16s%2Fg%2F1hc0_0jlj!19sChIJlz3HdTb_jYAR0cibq-3R7Dg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:18:13.125Z</t>
+  </si>
+  <si>
+    <t>Tan Danny DDS</t>
+  </si>
+  <si>
+    <t>(831) 449-9776</t>
+  </si>
+  <si>
+    <t>608 E Boronda Rd # B, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tan+Danny+DDS/data=!4m7!3m6!1s0x808dff5f494c7ca5:0x30d023f1ddf1eef3!8m2!3d36.7147027!4d-121.6262512!16s%2Fg%2F1tp1z0_3!19sChIJpXxMSV__jYAR8-7x3fEj0DA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:18:15.768Z</t>
+  </si>
+  <si>
+    <t>Ramirez Dental</t>
+  </si>
+  <si>
+    <t>(831) 235-8920</t>
+  </si>
+  <si>
+    <t>11 Maple St E, Salinas, CA 93901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ramirez+Dental/data=!4m7!3m6!1s0x808df94408872175:0x2a20eb2c90af3301!8m2!3d36.6686125!4d-121.6549844!16s%2Fg%2F11fscvsvzn!19sChIJdSGHCET5jYARATOvkCzrICo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:18:17.891Z</t>
+  </si>
+  <si>
+    <t>Jonathan N. Kristianto DDS - Parkway Dental</t>
+  </si>
+  <si>
+    <t>(831) 444-0882</t>
+  </si>
+  <si>
+    <t>1556 N Main St, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jonathan+N.+Kristianto+DDS+-+Parkway+Dental/data=!4m7!3m6!1s0x808dff38dd02a569:0x4bc73ae3eddd84e6!8m2!3d36.7131523!4d-121.6522682!16s%2Fg%2F1tgxj8pw!19sChIJaaUC3Tj_jYAR5oTd7eM6x0s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:18:20.144Z</t>
+  </si>
+  <si>
+    <t>Dr. HLA Myaing, DDS</t>
+  </si>
+  <si>
+    <t>(831) 758-0122</t>
+  </si>
+  <si>
+    <t>770 E Romie Ln, Salinas, CA 93901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+HLA+Myaing,+DDS/data=!4m7!3m6!1s0x808df862bc9c8527:0xf22957cf72b40f31!8m2!3d36.6584561!4d-121.6408643!16s%2Fg%2F1w665m_r!19sChIJJ4WcvGL4jYARMQ-0cs9XKfI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:18:22.720Z</t>
+  </si>
+  <si>
+    <t>Soria Julio C DDS</t>
+  </si>
+  <si>
+    <t>(831) 753-7606</t>
+  </si>
+  <si>
+    <t>1004 N Davis Rd, Salinas, CA 93907</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Soria+Julio+C+DDS/data=!4m7!3m6!1s0x808dff2ea84d4713:0xdd70ac32e63fd9fd!8m2!3d36.6948113!4d-121.6677217!16s%2Fg%2F11dftl6ld5!19sChIJE0dNqC7_jYAR_dk_5jKscN0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:19:01.015Z</t>
+  </si>
+  <si>
+    <t>Ngoi Steven T DDS</t>
+  </si>
+  <si>
+    <t>(831) 422-6461</t>
+  </si>
+  <si>
+    <t>972 Lupin Dr, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ngoi+Steven+T+DDS/data=!4m7!3m6!1s0x808df8cae4131717:0xa772f8b48ba6582a!8m2!3d36.6924743!4d-121.6536294!16s%2Fg%2F1tgnm9bc!19sChIJFxcT5Mr4jYARKlimi7T4cqc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:19:53.764Z</t>
+  </si>
+  <si>
+    <t>James D Kim Family Dentistry: Kim Ha Jung DDS</t>
+  </si>
+  <si>
+    <t>(831) 424-4230</t>
+  </si>
+  <si>
+    <t>601 E Romie Ln #6, Salinas, CA 93901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/James+D+Kim+Family+Dentistry:+Kim+Ha+Jung+DDS/data=!4m7!3m6!1s0x808df88998613e9d:0xbb0eee5a8a6b9106!8m2!3d36.6598919!4d-121.6440948!16s%2Fg%2F1hc4wq2gn!19sChIJnT5hmIn4jYARBpFrilruDrs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:19:55.653Z</t>
+  </si>
+  <si>
+    <t>Dr. Pooja Rattan, DDS</t>
+  </si>
+  <si>
+    <t>(831) 442-8878</t>
+  </si>
+  <si>
+    <t>631 E Alvin Dr j2, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Pooja+Rattan,+DDS/data=!4m7!3m6!1s0x808dff544a239bbd:0xc9e7d6f2a13ac124!8m2!3d36.7042466!4d-121.6310711!16s%2Fg%2F1vf9clqp!19sChIJvZsjSlT_jYARJME6ofLW58k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:20:40.893Z</t>
+  </si>
+  <si>
+    <t>Dominguez Jaime S DDS</t>
+  </si>
+  <si>
+    <t>(831) 751-2801</t>
+  </si>
+  <si>
+    <t>672 E Romie Ln, Salinas, CA 93901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dominguez+Jaime+S+DDS/data=!4m7!3m6!1s0x808df889c87bb14d:0x1459057ea483a8cc!8m2!3d36.6589792!4d-121.6439517!16s%2Fg%2F1tcvphgx!19sChIJTbF7yIn4jYARzKiDpH4FWRQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:20:43.311Z</t>
+  </si>
+  <si>
+    <t>Patel Chattan M DDS</t>
+  </si>
+  <si>
+    <t>(831) 775-0280</t>
+  </si>
+  <si>
+    <t>652 E Laurel Dr # C, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Patel+Chattan+M+DDS/data=!4m7!3m6!1s0x808df8ad7707b6bf:0x13c3edf01e57307a!8m2!3d36.6960727!4d-121.638864!16s%2Fg%2F1td7tdt9!19sChIJv7YHd634jYARejBXHvDtwxM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:20:45.238Z</t>
+  </si>
+  <si>
+    <t>Kenji B. Saisho, M.D., D.D.S.</t>
+  </si>
+  <si>
+    <t>(831) 424-0641</t>
+  </si>
+  <si>
+    <t>945 Blanco Cir Ste D, Salinas, CA 93901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kenji+B.+Saisho,+M.D.,+D.D.S./data=!4m7!3m6!1s0x808df87c993d444d:0xfbdfae5a8c6ce2a!8m2!3d36.6551403!4d-121.6379277!16s%2Fg%2F1tcx779b!19sChIJTUQ9mXz4jYARKs7GqOX6vQ8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:20:47.796Z</t>
+  </si>
+  <si>
+    <t>Val J Termotto Inc</t>
+  </si>
+  <si>
+    <t>(831) 758-3319</t>
+  </si>
+  <si>
+    <t>951 Blanco Cir C, Salinas, CA 93901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Val+J+Termotto+Inc/data=!4m7!3m6!1s0x808df889ec1a79cd:0x1e7ec8894b9b6a9f!8m2!3d36.6560334!4d-121.6368436!16s%2Fg%2F1v3h_6c5!19sChIJzXka7In4jYARn2qbS4nIfh4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:20:50.476Z</t>
+  </si>
+  <si>
+    <t>Wahl Randy DDS</t>
+  </si>
+  <si>
+    <t>(831) 443-3814</t>
+  </si>
+  <si>
+    <t>631 E Alvin Dr #D, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Wahl+Randy+DDS/data=!4m7!3m6!1s0x808dff544a239bbd:0x467a13132be40cad!8m2!3d36.7045089!4d-121.6315475!16s%2Fg%2F1tlqq6l7!19sChIJvZsjSlT_jYARrQzkKxMTekY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:21:04.727Z</t>
+  </si>
+  <si>
+    <t>Pacific Orthodontic Specialist</t>
+  </si>
+  <si>
+    <t>(831) 424-3255</t>
+  </si>
+  <si>
+    <t>1465 N Davis Rd A, Salinas, CA 93907</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pacific+Orthodontic+Specialist/data=!4m7!3m6!1s0x808dff22580a39d5:0x479b95bdac6a5713!8m2!3d36.7081717!4d-121.6663138!16s%2Fg%2F1261z4xwd!19sChIJ1TkKWCL_jYARE1dqrL2Vm0c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:21:06.826Z</t>
+  </si>
+  <si>
+    <t>Dr. Youngrim Kim, DDS</t>
+  </si>
+  <si>
+    <t>(831) 753-9505</t>
+  </si>
+  <si>
+    <t>1137 N Main St A, Salinas, CA 93906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Youngrim+Kim,+DDS/data=!4m7!3m6!1s0x808dff359ce765c9:0x54f6a05db71b9986!8m2!3d36.6969413!4d-121.6522369!16s%2Fg%2F1tfzxqkj!19sChIJyWXnnDX_jYARhpkbt12g9lQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:21:20.734Z</t>
+  </si>
+  <si>
+    <t>Sparkly Smile Spa</t>
+  </si>
+  <si>
+    <t>(831) 320-3106</t>
+  </si>
+  <si>
+    <t>35 E Romie Ln Suit D, Salinas, CA 93901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sparkly+Smile+Spa/data=!4m7!3m6!1s0x808df9244f714817:0x9375036709d1b197!8m2!3d36.6626983!4d-121.656379!16s%2Fg%2F11l5clzxf4!19sChIJF0hxTyT5jYARl7HRCWcDdZM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:22:18.704Z</t>
   </si>
 </sst>
 </file>
@@ -10699,7 +11824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M639"/>
+  <dimension ref="A1:M711"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -36915,6 +38040,2958 @@
         <v>3435</v>
       </c>
     </row>
+    <row r="640" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A640" t="s">
+        <v>3436</v>
+      </c>
+      <c r="B640" t="s">
+        <v>3437</v>
+      </c>
+      <c r="C640" t="s">
+        <v>15</v>
+      </c>
+      <c r="D640" t="s">
+        <v>3438</v>
+      </c>
+      <c r="E640" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F640" t="s">
+        <v>18</v>
+      </c>
+      <c r="G640" t="s">
+        <v>19</v>
+      </c>
+      <c r="H640" t="s">
+        <v>75</v>
+      </c>
+      <c r="I640" t="s">
+        <v>81</v>
+      </c>
+      <c r="J640" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K640" t="s">
+        <v>23</v>
+      </c>
+      <c r="L640" t="s">
+        <v>3440</v>
+      </c>
+      <c r="M640" t="s">
+        <v>3441</v>
+      </c>
+    </row>
+    <row r="641" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A641" t="s">
+        <v>3442</v>
+      </c>
+      <c r="B641" t="s">
+        <v>3443</v>
+      </c>
+      <c r="C641" t="s">
+        <v>477</v>
+      </c>
+      <c r="D641" t="s">
+        <v>3444</v>
+      </c>
+      <c r="E641" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F641" t="s">
+        <v>18</v>
+      </c>
+      <c r="G641" t="s">
+        <v>19</v>
+      </c>
+      <c r="H641" t="s">
+        <v>103</v>
+      </c>
+      <c r="I641" t="s">
+        <v>21</v>
+      </c>
+      <c r="J641" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K641" t="s">
+        <v>23</v>
+      </c>
+      <c r="L641" t="s">
+        <v>3445</v>
+      </c>
+      <c r="M641" t="s">
+        <v>3446</v>
+      </c>
+    </row>
+    <row r="642" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A642" t="s">
+        <v>3447</v>
+      </c>
+      <c r="B642" t="s">
+        <v>3448</v>
+      </c>
+      <c r="C642" t="s">
+        <v>477</v>
+      </c>
+      <c r="D642" t="s">
+        <v>3449</v>
+      </c>
+      <c r="E642" t="s">
+        <v>3450</v>
+      </c>
+      <c r="F642" t="s">
+        <v>18</v>
+      </c>
+      <c r="G642" t="s">
+        <v>19</v>
+      </c>
+      <c r="H642" t="s">
+        <v>120</v>
+      </c>
+      <c r="I642" t="s">
+        <v>21</v>
+      </c>
+      <c r="J642" t="s">
+        <v>75</v>
+      </c>
+      <c r="K642" t="s">
+        <v>23</v>
+      </c>
+      <c r="L642" t="s">
+        <v>3451</v>
+      </c>
+      <c r="M642" t="s">
+        <v>3452</v>
+      </c>
+    </row>
+    <row r="643" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A643" t="s">
+        <v>3453</v>
+      </c>
+      <c r="B643" t="s">
+        <v>3454</v>
+      </c>
+      <c r="C643" t="s">
+        <v>15</v>
+      </c>
+      <c r="D643" t="s">
+        <v>3455</v>
+      </c>
+      <c r="E643" t="s">
+        <v>3456</v>
+      </c>
+      <c r="F643" t="s">
+        <v>18</v>
+      </c>
+      <c r="G643" t="s">
+        <v>19</v>
+      </c>
+      <c r="H643" t="s">
+        <v>20</v>
+      </c>
+      <c r="I643" t="s">
+        <v>21</v>
+      </c>
+      <c r="J643" t="s">
+        <v>75</v>
+      </c>
+      <c r="K643" t="s">
+        <v>23</v>
+      </c>
+      <c r="L643" t="s">
+        <v>3457</v>
+      </c>
+      <c r="M643" t="s">
+        <v>3458</v>
+      </c>
+    </row>
+    <row r="644" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A644" t="s">
+        <v>3459</v>
+      </c>
+      <c r="B644" t="s">
+        <v>3460</v>
+      </c>
+      <c r="C644" t="s">
+        <v>73</v>
+      </c>
+      <c r="D644" t="s">
+        <v>3461</v>
+      </c>
+      <c r="E644" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F644" t="s">
+        <v>18</v>
+      </c>
+      <c r="G644" t="s">
+        <v>19</v>
+      </c>
+      <c r="H644" t="s">
+        <v>45</v>
+      </c>
+      <c r="I644" t="s">
+        <v>21</v>
+      </c>
+      <c r="J644" t="s">
+        <v>75</v>
+      </c>
+      <c r="K644" t="s">
+        <v>23</v>
+      </c>
+      <c r="L644" t="s">
+        <v>3462</v>
+      </c>
+      <c r="M644" t="s">
+        <v>3463</v>
+      </c>
+    </row>
+    <row r="645" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A645" t="s">
+        <v>3464</v>
+      </c>
+      <c r="B645" t="s">
+        <v>3465</v>
+      </c>
+      <c r="C645" t="s">
+        <v>15</v>
+      </c>
+      <c r="D645" t="s">
+        <v>3466</v>
+      </c>
+      <c r="E645" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F645" t="s">
+        <v>18</v>
+      </c>
+      <c r="G645" t="s">
+        <v>19</v>
+      </c>
+      <c r="H645" t="s">
+        <v>45</v>
+      </c>
+      <c r="I645" t="s">
+        <v>21</v>
+      </c>
+      <c r="J645" t="s">
+        <v>75</v>
+      </c>
+      <c r="K645" t="s">
+        <v>23</v>
+      </c>
+      <c r="L645" t="s">
+        <v>3467</v>
+      </c>
+      <c r="M645" t="s">
+        <v>3468</v>
+      </c>
+    </row>
+    <row r="646" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A646" t="s">
+        <v>3469</v>
+      </c>
+      <c r="B646" t="s">
+        <v>3470</v>
+      </c>
+      <c r="C646" t="s">
+        <v>15</v>
+      </c>
+      <c r="D646" t="s">
+        <v>3471</v>
+      </c>
+      <c r="E646" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F646" t="s">
+        <v>18</v>
+      </c>
+      <c r="G646" t="s">
+        <v>19</v>
+      </c>
+      <c r="H646" t="s">
+        <v>211</v>
+      </c>
+      <c r="I646" t="s">
+        <v>21</v>
+      </c>
+      <c r="J646" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K646" t="s">
+        <v>23</v>
+      </c>
+      <c r="L646" t="s">
+        <v>3472</v>
+      </c>
+      <c r="M646" t="s">
+        <v>3473</v>
+      </c>
+    </row>
+    <row r="647" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A647" t="s">
+        <v>3474</v>
+      </c>
+      <c r="B647" t="s">
+        <v>3475</v>
+      </c>
+      <c r="C647" t="s">
+        <v>58</v>
+      </c>
+      <c r="D647" t="s">
+        <v>3476</v>
+      </c>
+      <c r="E647" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F647" t="s">
+        <v>18</v>
+      </c>
+      <c r="G647" t="s">
+        <v>19</v>
+      </c>
+      <c r="H647" t="s">
+        <v>120</v>
+      </c>
+      <c r="I647" t="s">
+        <v>695</v>
+      </c>
+      <c r="J647" t="s">
+        <v>3477</v>
+      </c>
+      <c r="K647" t="s">
+        <v>23</v>
+      </c>
+      <c r="L647" t="s">
+        <v>3478</v>
+      </c>
+      <c r="M647" t="s">
+        <v>3479</v>
+      </c>
+    </row>
+    <row r="648" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A648" t="s">
+        <v>3480</v>
+      </c>
+      <c r="B648" t="s">
+        <v>3481</v>
+      </c>
+      <c r="C648" t="s">
+        <v>15</v>
+      </c>
+      <c r="D648" t="s">
+        <v>3482</v>
+      </c>
+      <c r="E648" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F648" t="s">
+        <v>18</v>
+      </c>
+      <c r="G648" t="s">
+        <v>19</v>
+      </c>
+      <c r="H648" t="s">
+        <v>45</v>
+      </c>
+      <c r="I648" t="s">
+        <v>21</v>
+      </c>
+      <c r="J648" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K648" t="s">
+        <v>23</v>
+      </c>
+      <c r="L648" t="s">
+        <v>3483</v>
+      </c>
+      <c r="M648" t="s">
+        <v>3484</v>
+      </c>
+    </row>
+    <row r="649" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A649" t="s">
+        <v>3485</v>
+      </c>
+      <c r="B649" t="s">
+        <v>3486</v>
+      </c>
+      <c r="C649" t="s">
+        <v>15</v>
+      </c>
+      <c r="D649" t="s">
+        <v>3487</v>
+      </c>
+      <c r="E649" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F649" t="s">
+        <v>18</v>
+      </c>
+      <c r="G649" t="s">
+        <v>19</v>
+      </c>
+      <c r="H649" t="s">
+        <v>45</v>
+      </c>
+      <c r="I649" t="s">
+        <v>21</v>
+      </c>
+      <c r="J649" t="s">
+        <v>75</v>
+      </c>
+      <c r="K649" t="s">
+        <v>23</v>
+      </c>
+      <c r="L649" t="s">
+        <v>3488</v>
+      </c>
+      <c r="M649" t="s">
+        <v>3489</v>
+      </c>
+    </row>
+    <row r="650" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A650" t="s">
+        <v>3490</v>
+      </c>
+      <c r="B650" t="s">
+        <v>3491</v>
+      </c>
+      <c r="C650" t="s">
+        <v>28</v>
+      </c>
+      <c r="D650" t="s">
+        <v>3492</v>
+      </c>
+      <c r="E650" t="s">
+        <v>3493</v>
+      </c>
+      <c r="F650" t="s">
+        <v>18</v>
+      </c>
+      <c r="G650" t="s">
+        <v>19</v>
+      </c>
+      <c r="H650" t="s">
+        <v>67</v>
+      </c>
+      <c r="I650" t="s">
+        <v>21</v>
+      </c>
+      <c r="J650" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K650" t="s">
+        <v>23</v>
+      </c>
+      <c r="L650" t="s">
+        <v>3494</v>
+      </c>
+      <c r="M650" t="s">
+        <v>3495</v>
+      </c>
+    </row>
+    <row r="651" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A651" t="s">
+        <v>3496</v>
+      </c>
+      <c r="B651" t="s">
+        <v>3497</v>
+      </c>
+      <c r="C651" t="s">
+        <v>175</v>
+      </c>
+      <c r="D651" t="s">
+        <v>3498</v>
+      </c>
+      <c r="E651" t="s">
+        <v>3493</v>
+      </c>
+      <c r="F651" t="s">
+        <v>18</v>
+      </c>
+      <c r="G651" t="s">
+        <v>19</v>
+      </c>
+      <c r="H651" t="s">
+        <v>45</v>
+      </c>
+      <c r="I651" t="s">
+        <v>21</v>
+      </c>
+      <c r="J651" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K651" t="s">
+        <v>23</v>
+      </c>
+      <c r="L651" t="s">
+        <v>3499</v>
+      </c>
+      <c r="M651" t="s">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="652" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A652" t="s">
+        <v>3501</v>
+      </c>
+      <c r="B652" t="s">
+        <v>3502</v>
+      </c>
+      <c r="C652" t="s">
+        <v>15</v>
+      </c>
+      <c r="D652" t="s">
+        <v>3503</v>
+      </c>
+      <c r="E652" t="s">
+        <v>3493</v>
+      </c>
+      <c r="F652" t="s">
+        <v>18</v>
+      </c>
+      <c r="G652" t="s">
+        <v>19</v>
+      </c>
+      <c r="H652" t="s">
+        <v>75</v>
+      </c>
+      <c r="I652" t="s">
+        <v>81</v>
+      </c>
+      <c r="J652" t="s">
+        <v>75</v>
+      </c>
+      <c r="K652" t="s">
+        <v>23</v>
+      </c>
+      <c r="L652" t="s">
+        <v>3504</v>
+      </c>
+      <c r="M652" t="s">
+        <v>3505</v>
+      </c>
+    </row>
+    <row r="653" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A653" t="s">
+        <v>3506</v>
+      </c>
+      <c r="B653" t="s">
+        <v>3507</v>
+      </c>
+      <c r="C653" t="s">
+        <v>15</v>
+      </c>
+      <c r="D653" t="s">
+        <v>3508</v>
+      </c>
+      <c r="E653" t="s">
+        <v>3493</v>
+      </c>
+      <c r="F653" t="s">
+        <v>18</v>
+      </c>
+      <c r="G653" t="s">
+        <v>19</v>
+      </c>
+      <c r="H653" t="s">
+        <v>45</v>
+      </c>
+      <c r="I653" t="s">
+        <v>21</v>
+      </c>
+      <c r="J653" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K653" t="s">
+        <v>23</v>
+      </c>
+      <c r="L653" t="s">
+        <v>3509</v>
+      </c>
+      <c r="M653" t="s">
+        <v>3510</v>
+      </c>
+    </row>
+    <row r="654" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A654" t="s">
+        <v>3511</v>
+      </c>
+      <c r="B654" t="s">
+        <v>3512</v>
+      </c>
+      <c r="C654" t="s">
+        <v>15</v>
+      </c>
+      <c r="D654" t="s">
+        <v>3513</v>
+      </c>
+      <c r="E654" t="s">
+        <v>3493</v>
+      </c>
+      <c r="F654" t="s">
+        <v>18</v>
+      </c>
+      <c r="G654" t="s">
+        <v>19</v>
+      </c>
+      <c r="H654" t="s">
+        <v>45</v>
+      </c>
+      <c r="I654" t="s">
+        <v>21</v>
+      </c>
+      <c r="J654" t="s">
+        <v>3514</v>
+      </c>
+      <c r="K654" t="s">
+        <v>23</v>
+      </c>
+      <c r="L654" t="s">
+        <v>3515</v>
+      </c>
+      <c r="M654" t="s">
+        <v>3516</v>
+      </c>
+    </row>
+    <row r="655" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A655" t="s">
+        <v>3517</v>
+      </c>
+      <c r="B655" t="s">
+        <v>3518</v>
+      </c>
+      <c r="C655" t="s">
+        <v>15</v>
+      </c>
+      <c r="D655" t="s">
+        <v>3519</v>
+      </c>
+      <c r="E655" t="s">
+        <v>3493</v>
+      </c>
+      <c r="F655" t="s">
+        <v>18</v>
+      </c>
+      <c r="G655" t="s">
+        <v>19</v>
+      </c>
+      <c r="H655" t="s">
+        <v>67</v>
+      </c>
+      <c r="I655" t="s">
+        <v>21</v>
+      </c>
+      <c r="J655" t="s">
+        <v>75</v>
+      </c>
+      <c r="K655" t="s">
+        <v>23</v>
+      </c>
+      <c r="L655" t="s">
+        <v>3520</v>
+      </c>
+      <c r="M655" t="s">
+        <v>3521</v>
+      </c>
+    </row>
+    <row r="656" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A656" t="s">
+        <v>3522</v>
+      </c>
+      <c r="B656" t="s">
+        <v>3523</v>
+      </c>
+      <c r="C656" t="s">
+        <v>15</v>
+      </c>
+      <c r="D656" t="s">
+        <v>3524</v>
+      </c>
+      <c r="E656" t="s">
+        <v>3493</v>
+      </c>
+      <c r="F656" t="s">
+        <v>18</v>
+      </c>
+      <c r="G656" t="s">
+        <v>19</v>
+      </c>
+      <c r="H656" t="s">
+        <v>45</v>
+      </c>
+      <c r="I656" t="s">
+        <v>21</v>
+      </c>
+      <c r="J656" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K656" t="s">
+        <v>23</v>
+      </c>
+      <c r="L656" t="s">
+        <v>3525</v>
+      </c>
+      <c r="M656" t="s">
+        <v>3526</v>
+      </c>
+    </row>
+    <row r="657" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A657" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B657" t="s">
+        <v>3528</v>
+      </c>
+      <c r="C657" t="s">
+        <v>15</v>
+      </c>
+      <c r="D657" t="s">
+        <v>3529</v>
+      </c>
+      <c r="E657" t="s">
+        <v>3493</v>
+      </c>
+      <c r="F657" t="s">
+        <v>18</v>
+      </c>
+      <c r="G657" t="s">
+        <v>19</v>
+      </c>
+      <c r="H657" t="s">
+        <v>466</v>
+      </c>
+      <c r="I657" t="s">
+        <v>21</v>
+      </c>
+      <c r="J657" t="s">
+        <v>75</v>
+      </c>
+      <c r="K657" t="s">
+        <v>23</v>
+      </c>
+      <c r="L657" t="s">
+        <v>3530</v>
+      </c>
+      <c r="M657" t="s">
+        <v>3531</v>
+      </c>
+    </row>
+    <row r="658" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A658" t="s">
+        <v>3532</v>
+      </c>
+      <c r="B658" t="s">
+        <v>3533</v>
+      </c>
+      <c r="C658" t="s">
+        <v>15</v>
+      </c>
+      <c r="D658" t="s">
+        <v>3534</v>
+      </c>
+      <c r="E658" t="s">
+        <v>3493</v>
+      </c>
+      <c r="F658" t="s">
+        <v>18</v>
+      </c>
+      <c r="G658" t="s">
+        <v>19</v>
+      </c>
+      <c r="H658" t="s">
+        <v>547</v>
+      </c>
+      <c r="I658" t="s">
+        <v>21</v>
+      </c>
+      <c r="J658" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K658" t="s">
+        <v>23</v>
+      </c>
+      <c r="L658" t="s">
+        <v>3535</v>
+      </c>
+      <c r="M658" t="s">
+        <v>3536</v>
+      </c>
+    </row>
+    <row r="659" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A659" t="s">
+        <v>3537</v>
+      </c>
+      <c r="B659" t="s">
+        <v>3538</v>
+      </c>
+      <c r="C659" t="s">
+        <v>28</v>
+      </c>
+      <c r="D659" t="s">
+        <v>3539</v>
+      </c>
+      <c r="E659" t="s">
+        <v>3540</v>
+      </c>
+      <c r="F659" t="s">
+        <v>18</v>
+      </c>
+      <c r="G659" t="s">
+        <v>19</v>
+      </c>
+      <c r="H659" t="s">
+        <v>37</v>
+      </c>
+      <c r="I659" t="s">
+        <v>21</v>
+      </c>
+      <c r="J659" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K659" t="s">
+        <v>23</v>
+      </c>
+      <c r="L659" t="s">
+        <v>3541</v>
+      </c>
+      <c r="M659" t="s">
+        <v>3542</v>
+      </c>
+    </row>
+    <row r="660" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A660" t="s">
+        <v>3543</v>
+      </c>
+      <c r="B660" t="s">
+        <v>3544</v>
+      </c>
+      <c r="C660" t="s">
+        <v>15</v>
+      </c>
+      <c r="D660" t="s">
+        <v>3545</v>
+      </c>
+      <c r="E660" t="s">
+        <v>3540</v>
+      </c>
+      <c r="F660" t="s">
+        <v>18</v>
+      </c>
+      <c r="G660" t="s">
+        <v>19</v>
+      </c>
+      <c r="H660" t="s">
+        <v>223</v>
+      </c>
+      <c r="I660" t="s">
+        <v>21</v>
+      </c>
+      <c r="J660" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K660" t="s">
+        <v>23</v>
+      </c>
+      <c r="L660" t="s">
+        <v>3546</v>
+      </c>
+      <c r="M660" t="s">
+        <v>3547</v>
+      </c>
+    </row>
+    <row r="661" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A661" t="s">
+        <v>3548</v>
+      </c>
+      <c r="B661" t="s">
+        <v>3549</v>
+      </c>
+      <c r="C661" t="s">
+        <v>15</v>
+      </c>
+      <c r="D661" t="s">
+        <v>3550</v>
+      </c>
+      <c r="E661" t="s">
+        <v>3540</v>
+      </c>
+      <c r="F661" t="s">
+        <v>18</v>
+      </c>
+      <c r="G661" t="s">
+        <v>19</v>
+      </c>
+      <c r="H661" t="s">
+        <v>627</v>
+      </c>
+      <c r="I661" t="s">
+        <v>21</v>
+      </c>
+      <c r="J661" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K661" t="s">
+        <v>23</v>
+      </c>
+      <c r="L661" t="s">
+        <v>3551</v>
+      </c>
+      <c r="M661" t="s">
+        <v>3552</v>
+      </c>
+    </row>
+    <row r="662" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A662" t="s">
+        <v>3553</v>
+      </c>
+      <c r="B662" t="s">
+        <v>3554</v>
+      </c>
+      <c r="C662" t="s">
+        <v>15</v>
+      </c>
+      <c r="D662" t="s">
+        <v>3555</v>
+      </c>
+      <c r="E662" t="s">
+        <v>3540</v>
+      </c>
+      <c r="F662" t="s">
+        <v>18</v>
+      </c>
+      <c r="G662" t="s">
+        <v>19</v>
+      </c>
+      <c r="H662" t="s">
+        <v>103</v>
+      </c>
+      <c r="I662" t="s">
+        <v>21</v>
+      </c>
+      <c r="J662" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K662" t="s">
+        <v>23</v>
+      </c>
+      <c r="L662" t="s">
+        <v>3556</v>
+      </c>
+      <c r="M662" t="s">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="663" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A663" t="s">
+        <v>3558</v>
+      </c>
+      <c r="B663" t="s">
+        <v>3559</v>
+      </c>
+      <c r="C663" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D663" t="s">
+        <v>3560</v>
+      </c>
+      <c r="E663" t="s">
+        <v>3540</v>
+      </c>
+      <c r="F663" t="s">
+        <v>18</v>
+      </c>
+      <c r="G663" t="s">
+        <v>19</v>
+      </c>
+      <c r="H663" t="s">
+        <v>547</v>
+      </c>
+      <c r="I663" t="s">
+        <v>21</v>
+      </c>
+      <c r="J663" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K663" t="s">
+        <v>23</v>
+      </c>
+      <c r="L663" t="s">
+        <v>3561</v>
+      </c>
+      <c r="M663" t="s">
+        <v>3562</v>
+      </c>
+    </row>
+    <row r="664" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A664" t="s">
+        <v>3563</v>
+      </c>
+      <c r="B664" t="s">
+        <v>3564</v>
+      </c>
+      <c r="C664" t="s">
+        <v>15</v>
+      </c>
+      <c r="D664" t="s">
+        <v>3565</v>
+      </c>
+      <c r="E664" t="s">
+        <v>3540</v>
+      </c>
+      <c r="F664" t="s">
+        <v>18</v>
+      </c>
+      <c r="G664" t="s">
+        <v>19</v>
+      </c>
+      <c r="H664" t="s">
+        <v>627</v>
+      </c>
+      <c r="I664" t="s">
+        <v>21</v>
+      </c>
+      <c r="J664" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K664" t="s">
+        <v>23</v>
+      </c>
+      <c r="L664" t="s">
+        <v>3566</v>
+      </c>
+      <c r="M664" t="s">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="665" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A665" t="s">
+        <v>3568</v>
+      </c>
+      <c r="B665" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C665" t="s">
+        <v>58</v>
+      </c>
+      <c r="D665" t="s">
+        <v>3570</v>
+      </c>
+      <c r="E665" t="s">
+        <v>3540</v>
+      </c>
+      <c r="F665" t="s">
+        <v>18</v>
+      </c>
+      <c r="G665" t="s">
+        <v>19</v>
+      </c>
+      <c r="H665" t="s">
+        <v>75</v>
+      </c>
+      <c r="I665" t="s">
+        <v>695</v>
+      </c>
+      <c r="J665" t="s">
+        <v>75</v>
+      </c>
+      <c r="K665" t="s">
+        <v>23</v>
+      </c>
+      <c r="L665" t="s">
+        <v>3571</v>
+      </c>
+      <c r="M665" t="s">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="666" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A666" t="s">
+        <v>3573</v>
+      </c>
+      <c r="B666" t="s">
+        <v>3574</v>
+      </c>
+      <c r="C666" t="s">
+        <v>3119</v>
+      </c>
+      <c r="D666" t="s">
+        <v>3575</v>
+      </c>
+      <c r="E666" t="s">
+        <v>3540</v>
+      </c>
+      <c r="F666" t="s">
+        <v>18</v>
+      </c>
+      <c r="G666" t="s">
+        <v>19</v>
+      </c>
+      <c r="H666" t="s">
+        <v>20</v>
+      </c>
+      <c r="I666" t="s">
+        <v>21</v>
+      </c>
+      <c r="J666" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K666" t="s">
+        <v>23</v>
+      </c>
+      <c r="L666" t="s">
+        <v>3576</v>
+      </c>
+      <c r="M666" t="s">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="667" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
+        <v>3578</v>
+      </c>
+      <c r="B667" t="s">
+        <v>3579</v>
+      </c>
+      <c r="C667" t="s">
+        <v>15</v>
+      </c>
+      <c r="D667" t="s">
+        <v>3580</v>
+      </c>
+      <c r="E667" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F667" t="s">
+        <v>18</v>
+      </c>
+      <c r="G667" t="s">
+        <v>19</v>
+      </c>
+      <c r="H667" t="s">
+        <v>120</v>
+      </c>
+      <c r="I667" t="s">
+        <v>21</v>
+      </c>
+      <c r="J667" t="s">
+        <v>3582</v>
+      </c>
+      <c r="K667" t="s">
+        <v>23</v>
+      </c>
+      <c r="L667" t="s">
+        <v>3583</v>
+      </c>
+      <c r="M667" t="s">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="668" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A668" t="s">
+        <v>3585</v>
+      </c>
+      <c r="B668" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C668" t="s">
+        <v>15</v>
+      </c>
+      <c r="D668" t="s">
+        <v>3587</v>
+      </c>
+      <c r="E668" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F668" t="s">
+        <v>18</v>
+      </c>
+      <c r="G668" t="s">
+        <v>19</v>
+      </c>
+      <c r="H668" t="s">
+        <v>381</v>
+      </c>
+      <c r="I668" t="s">
+        <v>21</v>
+      </c>
+      <c r="J668" t="s">
+        <v>3588</v>
+      </c>
+      <c r="K668" t="s">
+        <v>23</v>
+      </c>
+      <c r="L668" t="s">
+        <v>3589</v>
+      </c>
+      <c r="M668" t="s">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="669" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A669" t="s">
+        <v>3591</v>
+      </c>
+      <c r="B669" t="s">
+        <v>3592</v>
+      </c>
+      <c r="C669" t="s">
+        <v>15</v>
+      </c>
+      <c r="D669" t="s">
+        <v>3593</v>
+      </c>
+      <c r="E669" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F669" t="s">
+        <v>18</v>
+      </c>
+      <c r="G669" t="s">
+        <v>19</v>
+      </c>
+      <c r="H669" t="s">
+        <v>547</v>
+      </c>
+      <c r="I669" t="s">
+        <v>21</v>
+      </c>
+      <c r="J669" t="s">
+        <v>3582</v>
+      </c>
+      <c r="K669" t="s">
+        <v>23</v>
+      </c>
+      <c r="L669" t="s">
+        <v>3594</v>
+      </c>
+      <c r="M669" t="s">
+        <v>3595</v>
+      </c>
+    </row>
+    <row r="670" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A670" t="s">
+        <v>3596</v>
+      </c>
+      <c r="B670" t="s">
+        <v>3597</v>
+      </c>
+      <c r="C670" t="s">
+        <v>15</v>
+      </c>
+      <c r="D670" t="s">
+        <v>3598</v>
+      </c>
+      <c r="E670" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F670" t="s">
+        <v>18</v>
+      </c>
+      <c r="G670" t="s">
+        <v>19</v>
+      </c>
+      <c r="H670" t="s">
+        <v>45</v>
+      </c>
+      <c r="I670" t="s">
+        <v>21</v>
+      </c>
+      <c r="J670" t="s">
+        <v>3582</v>
+      </c>
+      <c r="K670" t="s">
+        <v>23</v>
+      </c>
+      <c r="L670" t="s">
+        <v>3599</v>
+      </c>
+      <c r="M670" t="s">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="671" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A671" t="s">
+        <v>3601</v>
+      </c>
+      <c r="B671" t="s">
+        <v>3602</v>
+      </c>
+      <c r="C671" t="s">
+        <v>15</v>
+      </c>
+      <c r="D671" t="s">
+        <v>3603</v>
+      </c>
+      <c r="E671" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F671" t="s">
+        <v>18</v>
+      </c>
+      <c r="G671" t="s">
+        <v>19</v>
+      </c>
+      <c r="H671" t="s">
+        <v>120</v>
+      </c>
+      <c r="I671" t="s">
+        <v>21</v>
+      </c>
+      <c r="J671" t="s">
+        <v>75</v>
+      </c>
+      <c r="K671" t="s">
+        <v>23</v>
+      </c>
+      <c r="L671" t="s">
+        <v>3604</v>
+      </c>
+      <c r="M671" t="s">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="672" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A672" t="s">
+        <v>3606</v>
+      </c>
+      <c r="B672" t="s">
+        <v>3607</v>
+      </c>
+      <c r="C672" t="s">
+        <v>15</v>
+      </c>
+      <c r="D672" t="s">
+        <v>3608</v>
+      </c>
+      <c r="E672" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F672" t="s">
+        <v>18</v>
+      </c>
+      <c r="G672" t="s">
+        <v>19</v>
+      </c>
+      <c r="H672" t="s">
+        <v>120</v>
+      </c>
+      <c r="I672" t="s">
+        <v>21</v>
+      </c>
+      <c r="J672" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K672" t="s">
+        <v>23</v>
+      </c>
+      <c r="L672" t="s">
+        <v>3609</v>
+      </c>
+      <c r="M672" t="s">
+        <v>3610</v>
+      </c>
+    </row>
+    <row r="673" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>3611</v>
+      </c>
+      <c r="B673" t="s">
+        <v>3612</v>
+      </c>
+      <c r="C673" t="s">
+        <v>15</v>
+      </c>
+      <c r="D673" t="s">
+        <v>3613</v>
+      </c>
+      <c r="E673" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F673" t="s">
+        <v>18</v>
+      </c>
+      <c r="G673" t="s">
+        <v>19</v>
+      </c>
+      <c r="H673" t="s">
+        <v>405</v>
+      </c>
+      <c r="I673" t="s">
+        <v>21</v>
+      </c>
+      <c r="J673" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K673" t="s">
+        <v>23</v>
+      </c>
+      <c r="L673" t="s">
+        <v>3614</v>
+      </c>
+      <c r="M673" t="s">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="674" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A674" t="s">
+        <v>3616</v>
+      </c>
+      <c r="B674" t="s">
+        <v>3617</v>
+      </c>
+      <c r="C674" t="s">
+        <v>15</v>
+      </c>
+      <c r="D674" t="s">
+        <v>3618</v>
+      </c>
+      <c r="E674" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F674" t="s">
+        <v>18</v>
+      </c>
+      <c r="G674" t="s">
+        <v>19</v>
+      </c>
+      <c r="H674" t="s">
+        <v>381</v>
+      </c>
+      <c r="I674" t="s">
+        <v>21</v>
+      </c>
+      <c r="J674" t="s">
+        <v>3582</v>
+      </c>
+      <c r="K674" t="s">
+        <v>23</v>
+      </c>
+      <c r="L674" t="s">
+        <v>3619</v>
+      </c>
+      <c r="M674" t="s">
+        <v>3620</v>
+      </c>
+    </row>
+    <row r="675" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A675" t="s">
+        <v>3621</v>
+      </c>
+      <c r="B675" t="s">
+        <v>3622</v>
+      </c>
+      <c r="C675" t="s">
+        <v>15</v>
+      </c>
+      <c r="D675" t="s">
+        <v>3623</v>
+      </c>
+      <c r="E675" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F675" t="s">
+        <v>18</v>
+      </c>
+      <c r="G675" t="s">
+        <v>19</v>
+      </c>
+      <c r="H675" t="s">
+        <v>37</v>
+      </c>
+      <c r="I675" t="s">
+        <v>21</v>
+      </c>
+      <c r="J675" t="s">
+        <v>75</v>
+      </c>
+      <c r="K675" t="s">
+        <v>23</v>
+      </c>
+      <c r="L675" t="s">
+        <v>3624</v>
+      </c>
+      <c r="M675" t="s">
+        <v>3625</v>
+      </c>
+    </row>
+    <row r="676" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>3626</v>
+      </c>
+      <c r="B676" t="s">
+        <v>3627</v>
+      </c>
+      <c r="C676" t="s">
+        <v>15</v>
+      </c>
+      <c r="D676" t="s">
+        <v>3628</v>
+      </c>
+      <c r="E676" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F676" t="s">
+        <v>18</v>
+      </c>
+      <c r="G676" t="s">
+        <v>19</v>
+      </c>
+      <c r="H676" t="s">
+        <v>405</v>
+      </c>
+      <c r="I676" t="s">
+        <v>21</v>
+      </c>
+      <c r="J676" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K676" t="s">
+        <v>23</v>
+      </c>
+      <c r="L676" t="s">
+        <v>3629</v>
+      </c>
+      <c r="M676" t="s">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="677" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>3631</v>
+      </c>
+      <c r="B677" t="s">
+        <v>3632</v>
+      </c>
+      <c r="C677" t="s">
+        <v>15</v>
+      </c>
+      <c r="D677" t="s">
+        <v>3633</v>
+      </c>
+      <c r="E677" t="s">
+        <v>3634</v>
+      </c>
+      <c r="F677" t="s">
+        <v>18</v>
+      </c>
+      <c r="G677" t="s">
+        <v>19</v>
+      </c>
+      <c r="H677" t="s">
+        <v>223</v>
+      </c>
+      <c r="I677" t="s">
+        <v>21</v>
+      </c>
+      <c r="J677" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K677" t="s">
+        <v>23</v>
+      </c>
+      <c r="L677" t="s">
+        <v>3635</v>
+      </c>
+      <c r="M677" t="s">
+        <v>3636</v>
+      </c>
+    </row>
+    <row r="678" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>3637</v>
+      </c>
+      <c r="B678" t="s">
+        <v>3638</v>
+      </c>
+      <c r="C678" t="s">
+        <v>15</v>
+      </c>
+      <c r="D678" t="s">
+        <v>3639</v>
+      </c>
+      <c r="E678" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F678" t="s">
+        <v>18</v>
+      </c>
+      <c r="G678" t="s">
+        <v>19</v>
+      </c>
+      <c r="H678" t="s">
+        <v>45</v>
+      </c>
+      <c r="I678" t="s">
+        <v>21</v>
+      </c>
+      <c r="J678" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K678" t="s">
+        <v>23</v>
+      </c>
+      <c r="L678" t="s">
+        <v>3640</v>
+      </c>
+      <c r="M678" t="s">
+        <v>3641</v>
+      </c>
+    </row>
+    <row r="679" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>3642</v>
+      </c>
+      <c r="B679" t="s">
+        <v>3643</v>
+      </c>
+      <c r="C679" t="s">
+        <v>15</v>
+      </c>
+      <c r="D679" t="s">
+        <v>3644</v>
+      </c>
+      <c r="E679" t="s">
+        <v>3645</v>
+      </c>
+      <c r="F679" t="s">
+        <v>18</v>
+      </c>
+      <c r="G679" t="s">
+        <v>19</v>
+      </c>
+      <c r="H679" t="s">
+        <v>45</v>
+      </c>
+      <c r="I679" t="s">
+        <v>21</v>
+      </c>
+      <c r="J679" t="s">
+        <v>75</v>
+      </c>
+      <c r="K679" t="s">
+        <v>23</v>
+      </c>
+      <c r="L679" t="s">
+        <v>3646</v>
+      </c>
+      <c r="M679" t="s">
+        <v>3647</v>
+      </c>
+    </row>
+    <row r="680" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>3648</v>
+      </c>
+      <c r="B680" t="s">
+        <v>3649</v>
+      </c>
+      <c r="C680" t="s">
+        <v>15</v>
+      </c>
+      <c r="D680" t="s">
+        <v>3650</v>
+      </c>
+      <c r="E680" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F680" t="s">
+        <v>18</v>
+      </c>
+      <c r="G680" t="s">
+        <v>19</v>
+      </c>
+      <c r="H680" t="s">
+        <v>45</v>
+      </c>
+      <c r="I680" t="s">
+        <v>21</v>
+      </c>
+      <c r="J680" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K680" t="s">
+        <v>23</v>
+      </c>
+      <c r="L680" t="s">
+        <v>3651</v>
+      </c>
+      <c r="M680" t="s">
+        <v>3652</v>
+      </c>
+    </row>
+    <row r="681" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>3653</v>
+      </c>
+      <c r="B681" t="s">
+        <v>3654</v>
+      </c>
+      <c r="C681" t="s">
+        <v>15</v>
+      </c>
+      <c r="D681" t="s">
+        <v>3655</v>
+      </c>
+      <c r="E681" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F681" t="s">
+        <v>18</v>
+      </c>
+      <c r="G681" t="s">
+        <v>19</v>
+      </c>
+      <c r="H681" t="s">
+        <v>45</v>
+      </c>
+      <c r="I681" t="s">
+        <v>21</v>
+      </c>
+      <c r="J681" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K681" t="s">
+        <v>23</v>
+      </c>
+      <c r="L681" t="s">
+        <v>3656</v>
+      </c>
+      <c r="M681" t="s">
+        <v>3657</v>
+      </c>
+    </row>
+    <row r="682" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B682" t="s">
+        <v>3659</v>
+      </c>
+      <c r="C682" t="s">
+        <v>15</v>
+      </c>
+      <c r="D682" t="s">
+        <v>3660</v>
+      </c>
+      <c r="E682" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F682" t="s">
+        <v>18</v>
+      </c>
+      <c r="G682" t="s">
+        <v>19</v>
+      </c>
+      <c r="H682" t="s">
+        <v>429</v>
+      </c>
+      <c r="I682" t="s">
+        <v>21</v>
+      </c>
+      <c r="J682" t="s">
+        <v>75</v>
+      </c>
+      <c r="K682" t="s">
+        <v>23</v>
+      </c>
+      <c r="L682" t="s">
+        <v>3661</v>
+      </c>
+      <c r="M682" t="s">
+        <v>3662</v>
+      </c>
+    </row>
+    <row r="683" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>3663</v>
+      </c>
+      <c r="B683" t="s">
+        <v>3664</v>
+      </c>
+      <c r="C683" t="s">
+        <v>15</v>
+      </c>
+      <c r="D683" t="s">
+        <v>3665</v>
+      </c>
+      <c r="E683" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F683" t="s">
+        <v>18</v>
+      </c>
+      <c r="G683" t="s">
+        <v>19</v>
+      </c>
+      <c r="H683" t="s">
+        <v>92</v>
+      </c>
+      <c r="I683" t="s">
+        <v>21</v>
+      </c>
+      <c r="J683" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K683" t="s">
+        <v>23</v>
+      </c>
+      <c r="L683" t="s">
+        <v>3666</v>
+      </c>
+      <c r="M683" t="s">
+        <v>3667</v>
+      </c>
+    </row>
+    <row r="684" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
+        <v>3668</v>
+      </c>
+      <c r="B684" t="s">
+        <v>3669</v>
+      </c>
+      <c r="C684" t="s">
+        <v>15</v>
+      </c>
+      <c r="D684" t="s">
+        <v>3670</v>
+      </c>
+      <c r="E684" t="s">
+        <v>3634</v>
+      </c>
+      <c r="F684" t="s">
+        <v>18</v>
+      </c>
+      <c r="G684" t="s">
+        <v>19</v>
+      </c>
+      <c r="H684" t="s">
+        <v>223</v>
+      </c>
+      <c r="I684" t="s">
+        <v>21</v>
+      </c>
+      <c r="J684" t="s">
+        <v>75</v>
+      </c>
+      <c r="K684" t="s">
+        <v>23</v>
+      </c>
+      <c r="L684" t="s">
+        <v>3671</v>
+      </c>
+      <c r="M684" t="s">
+        <v>3672</v>
+      </c>
+    </row>
+    <row r="685" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
+        <v>3673</v>
+      </c>
+      <c r="B685" t="s">
+        <v>3674</v>
+      </c>
+      <c r="C685" t="s">
+        <v>15</v>
+      </c>
+      <c r="D685" t="s">
+        <v>3675</v>
+      </c>
+      <c r="E685" t="s">
+        <v>3581</v>
+      </c>
+      <c r="F685" t="s">
+        <v>18</v>
+      </c>
+      <c r="G685" t="s">
+        <v>19</v>
+      </c>
+      <c r="H685" t="s">
+        <v>627</v>
+      </c>
+      <c r="I685" t="s">
+        <v>21</v>
+      </c>
+      <c r="J685" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K685" t="s">
+        <v>23</v>
+      </c>
+      <c r="L685" t="s">
+        <v>3676</v>
+      </c>
+      <c r="M685" t="s">
+        <v>3677</v>
+      </c>
+    </row>
+    <row r="686" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A686" t="s">
+        <v>3678</v>
+      </c>
+      <c r="B686" t="s">
+        <v>3679</v>
+      </c>
+      <c r="C686" t="s">
+        <v>28</v>
+      </c>
+      <c r="D686" t="s">
+        <v>3680</v>
+      </c>
+      <c r="E686" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F686" t="s">
+        <v>18</v>
+      </c>
+      <c r="G686" t="s">
+        <v>19</v>
+      </c>
+      <c r="H686" t="s">
+        <v>223</v>
+      </c>
+      <c r="I686" t="s">
+        <v>21</v>
+      </c>
+      <c r="J686" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K686" t="s">
+        <v>23</v>
+      </c>
+      <c r="L686" t="s">
+        <v>3682</v>
+      </c>
+      <c r="M686" t="s">
+        <v>3683</v>
+      </c>
+    </row>
+    <row r="687" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B687" t="s">
+        <v>3685</v>
+      </c>
+      <c r="C687" t="s">
+        <v>15</v>
+      </c>
+      <c r="D687" t="s">
+        <v>3686</v>
+      </c>
+      <c r="E687" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F687" t="s">
+        <v>18</v>
+      </c>
+      <c r="G687" t="s">
+        <v>19</v>
+      </c>
+      <c r="H687" t="s">
+        <v>120</v>
+      </c>
+      <c r="I687" t="s">
+        <v>21</v>
+      </c>
+      <c r="J687" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K687" t="s">
+        <v>23</v>
+      </c>
+      <c r="L687" t="s">
+        <v>3687</v>
+      </c>
+      <c r="M687" t="s">
+        <v>3688</v>
+      </c>
+    </row>
+    <row r="688" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B688" t="s">
+        <v>3690</v>
+      </c>
+      <c r="C688" t="s">
+        <v>15</v>
+      </c>
+      <c r="D688" t="s">
+        <v>3691</v>
+      </c>
+      <c r="E688" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F688" t="s">
+        <v>18</v>
+      </c>
+      <c r="G688" t="s">
+        <v>19</v>
+      </c>
+      <c r="H688" t="s">
+        <v>815</v>
+      </c>
+      <c r="I688" t="s">
+        <v>21</v>
+      </c>
+      <c r="J688" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K688" t="s">
+        <v>23</v>
+      </c>
+      <c r="L688" t="s">
+        <v>3692</v>
+      </c>
+      <c r="M688" t="s">
+        <v>3693</v>
+      </c>
+    </row>
+    <row r="689" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>3694</v>
+      </c>
+      <c r="B689" t="s">
+        <v>3695</v>
+      </c>
+      <c r="C689" t="s">
+        <v>15</v>
+      </c>
+      <c r="D689" t="s">
+        <v>3696</v>
+      </c>
+      <c r="E689" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F689" t="s">
+        <v>18</v>
+      </c>
+      <c r="G689" t="s">
+        <v>19</v>
+      </c>
+      <c r="H689" t="s">
+        <v>381</v>
+      </c>
+      <c r="I689" t="s">
+        <v>21</v>
+      </c>
+      <c r="J689" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K689" t="s">
+        <v>23</v>
+      </c>
+      <c r="L689" t="s">
+        <v>3697</v>
+      </c>
+      <c r="M689" t="s">
+        <v>3698</v>
+      </c>
+    </row>
+    <row r="690" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A690" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B690" t="s">
+        <v>3700</v>
+      </c>
+      <c r="C690" t="s">
+        <v>15</v>
+      </c>
+      <c r="D690" t="s">
+        <v>3701</v>
+      </c>
+      <c r="E690" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F690" t="s">
+        <v>18</v>
+      </c>
+      <c r="G690" t="s">
+        <v>19</v>
+      </c>
+      <c r="H690" t="s">
+        <v>92</v>
+      </c>
+      <c r="I690" t="s">
+        <v>21</v>
+      </c>
+      <c r="J690" t="s">
+        <v>75</v>
+      </c>
+      <c r="K690" t="s">
+        <v>23</v>
+      </c>
+      <c r="L690" t="s">
+        <v>3702</v>
+      </c>
+      <c r="M690" t="s">
+        <v>3703</v>
+      </c>
+    </row>
+    <row r="691" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>3704</v>
+      </c>
+      <c r="B691" t="s">
+        <v>3705</v>
+      </c>
+      <c r="C691" t="s">
+        <v>15</v>
+      </c>
+      <c r="D691" t="s">
+        <v>3706</v>
+      </c>
+      <c r="E691" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F691" t="s">
+        <v>18</v>
+      </c>
+      <c r="G691" t="s">
+        <v>19</v>
+      </c>
+      <c r="H691" t="s">
+        <v>103</v>
+      </c>
+      <c r="I691" t="s">
+        <v>21</v>
+      </c>
+      <c r="J691" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K691" t="s">
+        <v>23</v>
+      </c>
+      <c r="L691" t="s">
+        <v>3707</v>
+      </c>
+      <c r="M691" t="s">
+        <v>3708</v>
+      </c>
+    </row>
+    <row r="692" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>3709</v>
+      </c>
+      <c r="B692" t="s">
+        <v>3710</v>
+      </c>
+      <c r="C692" t="s">
+        <v>15</v>
+      </c>
+      <c r="D692" t="s">
+        <v>3711</v>
+      </c>
+      <c r="E692" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F692" t="s">
+        <v>18</v>
+      </c>
+      <c r="G692" t="s">
+        <v>19</v>
+      </c>
+      <c r="H692" t="s">
+        <v>67</v>
+      </c>
+      <c r="I692" t="s">
+        <v>21</v>
+      </c>
+      <c r="J692" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K692" t="s">
+        <v>23</v>
+      </c>
+      <c r="L692" t="s">
+        <v>3712</v>
+      </c>
+      <c r="M692" t="s">
+        <v>3713</v>
+      </c>
+    </row>
+    <row r="693" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>3714</v>
+      </c>
+      <c r="B693" t="s">
+        <v>3715</v>
+      </c>
+      <c r="C693" t="s">
+        <v>15</v>
+      </c>
+      <c r="D693" t="s">
+        <v>3716</v>
+      </c>
+      <c r="E693" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F693" t="s">
+        <v>18</v>
+      </c>
+      <c r="G693" t="s">
+        <v>19</v>
+      </c>
+      <c r="H693" t="s">
+        <v>20</v>
+      </c>
+      <c r="I693" t="s">
+        <v>21</v>
+      </c>
+      <c r="J693" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K693" t="s">
+        <v>23</v>
+      </c>
+      <c r="L693" t="s">
+        <v>3717</v>
+      </c>
+      <c r="M693" t="s">
+        <v>3718</v>
+      </c>
+    </row>
+    <row r="694" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>3719</v>
+      </c>
+      <c r="B694" t="s">
+        <v>3720</v>
+      </c>
+      <c r="C694" t="s">
+        <v>15</v>
+      </c>
+      <c r="D694" t="s">
+        <v>3721</v>
+      </c>
+      <c r="E694" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F694" t="s">
+        <v>18</v>
+      </c>
+      <c r="G694" t="s">
+        <v>19</v>
+      </c>
+      <c r="H694" t="s">
+        <v>3722</v>
+      </c>
+      <c r="I694" t="s">
+        <v>21</v>
+      </c>
+      <c r="J694" t="s">
+        <v>3723</v>
+      </c>
+      <c r="K694" t="s">
+        <v>23</v>
+      </c>
+      <c r="L694" t="s">
+        <v>3724</v>
+      </c>
+      <c r="M694" t="s">
+        <v>3725</v>
+      </c>
+    </row>
+    <row r="695" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>3726</v>
+      </c>
+      <c r="B695" t="s">
+        <v>3727</v>
+      </c>
+      <c r="C695" t="s">
+        <v>15</v>
+      </c>
+      <c r="D695" t="s">
+        <v>3728</v>
+      </c>
+      <c r="E695" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F695" t="s">
+        <v>18</v>
+      </c>
+      <c r="G695" t="s">
+        <v>19</v>
+      </c>
+      <c r="H695" t="s">
+        <v>45</v>
+      </c>
+      <c r="I695" t="s">
+        <v>21</v>
+      </c>
+      <c r="J695" t="s">
+        <v>75</v>
+      </c>
+      <c r="K695" t="s">
+        <v>23</v>
+      </c>
+      <c r="L695" t="s">
+        <v>3729</v>
+      </c>
+      <c r="M695" t="s">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="696" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>3731</v>
+      </c>
+      <c r="B696" t="s">
+        <v>3732</v>
+      </c>
+      <c r="C696" t="s">
+        <v>15</v>
+      </c>
+      <c r="D696" t="s">
+        <v>3733</v>
+      </c>
+      <c r="E696" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F696" t="s">
+        <v>18</v>
+      </c>
+      <c r="G696" t="s">
+        <v>19</v>
+      </c>
+      <c r="H696" t="s">
+        <v>20</v>
+      </c>
+      <c r="I696" t="s">
+        <v>21</v>
+      </c>
+      <c r="J696" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K696" t="s">
+        <v>23</v>
+      </c>
+      <c r="L696" t="s">
+        <v>3734</v>
+      </c>
+      <c r="M696" t="s">
+        <v>3735</v>
+      </c>
+    </row>
+    <row r="697" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>3736</v>
+      </c>
+      <c r="B697" t="s">
+        <v>3737</v>
+      </c>
+      <c r="C697" t="s">
+        <v>28</v>
+      </c>
+      <c r="D697" t="s">
+        <v>3738</v>
+      </c>
+      <c r="E697" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F697" t="s">
+        <v>18</v>
+      </c>
+      <c r="G697" t="s">
+        <v>19</v>
+      </c>
+      <c r="H697" t="s">
+        <v>346</v>
+      </c>
+      <c r="I697" t="s">
+        <v>21</v>
+      </c>
+      <c r="J697" t="s">
+        <v>75</v>
+      </c>
+      <c r="K697" t="s">
+        <v>23</v>
+      </c>
+      <c r="L697" t="s">
+        <v>3739</v>
+      </c>
+      <c r="M697" t="s">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="698" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>3741</v>
+      </c>
+      <c r="B698" t="s">
+        <v>3742</v>
+      </c>
+      <c r="C698" t="s">
+        <v>15</v>
+      </c>
+      <c r="D698" t="s">
+        <v>3743</v>
+      </c>
+      <c r="E698" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F698" t="s">
+        <v>18</v>
+      </c>
+      <c r="G698" t="s">
+        <v>19</v>
+      </c>
+      <c r="H698" t="s">
+        <v>45</v>
+      </c>
+      <c r="I698" t="s">
+        <v>21</v>
+      </c>
+      <c r="J698" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K698" t="s">
+        <v>23</v>
+      </c>
+      <c r="L698" t="s">
+        <v>3744</v>
+      </c>
+      <c r="M698" t="s">
+        <v>3745</v>
+      </c>
+    </row>
+    <row r="699" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>3746</v>
+      </c>
+      <c r="B699" t="s">
+        <v>3747</v>
+      </c>
+      <c r="C699" t="s">
+        <v>15</v>
+      </c>
+      <c r="D699" t="s">
+        <v>3748</v>
+      </c>
+      <c r="E699" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F699" t="s">
+        <v>18</v>
+      </c>
+      <c r="G699" t="s">
+        <v>19</v>
+      </c>
+      <c r="H699" t="s">
+        <v>45</v>
+      </c>
+      <c r="I699" t="s">
+        <v>21</v>
+      </c>
+      <c r="J699" t="s">
+        <v>75</v>
+      </c>
+      <c r="K699" t="s">
+        <v>23</v>
+      </c>
+      <c r="L699" t="s">
+        <v>3749</v>
+      </c>
+      <c r="M699" t="s">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="700" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>3751</v>
+      </c>
+      <c r="B700" t="s">
+        <v>3752</v>
+      </c>
+      <c r="C700" t="s">
+        <v>15</v>
+      </c>
+      <c r="D700" t="s">
+        <v>3753</v>
+      </c>
+      <c r="E700" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F700" t="s">
+        <v>18</v>
+      </c>
+      <c r="G700" t="s">
+        <v>19</v>
+      </c>
+      <c r="H700" t="s">
+        <v>37</v>
+      </c>
+      <c r="I700" t="s">
+        <v>21</v>
+      </c>
+      <c r="J700" t="s">
+        <v>75</v>
+      </c>
+      <c r="K700" t="s">
+        <v>23</v>
+      </c>
+      <c r="L700" t="s">
+        <v>3754</v>
+      </c>
+      <c r="M700" t="s">
+        <v>3755</v>
+      </c>
+    </row>
+    <row r="701" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>3756</v>
+      </c>
+      <c r="B701" t="s">
+        <v>3757</v>
+      </c>
+      <c r="C701" t="s">
+        <v>15</v>
+      </c>
+      <c r="D701" t="s">
+        <v>3758</v>
+      </c>
+      <c r="E701" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F701" t="s">
+        <v>18</v>
+      </c>
+      <c r="G701" t="s">
+        <v>19</v>
+      </c>
+      <c r="H701" t="s">
+        <v>37</v>
+      </c>
+      <c r="I701" t="s">
+        <v>21</v>
+      </c>
+      <c r="J701" t="s">
+        <v>75</v>
+      </c>
+      <c r="K701" t="s">
+        <v>23</v>
+      </c>
+      <c r="L701" t="s">
+        <v>3759</v>
+      </c>
+      <c r="M701" t="s">
+        <v>3760</v>
+      </c>
+    </row>
+    <row r="702" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>3761</v>
+      </c>
+      <c r="B702" t="s">
+        <v>3762</v>
+      </c>
+      <c r="C702" t="s">
+        <v>15</v>
+      </c>
+      <c r="D702" t="s">
+        <v>3763</v>
+      </c>
+      <c r="E702" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F702" t="s">
+        <v>18</v>
+      </c>
+      <c r="G702" t="s">
+        <v>19</v>
+      </c>
+      <c r="H702" t="s">
+        <v>75</v>
+      </c>
+      <c r="I702" t="s">
+        <v>81</v>
+      </c>
+      <c r="J702" t="s">
+        <v>75</v>
+      </c>
+      <c r="K702" t="s">
+        <v>23</v>
+      </c>
+      <c r="L702" t="s">
+        <v>3764</v>
+      </c>
+      <c r="M702" t="s">
+        <v>3765</v>
+      </c>
+    </row>
+    <row r="703" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>3766</v>
+      </c>
+      <c r="B703" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C703" t="s">
+        <v>477</v>
+      </c>
+      <c r="D703" t="s">
+        <v>3768</v>
+      </c>
+      <c r="E703" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F703" t="s">
+        <v>18</v>
+      </c>
+      <c r="G703" t="s">
+        <v>19</v>
+      </c>
+      <c r="H703" t="s">
+        <v>45</v>
+      </c>
+      <c r="I703" t="s">
+        <v>21</v>
+      </c>
+      <c r="J703" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K703" t="s">
+        <v>23</v>
+      </c>
+      <c r="L703" t="s">
+        <v>3769</v>
+      </c>
+      <c r="M703" t="s">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="704" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>3771</v>
+      </c>
+      <c r="B704" t="s">
+        <v>3772</v>
+      </c>
+      <c r="C704" t="s">
+        <v>15</v>
+      </c>
+      <c r="D704" t="s">
+        <v>3773</v>
+      </c>
+      <c r="E704" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F704" t="s">
+        <v>18</v>
+      </c>
+      <c r="G704" t="s">
+        <v>19</v>
+      </c>
+      <c r="H704" t="s">
+        <v>45</v>
+      </c>
+      <c r="I704" t="s">
+        <v>21</v>
+      </c>
+      <c r="J704" t="s">
+        <v>75</v>
+      </c>
+      <c r="K704" t="s">
+        <v>23</v>
+      </c>
+      <c r="L704" t="s">
+        <v>3774</v>
+      </c>
+      <c r="M704" t="s">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="705" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>3776</v>
+      </c>
+      <c r="B705" t="s">
+        <v>3777</v>
+      </c>
+      <c r="C705" t="s">
+        <v>15</v>
+      </c>
+      <c r="D705" t="s">
+        <v>3778</v>
+      </c>
+      <c r="E705" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F705" t="s">
+        <v>18</v>
+      </c>
+      <c r="G705" t="s">
+        <v>19</v>
+      </c>
+      <c r="H705" t="s">
+        <v>45</v>
+      </c>
+      <c r="I705" t="s">
+        <v>21</v>
+      </c>
+      <c r="J705" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K705" t="s">
+        <v>23</v>
+      </c>
+      <c r="L705" t="s">
+        <v>3779</v>
+      </c>
+      <c r="M705" t="s">
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="706" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A706" t="s">
+        <v>3781</v>
+      </c>
+      <c r="B706" t="s">
+        <v>3782</v>
+      </c>
+      <c r="C706" t="s">
+        <v>15</v>
+      </c>
+      <c r="D706" t="s">
+        <v>3783</v>
+      </c>
+      <c r="E706" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F706" t="s">
+        <v>18</v>
+      </c>
+      <c r="G706" t="s">
+        <v>19</v>
+      </c>
+      <c r="H706" t="s">
+        <v>75</v>
+      </c>
+      <c r="I706" t="s">
+        <v>81</v>
+      </c>
+      <c r="J706" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K706" t="s">
+        <v>23</v>
+      </c>
+      <c r="L706" t="s">
+        <v>3784</v>
+      </c>
+      <c r="M706" t="s">
+        <v>3785</v>
+      </c>
+    </row>
+    <row r="707" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
+        <v>3786</v>
+      </c>
+      <c r="B707" t="s">
+        <v>3787</v>
+      </c>
+      <c r="C707" t="s">
+        <v>15</v>
+      </c>
+      <c r="D707" t="s">
+        <v>3788</v>
+      </c>
+      <c r="E707" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F707" t="s">
+        <v>18</v>
+      </c>
+      <c r="G707" t="s">
+        <v>19</v>
+      </c>
+      <c r="H707" t="s">
+        <v>45</v>
+      </c>
+      <c r="I707" t="s">
+        <v>21</v>
+      </c>
+      <c r="J707" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K707" t="s">
+        <v>23</v>
+      </c>
+      <c r="L707" t="s">
+        <v>3789</v>
+      </c>
+      <c r="M707" t="s">
+        <v>3790</v>
+      </c>
+    </row>
+    <row r="708" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>3791</v>
+      </c>
+      <c r="B708" t="s">
+        <v>3792</v>
+      </c>
+      <c r="C708" t="s">
+        <v>181</v>
+      </c>
+      <c r="D708" t="s">
+        <v>3793</v>
+      </c>
+      <c r="E708" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F708" t="s">
+        <v>18</v>
+      </c>
+      <c r="G708" t="s">
+        <v>19</v>
+      </c>
+      <c r="H708" t="s">
+        <v>223</v>
+      </c>
+      <c r="I708" t="s">
+        <v>21</v>
+      </c>
+      <c r="J708" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K708" t="s">
+        <v>23</v>
+      </c>
+      <c r="L708" t="s">
+        <v>3794</v>
+      </c>
+      <c r="M708" t="s">
+        <v>3795</v>
+      </c>
+    </row>
+    <row r="709" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A709" t="s">
+        <v>3796</v>
+      </c>
+      <c r="B709" t="s">
+        <v>3797</v>
+      </c>
+      <c r="C709" t="s">
+        <v>181</v>
+      </c>
+      <c r="D709" t="s">
+        <v>3798</v>
+      </c>
+      <c r="E709" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F709" t="s">
+        <v>18</v>
+      </c>
+      <c r="G709" t="s">
+        <v>19</v>
+      </c>
+      <c r="H709" t="s">
+        <v>75</v>
+      </c>
+      <c r="I709" t="s">
+        <v>81</v>
+      </c>
+      <c r="J709" t="s">
+        <v>75</v>
+      </c>
+      <c r="K709" t="s">
+        <v>23</v>
+      </c>
+      <c r="L709" t="s">
+        <v>3799</v>
+      </c>
+      <c r="M709" t="s">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="710" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
+        <v>3801</v>
+      </c>
+      <c r="B710" t="s">
+        <v>3802</v>
+      </c>
+      <c r="C710" t="s">
+        <v>15</v>
+      </c>
+      <c r="D710" t="s">
+        <v>3803</v>
+      </c>
+      <c r="E710" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F710" t="s">
+        <v>18</v>
+      </c>
+      <c r="G710" t="s">
+        <v>19</v>
+      </c>
+      <c r="H710" t="s">
+        <v>120</v>
+      </c>
+      <c r="I710" t="s">
+        <v>21</v>
+      </c>
+      <c r="J710" t="s">
+        <v>3439</v>
+      </c>
+      <c r="K710" t="s">
+        <v>23</v>
+      </c>
+      <c r="L710" t="s">
+        <v>3804</v>
+      </c>
+      <c r="M710" t="s">
+        <v>3805</v>
+      </c>
+    </row>
+    <row r="711" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
+        <v>3806</v>
+      </c>
+      <c r="B711" t="s">
+        <v>3807</v>
+      </c>
+      <c r="C711" t="s">
+        <v>526</v>
+      </c>
+      <c r="D711" t="s">
+        <v>3808</v>
+      </c>
+      <c r="E711" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F711" t="s">
+        <v>18</v>
+      </c>
+      <c r="G711" t="s">
+        <v>19</v>
+      </c>
+      <c r="H711" t="s">
+        <v>75</v>
+      </c>
+      <c r="I711" t="s">
+        <v>81</v>
+      </c>
+      <c r="J711" t="s">
+        <v>3582</v>
+      </c>
+      <c r="K711" t="s">
+        <v>23</v>
+      </c>
+      <c r="L711" t="s">
+        <v>3809</v>
+      </c>
+      <c r="M711" t="s">
+        <v>3810</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
